--- a/projects/tel-appo/call-list.xlsx
+++ b/projects/tel-appo/call-list.xlsx
@@ -476,17 +476,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:B17"/>
+  <dimension ref="B2:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="90" customWidth="1" min="2" max="2"/>
+    <col width="96" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>架電管理シート（MAKRH / 栃木市 蔵の街エリア）</t>
+          <t>架電管理シート（MAKRH / 栃木県内 観光エリア）</t>
         </is>
       </c>
     </row>
@@ -507,61 +507,68 @@
     <row r="6">
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>第一波の対象: 蔵の街エリアの観光関連個人店（カフェ・飲食店・和菓子/雑貨店）＋ 美容室・理容室。</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" s="2" t="inlineStr">
+          <t>第一波の対象: 栃木県内の観光関連個人店（カフェ・飲食店・和菓子/雑貨店・陶器店/ギャラリー・土産店）＋ 美容室・理容室。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>栃木市（蔵の街）を起点に、益子町（益子焼）・那須町（那須高原）・日光市（東照宮周辺）まで対象を拡大。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>入力のしかた</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>黄色のセルは要確認・要入力です（電話番号・定休日など、Web検索だけでは確認できなかった項目）。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>「業種」「結果」列はプルダウンから選択できます。</t>
+          <t>黄色のセルは要確認・要入力です（電話番号・定休日など、Web検索だけでは確認できなかった項目）。</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="3" t="inlineStr">
         <is>
+          <t>「業種」「市町」「結果」列はプルダウンから選択できます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="3" t="inlineStr">
+        <is>
           <t>架電したら「架電日」「結果」「次回アクション予定日」を都度更新してください。</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="B13" s="2" t="inlineStr">
+    <row r="14">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>結果の記録ルール</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="B14" s="3" t="inlineStr">
+    <row r="15">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>未架電 / 不在 / 拒否 / 資料送付OK / アポ確定 / 見送り の6区分で統一します。</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="B16" s="2" t="inlineStr">
+    <row r="17">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>集計</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="B17" s="3" t="inlineStr">
+    <row r="18">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>「集計」タブに架電数・アポ率が自動計算されます（架電リストの入力に連動）。</t>
         </is>
@@ -578,21 +585,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L34"/>
+  <dimension ref="A1:M48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="30" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="26" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="28" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="26" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -613,45 +621,50 @@
       </c>
       <c r="D1" s="4" t="inlineStr">
         <is>
-          <t>エリア/住所</t>
+          <t>市町</t>
         </is>
       </c>
       <c r="E1" s="4" t="inlineStr">
         <is>
+          <t>住所/場所</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
           <t>電話番号</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="G1" s="4" t="inlineStr">
         <is>
           <t>定休日</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="H1" s="4" t="inlineStr">
         <is>
           <t>現状サイト有無</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="I1" s="4" t="inlineStr">
         <is>
           <t>情報源</t>
         </is>
       </c>
-      <c r="I1" s="4" t="inlineStr">
+      <c r="J1" s="4" t="inlineStr">
         <is>
           <t>架電日</t>
         </is>
       </c>
-      <c r="J1" s="4" t="inlineStr">
+      <c r="K1" s="4" t="inlineStr">
         <is>
           <t>結果</t>
         </is>
       </c>
-      <c r="K1" s="4" t="inlineStr">
+      <c r="L1" s="4" t="inlineStr">
         <is>
           <t>次回アクション予定日</t>
         </is>
       </c>
-      <c r="L1" s="4" t="inlineStr">
+      <c r="M1" s="4" t="inlineStr">
         <is>
           <t>メモ</t>
         </is>
@@ -673,29 +686,34 @@
       </c>
       <c r="D2" s="6" t="inlineStr">
         <is>
+          <t>栃木市</t>
+        </is>
+      </c>
+      <c r="E2" s="6" t="inlineStr">
+        <is>
           <t>蔵の街エリア（巴波川沿い・古民家）</t>
         </is>
       </c>
-      <c r="E2" s="7" t="inlineStr"/>
       <c r="F2" s="7" t="inlineStr"/>
-      <c r="G2" s="6" t="inlineStr">
+      <c r="G2" s="7" t="inlineStr"/>
+      <c r="H2" s="6" t="inlineStr">
         <is>
           <t>不明</t>
         </is>
       </c>
-      <c r="H2" s="6" t="inlineStr">
+      <c r="I2" s="6" t="inlineStr">
         <is>
           <t>栃木市観光協会 掲載店</t>
         </is>
       </c>
-      <c r="I2" s="6" t="inlineStr"/>
-      <c r="J2" s="6" t="inlineStr">
+      <c r="J2" s="6" t="inlineStr"/>
+      <c r="K2" s="6" t="inlineStr">
         <is>
           <t>未架電</t>
         </is>
       </c>
-      <c r="K2" s="6" t="inlineStr"/>
-      <c r="L2" s="6" t="inlineStr">
+      <c r="L2" s="6" t="inlineStr"/>
+      <c r="M2" s="6" t="inlineStr">
         <is>
           <t>明治期の古民家を改装、蔵の街並みを一望できるカフェ</t>
         </is>
@@ -717,29 +735,34 @@
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>栃木市小平町10-17</t>
-        </is>
-      </c>
-      <c r="E3" s="7" t="inlineStr"/>
+          <t>栃木市</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>小平町10-17</t>
+        </is>
+      </c>
       <c r="F3" s="7" t="inlineStr"/>
-      <c r="G3" s="6" t="inlineStr">
+      <c r="G3" s="7" t="inlineStr"/>
+      <c r="H3" s="6" t="inlineStr">
         <is>
           <t>不明</t>
         </is>
       </c>
-      <c r="H3" s="6" t="inlineStr">
+      <c r="I3" s="6" t="inlineStr">
         <is>
           <t>観光メディア掲載店</t>
         </is>
       </c>
-      <c r="I3" s="6" t="inlineStr"/>
-      <c r="J3" s="6" t="inlineStr">
+      <c r="J3" s="6" t="inlineStr"/>
+      <c r="K3" s="6" t="inlineStr">
         <is>
           <t>未架電</t>
         </is>
       </c>
-      <c r="K3" s="6" t="inlineStr"/>
-      <c r="L3" s="6" t="inlineStr">
+      <c r="L3" s="6" t="inlineStr"/>
+      <c r="M3" s="6" t="inlineStr">
         <is>
           <t>古民家を改装したカフェ</t>
         </is>
@@ -761,29 +784,34 @@
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
+          <t>栃木市</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
           <t>蔵の街エリア（光明寺 山門付近）</t>
         </is>
       </c>
-      <c r="E4" s="7" t="inlineStr"/>
       <c r="F4" s="7" t="inlineStr"/>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="G4" s="7" t="inlineStr"/>
+      <c r="H4" s="6" t="inlineStr">
         <is>
           <t>不明</t>
         </is>
       </c>
-      <c r="H4" s="6" t="inlineStr">
+      <c r="I4" s="6" t="inlineStr">
         <is>
           <t>観光メディア掲載店</t>
         </is>
       </c>
-      <c r="I4" s="6" t="inlineStr"/>
-      <c r="J4" s="6" t="inlineStr">
+      <c r="J4" s="6" t="inlineStr"/>
+      <c r="K4" s="6" t="inlineStr">
         <is>
           <t>未架電</t>
         </is>
       </c>
-      <c r="K4" s="6" t="inlineStr"/>
-      <c r="L4" s="6" t="inlineStr">
+      <c r="L4" s="6" t="inlineStr"/>
+      <c r="M4" s="6" t="inlineStr">
         <is>
           <t>蔵を使った小さなカフェ、ドリップコーヒー</t>
         </is>
@@ -805,29 +833,34 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
+          <t>栃木市</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
           <t>蔵の街エリア</t>
         </is>
       </c>
-      <c r="E5" s="7" t="inlineStr"/>
       <c r="F5" s="7" t="inlineStr"/>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="G5" s="7" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr">
         <is>
           <t>不明</t>
         </is>
       </c>
-      <c r="H5" s="6" t="inlineStr">
+      <c r="I5" s="6" t="inlineStr">
         <is>
           <t>グルメサイト掲載店</t>
         </is>
       </c>
-      <c r="I5" s="6" t="inlineStr"/>
-      <c r="J5" s="6" t="inlineStr">
+      <c r="J5" s="6" t="inlineStr"/>
+      <c r="K5" s="6" t="inlineStr">
         <is>
           <t>未架電</t>
         </is>
       </c>
-      <c r="K5" s="6" t="inlineStr"/>
-      <c r="L5" s="6" t="inlineStr">
+      <c r="L5" s="6" t="inlineStr"/>
+      <c r="M5" s="6" t="inlineStr">
         <is>
           <t>季節の創作和菓子</t>
         </is>
@@ -849,29 +882,34 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
+          <t>栃木市</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
           <t>蔵の街エリア</t>
         </is>
       </c>
-      <c r="E6" s="7" t="inlineStr"/>
       <c r="F6" s="7" t="inlineStr"/>
-      <c r="G6" s="6" t="inlineStr">
+      <c r="G6" s="7" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr">
         <is>
           <t>不明</t>
         </is>
       </c>
-      <c r="H6" s="6" t="inlineStr">
+      <c r="I6" s="6" t="inlineStr">
         <is>
           <t>地域情報サイト掲載店</t>
         </is>
       </c>
-      <c r="I6" s="6" t="inlineStr"/>
-      <c r="J6" s="6" t="inlineStr">
+      <c r="J6" s="6" t="inlineStr"/>
+      <c r="K6" s="6" t="inlineStr">
         <is>
           <t>未架電</t>
         </is>
       </c>
-      <c r="K6" s="6" t="inlineStr"/>
-      <c r="L6" s="6" t="inlineStr">
+      <c r="L6" s="6" t="inlineStr"/>
+      <c r="M6" s="6" t="inlineStr">
         <is>
           <t>石蔵をリノベーション、バームクーヘン等</t>
         </is>
@@ -893,29 +931,34 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
+          <t>栃木市</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
           <t>蔵の街エリア</t>
         </is>
       </c>
-      <c r="E7" s="7" t="inlineStr"/>
       <c r="F7" s="7" t="inlineStr"/>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="G7" s="7" t="inlineStr"/>
+      <c r="H7" s="6" t="inlineStr">
         <is>
           <t>不明</t>
         </is>
       </c>
-      <c r="H7" s="6" t="inlineStr">
+      <c r="I7" s="6" t="inlineStr">
         <is>
           <t>観光メディア掲載店</t>
         </is>
       </c>
-      <c r="I7" s="6" t="inlineStr"/>
-      <c r="J7" s="6" t="inlineStr">
+      <c r="J7" s="6" t="inlineStr"/>
+      <c r="K7" s="6" t="inlineStr">
         <is>
           <t>未架電</t>
         </is>
       </c>
-      <c r="K7" s="6" t="inlineStr"/>
-      <c r="L7" s="6" t="inlineStr">
+      <c r="L7" s="6" t="inlineStr"/>
+      <c r="M7" s="6" t="inlineStr">
         <is>
           <t>栃木・全国のお土産セレクトショップ</t>
         </is>
@@ -937,29 +980,34 @@
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
+          <t>栃木市</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
           <t>蔵の街大通り沿い（万町交番付近）</t>
         </is>
       </c>
-      <c r="E8" s="7" t="inlineStr"/>
       <c r="F8" s="7" t="inlineStr"/>
-      <c r="G8" s="6" t="inlineStr">
+      <c r="G8" s="7" t="inlineStr"/>
+      <c r="H8" s="6" t="inlineStr">
         <is>
           <t>不明</t>
         </is>
       </c>
-      <c r="H8" s="6" t="inlineStr">
+      <c r="I8" s="6" t="inlineStr">
         <is>
           <t>電話帳サイト掲載店</t>
         </is>
       </c>
-      <c r="I8" s="6" t="inlineStr"/>
-      <c r="J8" s="6" t="inlineStr">
+      <c r="J8" s="6" t="inlineStr"/>
+      <c r="K8" s="6" t="inlineStr">
         <is>
           <t>未架電</t>
         </is>
       </c>
-      <c r="K8" s="6" t="inlineStr"/>
       <c r="L8" s="6" t="inlineStr"/>
+      <c r="M8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="n">
@@ -977,253 +1025,712 @@
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>栃木市富士見町5-32</t>
-        </is>
-      </c>
-      <c r="E9" s="7" t="inlineStr"/>
+          <t>栃木市</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>富士見町5-32</t>
+        </is>
+      </c>
       <c r="F9" s="7" t="inlineStr"/>
-      <c r="G9" s="6" t="inlineStr">
+      <c r="G9" s="7" t="inlineStr"/>
+      <c r="H9" s="6" t="inlineStr">
         <is>
           <t>不明</t>
         </is>
       </c>
-      <c r="H9" s="6" t="inlineStr">
+      <c r="I9" s="6" t="inlineStr">
         <is>
           <t>地域情報サイト掲載店</t>
         </is>
       </c>
-      <c r="I9" s="6" t="inlineStr"/>
-      <c r="J9" s="6" t="inlineStr">
+      <c r="J9" s="6" t="inlineStr"/>
+      <c r="K9" s="6" t="inlineStr">
         <is>
           <t>未架電</t>
         </is>
       </c>
-      <c r="K9" s="6" t="inlineStr"/>
       <c r="L9" s="6" t="inlineStr"/>
+      <c r="M9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="8" t="inlineStr"/>
-      <c r="C10" s="8" t="inlineStr"/>
-      <c r="D10" s="8" t="inlineStr"/>
-      <c r="E10" s="8" t="inlineStr"/>
-      <c r="F10" s="8" t="inlineStr"/>
-      <c r="G10" s="8" t="inlineStr"/>
-      <c r="H10" s="8" t="inlineStr"/>
-      <c r="I10" s="8" t="inlineStr"/>
-      <c r="J10" s="8" t="inlineStr"/>
-      <c r="K10" s="8" t="inlineStr"/>
-      <c r="L10" s="8" t="inlineStr"/>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>やまに大塚</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>陶器店・ギャラリー</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>益子町</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>城内坂エリア</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr"/>
+      <c r="G10" s="7" t="inlineStr"/>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>公式サイト</t>
+        </is>
+      </c>
+      <c r="J10" s="6" t="inlineStr"/>
+      <c r="K10" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L10" s="6" t="inlineStr"/>
+      <c r="M10" s="6" t="inlineStr">
+        <is>
+          <t>益子焼ギャラリー・カフェ・陶芸教室を併設</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="8" t="inlineStr"/>
-      <c r="C11" s="8" t="inlineStr"/>
-      <c r="D11" s="8" t="inlineStr"/>
-      <c r="E11" s="8" t="inlineStr"/>
-      <c r="F11" s="8" t="inlineStr"/>
-      <c r="G11" s="8" t="inlineStr"/>
-      <c r="H11" s="8" t="inlineStr"/>
-      <c r="I11" s="8" t="inlineStr"/>
-      <c r="J11" s="8" t="inlineStr"/>
-      <c r="K11" s="8" t="inlineStr"/>
-      <c r="L11" s="8" t="inlineStr"/>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>益子焼窯元 つかもと</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>陶器店・ギャラリー</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>益子町</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>城内坂通り</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr"/>
+      <c r="G11" s="7" t="inlineStr"/>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>観光メディア掲載店</t>
+        </is>
+      </c>
+      <c r="J11" s="6" t="inlineStr"/>
+      <c r="K11" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L11" s="6" t="inlineStr"/>
+      <c r="M11" s="6" t="inlineStr">
+        <is>
+          <t>ギャラリー・カフェ・レストラン併設</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="8" t="inlineStr"/>
-      <c r="C12" s="8" t="inlineStr"/>
-      <c r="D12" s="8" t="inlineStr"/>
-      <c r="E12" s="8" t="inlineStr"/>
-      <c r="F12" s="8" t="inlineStr"/>
-      <c r="G12" s="8" t="inlineStr"/>
-      <c r="H12" s="8" t="inlineStr"/>
-      <c r="I12" s="8" t="inlineStr"/>
-      <c r="J12" s="8" t="inlineStr"/>
-      <c r="K12" s="8" t="inlineStr"/>
-      <c r="L12" s="8" t="inlineStr"/>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>tete+gallery</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>陶器店・ギャラリー</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>益子町</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>益子駅〜城内坂の途中</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr"/>
+      <c r="G12" s="7" t="inlineStr"/>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>観光メディア掲載店</t>
+        </is>
+      </c>
+      <c r="J12" s="6" t="inlineStr"/>
+      <c r="K12" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L12" s="6" t="inlineStr"/>
+      <c r="M12" s="6" t="inlineStr">
+        <is>
+          <t>作家本人が制作する陶器ギャラリー</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="8" t="inlineStr"/>
-      <c r="C13" s="8" t="inlineStr"/>
-      <c r="D13" s="8" t="inlineStr"/>
-      <c r="E13" s="8" t="inlineStr"/>
-      <c r="F13" s="8" t="inlineStr"/>
-      <c r="G13" s="8" t="inlineStr"/>
-      <c r="H13" s="8" t="inlineStr"/>
-      <c r="I13" s="8" t="inlineStr"/>
-      <c r="J13" s="8" t="inlineStr"/>
-      <c r="K13" s="8" t="inlineStr"/>
-      <c r="L13" s="8" t="inlineStr"/>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>益子の茶屋（窯元よこやま）</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>カフェ</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>益子町</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>城内坂エリア</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr"/>
+      <c r="G13" s="7" t="inlineStr"/>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>公式サイト</t>
+        </is>
+      </c>
+      <c r="J13" s="6" t="inlineStr"/>
+      <c r="K13" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L13" s="6" t="inlineStr"/>
+      <c r="M13" s="6" t="inlineStr">
+        <is>
+          <t>益子焼の器で提供する陶芸カフェレストラン</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="8" t="inlineStr"/>
-      <c r="C14" s="8" t="inlineStr"/>
-      <c r="D14" s="8" t="inlineStr"/>
-      <c r="E14" s="8" t="inlineStr"/>
-      <c r="F14" s="8" t="inlineStr"/>
-      <c r="G14" s="8" t="inlineStr"/>
-      <c r="H14" s="8" t="inlineStr"/>
-      <c r="I14" s="8" t="inlineStr"/>
-      <c r="J14" s="8" t="inlineStr"/>
-      <c r="K14" s="8" t="inlineStr"/>
-      <c r="L14" s="8" t="inlineStr"/>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>古民家のカフェ 夢屋</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>カフェ</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>那須町</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>那須高原（森の中）</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr"/>
+      <c r="G14" s="7" t="inlineStr"/>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>観光メディア掲載店</t>
+        </is>
+      </c>
+      <c r="J14" s="6" t="inlineStr"/>
+      <c r="K14" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L14" s="6" t="inlineStr"/>
+      <c r="M14" s="6" t="inlineStr">
+        <is>
+          <t>古民家を改装したカフェ</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="8" t="inlineStr"/>
-      <c r="C15" s="8" t="inlineStr"/>
-      <c r="D15" s="8" t="inlineStr"/>
-      <c r="E15" s="8" t="inlineStr"/>
-      <c r="F15" s="8" t="inlineStr"/>
-      <c r="G15" s="8" t="inlineStr"/>
-      <c r="H15" s="8" t="inlineStr"/>
-      <c r="I15" s="8" t="inlineStr"/>
-      <c r="J15" s="8" t="inlineStr"/>
-      <c r="K15" s="8" t="inlineStr"/>
-      <c r="L15" s="8" t="inlineStr"/>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>craft&amp;design WHITE NOTE</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>雑貨店</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>那須町</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>那須高原</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr"/>
+      <c r="G15" s="7" t="inlineStr"/>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>観光メディア掲載店</t>
+        </is>
+      </c>
+      <c r="J15" s="6" t="inlineStr"/>
+      <c r="K15" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L15" s="6" t="inlineStr"/>
+      <c r="M15" s="6" t="inlineStr">
+        <is>
+          <t>生活道具・手作り雑貨の店</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="8" t="inlineStr"/>
-      <c r="C16" s="8" t="inlineStr"/>
-      <c r="D16" s="8" t="inlineStr"/>
-      <c r="E16" s="8" t="inlineStr"/>
-      <c r="F16" s="8" t="inlineStr"/>
-      <c r="G16" s="8" t="inlineStr"/>
-      <c r="H16" s="8" t="inlineStr"/>
-      <c r="I16" s="8" t="inlineStr"/>
-      <c r="J16" s="8" t="inlineStr"/>
-      <c r="K16" s="8" t="inlineStr"/>
-      <c r="L16" s="8" t="inlineStr"/>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>ペニー・レイン 那須店</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>カフェ</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>那須町</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>那須高原</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr"/>
+      <c r="G16" s="7" t="inlineStr"/>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>観光メディア掲載店</t>
+        </is>
+      </c>
+      <c r="J16" s="6" t="inlineStr"/>
+      <c r="K16" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L16" s="6" t="inlineStr"/>
+      <c r="M16" s="6" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="8" t="inlineStr"/>
-      <c r="C17" s="8" t="inlineStr"/>
-      <c r="D17" s="8" t="inlineStr"/>
-      <c r="E17" s="8" t="inlineStr"/>
-      <c r="F17" s="8" t="inlineStr"/>
-      <c r="G17" s="8" t="inlineStr"/>
-      <c r="H17" s="8" t="inlineStr"/>
-      <c r="I17" s="8" t="inlineStr"/>
-      <c r="J17" s="8" t="inlineStr"/>
-      <c r="K17" s="8" t="inlineStr"/>
-      <c r="L17" s="8" t="inlineStr"/>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>NASU SHOZO CAFE</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>カフェ</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>那須町</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>那須高原</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr"/>
+      <c r="G17" s="7" t="inlineStr"/>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>観光メディア掲載店</t>
+        </is>
+      </c>
+      <c r="J17" s="6" t="inlineStr"/>
+      <c r="K17" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L17" s="6" t="inlineStr"/>
+      <c r="M17" s="6" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="8" t="inlineStr"/>
-      <c r="C18" s="8" t="inlineStr"/>
-      <c r="D18" s="8" t="inlineStr"/>
-      <c r="E18" s="8" t="inlineStr"/>
-      <c r="F18" s="8" t="inlineStr"/>
-      <c r="G18" s="8" t="inlineStr"/>
-      <c r="H18" s="8" t="inlineStr"/>
-      <c r="I18" s="8" t="inlineStr"/>
-      <c r="J18" s="8" t="inlineStr"/>
-      <c r="K18" s="8" t="inlineStr"/>
-      <c r="L18" s="8" t="inlineStr"/>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>Cafe La Detente（自家焙煎 那須珈琲）</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>カフェ</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>那須町</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>那須高原</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr"/>
+      <c r="G18" s="7" t="inlineStr"/>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>観光メディア掲載店</t>
+        </is>
+      </c>
+      <c r="J18" s="6" t="inlineStr"/>
+      <c r="K18" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L18" s="6" t="inlineStr"/>
+      <c r="M18" s="6" t="inlineStr">
+        <is>
+          <t>自家焙煎コーヒーの店</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="8" t="inlineStr"/>
-      <c r="C19" s="8" t="inlineStr"/>
-      <c r="D19" s="8" t="inlineStr"/>
-      <c r="E19" s="8" t="inlineStr"/>
-      <c r="F19" s="8" t="inlineStr"/>
-      <c r="G19" s="8" t="inlineStr"/>
-      <c r="H19" s="8" t="inlineStr"/>
-      <c r="I19" s="8" t="inlineStr"/>
-      <c r="J19" s="8" t="inlineStr"/>
-      <c r="K19" s="8" t="inlineStr"/>
-      <c r="L19" s="8" t="inlineStr"/>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>Cafe St.Croix</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>カフェ</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>那須町</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>那須高原</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr"/>
+      <c r="G19" s="7" t="inlineStr"/>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>観光メディア掲載店</t>
+        </is>
+      </c>
+      <c r="J19" s="6" t="inlineStr"/>
+      <c r="K19" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L19" s="6" t="inlineStr"/>
+      <c r="M19" s="6" t="inlineStr">
+        <is>
+          <t>薪ストーブと珈琲の店</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="8" t="inlineStr"/>
-      <c r="C20" s="8" t="inlineStr"/>
-      <c r="D20" s="8" t="inlineStr"/>
-      <c r="E20" s="8" t="inlineStr"/>
-      <c r="F20" s="8" t="inlineStr"/>
-      <c r="G20" s="8" t="inlineStr"/>
-      <c r="H20" s="8" t="inlineStr"/>
-      <c r="I20" s="8" t="inlineStr"/>
-      <c r="J20" s="8" t="inlineStr"/>
-      <c r="K20" s="8" t="inlineStr"/>
-      <c r="L20" s="8" t="inlineStr"/>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>本宮カフェ</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>カフェ</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>日光市</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>山内2384</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr"/>
+      <c r="G20" s="7" t="inlineStr"/>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>観光メディア掲載店</t>
+        </is>
+      </c>
+      <c r="J20" s="6" t="inlineStr"/>
+      <c r="K20" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L20" s="6" t="inlineStr"/>
+      <c r="M20" s="6" t="inlineStr">
+        <is>
+          <t>築330余年の古民家カフェ</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="8" t="inlineStr"/>
-      <c r="C21" s="8" t="inlineStr"/>
-      <c r="D21" s="8" t="inlineStr"/>
-      <c r="E21" s="8" t="inlineStr"/>
-      <c r="F21" s="8" t="inlineStr"/>
-      <c r="G21" s="8" t="inlineStr"/>
-      <c r="H21" s="8" t="inlineStr"/>
-      <c r="I21" s="8" t="inlineStr"/>
-      <c r="J21" s="8" t="inlineStr"/>
-      <c r="K21" s="8" t="inlineStr"/>
-      <c r="L21" s="8" t="inlineStr"/>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>湯沢屋直営カフェ</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>和菓子店</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>日光市</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>日光東照宮 参道エリア</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr"/>
+      <c r="G21" s="7" t="inlineStr"/>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I21" s="6" t="inlineStr">
+        <is>
+          <t>観光メディア掲載店</t>
+        </is>
+      </c>
+      <c r="J21" s="6" t="inlineStr"/>
+      <c r="K21" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L21" s="6" t="inlineStr"/>
+      <c r="M21" s="6" t="inlineStr">
+        <is>
+          <t>明治創業の老舗和菓子店直営、湯波料理も提供</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="n">
         <v>21</v>
       </c>
-      <c r="B22" s="8" t="inlineStr"/>
-      <c r="C22" s="8" t="inlineStr"/>
-      <c r="D22" s="8" t="inlineStr"/>
-      <c r="E22" s="8" t="inlineStr"/>
-      <c r="F22" s="8" t="inlineStr"/>
-      <c r="G22" s="8" t="inlineStr"/>
-      <c r="H22" s="8" t="inlineStr"/>
-      <c r="I22" s="8" t="inlineStr"/>
-      <c r="J22" s="8" t="inlineStr"/>
-      <c r="K22" s="8" t="inlineStr"/>
-      <c r="L22" s="8" t="inlineStr"/>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>さかえや</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>土産店</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>日光市</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>東武日光駅前</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="inlineStr"/>
+      <c r="G22" s="7" t="inlineStr"/>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I22" s="6" t="inlineStr">
+        <is>
+          <t>観光メディア掲載店</t>
+        </is>
+      </c>
+      <c r="J22" s="6" t="inlineStr"/>
+      <c r="K22" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L22" s="6" t="inlineStr"/>
+      <c r="M22" s="6" t="inlineStr">
+        <is>
+          <t>創業60年以上、揚げゆばまんじゅうが名物</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="8" t="inlineStr"/>
-      <c r="C23" s="8" t="inlineStr"/>
-      <c r="D23" s="8" t="inlineStr"/>
-      <c r="E23" s="8" t="inlineStr"/>
-      <c r="F23" s="8" t="inlineStr"/>
-      <c r="G23" s="8" t="inlineStr"/>
-      <c r="H23" s="8" t="inlineStr"/>
-      <c r="I23" s="8" t="inlineStr"/>
-      <c r="J23" s="8" t="inlineStr"/>
-      <c r="K23" s="8" t="inlineStr"/>
-      <c r="L23" s="8" t="inlineStr"/>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>油源</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>土産店</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>日光市</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>日光東照宮周辺</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr"/>
+      <c r="G23" s="7" t="inlineStr"/>
+      <c r="H23" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I23" s="6" t="inlineStr">
+        <is>
+          <t>観光メディア掲載店</t>
+        </is>
+      </c>
+      <c r="J23" s="6" t="inlineStr"/>
+      <c r="K23" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L23" s="6" t="inlineStr"/>
+      <c r="M23" s="6" t="inlineStr">
+        <is>
+          <t>1859年創業の老舗</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="n">
@@ -1240,6 +1747,7 @@
       <c r="J24" s="8" t="inlineStr"/>
       <c r="K24" s="8" t="inlineStr"/>
       <c r="L24" s="8" t="inlineStr"/>
+      <c r="M24" s="8" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="5" t="n">
@@ -1256,6 +1764,7 @@
       <c r="J25" s="8" t="inlineStr"/>
       <c r="K25" s="8" t="inlineStr"/>
       <c r="L25" s="8" t="inlineStr"/>
+      <c r="M25" s="8" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="5" t="n">
@@ -1272,6 +1781,7 @@
       <c r="J26" s="8" t="inlineStr"/>
       <c r="K26" s="8" t="inlineStr"/>
       <c r="L26" s="8" t="inlineStr"/>
+      <c r="M26" s="8" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="n">
@@ -1288,6 +1798,7 @@
       <c r="J27" s="8" t="inlineStr"/>
       <c r="K27" s="8" t="inlineStr"/>
       <c r="L27" s="8" t="inlineStr"/>
+      <c r="M27" s="8" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="n">
@@ -1304,6 +1815,7 @@
       <c r="J28" s="8" t="inlineStr"/>
       <c r="K28" s="8" t="inlineStr"/>
       <c r="L28" s="8" t="inlineStr"/>
+      <c r="M28" s="8" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="5" t="n">
@@ -1320,6 +1832,7 @@
       <c r="J29" s="8" t="inlineStr"/>
       <c r="K29" s="8" t="inlineStr"/>
       <c r="L29" s="8" t="inlineStr"/>
+      <c r="M29" s="8" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="5" t="n">
@@ -1336,6 +1849,7 @@
       <c r="J30" s="8" t="inlineStr"/>
       <c r="K30" s="8" t="inlineStr"/>
       <c r="L30" s="8" t="inlineStr"/>
+      <c r="M30" s="8" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="5" t="n">
@@ -1352,6 +1866,7 @@
       <c r="J31" s="8" t="inlineStr"/>
       <c r="K31" s="8" t="inlineStr"/>
       <c r="L31" s="8" t="inlineStr"/>
+      <c r="M31" s="8" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="5" t="n">
@@ -1368,6 +1883,7 @@
       <c r="J32" s="8" t="inlineStr"/>
       <c r="K32" s="8" t="inlineStr"/>
       <c r="L32" s="8" t="inlineStr"/>
+      <c r="M32" s="8" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="5" t="n">
@@ -1384,6 +1900,7 @@
       <c r="J33" s="8" t="inlineStr"/>
       <c r="K33" s="8" t="inlineStr"/>
       <c r="L33" s="8" t="inlineStr"/>
+      <c r="M33" s="8" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="5" t="n">
@@ -1400,16 +1917,258 @@
       <c r="J34" s="8" t="inlineStr"/>
       <c r="K34" s="8" t="inlineStr"/>
       <c r="L34" s="8" t="inlineStr"/>
+      <c r="M34" s="8" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="8" t="inlineStr"/>
+      <c r="C35" s="8" t="inlineStr"/>
+      <c r="D35" s="8" t="inlineStr"/>
+      <c r="E35" s="8" t="inlineStr"/>
+      <c r="F35" s="8" t="inlineStr"/>
+      <c r="G35" s="8" t="inlineStr"/>
+      <c r="H35" s="8" t="inlineStr"/>
+      <c r="I35" s="8" t="inlineStr"/>
+      <c r="J35" s="8" t="inlineStr"/>
+      <c r="K35" s="8" t="inlineStr"/>
+      <c r="L35" s="8" t="inlineStr"/>
+      <c r="M35" s="8" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="8" t="inlineStr"/>
+      <c r="C36" s="8" t="inlineStr"/>
+      <c r="D36" s="8" t="inlineStr"/>
+      <c r="E36" s="8" t="inlineStr"/>
+      <c r="F36" s="8" t="inlineStr"/>
+      <c r="G36" s="8" t="inlineStr"/>
+      <c r="H36" s="8" t="inlineStr"/>
+      <c r="I36" s="8" t="inlineStr"/>
+      <c r="J36" s="8" t="inlineStr"/>
+      <c r="K36" s="8" t="inlineStr"/>
+      <c r="L36" s="8" t="inlineStr"/>
+      <c r="M36" s="8" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="8" t="inlineStr"/>
+      <c r="C37" s="8" t="inlineStr"/>
+      <c r="D37" s="8" t="inlineStr"/>
+      <c r="E37" s="8" t="inlineStr"/>
+      <c r="F37" s="8" t="inlineStr"/>
+      <c r="G37" s="8" t="inlineStr"/>
+      <c r="H37" s="8" t="inlineStr"/>
+      <c r="I37" s="8" t="inlineStr"/>
+      <c r="J37" s="8" t="inlineStr"/>
+      <c r="K37" s="8" t="inlineStr"/>
+      <c r="L37" s="8" t="inlineStr"/>
+      <c r="M37" s="8" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="8" t="inlineStr"/>
+      <c r="C38" s="8" t="inlineStr"/>
+      <c r="D38" s="8" t="inlineStr"/>
+      <c r="E38" s="8" t="inlineStr"/>
+      <c r="F38" s="8" t="inlineStr"/>
+      <c r="G38" s="8" t="inlineStr"/>
+      <c r="H38" s="8" t="inlineStr"/>
+      <c r="I38" s="8" t="inlineStr"/>
+      <c r="J38" s="8" t="inlineStr"/>
+      <c r="K38" s="8" t="inlineStr"/>
+      <c r="L38" s="8" t="inlineStr"/>
+      <c r="M38" s="8" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="8" t="inlineStr"/>
+      <c r="C39" s="8" t="inlineStr"/>
+      <c r="D39" s="8" t="inlineStr"/>
+      <c r="E39" s="8" t="inlineStr"/>
+      <c r="F39" s="8" t="inlineStr"/>
+      <c r="G39" s="8" t="inlineStr"/>
+      <c r="H39" s="8" t="inlineStr"/>
+      <c r="I39" s="8" t="inlineStr"/>
+      <c r="J39" s="8" t="inlineStr"/>
+      <c r="K39" s="8" t="inlineStr"/>
+      <c r="L39" s="8" t="inlineStr"/>
+      <c r="M39" s="8" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="8" t="inlineStr"/>
+      <c r="C40" s="8" t="inlineStr"/>
+      <c r="D40" s="8" t="inlineStr"/>
+      <c r="E40" s="8" t="inlineStr"/>
+      <c r="F40" s="8" t="inlineStr"/>
+      <c r="G40" s="8" t="inlineStr"/>
+      <c r="H40" s="8" t="inlineStr"/>
+      <c r="I40" s="8" t="inlineStr"/>
+      <c r="J40" s="8" t="inlineStr"/>
+      <c r="K40" s="8" t="inlineStr"/>
+      <c r="L40" s="8" t="inlineStr"/>
+      <c r="M40" s="8" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="8" t="inlineStr"/>
+      <c r="C41" s="8" t="inlineStr"/>
+      <c r="D41" s="8" t="inlineStr"/>
+      <c r="E41" s="8" t="inlineStr"/>
+      <c r="F41" s="8" t="inlineStr"/>
+      <c r="G41" s="8" t="inlineStr"/>
+      <c r="H41" s="8" t="inlineStr"/>
+      <c r="I41" s="8" t="inlineStr"/>
+      <c r="J41" s="8" t="inlineStr"/>
+      <c r="K41" s="8" t="inlineStr"/>
+      <c r="L41" s="8" t="inlineStr"/>
+      <c r="M41" s="8" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="8" t="inlineStr"/>
+      <c r="C42" s="8" t="inlineStr"/>
+      <c r="D42" s="8" t="inlineStr"/>
+      <c r="E42" s="8" t="inlineStr"/>
+      <c r="F42" s="8" t="inlineStr"/>
+      <c r="G42" s="8" t="inlineStr"/>
+      <c r="H42" s="8" t="inlineStr"/>
+      <c r="I42" s="8" t="inlineStr"/>
+      <c r="J42" s="8" t="inlineStr"/>
+      <c r="K42" s="8" t="inlineStr"/>
+      <c r="L42" s="8" t="inlineStr"/>
+      <c r="M42" s="8" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="8" t="inlineStr"/>
+      <c r="C43" s="8" t="inlineStr"/>
+      <c r="D43" s="8" t="inlineStr"/>
+      <c r="E43" s="8" t="inlineStr"/>
+      <c r="F43" s="8" t="inlineStr"/>
+      <c r="G43" s="8" t="inlineStr"/>
+      <c r="H43" s="8" t="inlineStr"/>
+      <c r="I43" s="8" t="inlineStr"/>
+      <c r="J43" s="8" t="inlineStr"/>
+      <c r="K43" s="8" t="inlineStr"/>
+      <c r="L43" s="8" t="inlineStr"/>
+      <c r="M43" s="8" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="8" t="inlineStr"/>
+      <c r="C44" s="8" t="inlineStr"/>
+      <c r="D44" s="8" t="inlineStr"/>
+      <c r="E44" s="8" t="inlineStr"/>
+      <c r="F44" s="8" t="inlineStr"/>
+      <c r="G44" s="8" t="inlineStr"/>
+      <c r="H44" s="8" t="inlineStr"/>
+      <c r="I44" s="8" t="inlineStr"/>
+      <c r="J44" s="8" t="inlineStr"/>
+      <c r="K44" s="8" t="inlineStr"/>
+      <c r="L44" s="8" t="inlineStr"/>
+      <c r="M44" s="8" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="8" t="inlineStr"/>
+      <c r="C45" s="8" t="inlineStr"/>
+      <c r="D45" s="8" t="inlineStr"/>
+      <c r="E45" s="8" t="inlineStr"/>
+      <c r="F45" s="8" t="inlineStr"/>
+      <c r="G45" s="8" t="inlineStr"/>
+      <c r="H45" s="8" t="inlineStr"/>
+      <c r="I45" s="8" t="inlineStr"/>
+      <c r="J45" s="8" t="inlineStr"/>
+      <c r="K45" s="8" t="inlineStr"/>
+      <c r="L45" s="8" t="inlineStr"/>
+      <c r="M45" s="8" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="8" t="inlineStr"/>
+      <c r="C46" s="8" t="inlineStr"/>
+      <c r="D46" s="8" t="inlineStr"/>
+      <c r="E46" s="8" t="inlineStr"/>
+      <c r="F46" s="8" t="inlineStr"/>
+      <c r="G46" s="8" t="inlineStr"/>
+      <c r="H46" s="8" t="inlineStr"/>
+      <c r="I46" s="8" t="inlineStr"/>
+      <c r="J46" s="8" t="inlineStr"/>
+      <c r="K46" s="8" t="inlineStr"/>
+      <c r="L46" s="8" t="inlineStr"/>
+      <c r="M46" s="8" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="8" t="inlineStr"/>
+      <c r="C47" s="8" t="inlineStr"/>
+      <c r="D47" s="8" t="inlineStr"/>
+      <c r="E47" s="8" t="inlineStr"/>
+      <c r="F47" s="8" t="inlineStr"/>
+      <c r="G47" s="8" t="inlineStr"/>
+      <c r="H47" s="8" t="inlineStr"/>
+      <c r="I47" s="8" t="inlineStr"/>
+      <c r="J47" s="8" t="inlineStr"/>
+      <c r="K47" s="8" t="inlineStr"/>
+      <c r="L47" s="8" t="inlineStr"/>
+      <c r="M47" s="8" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" s="8" t="inlineStr"/>
+      <c r="C48" s="8" t="inlineStr"/>
+      <c r="D48" s="8" t="inlineStr"/>
+      <c r="E48" s="8" t="inlineStr"/>
+      <c r="F48" s="8" t="inlineStr"/>
+      <c r="G48" s="8" t="inlineStr"/>
+      <c r="H48" s="8" t="inlineStr"/>
+      <c r="I48" s="8" t="inlineStr"/>
+      <c r="J48" s="8" t="inlineStr"/>
+      <c r="K48" s="8" t="inlineStr"/>
+      <c r="L48" s="8" t="inlineStr"/>
+      <c r="M48" s="8" t="inlineStr"/>
     </row>
   </sheetData>
-  <dataValidations count="3">
-    <dataValidation sqref="C2:C34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"カフェ,飲食店,和菓子店,雑貨店,美容室,理容室,その他"</formula1>
+  <dataValidations count="4">
+    <dataValidation sqref="C2:C48" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"カフェ,飲食店,和菓子店,雑貨店,陶器店・ギャラリー,土産店,美容室,理容室,その他"</formula1>
     </dataValidation>
-    <dataValidation sqref="J2:J34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="D2:D48" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"栃木市,益子町,那須町,日光市,その他"</formula1>
+    </dataValidation>
+    <dataValidation sqref="K2:K48" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"未架電,不在,拒否,資料送付OK,アポ確定,見送り"</formula1>
     </dataValidation>
-    <dataValidation sqref="G2:G34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H2:H48" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"不明,あり（古い）,あり（最近）,なし"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1423,7 +2182,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:D8"/>
+  <dimension ref="B2:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="2" max="2"/>
@@ -1444,7 +2203,7 @@
         </is>
       </c>
       <c r="D4" s="2">
-        <f>COUNTIF(架電リスト!B2:B34,"?*")</f>
+        <f>COUNTIF(架電リスト!B2:B48,"?*")</f>
         <v/>
       </c>
     </row>
@@ -1455,7 +2214,7 @@
         </is>
       </c>
       <c r="D5" s="2">
-        <f>COUNTIFS(架電リスト!J2:J34,"&lt;&gt;未架電",架電リスト!J2:J34,"&lt;&gt;")</f>
+        <f>COUNTIFS(架電リスト!K2:K48,"&lt;&gt;未架電",架電リスト!K2:K48,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -1466,7 +2225,7 @@
         </is>
       </c>
       <c r="D6" s="2">
-        <f>COUNTIF(架電リスト!J2:J34,"資料送付OK")</f>
+        <f>COUNTIF(架電リスト!K2:K48,"資料送付OK")</f>
         <v/>
       </c>
     </row>
@@ -1477,7 +2236,7 @@
         </is>
       </c>
       <c r="D7" s="2">
-        <f>COUNTIF(架電リスト!J2:J34,"アポ確定")</f>
+        <f>COUNTIF(架電リスト!K2:K48,"アポ確定")</f>
         <v/>
       </c>
     </row>
@@ -1489,6 +2248,57 @@
       </c>
       <c r="D8" s="9">
         <f>IFERROR(D7/D5,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>市町別 登録件数</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>栃木市</t>
+        </is>
+      </c>
+      <c r="D11" s="2">
+        <f>COUNTIF(架電リスト!D2:D48,"栃木市")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>益子町</t>
+        </is>
+      </c>
+      <c r="D12" s="2">
+        <f>COUNTIF(架電リスト!D2:D48,"益子町")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>那須町</t>
+        </is>
+      </c>
+      <c r="D13" s="2">
+        <f>COUNTIF(架電リスト!D2:D48,"那須町")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>日光市</t>
+        </is>
+      </c>
+      <c r="D14" s="2">
+        <f>COUNTIF(架電リスト!D2:D48,"日光市")</f>
         <v/>
       </c>
     </row>

--- a/projects/tel-appo/call-list.xlsx
+++ b/projects/tel-appo/call-list.xlsx
@@ -21,7 +21,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -47,6 +47,11 @@
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -94,7 +99,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -111,6 +116,7 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -476,17 +482,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:B18"/>
+  <dimension ref="B2:B24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="96" customWidth="1" min="2" max="2"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>架電管理シート（MAKRH / 栃木県内 観光エリア）</t>
+          <t>架電管理シート（MAKRH / 栃木県内）</t>
         </is>
       </c>
     </row>
@@ -507,70 +513,105 @@
     <row r="6">
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>第一波の対象: 栃木県内の観光関連個人店（カフェ・飲食店・和菓子/雑貨店・陶器店/ギャラリー・土産店）＋ 美容室・理容室。</t>
+          <t>対象: 栃木県内の観光関連個人店（カフェ・飲食店・和菓子/雑貨店・陶器店/ギャラリー・土産店）＋ 美容室・理容室。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>栃木市（蔵の街）を起点に、益子町（益子焼）・那須町（那須高原）・日光市（東照宮周辺）まで対象を拡大。</t>
+          <t>現在20市町にまたがる候補を掲載（栃木市・益子町・那須町・日光市を中心に、宇都宮市など主要都市にも拡大）。</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>入力のしかた</t>
+          <t>500件を目指す上での注意</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>黄色のセルは要確認・要入力です（電話番号・定休日など、Web検索だけでは確認できなかった項目）。</t>
+          <t>このシートはWeb検索で見つけた実在店舗の下調べリストです。件数を大きく伸ばすには限界があり、</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>「業種」「市町」「結果」列はプルダウンから選択できます。</t>
+          <t>特に美容室・理容室は店舗数が非常に多い一方、Web検索の要約からは個別店名が拾いにくい業態です。</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>架電したら「架電日」「結果」「次回アクション予定日」を都度更新してください。</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>結果の記録ルール</t>
+          <t>母数を一気に増やすには「iタウンページ」（https://itp.ne.jp/）で業種×市区町村を指定して検索・</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>コピペする方法がもっとも効率的です（店名・電話番号・住所が一覧で出ます）。詳細は knowledge フォルダのメモ参照。</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>未架電 / 不在 / 拒否 / 資料送付OK / アポ確定 / 見送り の6区分で統一します。</t>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>入力のしかた</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>黄色のセルは要確認・要入力です（電話番号・定休日など、Web検索だけでは確認できなかった項目）。</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>集計</t>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>「業種」「市町」「結果」列はプルダウンから選択できます。</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>「集計」タブに架電数・アポ率が自動計算されます（架電リストの入力に連動）。</t>
+          <t>架電したら「架電日」「結果」「次回アクション予定日」を都度更新してください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>結果の記録ルール</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>未架電 / 不在 / 拒否 / 資料送付OK / アポ確定 / 見送り の6区分で統一します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>集計</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>「集計」タブに架電数・アポ率・市町別件数が自動計算されます（架電リストの入力に連動）。</t>
         </is>
       </c>
     </row>
@@ -585,11 +626,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M48"/>
+  <dimension ref="A1:M106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="26" customWidth="1" min="5" max="5"/>
@@ -600,7 +641,7 @@
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="13" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
-    <col width="26" customWidth="1" min="13" max="13"/>
+    <col width="28" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -695,7 +736,11 @@
         </is>
       </c>
       <c r="F2" s="7" t="inlineStr"/>
-      <c r="G2" s="7" t="inlineStr"/>
+      <c r="G2" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
       <c r="H2" s="6" t="inlineStr">
         <is>
           <t>不明</t>
@@ -744,7 +789,11 @@
         </is>
       </c>
       <c r="F3" s="7" t="inlineStr"/>
-      <c r="G3" s="7" t="inlineStr"/>
+      <c r="G3" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
       <c r="H3" s="6" t="inlineStr">
         <is>
           <t>不明</t>
@@ -793,7 +842,11 @@
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr"/>
-      <c r="G4" s="7" t="inlineStr"/>
+      <c r="G4" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
           <t>不明</t>
@@ -842,7 +895,11 @@
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr"/>
-      <c r="G5" s="7" t="inlineStr"/>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
       <c r="H5" s="6" t="inlineStr">
         <is>
           <t>不明</t>
@@ -891,7 +948,11 @@
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr"/>
-      <c r="G6" s="7" t="inlineStr"/>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
           <t>不明</t>
@@ -940,7 +1001,11 @@
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr"/>
-      <c r="G7" s="7" t="inlineStr"/>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
           <t>不明</t>
@@ -989,7 +1054,11 @@
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr"/>
-      <c r="G8" s="7" t="inlineStr"/>
+      <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
           <t>不明</t>
@@ -1034,7 +1103,11 @@
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr"/>
-      <c r="G9" s="7" t="inlineStr"/>
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
           <t>不明</t>
@@ -1079,7 +1152,11 @@
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr"/>
-      <c r="G10" s="7" t="inlineStr"/>
+      <c r="G10" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
           <t>不明</t>
@@ -1128,7 +1205,11 @@
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr"/>
-      <c r="G11" s="7" t="inlineStr"/>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
           <t>不明</t>
@@ -1177,7 +1258,11 @@
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr"/>
-      <c r="G12" s="7" t="inlineStr"/>
+      <c r="G12" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
           <t>不明</t>
@@ -1226,7 +1311,11 @@
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr"/>
-      <c r="G13" s="7" t="inlineStr"/>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
           <t>不明</t>
@@ -1275,7 +1364,11 @@
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr"/>
-      <c r="G14" s="7" t="inlineStr"/>
+      <c r="G14" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
           <t>不明</t>
@@ -1324,7 +1417,11 @@
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr"/>
-      <c r="G15" s="7" t="inlineStr"/>
+      <c r="G15" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
           <t>不明</t>
@@ -1373,7 +1470,11 @@
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr"/>
-      <c r="G16" s="7" t="inlineStr"/>
+      <c r="G16" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
       <c r="H16" s="6" t="inlineStr">
         <is>
           <t>不明</t>
@@ -1418,7 +1519,11 @@
         </is>
       </c>
       <c r="F17" s="7" t="inlineStr"/>
-      <c r="G17" s="7" t="inlineStr"/>
+      <c r="G17" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
           <t>不明</t>
@@ -1463,7 +1568,11 @@
         </is>
       </c>
       <c r="F18" s="7" t="inlineStr"/>
-      <c r="G18" s="7" t="inlineStr"/>
+      <c r="G18" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
       <c r="H18" s="6" t="inlineStr">
         <is>
           <t>不明</t>
@@ -1512,7 +1621,11 @@
         </is>
       </c>
       <c r="F19" s="7" t="inlineStr"/>
-      <c r="G19" s="7" t="inlineStr"/>
+      <c r="G19" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
       <c r="H19" s="6" t="inlineStr">
         <is>
           <t>不明</t>
@@ -1561,7 +1674,11 @@
         </is>
       </c>
       <c r="F20" s="7" t="inlineStr"/>
-      <c r="G20" s="7" t="inlineStr"/>
+      <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
       <c r="H20" s="6" t="inlineStr">
         <is>
           <t>不明</t>
@@ -1610,7 +1727,11 @@
         </is>
       </c>
       <c r="F21" s="7" t="inlineStr"/>
-      <c r="G21" s="7" t="inlineStr"/>
+      <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
       <c r="H21" s="6" t="inlineStr">
         <is>
           <t>不明</t>
@@ -1659,7 +1780,11 @@
         </is>
       </c>
       <c r="F22" s="7" t="inlineStr"/>
-      <c r="G22" s="7" t="inlineStr"/>
+      <c r="G22" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
       <c r="H22" s="6" t="inlineStr">
         <is>
           <t>不明</t>
@@ -1708,7 +1833,11 @@
         </is>
       </c>
       <c r="F23" s="7" t="inlineStr"/>
-      <c r="G23" s="7" t="inlineStr"/>
+      <c r="G23" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
       <c r="H23" s="6" t="inlineStr">
         <is>
           <t>不明</t>
@@ -1736,439 +1865,2865 @@
       <c r="A24" s="5" t="n">
         <v>23</v>
       </c>
-      <c r="B24" s="8" t="inlineStr"/>
-      <c r="C24" s="8" t="inlineStr"/>
-      <c r="D24" s="8" t="inlineStr"/>
-      <c r="E24" s="8" t="inlineStr"/>
-      <c r="F24" s="8" t="inlineStr"/>
-      <c r="G24" s="8" t="inlineStr"/>
-      <c r="H24" s="8" t="inlineStr"/>
-      <c r="I24" s="8" t="inlineStr"/>
-      <c r="J24" s="8" t="inlineStr"/>
-      <c r="K24" s="8" t="inlineStr"/>
-      <c r="L24" s="8" t="inlineStr"/>
-      <c r="M24" s="8" t="inlineStr"/>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>宇都宮みんみん 本店</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>飲食店</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>宇都宮市</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>宇都宮駅前エリア</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr"/>
+      <c r="G24" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I24" s="6" t="inlineStr">
+        <is>
+          <t>観光メディア掲載店</t>
+        </is>
+      </c>
+      <c r="J24" s="6" t="inlineStr"/>
+      <c r="K24" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L24" s="6" t="inlineStr"/>
+      <c r="M24" s="6" t="inlineStr">
+        <is>
+          <t>昭和33年創業の老舗餃子専門店</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="B25" s="8" t="inlineStr"/>
-      <c r="C25" s="8" t="inlineStr"/>
-      <c r="D25" s="8" t="inlineStr"/>
-      <c r="E25" s="8" t="inlineStr"/>
-      <c r="F25" s="8" t="inlineStr"/>
-      <c r="G25" s="8" t="inlineStr"/>
-      <c r="H25" s="8" t="inlineStr"/>
-      <c r="I25" s="8" t="inlineStr"/>
-      <c r="J25" s="8" t="inlineStr"/>
-      <c r="K25" s="8" t="inlineStr"/>
-      <c r="L25" s="8" t="inlineStr"/>
-      <c r="M25" s="8" t="inlineStr"/>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>正嗣 宮島本店</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>飲食店</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>宇都宮市</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>宮島町</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="inlineStr"/>
+      <c r="G25" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I25" s="6" t="inlineStr">
+        <is>
+          <t>観光メディア掲載店</t>
+        </is>
+      </c>
+      <c r="J25" s="6" t="inlineStr"/>
+      <c r="K25" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L25" s="6" t="inlineStr"/>
+      <c r="M25" s="6" t="inlineStr">
+        <is>
+          <t>昭和40年創業、焼餃子と水餃子のみの専門店</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="n">
         <v>25</v>
       </c>
-      <c r="B26" s="8" t="inlineStr"/>
-      <c r="C26" s="8" t="inlineStr"/>
-      <c r="D26" s="8" t="inlineStr"/>
-      <c r="E26" s="8" t="inlineStr"/>
-      <c r="F26" s="8" t="inlineStr"/>
-      <c r="G26" s="8" t="inlineStr"/>
-      <c r="H26" s="8" t="inlineStr"/>
-      <c r="I26" s="8" t="inlineStr"/>
-      <c r="J26" s="8" t="inlineStr"/>
-      <c r="K26" s="8" t="inlineStr"/>
-      <c r="L26" s="8" t="inlineStr"/>
-      <c r="M26" s="8" t="inlineStr"/>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>香蘭</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>飲食店</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>宇都宮市</t>
+        </is>
+      </c>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>宇都宮駅前</t>
+        </is>
+      </c>
+      <c r="F26" s="7" t="inlineStr"/>
+      <c r="G26" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H26" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I26" s="6" t="inlineStr">
+        <is>
+          <t>公式サイト</t>
+        </is>
+      </c>
+      <c r="J26" s="6" t="inlineStr"/>
+      <c r="K26" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L26" s="6" t="inlineStr"/>
+      <c r="M26" s="6" t="inlineStr">
+        <is>
+          <t>創業昭和34年の老舗餃子店</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="B27" s="8" t="inlineStr"/>
-      <c r="C27" s="8" t="inlineStr"/>
-      <c r="D27" s="8" t="inlineStr"/>
-      <c r="E27" s="8" t="inlineStr"/>
-      <c r="F27" s="8" t="inlineStr"/>
-      <c r="G27" s="8" t="inlineStr"/>
-      <c r="H27" s="8" t="inlineStr"/>
-      <c r="I27" s="8" t="inlineStr"/>
-      <c r="J27" s="8" t="inlineStr"/>
-      <c r="K27" s="8" t="inlineStr"/>
-      <c r="L27" s="8" t="inlineStr"/>
-      <c r="M27" s="8" t="inlineStr"/>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>青源</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>飲食店</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>宇都宮市</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="inlineStr"/>
+      <c r="F27" s="7" t="inlineStr"/>
+      <c r="G27" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H27" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I27" s="6" t="inlineStr">
+        <is>
+          <t>観光メディア掲載店</t>
+        </is>
+      </c>
+      <c r="J27" s="6" t="inlineStr"/>
+      <c r="K27" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L27" s="6" t="inlineStr"/>
+      <c r="M27" s="6" t="inlineStr">
+        <is>
+          <t>創業300年以上の老舗味噌屋が手がける餃子店</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="n">
         <v>27</v>
       </c>
-      <c r="B28" s="8" t="inlineStr"/>
-      <c r="C28" s="8" t="inlineStr"/>
-      <c r="D28" s="8" t="inlineStr"/>
-      <c r="E28" s="8" t="inlineStr"/>
-      <c r="F28" s="8" t="inlineStr"/>
-      <c r="G28" s="8" t="inlineStr"/>
-      <c r="H28" s="8" t="inlineStr"/>
-      <c r="I28" s="8" t="inlineStr"/>
-      <c r="J28" s="8" t="inlineStr"/>
-      <c r="K28" s="8" t="inlineStr"/>
-      <c r="L28" s="8" t="inlineStr"/>
-      <c r="M28" s="8" t="inlineStr"/>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>かふえあんでぃーぶ</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>カフェ</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>足利市</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="inlineStr"/>
+      <c r="F28" s="7" t="inlineStr"/>
+      <c r="G28" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H28" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I28" s="6" t="inlineStr">
+        <is>
+          <t>観光メディア掲載店</t>
+        </is>
+      </c>
+      <c r="J28" s="6" t="inlineStr"/>
+      <c r="K28" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L28" s="6" t="inlineStr"/>
+      <c r="M28" s="6" t="inlineStr">
+        <is>
+          <t>老舗カフェ、ドリップコーヒー</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="n">
         <v>28</v>
       </c>
-      <c r="B29" s="8" t="inlineStr"/>
-      <c r="C29" s="8" t="inlineStr"/>
-      <c r="D29" s="8" t="inlineStr"/>
-      <c r="E29" s="8" t="inlineStr"/>
-      <c r="F29" s="8" t="inlineStr"/>
-      <c r="G29" s="8" t="inlineStr"/>
-      <c r="H29" s="8" t="inlineStr"/>
-      <c r="I29" s="8" t="inlineStr"/>
-      <c r="J29" s="8" t="inlineStr"/>
-      <c r="K29" s="8" t="inlineStr"/>
-      <c r="L29" s="8" t="inlineStr"/>
-      <c r="M29" s="8" t="inlineStr"/>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>珈琲蔵</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>カフェ</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>足利市</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="inlineStr"/>
+      <c r="F29" s="7" t="inlineStr"/>
+      <c r="G29" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H29" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I29" s="6" t="inlineStr">
+        <is>
+          <t>観光メディア掲載店</t>
+        </is>
+      </c>
+      <c r="J29" s="6" t="inlineStr"/>
+      <c r="K29" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L29" s="6" t="inlineStr"/>
+      <c r="M29" s="6" t="inlineStr">
+        <is>
+          <t>蔵を改装した喫茶店</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="n">
         <v>29</v>
       </c>
-      <c r="B30" s="8" t="inlineStr"/>
-      <c r="C30" s="8" t="inlineStr"/>
-      <c r="D30" s="8" t="inlineStr"/>
-      <c r="E30" s="8" t="inlineStr"/>
-      <c r="F30" s="8" t="inlineStr"/>
-      <c r="G30" s="8" t="inlineStr"/>
-      <c r="H30" s="8" t="inlineStr"/>
-      <c r="I30" s="8" t="inlineStr"/>
-      <c r="J30" s="8" t="inlineStr"/>
-      <c r="K30" s="8" t="inlineStr"/>
-      <c r="L30" s="8" t="inlineStr"/>
-      <c r="M30" s="8" t="inlineStr"/>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>八蔵（はちくら）</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>カフェ</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>足利市</t>
+        </is>
+      </c>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>足利駅南口徒歩8分・石畳通り</t>
+        </is>
+      </c>
+      <c r="F30" s="7" t="inlineStr"/>
+      <c r="G30" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H30" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I30" s="6" t="inlineStr">
+        <is>
+          <t>観光メディア掲載店</t>
+        </is>
+      </c>
+      <c r="J30" s="6" t="inlineStr"/>
+      <c r="K30" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L30" s="6" t="inlineStr"/>
+      <c r="M30" s="6" t="inlineStr">
+        <is>
+          <t>米蔵をリノベーションした古民家カフェ</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="B31" s="8" t="inlineStr"/>
-      <c r="C31" s="8" t="inlineStr"/>
-      <c r="D31" s="8" t="inlineStr"/>
-      <c r="E31" s="8" t="inlineStr"/>
-      <c r="F31" s="8" t="inlineStr"/>
-      <c r="G31" s="8" t="inlineStr"/>
-      <c r="H31" s="8" t="inlineStr"/>
-      <c r="I31" s="8" t="inlineStr"/>
-      <c r="J31" s="8" t="inlineStr"/>
-      <c r="K31" s="8" t="inlineStr"/>
-      <c r="L31" s="8" t="inlineStr"/>
-      <c r="M31" s="8" t="inlineStr"/>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>茶房のの</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>カフェ</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>足利市</t>
+        </is>
+      </c>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>八幡町</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="inlineStr"/>
+      <c r="G31" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H31" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I31" s="6" t="inlineStr">
+        <is>
+          <t>公式サイト</t>
+        </is>
+      </c>
+      <c r="J31" s="6" t="inlineStr"/>
+      <c r="K31" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L31" s="6" t="inlineStr"/>
+      <c r="M31" s="6" t="inlineStr">
+        <is>
+          <t>古民家カフェ、あんみつ・かき氷</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="n">
         <v>31</v>
       </c>
-      <c r="B32" s="8" t="inlineStr"/>
-      <c r="C32" s="8" t="inlineStr"/>
-      <c r="D32" s="8" t="inlineStr"/>
-      <c r="E32" s="8" t="inlineStr"/>
-      <c r="F32" s="8" t="inlineStr"/>
-      <c r="G32" s="8" t="inlineStr"/>
-      <c r="H32" s="8" t="inlineStr"/>
-      <c r="I32" s="8" t="inlineStr"/>
-      <c r="J32" s="8" t="inlineStr"/>
-      <c r="K32" s="8" t="inlineStr"/>
-      <c r="L32" s="8" t="inlineStr"/>
-      <c r="M32" s="8" t="inlineStr"/>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>麺や 大山</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>飲食店</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>佐野市</t>
+        </is>
+      </c>
+      <c r="E32" s="6" t="inlineStr"/>
+      <c r="F32" s="7" t="inlineStr"/>
+      <c r="G32" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H32" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I32" s="6" t="inlineStr">
+        <is>
+          <t>グルメサイト掲載店</t>
+        </is>
+      </c>
+      <c r="J32" s="6" t="inlineStr"/>
+      <c r="K32" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L32" s="6" t="inlineStr"/>
+      <c r="M32" s="6" t="inlineStr">
+        <is>
+          <t>佐野ラーメンの名店、青竹手打ち麺</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="n">
         <v>32</v>
       </c>
-      <c r="B33" s="8" t="inlineStr"/>
-      <c r="C33" s="8" t="inlineStr"/>
-      <c r="D33" s="8" t="inlineStr"/>
-      <c r="E33" s="8" t="inlineStr"/>
-      <c r="F33" s="8" t="inlineStr"/>
-      <c r="G33" s="8" t="inlineStr"/>
-      <c r="H33" s="8" t="inlineStr"/>
-      <c r="I33" s="8" t="inlineStr"/>
-      <c r="J33" s="8" t="inlineStr"/>
-      <c r="K33" s="8" t="inlineStr"/>
-      <c r="L33" s="8" t="inlineStr"/>
-      <c r="M33" s="8" t="inlineStr"/>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>麺屋ようすけ</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>飲食店</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>佐野市</t>
+        </is>
+      </c>
+      <c r="E33" s="6" t="inlineStr"/>
+      <c r="F33" s="7" t="inlineStr"/>
+      <c r="G33" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H33" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I33" s="6" t="inlineStr">
+        <is>
+          <t>グルメサイト掲載店</t>
+        </is>
+      </c>
+      <c r="J33" s="6" t="inlineStr"/>
+      <c r="K33" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L33" s="6" t="inlineStr"/>
+      <c r="M33" s="6" t="inlineStr">
+        <is>
+          <t>佐野ラーメン、透き通るスープ</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="B34" s="8" t="inlineStr"/>
-      <c r="C34" s="8" t="inlineStr"/>
-      <c r="D34" s="8" t="inlineStr"/>
-      <c r="E34" s="8" t="inlineStr"/>
-      <c r="F34" s="8" t="inlineStr"/>
-      <c r="G34" s="8" t="inlineStr"/>
-      <c r="H34" s="8" t="inlineStr"/>
-      <c r="I34" s="8" t="inlineStr"/>
-      <c r="J34" s="8" t="inlineStr"/>
-      <c r="K34" s="8" t="inlineStr"/>
-      <c r="L34" s="8" t="inlineStr"/>
-      <c r="M34" s="8" t="inlineStr"/>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>森田屋総本店</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>飲食店</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>佐野市</t>
+        </is>
+      </c>
+      <c r="E34" s="6" t="inlineStr"/>
+      <c r="F34" s="7" t="inlineStr"/>
+      <c r="G34" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H34" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I34" s="6" t="inlineStr">
+        <is>
+          <t>グルメサイト掲載店</t>
+        </is>
+      </c>
+      <c r="J34" s="6" t="inlineStr"/>
+      <c r="K34" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L34" s="6" t="inlineStr"/>
+      <c r="M34" s="6" t="inlineStr">
+        <is>
+          <t>佐野ラーメン、麺・チャーシュー・スープ全て自家製</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="n">
         <v>34</v>
       </c>
-      <c r="B35" s="8" t="inlineStr"/>
-      <c r="C35" s="8" t="inlineStr"/>
-      <c r="D35" s="8" t="inlineStr"/>
-      <c r="E35" s="8" t="inlineStr"/>
-      <c r="F35" s="8" t="inlineStr"/>
-      <c r="G35" s="8" t="inlineStr"/>
-      <c r="H35" s="8" t="inlineStr"/>
-      <c r="I35" s="8" t="inlineStr"/>
-      <c r="J35" s="8" t="inlineStr"/>
-      <c r="K35" s="8" t="inlineStr"/>
-      <c r="L35" s="8" t="inlineStr"/>
-      <c r="M35" s="8" t="inlineStr"/>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>クラシック・カフェ音楽館</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>カフェ</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>小山市</t>
+        </is>
+      </c>
+      <c r="E35" s="6" t="inlineStr">
+        <is>
+          <t>犬塚5丁目</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="inlineStr"/>
+      <c r="G35" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H35" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I35" s="6" t="inlineStr">
+        <is>
+          <t>グルメサイト掲載店</t>
+        </is>
+      </c>
+      <c r="J35" s="6" t="inlineStr"/>
+      <c r="K35" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L35" s="6" t="inlineStr"/>
+      <c r="M35" s="6" t="inlineStr">
+        <is>
+          <t>古民家、クラシック音楽が流れる店内</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="n">
         <v>35</v>
       </c>
-      <c r="B36" s="8" t="inlineStr"/>
-      <c r="C36" s="8" t="inlineStr"/>
-      <c r="D36" s="8" t="inlineStr"/>
-      <c r="E36" s="8" t="inlineStr"/>
-      <c r="F36" s="8" t="inlineStr"/>
-      <c r="G36" s="8" t="inlineStr"/>
-      <c r="H36" s="8" t="inlineStr"/>
-      <c r="I36" s="8" t="inlineStr"/>
-      <c r="J36" s="8" t="inlineStr"/>
-      <c r="K36" s="8" t="inlineStr"/>
-      <c r="L36" s="8" t="inlineStr"/>
-      <c r="M36" s="8" t="inlineStr"/>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>だんご茶屋</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>和菓子店</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>小山市</t>
+        </is>
+      </c>
+      <c r="E36" s="6" t="inlineStr">
+        <is>
+          <t>小山第二中学校付近</t>
+        </is>
+      </c>
+      <c r="F36" s="7" t="inlineStr"/>
+      <c r="G36" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H36" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I36" s="6" t="inlineStr">
+        <is>
+          <t>グルメサイト掲載店</t>
+        </is>
+      </c>
+      <c r="J36" s="6" t="inlineStr"/>
+      <c r="K36" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L36" s="6" t="inlineStr"/>
+      <c r="M36" s="6" t="inlineStr">
+        <is>
+          <t>白玉ぜんざいなど</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="n">
         <v>36</v>
       </c>
-      <c r="B37" s="8" t="inlineStr"/>
-      <c r="C37" s="8" t="inlineStr"/>
-      <c r="D37" s="8" t="inlineStr"/>
-      <c r="E37" s="8" t="inlineStr"/>
-      <c r="F37" s="8" t="inlineStr"/>
-      <c r="G37" s="8" t="inlineStr"/>
-      <c r="H37" s="8" t="inlineStr"/>
-      <c r="I37" s="8" t="inlineStr"/>
-      <c r="J37" s="8" t="inlineStr"/>
-      <c r="K37" s="8" t="inlineStr"/>
-      <c r="L37" s="8" t="inlineStr"/>
-      <c r="M37" s="8" t="inlineStr"/>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>居場所カフェ・あおぞら</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>カフェ</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>小山市</t>
+        </is>
+      </c>
+      <c r="E37" s="6" t="inlineStr"/>
+      <c r="F37" s="7" t="inlineStr"/>
+      <c r="G37" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H37" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I37" s="6" t="inlineStr">
+        <is>
+          <t>グルメサイト掲載店</t>
+        </is>
+      </c>
+      <c r="J37" s="6" t="inlineStr"/>
+      <c r="K37" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L37" s="6" t="inlineStr"/>
+      <c r="M37" s="6" t="inlineStr">
+        <is>
+          <t>無農薬野菜を使った健康志向カフェ</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="n">
         <v>37</v>
       </c>
-      <c r="B38" s="8" t="inlineStr"/>
-      <c r="C38" s="8" t="inlineStr"/>
-      <c r="D38" s="8" t="inlineStr"/>
-      <c r="E38" s="8" t="inlineStr"/>
-      <c r="F38" s="8" t="inlineStr"/>
-      <c r="G38" s="8" t="inlineStr"/>
-      <c r="H38" s="8" t="inlineStr"/>
-      <c r="I38" s="8" t="inlineStr"/>
-      <c r="J38" s="8" t="inlineStr"/>
-      <c r="K38" s="8" t="inlineStr"/>
-      <c r="L38" s="8" t="inlineStr"/>
-      <c r="M38" s="8" t="inlineStr"/>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>CafeQ</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>カフェ</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>小山市</t>
+        </is>
+      </c>
+      <c r="E38" s="6" t="inlineStr">
+        <is>
+          <t>城東</t>
+        </is>
+      </c>
+      <c r="F38" s="7" t="inlineStr"/>
+      <c r="G38" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H38" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I38" s="6" t="inlineStr">
+        <is>
+          <t>グルメサイト掲載店</t>
+        </is>
+      </c>
+      <c r="J38" s="6" t="inlineStr"/>
+      <c r="K38" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L38" s="6" t="inlineStr"/>
+      <c r="M38" s="6" t="inlineStr">
+        <is>
+          <t>山小屋風、ハンバーガーが名物</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="n">
         <v>38</v>
       </c>
-      <c r="B39" s="8" t="inlineStr"/>
-      <c r="C39" s="8" t="inlineStr"/>
-      <c r="D39" s="8" t="inlineStr"/>
-      <c r="E39" s="8" t="inlineStr"/>
-      <c r="F39" s="8" t="inlineStr"/>
-      <c r="G39" s="8" t="inlineStr"/>
-      <c r="H39" s="8" t="inlineStr"/>
-      <c r="I39" s="8" t="inlineStr"/>
-      <c r="J39" s="8" t="inlineStr"/>
-      <c r="K39" s="8" t="inlineStr"/>
-      <c r="L39" s="8" t="inlineStr"/>
-      <c r="M39" s="8" t="inlineStr"/>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>Bee House</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>カフェ</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>小山市</t>
+        </is>
+      </c>
+      <c r="E39" s="6" t="inlineStr">
+        <is>
+          <t>国道50号沿い</t>
+        </is>
+      </c>
+      <c r="F39" s="7" t="inlineStr"/>
+      <c r="G39" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H39" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I39" s="6" t="inlineStr">
+        <is>
+          <t>グルメサイト掲載店</t>
+        </is>
+      </c>
+      <c r="J39" s="6" t="inlineStr"/>
+      <c r="K39" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L39" s="6" t="inlineStr"/>
+      <c r="M39" s="6" t="inlineStr">
+        <is>
+          <t>ホットケーキが名物</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="n">
         <v>39</v>
       </c>
-      <c r="B40" s="8" t="inlineStr"/>
-      <c r="C40" s="8" t="inlineStr"/>
-      <c r="D40" s="8" t="inlineStr"/>
-      <c r="E40" s="8" t="inlineStr"/>
-      <c r="F40" s="8" t="inlineStr"/>
-      <c r="G40" s="8" t="inlineStr"/>
-      <c r="H40" s="8" t="inlineStr"/>
-      <c r="I40" s="8" t="inlineStr"/>
-      <c r="J40" s="8" t="inlineStr"/>
-      <c r="K40" s="8" t="inlineStr"/>
-      <c r="L40" s="8" t="inlineStr"/>
-      <c r="M40" s="8" t="inlineStr"/>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>みやいりそば</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>飲食店</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>鹿沼市</t>
+        </is>
+      </c>
+      <c r="E40" s="6" t="inlineStr">
+        <is>
+          <t>深程1386-1</t>
+        </is>
+      </c>
+      <c r="F40" s="7" t="inlineStr"/>
+      <c r="G40" s="6" t="inlineStr">
+        <is>
+          <t>月曜日</t>
+        </is>
+      </c>
+      <c r="H40" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I40" s="6" t="inlineStr">
+        <is>
+          <t>グルメサイト掲載店</t>
+        </is>
+      </c>
+      <c r="J40" s="6" t="inlineStr"/>
+      <c r="K40" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L40" s="6" t="inlineStr"/>
+      <c r="M40" s="6" t="inlineStr">
+        <is>
+          <t>鹿沼名物ニラそば、定休日: 月曜（要再確認）</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="n">
         <v>40</v>
       </c>
-      <c r="B41" s="8" t="inlineStr"/>
-      <c r="C41" s="8" t="inlineStr"/>
-      <c r="D41" s="8" t="inlineStr"/>
-      <c r="E41" s="8" t="inlineStr"/>
-      <c r="F41" s="8" t="inlineStr"/>
-      <c r="G41" s="8" t="inlineStr"/>
-      <c r="H41" s="8" t="inlineStr"/>
-      <c r="I41" s="8" t="inlineStr"/>
-      <c r="J41" s="8" t="inlineStr"/>
-      <c r="K41" s="8" t="inlineStr"/>
-      <c r="L41" s="8" t="inlineStr"/>
-      <c r="M41" s="8" t="inlineStr"/>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>そば花</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>飲食店</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>鹿沼市</t>
+        </is>
+      </c>
+      <c r="E41" s="6" t="inlineStr"/>
+      <c r="F41" s="7" t="inlineStr"/>
+      <c r="G41" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H41" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I41" s="6" t="inlineStr">
+        <is>
+          <t>グルメサイト掲載店</t>
+        </is>
+      </c>
+      <c r="J41" s="6" t="inlineStr"/>
+      <c r="K41" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L41" s="6" t="inlineStr"/>
+      <c r="M41" s="6" t="inlineStr">
+        <is>
+          <t>行列のできる人気そば店</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="n">
         <v>41</v>
       </c>
-      <c r="B42" s="8" t="inlineStr"/>
-      <c r="C42" s="8" t="inlineStr"/>
-      <c r="D42" s="8" t="inlineStr"/>
-      <c r="E42" s="8" t="inlineStr"/>
-      <c r="F42" s="8" t="inlineStr"/>
-      <c r="G42" s="8" t="inlineStr"/>
-      <c r="H42" s="8" t="inlineStr"/>
-      <c r="I42" s="8" t="inlineStr"/>
-      <c r="J42" s="8" t="inlineStr"/>
-      <c r="K42" s="8" t="inlineStr"/>
-      <c r="L42" s="8" t="inlineStr"/>
-      <c r="M42" s="8" t="inlineStr"/>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>くだものやカフェ 通りの茶屋 藤屋</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>カフェ</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>那須塩原市</t>
+        </is>
+      </c>
+      <c r="E42" s="6" t="inlineStr">
+        <is>
+          <t>塩原温泉</t>
+        </is>
+      </c>
+      <c r="F42" s="7" t="inlineStr"/>
+      <c r="G42" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H42" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I42" s="6" t="inlineStr">
+        <is>
+          <t>グルメサイト掲載店</t>
+        </is>
+      </c>
+      <c r="J42" s="6" t="inlineStr"/>
+      <c r="K42" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L42" s="6" t="inlineStr"/>
+      <c r="M42" s="6" t="inlineStr">
+        <is>
+          <t>大正元年創業、元青果店のカフェ</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="n">
         <v>42</v>
       </c>
-      <c r="B43" s="8" t="inlineStr"/>
-      <c r="C43" s="8" t="inlineStr"/>
-      <c r="D43" s="8" t="inlineStr"/>
-      <c r="E43" s="8" t="inlineStr"/>
-      <c r="F43" s="8" t="inlineStr"/>
-      <c r="G43" s="8" t="inlineStr"/>
-      <c r="H43" s="8" t="inlineStr"/>
-      <c r="I43" s="8" t="inlineStr"/>
-      <c r="J43" s="8" t="inlineStr"/>
-      <c r="K43" s="8" t="inlineStr"/>
-      <c r="L43" s="8" t="inlineStr"/>
-      <c r="M43" s="8" t="inlineStr"/>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>栄太楼</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>和菓子店</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>那須塩原市</t>
+        </is>
+      </c>
+      <c r="E43" s="6" t="inlineStr">
+        <is>
+          <t>塩原温泉</t>
+        </is>
+      </c>
+      <c r="F43" s="7" t="inlineStr"/>
+      <c r="G43" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H43" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I43" s="6" t="inlineStr">
+        <is>
+          <t>グルメサイト掲載店</t>
+        </is>
+      </c>
+      <c r="J43" s="6" t="inlineStr"/>
+      <c r="K43" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L43" s="6" t="inlineStr"/>
+      <c r="M43" s="6" t="inlineStr">
+        <is>
+          <t>昭和初期創業の老舗和菓子屋、2階カフェで「とて焼き」</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="n">
         <v>43</v>
       </c>
-      <c r="B44" s="8" t="inlineStr"/>
-      <c r="C44" s="8" t="inlineStr"/>
-      <c r="D44" s="8" t="inlineStr"/>
-      <c r="E44" s="8" t="inlineStr"/>
-      <c r="F44" s="8" t="inlineStr"/>
-      <c r="G44" s="8" t="inlineStr"/>
-      <c r="H44" s="8" t="inlineStr"/>
-      <c r="I44" s="8" t="inlineStr"/>
-      <c r="J44" s="8" t="inlineStr"/>
-      <c r="K44" s="8" t="inlineStr"/>
-      <c r="L44" s="8" t="inlineStr"/>
-      <c r="M44" s="8" t="inlineStr"/>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>SUZUの森cafe</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>カフェ</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>那須塩原市</t>
+        </is>
+      </c>
+      <c r="E44" s="6" t="inlineStr">
+        <is>
+          <t>塩原温泉近く</t>
+        </is>
+      </c>
+      <c r="F44" s="7" t="inlineStr"/>
+      <c r="G44" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H44" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I44" s="6" t="inlineStr">
+        <is>
+          <t>グルメサイト掲載店</t>
+        </is>
+      </c>
+      <c r="J44" s="6" t="inlineStr"/>
+      <c r="K44" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L44" s="6" t="inlineStr"/>
+      <c r="M44" s="6" t="inlineStr">
+        <is>
+          <t>箒川を一望するテラス席</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="n">
         <v>44</v>
       </c>
-      <c r="B45" s="8" t="inlineStr"/>
-      <c r="C45" s="8" t="inlineStr"/>
-      <c r="D45" s="8" t="inlineStr"/>
-      <c r="E45" s="8" t="inlineStr"/>
-      <c r="F45" s="8" t="inlineStr"/>
-      <c r="G45" s="8" t="inlineStr"/>
-      <c r="H45" s="8" t="inlineStr"/>
-      <c r="I45" s="8" t="inlineStr"/>
-      <c r="J45" s="8" t="inlineStr"/>
-      <c r="K45" s="8" t="inlineStr"/>
-      <c r="L45" s="8" t="inlineStr"/>
-      <c r="M45" s="8" t="inlineStr"/>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>チーズガーデン 塩原珈琲</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>カフェ</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>那須塩原市</t>
+        </is>
+      </c>
+      <c r="E45" s="6" t="inlineStr">
+        <is>
+          <t>塩原温泉郷入口</t>
+        </is>
+      </c>
+      <c r="F45" s="7" t="inlineStr"/>
+      <c r="G45" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H45" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I45" s="6" t="inlineStr">
+        <is>
+          <t>公式サイト</t>
+        </is>
+      </c>
+      <c r="J45" s="6" t="inlineStr"/>
+      <c r="K45" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L45" s="6" t="inlineStr"/>
+      <c r="M45" s="6" t="inlineStr">
+        <is>
+          <t>チーズ菓子専門店併設カフェ</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="n">
         <v>45</v>
       </c>
-      <c r="B46" s="8" t="inlineStr"/>
-      <c r="C46" s="8" t="inlineStr"/>
-      <c r="D46" s="8" t="inlineStr"/>
-      <c r="E46" s="8" t="inlineStr"/>
-      <c r="F46" s="8" t="inlineStr"/>
-      <c r="G46" s="8" t="inlineStr"/>
-      <c r="H46" s="8" t="inlineStr"/>
-      <c r="I46" s="8" t="inlineStr"/>
-      <c r="J46" s="8" t="inlineStr"/>
-      <c r="K46" s="8" t="inlineStr"/>
-      <c r="L46" s="8" t="inlineStr"/>
-      <c r="M46" s="8" t="inlineStr"/>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>カフェ いちごや</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>カフェ</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>真岡市</t>
+        </is>
+      </c>
+      <c r="E46" s="6" t="inlineStr">
+        <is>
+          <t>高田1019-1</t>
+        </is>
+      </c>
+      <c r="F46" s="7" t="inlineStr"/>
+      <c r="G46" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H46" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I46" s="6" t="inlineStr">
+        <is>
+          <t>地域情報サイト掲載店</t>
+        </is>
+      </c>
+      <c r="J46" s="6" t="inlineStr"/>
+      <c r="K46" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L46" s="6" t="inlineStr"/>
+      <c r="M46" s="6" t="inlineStr">
+        <is>
+          <t>いちご農家が営むカフェ</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="n">
         <v>46</v>
       </c>
-      <c r="B47" s="8" t="inlineStr"/>
-      <c r="C47" s="8" t="inlineStr"/>
-      <c r="D47" s="8" t="inlineStr"/>
-      <c r="E47" s="8" t="inlineStr"/>
-      <c r="F47" s="8" t="inlineStr"/>
-      <c r="G47" s="8" t="inlineStr"/>
-      <c r="H47" s="8" t="inlineStr"/>
-      <c r="I47" s="8" t="inlineStr"/>
-      <c r="J47" s="8" t="inlineStr"/>
-      <c r="K47" s="8" t="inlineStr"/>
-      <c r="L47" s="8" t="inlineStr"/>
-      <c r="M47" s="8" t="inlineStr"/>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>御菓子司 紅谷三宅</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>和菓子店</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>真岡市</t>
+        </is>
+      </c>
+      <c r="E47" s="6" t="inlineStr"/>
+      <c r="F47" s="7" t="inlineStr"/>
+      <c r="G47" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H47" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I47" s="6" t="inlineStr">
+        <is>
+          <t>地域情報サイト掲載店</t>
+        </is>
+      </c>
+      <c r="J47" s="6" t="inlineStr"/>
+      <c r="K47" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L47" s="6" t="inlineStr"/>
+      <c r="M47" s="6" t="inlineStr">
+        <is>
+          <t>いちご大福が名物</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="n">
         <v>47</v>
       </c>
-      <c r="B48" s="8" t="inlineStr"/>
-      <c r="C48" s="8" t="inlineStr"/>
-      <c r="D48" s="8" t="inlineStr"/>
-      <c r="E48" s="8" t="inlineStr"/>
-      <c r="F48" s="8" t="inlineStr"/>
-      <c r="G48" s="8" t="inlineStr"/>
-      <c r="H48" s="8" t="inlineStr"/>
-      <c r="I48" s="8" t="inlineStr"/>
-      <c r="J48" s="8" t="inlineStr"/>
-      <c r="K48" s="8" t="inlineStr"/>
-      <c r="L48" s="8" t="inlineStr"/>
-      <c r="M48" s="8" t="inlineStr"/>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>山吉商店</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>カフェ</t>
+        </is>
+      </c>
+      <c r="D48" s="6" t="inlineStr">
+        <is>
+          <t>大田原市</t>
+        </is>
+      </c>
+      <c r="E48" s="6" t="inlineStr"/>
+      <c r="F48" s="7" t="inlineStr"/>
+      <c r="G48" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H48" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I48" s="6" t="inlineStr">
+        <is>
+          <t>グルメサイト掲載店</t>
+        </is>
+      </c>
+      <c r="J48" s="6" t="inlineStr"/>
+      <c r="K48" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L48" s="6" t="inlineStr"/>
+      <c r="M48" s="6" t="inlineStr">
+        <is>
+          <t>珈琲ショップ</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t>喫茶ハナモリ大田原店</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>カフェ</t>
+        </is>
+      </c>
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t>大田原市</t>
+        </is>
+      </c>
+      <c r="E49" s="6" t="inlineStr"/>
+      <c r="F49" s="7" t="inlineStr"/>
+      <c r="G49" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H49" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I49" s="6" t="inlineStr">
+        <is>
+          <t>公式サイト</t>
+        </is>
+      </c>
+      <c r="J49" s="6" t="inlineStr"/>
+      <c r="K49" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L49" s="6" t="inlineStr"/>
+      <c r="M49" s="6" t="inlineStr">
+        <is>
+          <t>2025年6月オープン、ナポリタン・手作りプリン</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" s="6" t="inlineStr">
+        <is>
+          <t>Cafe：甘茶</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>カフェ</t>
+        </is>
+      </c>
+      <c r="D50" s="6" t="inlineStr">
+        <is>
+          <t>壬生町</t>
+        </is>
+      </c>
+      <c r="E50" s="6" t="inlineStr"/>
+      <c r="F50" s="7" t="inlineStr"/>
+      <c r="G50" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H50" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I50" s="6" t="inlineStr">
+        <is>
+          <t>地域ブログ掲載店</t>
+        </is>
+      </c>
+      <c r="J50" s="6" t="inlineStr"/>
+      <c r="K50" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L50" s="6" t="inlineStr"/>
+      <c r="M50" s="6" t="inlineStr">
+        <is>
+          <t>抹茶メニュー中心</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" s="6" t="inlineStr">
+        <is>
+          <t>魚良（うおりょう）</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>飲食店</t>
+        </is>
+      </c>
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t>那珂川町</t>
+        </is>
+      </c>
+      <c r="E51" s="6" t="inlineStr"/>
+      <c r="F51" s="7" t="inlineStr"/>
+      <c r="G51" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H51" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I51" s="6" t="inlineStr">
+        <is>
+          <t>公式サイト</t>
+        </is>
+      </c>
+      <c r="J51" s="6" t="inlineStr"/>
+      <c r="K51" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L51" s="6" t="inlineStr"/>
+      <c r="M51" s="6" t="inlineStr">
+        <is>
+          <t>天然鮎の炭火焼き</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" s="6" t="inlineStr">
+        <is>
+          <t>黒羽観光やな</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>飲食店</t>
+        </is>
+      </c>
+      <c r="D52" s="6" t="inlineStr">
+        <is>
+          <t>那珂川町</t>
+        </is>
+      </c>
+      <c r="E52" s="6" t="inlineStr"/>
+      <c r="F52" s="7" t="inlineStr"/>
+      <c r="G52" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H52" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I52" s="6" t="inlineStr">
+        <is>
+          <t>公式サイト</t>
+        </is>
+      </c>
+      <c r="J52" s="6" t="inlineStr"/>
+      <c r="K52" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L52" s="6" t="inlineStr"/>
+      <c r="M52" s="6" t="inlineStr">
+        <is>
+          <t>鮎塩焼き・鮎釜めし・鮎刺身</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" s="6" t="inlineStr">
+        <is>
+          <t>菓子工房 SHIMADAYA</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>和菓子店</t>
+        </is>
+      </c>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>那須烏山市</t>
+        </is>
+      </c>
+      <c r="E53" s="6" t="inlineStr"/>
+      <c r="F53" s="7" t="inlineStr"/>
+      <c r="G53" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H53" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I53" s="6" t="inlineStr">
+        <is>
+          <t>地域情報サイト掲載店</t>
+        </is>
+      </c>
+      <c r="J53" s="6" t="inlineStr"/>
+      <c r="K53" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L53" s="6" t="inlineStr"/>
+      <c r="M53" s="6" t="inlineStr">
+        <is>
+          <t>4代続く老舗、烏山銘菓しらつゆ</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
+        <is>
+          <t>あん姫</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>カフェ</t>
+        </is>
+      </c>
+      <c r="D54" s="6" t="inlineStr">
+        <is>
+          <t>矢板市</t>
+        </is>
+      </c>
+      <c r="E54" s="6" t="inlineStr">
+        <is>
+          <t>国道461号沿い・南平公園前</t>
+        </is>
+      </c>
+      <c r="F54" s="7" t="inlineStr"/>
+      <c r="G54" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H54" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I54" s="6" t="inlineStr">
+        <is>
+          <t>地域情報サイト掲載店</t>
+        </is>
+      </c>
+      <c r="J54" s="6" t="inlineStr"/>
+      <c r="K54" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L54" s="6" t="inlineStr"/>
+      <c r="M54" s="6" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" s="6" t="inlineStr">
+        <is>
+          <t>道の駅もてぎ もてぎプラザ</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>カフェ</t>
+        </is>
+      </c>
+      <c r="D55" s="6" t="inlineStr">
+        <is>
+          <t>茂木町</t>
+        </is>
+      </c>
+      <c r="E55" s="6" t="inlineStr">
+        <is>
+          <t>道の駅もてぎ</t>
+        </is>
+      </c>
+      <c r="F55" s="7" t="inlineStr"/>
+      <c r="G55" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H55" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I55" s="6" t="inlineStr">
+        <is>
+          <t>公式サイト</t>
+        </is>
+      </c>
+      <c r="J55" s="6" t="inlineStr"/>
+      <c r="K55" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L55" s="6" t="inlineStr"/>
+      <c r="M55" s="6" t="inlineStr">
+        <is>
+          <t>カフェ・スイーツ</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" s="6" t="inlineStr">
+        <is>
+          <t>茂木満天家</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="inlineStr">
+        <is>
+          <t>カフェ</t>
+        </is>
+      </c>
+      <c r="D56" s="6" t="inlineStr">
+        <is>
+          <t>茂木町</t>
+        </is>
+      </c>
+      <c r="E56" s="6" t="inlineStr"/>
+      <c r="F56" s="7" t="inlineStr"/>
+      <c r="G56" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H56" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I56" s="6" t="inlineStr">
+        <is>
+          <t>地域情報サイト掲載店</t>
+        </is>
+      </c>
+      <c r="J56" s="6" t="inlineStr"/>
+      <c r="K56" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L56" s="6" t="inlineStr"/>
+      <c r="M56" s="6" t="inlineStr">
+        <is>
+          <t>天然かき氷が名物</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" s="6" t="inlineStr">
+        <is>
+          <t>COFFEE HOUSE PARCEL</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t>カフェ</t>
+        </is>
+      </c>
+      <c r="D57" s="6" t="inlineStr">
+        <is>
+          <t>下野市</t>
+        </is>
+      </c>
+      <c r="E57" s="6" t="inlineStr"/>
+      <c r="F57" s="7" t="inlineStr"/>
+      <c r="G57" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H57" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I57" s="6" t="inlineStr">
+        <is>
+          <t>地域情報サイト掲載店</t>
+        </is>
+      </c>
+      <c r="J57" s="6" t="inlineStr"/>
+      <c r="K57" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L57" s="6" t="inlineStr"/>
+      <c r="M57" s="6" t="inlineStr">
+        <is>
+          <t>創業40周年以上の老舗喫茶店</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" s="6" t="inlineStr">
+        <is>
+          <t>カフェギャラリー土筆</t>
+        </is>
+      </c>
+      <c r="C58" s="6" t="inlineStr">
+        <is>
+          <t>カフェ</t>
+        </is>
+      </c>
+      <c r="D58" s="6" t="inlineStr">
+        <is>
+          <t>下野市</t>
+        </is>
+      </c>
+      <c r="E58" s="6" t="inlineStr"/>
+      <c r="F58" s="7" t="inlineStr"/>
+      <c r="G58" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H58" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I58" s="6" t="inlineStr">
+        <is>
+          <t>地域情報サイト掲載店</t>
+        </is>
+      </c>
+      <c r="J58" s="6" t="inlineStr"/>
+      <c r="K58" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L58" s="6" t="inlineStr"/>
+      <c r="M58" s="6" t="inlineStr">
+        <is>
+          <t>古民家風、書・陶器展示併設</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" s="6" t="inlineStr">
+        <is>
+          <t>ごはんカフェ 坂の途中</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="inlineStr">
+        <is>
+          <t>カフェ</t>
+        </is>
+      </c>
+      <c r="D59" s="6" t="inlineStr">
+        <is>
+          <t>下野市</t>
+        </is>
+      </c>
+      <c r="E59" s="6" t="inlineStr"/>
+      <c r="F59" s="7" t="inlineStr"/>
+      <c r="G59" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H59" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I59" s="6" t="inlineStr">
+        <is>
+          <t>地域情報サイト掲載店</t>
+        </is>
+      </c>
+      <c r="J59" s="6" t="inlineStr"/>
+      <c r="K59" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L59" s="6" t="inlineStr"/>
+      <c r="M59" s="6" t="inlineStr">
+        <is>
+          <t>地元野菜を使った料理、2023年3月オープン</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="5" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" s="6" t="inlineStr">
+        <is>
+          <t>喫茶みるく</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="inlineStr">
+        <is>
+          <t>カフェ</t>
+        </is>
+      </c>
+      <c r="D60" s="6" t="inlineStr">
+        <is>
+          <t>下野市</t>
+        </is>
+      </c>
+      <c r="E60" s="6" t="inlineStr">
+        <is>
+          <t>大光寺2丁目</t>
+        </is>
+      </c>
+      <c r="F60" s="7" t="inlineStr"/>
+      <c r="G60" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H60" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I60" s="6" t="inlineStr">
+        <is>
+          <t>地域情報サイト掲載店</t>
+        </is>
+      </c>
+      <c r="J60" s="6" t="inlineStr"/>
+      <c r="K60" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L60" s="6" t="inlineStr"/>
+      <c r="M60" s="6" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" s="6" t="inlineStr">
+        <is>
+          <t>こびとカフェ</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>カフェ</t>
+        </is>
+      </c>
+      <c r="D61" s="6" t="inlineStr">
+        <is>
+          <t>野木町</t>
+        </is>
+      </c>
+      <c r="E61" s="6" t="inlineStr">
+        <is>
+          <t>野木町煉瓦窯 隣接</t>
+        </is>
+      </c>
+      <c r="F61" s="7" t="inlineStr"/>
+      <c r="G61" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H61" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I61" s="6" t="inlineStr">
+        <is>
+          <t>地域情報サイト掲載店</t>
+        </is>
+      </c>
+      <c r="J61" s="6" t="inlineStr"/>
+      <c r="K61" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L61" s="6" t="inlineStr"/>
+      <c r="M61" s="6" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="5" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" s="6" t="inlineStr">
+        <is>
+          <t>中西珈琲</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="inlineStr">
+        <is>
+          <t>カフェ</t>
+        </is>
+      </c>
+      <c r="D62" s="6" t="inlineStr">
+        <is>
+          <t>野木町</t>
+        </is>
+      </c>
+      <c r="E62" s="6" t="inlineStr"/>
+      <c r="F62" s="7" t="inlineStr"/>
+      <c r="G62" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H62" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I62" s="6" t="inlineStr">
+        <is>
+          <t>地域情報サイト掲載店</t>
+        </is>
+      </c>
+      <c r="J62" s="6" t="inlineStr"/>
+      <c r="K62" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L62" s="6" t="inlineStr"/>
+      <c r="M62" s="6" t="inlineStr">
+        <is>
+          <t>自家焙煎珈琲店、2018年2月開業</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" s="6" t="inlineStr">
+        <is>
+          <t>fu.+（パン工房fu×焼菓子Toko toko）</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="inlineStr">
+        <is>
+          <t>カフェ</t>
+        </is>
+      </c>
+      <c r="D63" s="6" t="inlineStr">
+        <is>
+          <t>高根沢町</t>
+        </is>
+      </c>
+      <c r="E63" s="6" t="inlineStr">
+        <is>
+          <t>宝石台4-14-5</t>
+        </is>
+      </c>
+      <c r="F63" s="7" t="inlineStr"/>
+      <c r="G63" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H63" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I63" s="6" t="inlineStr">
+        <is>
+          <t>地域情報サイト掲載店</t>
+        </is>
+      </c>
+      <c r="J63" s="6" t="inlineStr"/>
+      <c r="K63" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L63" s="6" t="inlineStr"/>
+      <c r="M63" s="6" t="inlineStr">
+        <is>
+          <t>天然酵母パン・焼き菓子のログハウスカフェ</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" s="6" t="inlineStr">
+        <is>
+          <t>hisui coffee</t>
+        </is>
+      </c>
+      <c r="C64" s="6" t="inlineStr">
+        <is>
+          <t>カフェ</t>
+        </is>
+      </c>
+      <c r="D64" s="6" t="inlineStr">
+        <is>
+          <t>高根沢町</t>
+        </is>
+      </c>
+      <c r="E64" s="6" t="inlineStr"/>
+      <c r="F64" s="7" t="inlineStr"/>
+      <c r="G64" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H64" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I64" s="6" t="inlineStr">
+        <is>
+          <t>地域情報サイト掲載店</t>
+        </is>
+      </c>
+      <c r="J64" s="6" t="inlineStr"/>
+      <c r="K64" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L64" s="6" t="inlineStr"/>
+      <c r="M64" s="6" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" s="6" t="inlineStr">
+        <is>
+          <t>さかさみせ</t>
+        </is>
+      </c>
+      <c r="C65" s="6" t="inlineStr">
+        <is>
+          <t>カフェ</t>
+        </is>
+      </c>
+      <c r="D65" s="6" t="inlineStr">
+        <is>
+          <t>高根沢町</t>
+        </is>
+      </c>
+      <c r="E65" s="6" t="inlineStr">
+        <is>
+          <t>石末2805-9</t>
+        </is>
+      </c>
+      <c r="F65" s="7" t="inlineStr"/>
+      <c r="G65" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H65" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I65" s="6" t="inlineStr">
+        <is>
+          <t>地域情報サイト掲載店</t>
+        </is>
+      </c>
+      <c r="J65" s="6" t="inlineStr"/>
+      <c r="K65" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L65" s="6" t="inlineStr"/>
+      <c r="M65" s="6" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="5" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" s="6" t="inlineStr">
+        <is>
+          <t>花の丘</t>
+        </is>
+      </c>
+      <c r="C66" s="6" t="inlineStr">
+        <is>
+          <t>カフェ</t>
+        </is>
+      </c>
+      <c r="D66" s="6" t="inlineStr">
+        <is>
+          <t>高根沢町</t>
+        </is>
+      </c>
+      <c r="E66" s="6" t="inlineStr">
+        <is>
+          <t>花岡1503-3</t>
+        </is>
+      </c>
+      <c r="F66" s="7" t="inlineStr"/>
+      <c r="G66" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H66" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I66" s="6" t="inlineStr">
+        <is>
+          <t>地域情報サイト掲載店</t>
+        </is>
+      </c>
+      <c r="J66" s="6" t="inlineStr"/>
+      <c r="K66" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L66" s="6" t="inlineStr"/>
+      <c r="M66" s="6" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" s="8" t="inlineStr"/>
+      <c r="C67" s="8" t="inlineStr"/>
+      <c r="D67" s="8" t="inlineStr"/>
+      <c r="E67" s="8" t="inlineStr"/>
+      <c r="F67" s="8" t="inlineStr"/>
+      <c r="G67" s="8" t="inlineStr"/>
+      <c r="H67" s="8" t="inlineStr"/>
+      <c r="I67" s="8" t="inlineStr"/>
+      <c r="J67" s="8" t="inlineStr"/>
+      <c r="K67" s="8" t="inlineStr"/>
+      <c r="L67" s="8" t="inlineStr"/>
+      <c r="M67" s="8" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="5" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" s="8" t="inlineStr"/>
+      <c r="C68" s="8" t="inlineStr"/>
+      <c r="D68" s="8" t="inlineStr"/>
+      <c r="E68" s="8" t="inlineStr"/>
+      <c r="F68" s="8" t="inlineStr"/>
+      <c r="G68" s="8" t="inlineStr"/>
+      <c r="H68" s="8" t="inlineStr"/>
+      <c r="I68" s="8" t="inlineStr"/>
+      <c r="J68" s="8" t="inlineStr"/>
+      <c r="K68" s="8" t="inlineStr"/>
+      <c r="L68" s="8" t="inlineStr"/>
+      <c r="M68" s="8" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="5" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" s="8" t="inlineStr"/>
+      <c r="C69" s="8" t="inlineStr"/>
+      <c r="D69" s="8" t="inlineStr"/>
+      <c r="E69" s="8" t="inlineStr"/>
+      <c r="F69" s="8" t="inlineStr"/>
+      <c r="G69" s="8" t="inlineStr"/>
+      <c r="H69" s="8" t="inlineStr"/>
+      <c r="I69" s="8" t="inlineStr"/>
+      <c r="J69" s="8" t="inlineStr"/>
+      <c r="K69" s="8" t="inlineStr"/>
+      <c r="L69" s="8" t="inlineStr"/>
+      <c r="M69" s="8" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="5" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" s="8" t="inlineStr"/>
+      <c r="C70" s="8" t="inlineStr"/>
+      <c r="D70" s="8" t="inlineStr"/>
+      <c r="E70" s="8" t="inlineStr"/>
+      <c r="F70" s="8" t="inlineStr"/>
+      <c r="G70" s="8" t="inlineStr"/>
+      <c r="H70" s="8" t="inlineStr"/>
+      <c r="I70" s="8" t="inlineStr"/>
+      <c r="J70" s="8" t="inlineStr"/>
+      <c r="K70" s="8" t="inlineStr"/>
+      <c r="L70" s="8" t="inlineStr"/>
+      <c r="M70" s="8" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="5" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" s="8" t="inlineStr"/>
+      <c r="C71" s="8" t="inlineStr"/>
+      <c r="D71" s="8" t="inlineStr"/>
+      <c r="E71" s="8" t="inlineStr"/>
+      <c r="F71" s="8" t="inlineStr"/>
+      <c r="G71" s="8" t="inlineStr"/>
+      <c r="H71" s="8" t="inlineStr"/>
+      <c r="I71" s="8" t="inlineStr"/>
+      <c r="J71" s="8" t="inlineStr"/>
+      <c r="K71" s="8" t="inlineStr"/>
+      <c r="L71" s="8" t="inlineStr"/>
+      <c r="M71" s="8" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="5" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" s="8" t="inlineStr"/>
+      <c r="C72" s="8" t="inlineStr"/>
+      <c r="D72" s="8" t="inlineStr"/>
+      <c r="E72" s="8" t="inlineStr"/>
+      <c r="F72" s="8" t="inlineStr"/>
+      <c r="G72" s="8" t="inlineStr"/>
+      <c r="H72" s="8" t="inlineStr"/>
+      <c r="I72" s="8" t="inlineStr"/>
+      <c r="J72" s="8" t="inlineStr"/>
+      <c r="K72" s="8" t="inlineStr"/>
+      <c r="L72" s="8" t="inlineStr"/>
+      <c r="M72" s="8" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" s="8" t="inlineStr"/>
+      <c r="C73" s="8" t="inlineStr"/>
+      <c r="D73" s="8" t="inlineStr"/>
+      <c r="E73" s="8" t="inlineStr"/>
+      <c r="F73" s="8" t="inlineStr"/>
+      <c r="G73" s="8" t="inlineStr"/>
+      <c r="H73" s="8" t="inlineStr"/>
+      <c r="I73" s="8" t="inlineStr"/>
+      <c r="J73" s="8" t="inlineStr"/>
+      <c r="K73" s="8" t="inlineStr"/>
+      <c r="L73" s="8" t="inlineStr"/>
+      <c r="M73" s="8" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="5" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" s="8" t="inlineStr"/>
+      <c r="C74" s="8" t="inlineStr"/>
+      <c r="D74" s="8" t="inlineStr"/>
+      <c r="E74" s="8" t="inlineStr"/>
+      <c r="F74" s="8" t="inlineStr"/>
+      <c r="G74" s="8" t="inlineStr"/>
+      <c r="H74" s="8" t="inlineStr"/>
+      <c r="I74" s="8" t="inlineStr"/>
+      <c r="J74" s="8" t="inlineStr"/>
+      <c r="K74" s="8" t="inlineStr"/>
+      <c r="L74" s="8" t="inlineStr"/>
+      <c r="M74" s="8" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="5" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" s="8" t="inlineStr"/>
+      <c r="C75" s="8" t="inlineStr"/>
+      <c r="D75" s="8" t="inlineStr"/>
+      <c r="E75" s="8" t="inlineStr"/>
+      <c r="F75" s="8" t="inlineStr"/>
+      <c r="G75" s="8" t="inlineStr"/>
+      <c r="H75" s="8" t="inlineStr"/>
+      <c r="I75" s="8" t="inlineStr"/>
+      <c r="J75" s="8" t="inlineStr"/>
+      <c r="K75" s="8" t="inlineStr"/>
+      <c r="L75" s="8" t="inlineStr"/>
+      <c r="M75" s="8" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="5" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" s="8" t="inlineStr"/>
+      <c r="C76" s="8" t="inlineStr"/>
+      <c r="D76" s="8" t="inlineStr"/>
+      <c r="E76" s="8" t="inlineStr"/>
+      <c r="F76" s="8" t="inlineStr"/>
+      <c r="G76" s="8" t="inlineStr"/>
+      <c r="H76" s="8" t="inlineStr"/>
+      <c r="I76" s="8" t="inlineStr"/>
+      <c r="J76" s="8" t="inlineStr"/>
+      <c r="K76" s="8" t="inlineStr"/>
+      <c r="L76" s="8" t="inlineStr"/>
+      <c r="M76" s="8" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="5" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" s="8" t="inlineStr"/>
+      <c r="C77" s="8" t="inlineStr"/>
+      <c r="D77" s="8" t="inlineStr"/>
+      <c r="E77" s="8" t="inlineStr"/>
+      <c r="F77" s="8" t="inlineStr"/>
+      <c r="G77" s="8" t="inlineStr"/>
+      <c r="H77" s="8" t="inlineStr"/>
+      <c r="I77" s="8" t="inlineStr"/>
+      <c r="J77" s="8" t="inlineStr"/>
+      <c r="K77" s="8" t="inlineStr"/>
+      <c r="L77" s="8" t="inlineStr"/>
+      <c r="M77" s="8" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="5" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" s="8" t="inlineStr"/>
+      <c r="C78" s="8" t="inlineStr"/>
+      <c r="D78" s="8" t="inlineStr"/>
+      <c r="E78" s="8" t="inlineStr"/>
+      <c r="F78" s="8" t="inlineStr"/>
+      <c r="G78" s="8" t="inlineStr"/>
+      <c r="H78" s="8" t="inlineStr"/>
+      <c r="I78" s="8" t="inlineStr"/>
+      <c r="J78" s="8" t="inlineStr"/>
+      <c r="K78" s="8" t="inlineStr"/>
+      <c r="L78" s="8" t="inlineStr"/>
+      <c r="M78" s="8" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="5" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" s="8" t="inlineStr"/>
+      <c r="C79" s="8" t="inlineStr"/>
+      <c r="D79" s="8" t="inlineStr"/>
+      <c r="E79" s="8" t="inlineStr"/>
+      <c r="F79" s="8" t="inlineStr"/>
+      <c r="G79" s="8" t="inlineStr"/>
+      <c r="H79" s="8" t="inlineStr"/>
+      <c r="I79" s="8" t="inlineStr"/>
+      <c r="J79" s="8" t="inlineStr"/>
+      <c r="K79" s="8" t="inlineStr"/>
+      <c r="L79" s="8" t="inlineStr"/>
+      <c r="M79" s="8" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="5" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" s="8" t="inlineStr"/>
+      <c r="C80" s="8" t="inlineStr"/>
+      <c r="D80" s="8" t="inlineStr"/>
+      <c r="E80" s="8" t="inlineStr"/>
+      <c r="F80" s="8" t="inlineStr"/>
+      <c r="G80" s="8" t="inlineStr"/>
+      <c r="H80" s="8" t="inlineStr"/>
+      <c r="I80" s="8" t="inlineStr"/>
+      <c r="J80" s="8" t="inlineStr"/>
+      <c r="K80" s="8" t="inlineStr"/>
+      <c r="L80" s="8" t="inlineStr"/>
+      <c r="M80" s="8" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="5" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" s="8" t="inlineStr"/>
+      <c r="C81" s="8" t="inlineStr"/>
+      <c r="D81" s="8" t="inlineStr"/>
+      <c r="E81" s="8" t="inlineStr"/>
+      <c r="F81" s="8" t="inlineStr"/>
+      <c r="G81" s="8" t="inlineStr"/>
+      <c r="H81" s="8" t="inlineStr"/>
+      <c r="I81" s="8" t="inlineStr"/>
+      <c r="J81" s="8" t="inlineStr"/>
+      <c r="K81" s="8" t="inlineStr"/>
+      <c r="L81" s="8" t="inlineStr"/>
+      <c r="M81" s="8" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="5" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" s="8" t="inlineStr"/>
+      <c r="C82" s="8" t="inlineStr"/>
+      <c r="D82" s="8" t="inlineStr"/>
+      <c r="E82" s="8" t="inlineStr"/>
+      <c r="F82" s="8" t="inlineStr"/>
+      <c r="G82" s="8" t="inlineStr"/>
+      <c r="H82" s="8" t="inlineStr"/>
+      <c r="I82" s="8" t="inlineStr"/>
+      <c r="J82" s="8" t="inlineStr"/>
+      <c r="K82" s="8" t="inlineStr"/>
+      <c r="L82" s="8" t="inlineStr"/>
+      <c r="M82" s="8" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="5" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" s="8" t="inlineStr"/>
+      <c r="C83" s="8" t="inlineStr"/>
+      <c r="D83" s="8" t="inlineStr"/>
+      <c r="E83" s="8" t="inlineStr"/>
+      <c r="F83" s="8" t="inlineStr"/>
+      <c r="G83" s="8" t="inlineStr"/>
+      <c r="H83" s="8" t="inlineStr"/>
+      <c r="I83" s="8" t="inlineStr"/>
+      <c r="J83" s="8" t="inlineStr"/>
+      <c r="K83" s="8" t="inlineStr"/>
+      <c r="L83" s="8" t="inlineStr"/>
+      <c r="M83" s="8" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="5" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" s="8" t="inlineStr"/>
+      <c r="C84" s="8" t="inlineStr"/>
+      <c r="D84" s="8" t="inlineStr"/>
+      <c r="E84" s="8" t="inlineStr"/>
+      <c r="F84" s="8" t="inlineStr"/>
+      <c r="G84" s="8" t="inlineStr"/>
+      <c r="H84" s="8" t="inlineStr"/>
+      <c r="I84" s="8" t="inlineStr"/>
+      <c r="J84" s="8" t="inlineStr"/>
+      <c r="K84" s="8" t="inlineStr"/>
+      <c r="L84" s="8" t="inlineStr"/>
+      <c r="M84" s="8" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="5" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" s="8" t="inlineStr"/>
+      <c r="C85" s="8" t="inlineStr"/>
+      <c r="D85" s="8" t="inlineStr"/>
+      <c r="E85" s="8" t="inlineStr"/>
+      <c r="F85" s="8" t="inlineStr"/>
+      <c r="G85" s="8" t="inlineStr"/>
+      <c r="H85" s="8" t="inlineStr"/>
+      <c r="I85" s="8" t="inlineStr"/>
+      <c r="J85" s="8" t="inlineStr"/>
+      <c r="K85" s="8" t="inlineStr"/>
+      <c r="L85" s="8" t="inlineStr"/>
+      <c r="M85" s="8" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="5" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" s="8" t="inlineStr"/>
+      <c r="C86" s="8" t="inlineStr"/>
+      <c r="D86" s="8" t="inlineStr"/>
+      <c r="E86" s="8" t="inlineStr"/>
+      <c r="F86" s="8" t="inlineStr"/>
+      <c r="G86" s="8" t="inlineStr"/>
+      <c r="H86" s="8" t="inlineStr"/>
+      <c r="I86" s="8" t="inlineStr"/>
+      <c r="J86" s="8" t="inlineStr"/>
+      <c r="K86" s="8" t="inlineStr"/>
+      <c r="L86" s="8" t="inlineStr"/>
+      <c r="M86" s="8" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="5" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" s="8" t="inlineStr"/>
+      <c r="C87" s="8" t="inlineStr"/>
+      <c r="D87" s="8" t="inlineStr"/>
+      <c r="E87" s="8" t="inlineStr"/>
+      <c r="F87" s="8" t="inlineStr"/>
+      <c r="G87" s="8" t="inlineStr"/>
+      <c r="H87" s="8" t="inlineStr"/>
+      <c r="I87" s="8" t="inlineStr"/>
+      <c r="J87" s="8" t="inlineStr"/>
+      <c r="K87" s="8" t="inlineStr"/>
+      <c r="L87" s="8" t="inlineStr"/>
+      <c r="M87" s="8" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="5" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" s="8" t="inlineStr"/>
+      <c r="C88" s="8" t="inlineStr"/>
+      <c r="D88" s="8" t="inlineStr"/>
+      <c r="E88" s="8" t="inlineStr"/>
+      <c r="F88" s="8" t="inlineStr"/>
+      <c r="G88" s="8" t="inlineStr"/>
+      <c r="H88" s="8" t="inlineStr"/>
+      <c r="I88" s="8" t="inlineStr"/>
+      <c r="J88" s="8" t="inlineStr"/>
+      <c r="K88" s="8" t="inlineStr"/>
+      <c r="L88" s="8" t="inlineStr"/>
+      <c r="M88" s="8" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="5" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" s="8" t="inlineStr"/>
+      <c r="C89" s="8" t="inlineStr"/>
+      <c r="D89" s="8" t="inlineStr"/>
+      <c r="E89" s="8" t="inlineStr"/>
+      <c r="F89" s="8" t="inlineStr"/>
+      <c r="G89" s="8" t="inlineStr"/>
+      <c r="H89" s="8" t="inlineStr"/>
+      <c r="I89" s="8" t="inlineStr"/>
+      <c r="J89" s="8" t="inlineStr"/>
+      <c r="K89" s="8" t="inlineStr"/>
+      <c r="L89" s="8" t="inlineStr"/>
+      <c r="M89" s="8" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="5" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" s="8" t="inlineStr"/>
+      <c r="C90" s="8" t="inlineStr"/>
+      <c r="D90" s="8" t="inlineStr"/>
+      <c r="E90" s="8" t="inlineStr"/>
+      <c r="F90" s="8" t="inlineStr"/>
+      <c r="G90" s="8" t="inlineStr"/>
+      <c r="H90" s="8" t="inlineStr"/>
+      <c r="I90" s="8" t="inlineStr"/>
+      <c r="J90" s="8" t="inlineStr"/>
+      <c r="K90" s="8" t="inlineStr"/>
+      <c r="L90" s="8" t="inlineStr"/>
+      <c r="M90" s="8" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="5" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" s="8" t="inlineStr"/>
+      <c r="C91" s="8" t="inlineStr"/>
+      <c r="D91" s="8" t="inlineStr"/>
+      <c r="E91" s="8" t="inlineStr"/>
+      <c r="F91" s="8" t="inlineStr"/>
+      <c r="G91" s="8" t="inlineStr"/>
+      <c r="H91" s="8" t="inlineStr"/>
+      <c r="I91" s="8" t="inlineStr"/>
+      <c r="J91" s="8" t="inlineStr"/>
+      <c r="K91" s="8" t="inlineStr"/>
+      <c r="L91" s="8" t="inlineStr"/>
+      <c r="M91" s="8" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="5" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" s="8" t="inlineStr"/>
+      <c r="C92" s="8" t="inlineStr"/>
+      <c r="D92" s="8" t="inlineStr"/>
+      <c r="E92" s="8" t="inlineStr"/>
+      <c r="F92" s="8" t="inlineStr"/>
+      <c r="G92" s="8" t="inlineStr"/>
+      <c r="H92" s="8" t="inlineStr"/>
+      <c r="I92" s="8" t="inlineStr"/>
+      <c r="J92" s="8" t="inlineStr"/>
+      <c r="K92" s="8" t="inlineStr"/>
+      <c r="L92" s="8" t="inlineStr"/>
+      <c r="M92" s="8" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="5" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" s="8" t="inlineStr"/>
+      <c r="C93" s="8" t="inlineStr"/>
+      <c r="D93" s="8" t="inlineStr"/>
+      <c r="E93" s="8" t="inlineStr"/>
+      <c r="F93" s="8" t="inlineStr"/>
+      <c r="G93" s="8" t="inlineStr"/>
+      <c r="H93" s="8" t="inlineStr"/>
+      <c r="I93" s="8" t="inlineStr"/>
+      <c r="J93" s="8" t="inlineStr"/>
+      <c r="K93" s="8" t="inlineStr"/>
+      <c r="L93" s="8" t="inlineStr"/>
+      <c r="M93" s="8" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="5" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" s="8" t="inlineStr"/>
+      <c r="C94" s="8" t="inlineStr"/>
+      <c r="D94" s="8" t="inlineStr"/>
+      <c r="E94" s="8" t="inlineStr"/>
+      <c r="F94" s="8" t="inlineStr"/>
+      <c r="G94" s="8" t="inlineStr"/>
+      <c r="H94" s="8" t="inlineStr"/>
+      <c r="I94" s="8" t="inlineStr"/>
+      <c r="J94" s="8" t="inlineStr"/>
+      <c r="K94" s="8" t="inlineStr"/>
+      <c r="L94" s="8" t="inlineStr"/>
+      <c r="M94" s="8" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="5" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" s="8" t="inlineStr"/>
+      <c r="C95" s="8" t="inlineStr"/>
+      <c r="D95" s="8" t="inlineStr"/>
+      <c r="E95" s="8" t="inlineStr"/>
+      <c r="F95" s="8" t="inlineStr"/>
+      <c r="G95" s="8" t="inlineStr"/>
+      <c r="H95" s="8" t="inlineStr"/>
+      <c r="I95" s="8" t="inlineStr"/>
+      <c r="J95" s="8" t="inlineStr"/>
+      <c r="K95" s="8" t="inlineStr"/>
+      <c r="L95" s="8" t="inlineStr"/>
+      <c r="M95" s="8" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="5" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" s="8" t="inlineStr"/>
+      <c r="C96" s="8" t="inlineStr"/>
+      <c r="D96" s="8" t="inlineStr"/>
+      <c r="E96" s="8" t="inlineStr"/>
+      <c r="F96" s="8" t="inlineStr"/>
+      <c r="G96" s="8" t="inlineStr"/>
+      <c r="H96" s="8" t="inlineStr"/>
+      <c r="I96" s="8" t="inlineStr"/>
+      <c r="J96" s="8" t="inlineStr"/>
+      <c r="K96" s="8" t="inlineStr"/>
+      <c r="L96" s="8" t="inlineStr"/>
+      <c r="M96" s="8" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="5" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" s="8" t="inlineStr"/>
+      <c r="C97" s="8" t="inlineStr"/>
+      <c r="D97" s="8" t="inlineStr"/>
+      <c r="E97" s="8" t="inlineStr"/>
+      <c r="F97" s="8" t="inlineStr"/>
+      <c r="G97" s="8" t="inlineStr"/>
+      <c r="H97" s="8" t="inlineStr"/>
+      <c r="I97" s="8" t="inlineStr"/>
+      <c r="J97" s="8" t="inlineStr"/>
+      <c r="K97" s="8" t="inlineStr"/>
+      <c r="L97" s="8" t="inlineStr"/>
+      <c r="M97" s="8" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="5" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" s="8" t="inlineStr"/>
+      <c r="C98" s="8" t="inlineStr"/>
+      <c r="D98" s="8" t="inlineStr"/>
+      <c r="E98" s="8" t="inlineStr"/>
+      <c r="F98" s="8" t="inlineStr"/>
+      <c r="G98" s="8" t="inlineStr"/>
+      <c r="H98" s="8" t="inlineStr"/>
+      <c r="I98" s="8" t="inlineStr"/>
+      <c r="J98" s="8" t="inlineStr"/>
+      <c r="K98" s="8" t="inlineStr"/>
+      <c r="L98" s="8" t="inlineStr"/>
+      <c r="M98" s="8" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="5" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" s="8" t="inlineStr"/>
+      <c r="C99" s="8" t="inlineStr"/>
+      <c r="D99" s="8" t="inlineStr"/>
+      <c r="E99" s="8" t="inlineStr"/>
+      <c r="F99" s="8" t="inlineStr"/>
+      <c r="G99" s="8" t="inlineStr"/>
+      <c r="H99" s="8" t="inlineStr"/>
+      <c r="I99" s="8" t="inlineStr"/>
+      <c r="J99" s="8" t="inlineStr"/>
+      <c r="K99" s="8" t="inlineStr"/>
+      <c r="L99" s="8" t="inlineStr"/>
+      <c r="M99" s="8" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="5" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" s="8" t="inlineStr"/>
+      <c r="C100" s="8" t="inlineStr"/>
+      <c r="D100" s="8" t="inlineStr"/>
+      <c r="E100" s="8" t="inlineStr"/>
+      <c r="F100" s="8" t="inlineStr"/>
+      <c r="G100" s="8" t="inlineStr"/>
+      <c r="H100" s="8" t="inlineStr"/>
+      <c r="I100" s="8" t="inlineStr"/>
+      <c r="J100" s="8" t="inlineStr"/>
+      <c r="K100" s="8" t="inlineStr"/>
+      <c r="L100" s="8" t="inlineStr"/>
+      <c r="M100" s="8" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" s="8" t="inlineStr"/>
+      <c r="C101" s="8" t="inlineStr"/>
+      <c r="D101" s="8" t="inlineStr"/>
+      <c r="E101" s="8" t="inlineStr"/>
+      <c r="F101" s="8" t="inlineStr"/>
+      <c r="G101" s="8" t="inlineStr"/>
+      <c r="H101" s="8" t="inlineStr"/>
+      <c r="I101" s="8" t="inlineStr"/>
+      <c r="J101" s="8" t="inlineStr"/>
+      <c r="K101" s="8" t="inlineStr"/>
+      <c r="L101" s="8" t="inlineStr"/>
+      <c r="M101" s="8" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="5" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" s="8" t="inlineStr"/>
+      <c r="C102" s="8" t="inlineStr"/>
+      <c r="D102" s="8" t="inlineStr"/>
+      <c r="E102" s="8" t="inlineStr"/>
+      <c r="F102" s="8" t="inlineStr"/>
+      <c r="G102" s="8" t="inlineStr"/>
+      <c r="H102" s="8" t="inlineStr"/>
+      <c r="I102" s="8" t="inlineStr"/>
+      <c r="J102" s="8" t="inlineStr"/>
+      <c r="K102" s="8" t="inlineStr"/>
+      <c r="L102" s="8" t="inlineStr"/>
+      <c r="M102" s="8" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="5" t="n">
+        <v>102</v>
+      </c>
+      <c r="B103" s="8" t="inlineStr"/>
+      <c r="C103" s="8" t="inlineStr"/>
+      <c r="D103" s="8" t="inlineStr"/>
+      <c r="E103" s="8" t="inlineStr"/>
+      <c r="F103" s="8" t="inlineStr"/>
+      <c r="G103" s="8" t="inlineStr"/>
+      <c r="H103" s="8" t="inlineStr"/>
+      <c r="I103" s="8" t="inlineStr"/>
+      <c r="J103" s="8" t="inlineStr"/>
+      <c r="K103" s="8" t="inlineStr"/>
+      <c r="L103" s="8" t="inlineStr"/>
+      <c r="M103" s="8" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="5" t="n">
+        <v>103</v>
+      </c>
+      <c r="B104" s="8" t="inlineStr"/>
+      <c r="C104" s="8" t="inlineStr"/>
+      <c r="D104" s="8" t="inlineStr"/>
+      <c r="E104" s="8" t="inlineStr"/>
+      <c r="F104" s="8" t="inlineStr"/>
+      <c r="G104" s="8" t="inlineStr"/>
+      <c r="H104" s="8" t="inlineStr"/>
+      <c r="I104" s="8" t="inlineStr"/>
+      <c r="J104" s="8" t="inlineStr"/>
+      <c r="K104" s="8" t="inlineStr"/>
+      <c r="L104" s="8" t="inlineStr"/>
+      <c r="M104" s="8" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="5" t="n">
+        <v>104</v>
+      </c>
+      <c r="B105" s="8" t="inlineStr"/>
+      <c r="C105" s="8" t="inlineStr"/>
+      <c r="D105" s="8" t="inlineStr"/>
+      <c r="E105" s="8" t="inlineStr"/>
+      <c r="F105" s="8" t="inlineStr"/>
+      <c r="G105" s="8" t="inlineStr"/>
+      <c r="H105" s="8" t="inlineStr"/>
+      <c r="I105" s="8" t="inlineStr"/>
+      <c r="J105" s="8" t="inlineStr"/>
+      <c r="K105" s="8" t="inlineStr"/>
+      <c r="L105" s="8" t="inlineStr"/>
+      <c r="M105" s="8" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="5" t="n">
+        <v>105</v>
+      </c>
+      <c r="B106" s="8" t="inlineStr"/>
+      <c r="C106" s="8" t="inlineStr"/>
+      <c r="D106" s="8" t="inlineStr"/>
+      <c r="E106" s="8" t="inlineStr"/>
+      <c r="F106" s="8" t="inlineStr"/>
+      <c r="G106" s="8" t="inlineStr"/>
+      <c r="H106" s="8" t="inlineStr"/>
+      <c r="I106" s="8" t="inlineStr"/>
+      <c r="J106" s="8" t="inlineStr"/>
+      <c r="K106" s="8" t="inlineStr"/>
+      <c r="L106" s="8" t="inlineStr"/>
+      <c r="M106" s="8" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="4">
-    <dataValidation sqref="C2:C48" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C2:C106" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"カフェ,飲食店,和菓子店,雑貨店,陶器店・ギャラリー,土産店,美容室,理容室,その他"</formula1>
     </dataValidation>
-    <dataValidation sqref="D2:D48" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"栃木市,益子町,那須町,日光市,その他"</formula1>
+    <dataValidation sqref="D2:D106" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"栃木市,益子町,那須町,日光市,宇都宮市,足利市,佐野市,小山市,鹿沼市,那須塩原市,真岡市,大田原市,壬生町,那珂川町,那須烏山市,矢板市,茂木町,下野市,野木町,高根沢町,その他"</formula1>
     </dataValidation>
-    <dataValidation sqref="K2:K48" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K2:K106" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"未架電,不在,拒否,資料送付OK,アポ確定,見送り"</formula1>
     </dataValidation>
-    <dataValidation sqref="H2:H48" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H2:H106" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"不明,あり（古い）,あり（最近）,なし"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2182,7 +4737,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:D14"/>
+  <dimension ref="B2:D30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="2" max="2"/>
@@ -2203,7 +4758,7 @@
         </is>
       </c>
       <c r="D4" s="2">
-        <f>COUNTIF(架電リスト!B2:B48,"?*")</f>
+        <f>COUNTIF(架電リスト!B2:B106,"?*")</f>
         <v/>
       </c>
     </row>
@@ -2214,7 +4769,7 @@
         </is>
       </c>
       <c r="D5" s="2">
-        <f>COUNTIFS(架電リスト!K2:K48,"&lt;&gt;未架電",架電リスト!K2:K48,"&lt;&gt;")</f>
+        <f>COUNTIFS(架電リスト!K2:K106,"&lt;&gt;未架電",架電リスト!K2:K106,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -2225,7 +4780,7 @@
         </is>
       </c>
       <c r="D6" s="2">
-        <f>COUNTIF(架電リスト!K2:K48,"資料送付OK")</f>
+        <f>COUNTIF(架電リスト!K2:K106,"資料送付OK")</f>
         <v/>
       </c>
     </row>
@@ -2236,7 +4791,7 @@
         </is>
       </c>
       <c r="D7" s="2">
-        <f>COUNTIF(架電リスト!K2:K48,"アポ確定")</f>
+        <f>COUNTIF(架電リスト!K2:K106,"アポ確定")</f>
         <v/>
       </c>
     </row>
@@ -2264,8 +4819,8 @@
           <t>栃木市</t>
         </is>
       </c>
-      <c r="D11" s="2">
-        <f>COUNTIF(架電リスト!D2:D48,"栃木市")</f>
+      <c r="D11" s="10">
+        <f>COUNTIF(架電リスト!D2:D106,"栃木市")</f>
         <v/>
       </c>
     </row>
@@ -2275,8 +4830,8 @@
           <t>益子町</t>
         </is>
       </c>
-      <c r="D12" s="2">
-        <f>COUNTIF(架電リスト!D2:D48,"益子町")</f>
+      <c r="D12" s="10">
+        <f>COUNTIF(架電リスト!D2:D106,"益子町")</f>
         <v/>
       </c>
     </row>
@@ -2286,8 +4841,8 @@
           <t>那須町</t>
         </is>
       </c>
-      <c r="D13" s="2">
-        <f>COUNTIF(架電リスト!D2:D48,"那須町")</f>
+      <c r="D13" s="10">
+        <f>COUNTIF(架電リスト!D2:D106,"那須町")</f>
         <v/>
       </c>
     </row>
@@ -2297,8 +4852,184 @@
           <t>日光市</t>
         </is>
       </c>
-      <c r="D14" s="2">
-        <f>COUNTIF(架電リスト!D2:D48,"日光市")</f>
+      <c r="D14" s="10">
+        <f>COUNTIF(架電リスト!D2:D106,"日光市")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>宇都宮市</t>
+        </is>
+      </c>
+      <c r="D15" s="10">
+        <f>COUNTIF(架電リスト!D2:D106,"宇都宮市")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>足利市</t>
+        </is>
+      </c>
+      <c r="D16" s="10">
+        <f>COUNTIF(架電リスト!D2:D106,"足利市")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>佐野市</t>
+        </is>
+      </c>
+      <c r="D17" s="10">
+        <f>COUNTIF(架電リスト!D2:D106,"佐野市")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>小山市</t>
+        </is>
+      </c>
+      <c r="D18" s="10">
+        <f>COUNTIF(架電リスト!D2:D106,"小山市")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>鹿沼市</t>
+        </is>
+      </c>
+      <c r="D19" s="10">
+        <f>COUNTIF(架電リスト!D2:D106,"鹿沼市")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>那須塩原市</t>
+        </is>
+      </c>
+      <c r="D20" s="10">
+        <f>COUNTIF(架電リスト!D2:D106,"那須塩原市")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>真岡市</t>
+        </is>
+      </c>
+      <c r="D21" s="10">
+        <f>COUNTIF(架電リスト!D2:D106,"真岡市")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>大田原市</t>
+        </is>
+      </c>
+      <c r="D22" s="10">
+        <f>COUNTIF(架電リスト!D2:D106,"大田原市")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>壬生町</t>
+        </is>
+      </c>
+      <c r="D23" s="10">
+        <f>COUNTIF(架電リスト!D2:D106,"壬生町")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>那珂川町</t>
+        </is>
+      </c>
+      <c r="D24" s="10">
+        <f>COUNTIF(架電リスト!D2:D106,"那珂川町")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>那須烏山市</t>
+        </is>
+      </c>
+      <c r="D25" s="10">
+        <f>COUNTIF(架電リスト!D2:D106,"那須烏山市")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>矢板市</t>
+        </is>
+      </c>
+      <c r="D26" s="10">
+        <f>COUNTIF(架電リスト!D2:D106,"矢板市")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>茂木町</t>
+        </is>
+      </c>
+      <c r="D27" s="10">
+        <f>COUNTIF(架電リスト!D2:D106,"茂木町")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>下野市</t>
+        </is>
+      </c>
+      <c r="D28" s="10">
+        <f>COUNTIF(架電リスト!D2:D106,"下野市")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>野木町</t>
+        </is>
+      </c>
+      <c r="D29" s="10">
+        <f>COUNTIF(架電リスト!D2:D106,"野木町")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>高根沢町</t>
+        </is>
+      </c>
+      <c r="D30" s="10">
+        <f>COUNTIF(架電リスト!D2:D106,"高根沢町")</f>
         <v/>
       </c>
     </row>

--- a/projects/tel-appo/call-list.xlsx
+++ b/projects/tel-appo/call-list.xlsx
@@ -626,7 +626,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M106"/>
+  <dimension ref="A1:M108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -4036,35 +4036,103 @@
       <c r="A67" s="5" t="n">
         <v>66</v>
       </c>
-      <c r="B67" s="8" t="inlineStr"/>
-      <c r="C67" s="8" t="inlineStr"/>
-      <c r="D67" s="8" t="inlineStr"/>
-      <c r="E67" s="8" t="inlineStr"/>
-      <c r="F67" s="8" t="inlineStr"/>
-      <c r="G67" s="8" t="inlineStr"/>
-      <c r="H67" s="8" t="inlineStr"/>
-      <c r="I67" s="8" t="inlineStr"/>
-      <c r="J67" s="8" t="inlineStr"/>
-      <c r="K67" s="8" t="inlineStr"/>
-      <c r="L67" s="8" t="inlineStr"/>
-      <c r="M67" s="8" t="inlineStr"/>
+      <c r="B67" s="6" t="inlineStr">
+        <is>
+          <t>cafe mikumari</t>
+        </is>
+      </c>
+      <c r="C67" s="6" t="inlineStr">
+        <is>
+          <t>カフェ</t>
+        </is>
+      </c>
+      <c r="D67" s="6" t="inlineStr">
+        <is>
+          <t>芳賀町</t>
+        </is>
+      </c>
+      <c r="E67" s="6" t="inlineStr">
+        <is>
+          <t>東水沼1032-12</t>
+        </is>
+      </c>
+      <c r="F67" s="7" t="inlineStr"/>
+      <c r="G67" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H67" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I67" s="6" t="inlineStr">
+        <is>
+          <t>地域情報サイト掲載店</t>
+        </is>
+      </c>
+      <c r="J67" s="6" t="inlineStr"/>
+      <c r="K67" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L67" s="6" t="inlineStr"/>
+      <c r="M67" s="6" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="5" t="n">
         <v>67</v>
       </c>
-      <c r="B68" s="8" t="inlineStr"/>
-      <c r="C68" s="8" t="inlineStr"/>
-      <c r="D68" s="8" t="inlineStr"/>
-      <c r="E68" s="8" t="inlineStr"/>
-      <c r="F68" s="8" t="inlineStr"/>
-      <c r="G68" s="8" t="inlineStr"/>
-      <c r="H68" s="8" t="inlineStr"/>
-      <c r="I68" s="8" t="inlineStr"/>
-      <c r="J68" s="8" t="inlineStr"/>
-      <c r="K68" s="8" t="inlineStr"/>
-      <c r="L68" s="8" t="inlineStr"/>
-      <c r="M68" s="8" t="inlineStr"/>
+      <c r="B68" s="6" t="inlineStr">
+        <is>
+          <t>まがりな</t>
+        </is>
+      </c>
+      <c r="C68" s="6" t="inlineStr">
+        <is>
+          <t>カフェ</t>
+        </is>
+      </c>
+      <c r="D68" s="6" t="inlineStr">
+        <is>
+          <t>塩谷町</t>
+        </is>
+      </c>
+      <c r="E68" s="6" t="inlineStr">
+        <is>
+          <t>道の駅湧水の郷しおや 飲食館内</t>
+        </is>
+      </c>
+      <c r="F68" s="7" t="inlineStr"/>
+      <c r="G68" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H68" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I68" s="6" t="inlineStr">
+        <is>
+          <t>地域情報サイト掲載店</t>
+        </is>
+      </c>
+      <c r="J68" s="6" t="inlineStr"/>
+      <c r="K68" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L68" s="6" t="inlineStr"/>
+      <c r="M68" s="6" t="inlineStr">
+        <is>
+          <t>農村カフェ、オリジナルメニュー</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="5" t="n">
@@ -4712,18 +4780,52 @@
       <c r="L106" s="8" t="inlineStr"/>
       <c r="M106" s="8" t="inlineStr"/>
     </row>
+    <row r="107">
+      <c r="A107" s="5" t="n">
+        <v>106</v>
+      </c>
+      <c r="B107" s="8" t="inlineStr"/>
+      <c r="C107" s="8" t="inlineStr"/>
+      <c r="D107" s="8" t="inlineStr"/>
+      <c r="E107" s="8" t="inlineStr"/>
+      <c r="F107" s="8" t="inlineStr"/>
+      <c r="G107" s="8" t="inlineStr"/>
+      <c r="H107" s="8" t="inlineStr"/>
+      <c r="I107" s="8" t="inlineStr"/>
+      <c r="J107" s="8" t="inlineStr"/>
+      <c r="K107" s="8" t="inlineStr"/>
+      <c r="L107" s="8" t="inlineStr"/>
+      <c r="M107" s="8" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="5" t="n">
+        <v>107</v>
+      </c>
+      <c r="B108" s="8" t="inlineStr"/>
+      <c r="C108" s="8" t="inlineStr"/>
+      <c r="D108" s="8" t="inlineStr"/>
+      <c r="E108" s="8" t="inlineStr"/>
+      <c r="F108" s="8" t="inlineStr"/>
+      <c r="G108" s="8" t="inlineStr"/>
+      <c r="H108" s="8" t="inlineStr"/>
+      <c r="I108" s="8" t="inlineStr"/>
+      <c r="J108" s="8" t="inlineStr"/>
+      <c r="K108" s="8" t="inlineStr"/>
+      <c r="L108" s="8" t="inlineStr"/>
+      <c r="M108" s="8" t="inlineStr"/>
+    </row>
   </sheetData>
   <dataValidations count="4">
-    <dataValidation sqref="C2:C106" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C2:C108" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"カフェ,飲食店,和菓子店,雑貨店,陶器店・ギャラリー,土産店,美容室,理容室,その他"</formula1>
     </dataValidation>
-    <dataValidation sqref="D2:D106" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"栃木市,益子町,那須町,日光市,宇都宮市,足利市,佐野市,小山市,鹿沼市,那須塩原市,真岡市,大田原市,壬生町,那珂川町,那須烏山市,矢板市,茂木町,下野市,野木町,高根沢町,その他"</formula1>
+    <dataValidation sqref="D2:D108" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"栃木市,益子町,那須町,日光市,宇都宮市,足利市,佐野市,小山市,鹿沼市,那須塩原市,真岡市,大田原市,壬生町,那珂川町,那須烏山市,矢板市,茂木町,下野市,野木町,高根沢町,芳賀町,塩谷町,その他"</formula1>
     </dataValidation>
-    <dataValidation sqref="K2:K106" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K2:K108" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"未架電,不在,拒否,資料送付OK,アポ確定,見送り"</formula1>
     </dataValidation>
-    <dataValidation sqref="H2:H106" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H2:H108" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"不明,あり（古い）,あり（最近）,なし"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4737,7 +4839,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:D30"/>
+  <dimension ref="B2:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="2" max="2"/>
@@ -4758,7 +4860,7 @@
         </is>
       </c>
       <c r="D4" s="2">
-        <f>COUNTIF(架電リスト!B2:B106,"?*")</f>
+        <f>COUNTIF(架電リスト!B2:B108,"?*")</f>
         <v/>
       </c>
     </row>
@@ -4769,7 +4871,7 @@
         </is>
       </c>
       <c r="D5" s="2">
-        <f>COUNTIFS(架電リスト!K2:K106,"&lt;&gt;未架電",架電リスト!K2:K106,"&lt;&gt;")</f>
+        <f>COUNTIFS(架電リスト!K2:K108,"&lt;&gt;未架電",架電リスト!K2:K108,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -4780,7 +4882,7 @@
         </is>
       </c>
       <c r="D6" s="2">
-        <f>COUNTIF(架電リスト!K2:K106,"資料送付OK")</f>
+        <f>COUNTIF(架電リスト!K2:K108,"資料送付OK")</f>
         <v/>
       </c>
     </row>
@@ -4791,7 +4893,7 @@
         </is>
       </c>
       <c r="D7" s="2">
-        <f>COUNTIF(架電リスト!K2:K106,"アポ確定")</f>
+        <f>COUNTIF(架電リスト!K2:K108,"アポ確定")</f>
         <v/>
       </c>
     </row>
@@ -4820,7 +4922,7 @@
         </is>
       </c>
       <c r="D11" s="10">
-        <f>COUNTIF(架電リスト!D2:D106,"栃木市")</f>
+        <f>COUNTIF(架電リスト!D2:D108,"栃木市")</f>
         <v/>
       </c>
     </row>
@@ -4831,7 +4933,7 @@
         </is>
       </c>
       <c r="D12" s="10">
-        <f>COUNTIF(架電リスト!D2:D106,"益子町")</f>
+        <f>COUNTIF(架電リスト!D2:D108,"益子町")</f>
         <v/>
       </c>
     </row>
@@ -4842,7 +4944,7 @@
         </is>
       </c>
       <c r="D13" s="10">
-        <f>COUNTIF(架電リスト!D2:D106,"那須町")</f>
+        <f>COUNTIF(架電リスト!D2:D108,"那須町")</f>
         <v/>
       </c>
     </row>
@@ -4853,7 +4955,7 @@
         </is>
       </c>
       <c r="D14" s="10">
-        <f>COUNTIF(架電リスト!D2:D106,"日光市")</f>
+        <f>COUNTIF(架電リスト!D2:D108,"日光市")</f>
         <v/>
       </c>
     </row>
@@ -4864,7 +4966,7 @@
         </is>
       </c>
       <c r="D15" s="10">
-        <f>COUNTIF(架電リスト!D2:D106,"宇都宮市")</f>
+        <f>COUNTIF(架電リスト!D2:D108,"宇都宮市")</f>
         <v/>
       </c>
     </row>
@@ -4875,7 +4977,7 @@
         </is>
       </c>
       <c r="D16" s="10">
-        <f>COUNTIF(架電リスト!D2:D106,"足利市")</f>
+        <f>COUNTIF(架電リスト!D2:D108,"足利市")</f>
         <v/>
       </c>
     </row>
@@ -4886,7 +4988,7 @@
         </is>
       </c>
       <c r="D17" s="10">
-        <f>COUNTIF(架電リスト!D2:D106,"佐野市")</f>
+        <f>COUNTIF(架電リスト!D2:D108,"佐野市")</f>
         <v/>
       </c>
     </row>
@@ -4897,7 +4999,7 @@
         </is>
       </c>
       <c r="D18" s="10">
-        <f>COUNTIF(架電リスト!D2:D106,"小山市")</f>
+        <f>COUNTIF(架電リスト!D2:D108,"小山市")</f>
         <v/>
       </c>
     </row>
@@ -4908,7 +5010,7 @@
         </is>
       </c>
       <c r="D19" s="10">
-        <f>COUNTIF(架電リスト!D2:D106,"鹿沼市")</f>
+        <f>COUNTIF(架電リスト!D2:D108,"鹿沼市")</f>
         <v/>
       </c>
     </row>
@@ -4919,7 +5021,7 @@
         </is>
       </c>
       <c r="D20" s="10">
-        <f>COUNTIF(架電リスト!D2:D106,"那須塩原市")</f>
+        <f>COUNTIF(架電リスト!D2:D108,"那須塩原市")</f>
         <v/>
       </c>
     </row>
@@ -4930,7 +5032,7 @@
         </is>
       </c>
       <c r="D21" s="10">
-        <f>COUNTIF(架電リスト!D2:D106,"真岡市")</f>
+        <f>COUNTIF(架電リスト!D2:D108,"真岡市")</f>
         <v/>
       </c>
     </row>
@@ -4941,7 +5043,7 @@
         </is>
       </c>
       <c r="D22" s="10">
-        <f>COUNTIF(架電リスト!D2:D106,"大田原市")</f>
+        <f>COUNTIF(架電リスト!D2:D108,"大田原市")</f>
         <v/>
       </c>
     </row>
@@ -4952,7 +5054,7 @@
         </is>
       </c>
       <c r="D23" s="10">
-        <f>COUNTIF(架電リスト!D2:D106,"壬生町")</f>
+        <f>COUNTIF(架電リスト!D2:D108,"壬生町")</f>
         <v/>
       </c>
     </row>
@@ -4963,7 +5065,7 @@
         </is>
       </c>
       <c r="D24" s="10">
-        <f>COUNTIF(架電リスト!D2:D106,"那珂川町")</f>
+        <f>COUNTIF(架電リスト!D2:D108,"那珂川町")</f>
         <v/>
       </c>
     </row>
@@ -4974,7 +5076,7 @@
         </is>
       </c>
       <c r="D25" s="10">
-        <f>COUNTIF(架電リスト!D2:D106,"那須烏山市")</f>
+        <f>COUNTIF(架電リスト!D2:D108,"那須烏山市")</f>
         <v/>
       </c>
     </row>
@@ -4985,7 +5087,7 @@
         </is>
       </c>
       <c r="D26" s="10">
-        <f>COUNTIF(架電リスト!D2:D106,"矢板市")</f>
+        <f>COUNTIF(架電リスト!D2:D108,"矢板市")</f>
         <v/>
       </c>
     </row>
@@ -4996,7 +5098,7 @@
         </is>
       </c>
       <c r="D27" s="10">
-        <f>COUNTIF(架電リスト!D2:D106,"茂木町")</f>
+        <f>COUNTIF(架電リスト!D2:D108,"茂木町")</f>
         <v/>
       </c>
     </row>
@@ -5007,7 +5109,7 @@
         </is>
       </c>
       <c r="D28" s="10">
-        <f>COUNTIF(架電リスト!D2:D106,"下野市")</f>
+        <f>COUNTIF(架電リスト!D2:D108,"下野市")</f>
         <v/>
       </c>
     </row>
@@ -5018,7 +5120,7 @@
         </is>
       </c>
       <c r="D29" s="10">
-        <f>COUNTIF(架電リスト!D2:D106,"野木町")</f>
+        <f>COUNTIF(架電リスト!D2:D108,"野木町")</f>
         <v/>
       </c>
     </row>
@@ -5029,7 +5131,29 @@
         </is>
       </c>
       <c r="D30" s="10">
-        <f>COUNTIF(架電リスト!D2:D106,"高根沢町")</f>
+        <f>COUNTIF(架電リスト!D2:D108,"高根沢町")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>芳賀町</t>
+        </is>
+      </c>
+      <c r="D31" s="10">
+        <f>COUNTIF(架電リスト!D2:D108,"芳賀町")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>塩谷町</t>
+        </is>
+      </c>
+      <c r="D32" s="10">
+        <f>COUNTIF(架電リスト!D2:D108,"塩谷町")</f>
         <v/>
       </c>
     </row>

--- a/projects/tel-appo/call-list.xlsx
+++ b/projects/tel-appo/call-list.xlsx
@@ -626,7 +626,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M108"/>
+  <dimension ref="A1:M146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -4138,647 +4138,1851 @@
       <c r="A69" s="5" t="n">
         <v>68</v>
       </c>
-      <c r="B69" s="8" t="inlineStr"/>
-      <c r="C69" s="8" t="inlineStr"/>
-      <c r="D69" s="8" t="inlineStr"/>
-      <c r="E69" s="8" t="inlineStr"/>
-      <c r="F69" s="8" t="inlineStr"/>
-      <c r="G69" s="8" t="inlineStr"/>
-      <c r="H69" s="8" t="inlineStr"/>
-      <c r="I69" s="8" t="inlineStr"/>
-      <c r="J69" s="8" t="inlineStr"/>
-      <c r="K69" s="8" t="inlineStr"/>
-      <c r="L69" s="8" t="inlineStr"/>
-      <c r="M69" s="8" t="inlineStr"/>
+      <c r="B69" s="6" t="inlineStr">
+        <is>
+          <t>福田屋</t>
+        </is>
+      </c>
+      <c r="C69" s="6" t="inlineStr">
+        <is>
+          <t>陶器店・ギャラリー</t>
+        </is>
+      </c>
+      <c r="D69" s="6" t="inlineStr">
+        <is>
+          <t>益子町</t>
+        </is>
+      </c>
+      <c r="E69" s="6" t="inlineStr">
+        <is>
+          <t>城内坂エリア</t>
+        </is>
+      </c>
+      <c r="F69" s="7" t="inlineStr"/>
+      <c r="G69" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H69" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I69" s="6" t="inlineStr">
+        <is>
+          <t>観光メディア掲載店</t>
+        </is>
+      </c>
+      <c r="J69" s="6" t="inlineStr"/>
+      <c r="K69" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L69" s="6" t="inlineStr"/>
+      <c r="M69" s="6" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="5" t="n">
         <v>69</v>
       </c>
-      <c r="B70" s="8" t="inlineStr"/>
-      <c r="C70" s="8" t="inlineStr"/>
-      <c r="D70" s="8" t="inlineStr"/>
-      <c r="E70" s="8" t="inlineStr"/>
-      <c r="F70" s="8" t="inlineStr"/>
-      <c r="G70" s="8" t="inlineStr"/>
-      <c r="H70" s="8" t="inlineStr"/>
-      <c r="I70" s="8" t="inlineStr"/>
-      <c r="J70" s="8" t="inlineStr"/>
-      <c r="K70" s="8" t="inlineStr"/>
-      <c r="L70" s="8" t="inlineStr"/>
-      <c r="M70" s="8" t="inlineStr"/>
+      <c r="B70" s="6" t="inlineStr">
+        <is>
+          <t>陶知庵（蒼い器の店）</t>
+        </is>
+      </c>
+      <c r="C70" s="6" t="inlineStr">
+        <is>
+          <t>陶器店・ギャラリー</t>
+        </is>
+      </c>
+      <c r="D70" s="6" t="inlineStr">
+        <is>
+          <t>益子町</t>
+        </is>
+      </c>
+      <c r="E70" s="6" t="inlineStr">
+        <is>
+          <t>城内坂エリア</t>
+        </is>
+      </c>
+      <c r="F70" s="7" t="inlineStr"/>
+      <c r="G70" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H70" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I70" s="6" t="inlineStr">
+        <is>
+          <t>観光メディア掲載店</t>
+        </is>
+      </c>
+      <c r="J70" s="6" t="inlineStr"/>
+      <c r="K70" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L70" s="6" t="inlineStr"/>
+      <c r="M70" s="6" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="5" t="n">
         <v>70</v>
       </c>
-      <c r="B71" s="8" t="inlineStr"/>
-      <c r="C71" s="8" t="inlineStr"/>
-      <c r="D71" s="8" t="inlineStr"/>
-      <c r="E71" s="8" t="inlineStr"/>
-      <c r="F71" s="8" t="inlineStr"/>
-      <c r="G71" s="8" t="inlineStr"/>
-      <c r="H71" s="8" t="inlineStr"/>
-      <c r="I71" s="8" t="inlineStr"/>
-      <c r="J71" s="8" t="inlineStr"/>
-      <c r="K71" s="8" t="inlineStr"/>
-      <c r="L71" s="8" t="inlineStr"/>
-      <c r="M71" s="8" t="inlineStr"/>
+      <c r="B71" s="6" t="inlineStr">
+        <is>
+          <t>見目陶苑</t>
+        </is>
+      </c>
+      <c r="C71" s="6" t="inlineStr">
+        <is>
+          <t>陶器店・ギャラリー</t>
+        </is>
+      </c>
+      <c r="D71" s="6" t="inlineStr">
+        <is>
+          <t>益子町</t>
+        </is>
+      </c>
+      <c r="E71" s="6" t="inlineStr"/>
+      <c r="F71" s="7" t="inlineStr"/>
+      <c r="G71" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H71" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I71" s="6" t="inlineStr">
+        <is>
+          <t>観光メディア掲載店</t>
+        </is>
+      </c>
+      <c r="J71" s="6" t="inlineStr"/>
+      <c r="K71" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L71" s="6" t="inlineStr"/>
+      <c r="M71" s="6" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="5" t="n">
         <v>71</v>
       </c>
-      <c r="B72" s="8" t="inlineStr"/>
-      <c r="C72" s="8" t="inlineStr"/>
-      <c r="D72" s="8" t="inlineStr"/>
-      <c r="E72" s="8" t="inlineStr"/>
-      <c r="F72" s="8" t="inlineStr"/>
-      <c r="G72" s="8" t="inlineStr"/>
-      <c r="H72" s="8" t="inlineStr"/>
-      <c r="I72" s="8" t="inlineStr"/>
-      <c r="J72" s="8" t="inlineStr"/>
-      <c r="K72" s="8" t="inlineStr"/>
-      <c r="L72" s="8" t="inlineStr"/>
-      <c r="M72" s="8" t="inlineStr"/>
+      <c r="B72" s="6" t="inlineStr">
+        <is>
+          <t>象嵌てん</t>
+        </is>
+      </c>
+      <c r="C72" s="6" t="inlineStr">
+        <is>
+          <t>陶器店・ギャラリー</t>
+        </is>
+      </c>
+      <c r="D72" s="6" t="inlineStr">
+        <is>
+          <t>益子町</t>
+        </is>
+      </c>
+      <c r="E72" s="6" t="inlineStr"/>
+      <c r="F72" s="7" t="inlineStr"/>
+      <c r="G72" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H72" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I72" s="6" t="inlineStr">
+        <is>
+          <t>観光メディア掲載店</t>
+        </is>
+      </c>
+      <c r="J72" s="6" t="inlineStr"/>
+      <c r="K72" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L72" s="6" t="inlineStr"/>
+      <c r="M72" s="6" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="5" t="n">
         <v>72</v>
       </c>
-      <c r="B73" s="8" t="inlineStr"/>
-      <c r="C73" s="8" t="inlineStr"/>
-      <c r="D73" s="8" t="inlineStr"/>
-      <c r="E73" s="8" t="inlineStr"/>
-      <c r="F73" s="8" t="inlineStr"/>
-      <c r="G73" s="8" t="inlineStr"/>
-      <c r="H73" s="8" t="inlineStr"/>
-      <c r="I73" s="8" t="inlineStr"/>
-      <c r="J73" s="8" t="inlineStr"/>
-      <c r="K73" s="8" t="inlineStr"/>
-      <c r="L73" s="8" t="inlineStr"/>
-      <c r="M73" s="8" t="inlineStr"/>
+      <c r="B73" s="6" t="inlineStr">
+        <is>
+          <t>趣味の器 陶楽</t>
+        </is>
+      </c>
+      <c r="C73" s="6" t="inlineStr">
+        <is>
+          <t>陶器店・ギャラリー</t>
+        </is>
+      </c>
+      <c r="D73" s="6" t="inlineStr">
+        <is>
+          <t>益子町</t>
+        </is>
+      </c>
+      <c r="E73" s="6" t="inlineStr"/>
+      <c r="F73" s="7" t="inlineStr"/>
+      <c r="G73" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H73" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I73" s="6" t="inlineStr">
+        <is>
+          <t>観光メディア掲載店</t>
+        </is>
+      </c>
+      <c r="J73" s="6" t="inlineStr"/>
+      <c r="K73" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L73" s="6" t="inlineStr"/>
+      <c r="M73" s="6" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="5" t="n">
         <v>73</v>
       </c>
-      <c r="B74" s="8" t="inlineStr"/>
-      <c r="C74" s="8" t="inlineStr"/>
-      <c r="D74" s="8" t="inlineStr"/>
-      <c r="E74" s="8" t="inlineStr"/>
-      <c r="F74" s="8" t="inlineStr"/>
-      <c r="G74" s="8" t="inlineStr"/>
-      <c r="H74" s="8" t="inlineStr"/>
-      <c r="I74" s="8" t="inlineStr"/>
-      <c r="J74" s="8" t="inlineStr"/>
-      <c r="K74" s="8" t="inlineStr"/>
-      <c r="L74" s="8" t="inlineStr"/>
-      <c r="M74" s="8" t="inlineStr"/>
+      <c r="B74" s="6" t="inlineStr">
+        <is>
+          <t>長豊陶苑</t>
+        </is>
+      </c>
+      <c r="C74" s="6" t="inlineStr">
+        <is>
+          <t>陶器店・ギャラリー</t>
+        </is>
+      </c>
+      <c r="D74" s="6" t="inlineStr">
+        <is>
+          <t>益子町</t>
+        </is>
+      </c>
+      <c r="E74" s="6" t="inlineStr"/>
+      <c r="F74" s="7" t="inlineStr"/>
+      <c r="G74" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H74" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I74" s="6" t="inlineStr">
+        <is>
+          <t>観光メディア掲載店</t>
+        </is>
+      </c>
+      <c r="J74" s="6" t="inlineStr"/>
+      <c r="K74" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L74" s="6" t="inlineStr"/>
+      <c r="M74" s="6" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="5" t="n">
         <v>74</v>
       </c>
-      <c r="B75" s="8" t="inlineStr"/>
-      <c r="C75" s="8" t="inlineStr"/>
-      <c r="D75" s="8" t="inlineStr"/>
-      <c r="E75" s="8" t="inlineStr"/>
-      <c r="F75" s="8" t="inlineStr"/>
-      <c r="G75" s="8" t="inlineStr"/>
-      <c r="H75" s="8" t="inlineStr"/>
-      <c r="I75" s="8" t="inlineStr"/>
-      <c r="J75" s="8" t="inlineStr"/>
-      <c r="K75" s="8" t="inlineStr"/>
-      <c r="L75" s="8" t="inlineStr"/>
-      <c r="M75" s="8" t="inlineStr"/>
+      <c r="B75" s="6" t="inlineStr">
+        <is>
+          <t>陶・ギャラリー田</t>
+        </is>
+      </c>
+      <c r="C75" s="6" t="inlineStr">
+        <is>
+          <t>陶器店・ギャラリー</t>
+        </is>
+      </c>
+      <c r="D75" s="6" t="inlineStr">
+        <is>
+          <t>益子町</t>
+        </is>
+      </c>
+      <c r="E75" s="6" t="inlineStr"/>
+      <c r="F75" s="7" t="inlineStr"/>
+      <c r="G75" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H75" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I75" s="6" t="inlineStr">
+        <is>
+          <t>観光メディア掲載店</t>
+        </is>
+      </c>
+      <c r="J75" s="6" t="inlineStr"/>
+      <c r="K75" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L75" s="6" t="inlineStr"/>
+      <c r="M75" s="6" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="5" t="n">
         <v>75</v>
       </c>
-      <c r="B76" s="8" t="inlineStr"/>
-      <c r="C76" s="8" t="inlineStr"/>
-      <c r="D76" s="8" t="inlineStr"/>
-      <c r="E76" s="8" t="inlineStr"/>
-      <c r="F76" s="8" t="inlineStr"/>
-      <c r="G76" s="8" t="inlineStr"/>
-      <c r="H76" s="8" t="inlineStr"/>
-      <c r="I76" s="8" t="inlineStr"/>
-      <c r="J76" s="8" t="inlineStr"/>
-      <c r="K76" s="8" t="inlineStr"/>
-      <c r="L76" s="8" t="inlineStr"/>
-      <c r="M76" s="8" t="inlineStr"/>
+      <c r="B76" s="6" t="inlineStr">
+        <is>
+          <t>陶房なかむら</t>
+        </is>
+      </c>
+      <c r="C76" s="6" t="inlineStr">
+        <is>
+          <t>陶器店・ギャラリー</t>
+        </is>
+      </c>
+      <c r="D76" s="6" t="inlineStr">
+        <is>
+          <t>益子町</t>
+        </is>
+      </c>
+      <c r="E76" s="6" t="inlineStr"/>
+      <c r="F76" s="7" t="inlineStr"/>
+      <c r="G76" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H76" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I76" s="6" t="inlineStr">
+        <is>
+          <t>観光メディア掲載店</t>
+        </is>
+      </c>
+      <c r="J76" s="6" t="inlineStr"/>
+      <c r="K76" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L76" s="6" t="inlineStr"/>
+      <c r="M76" s="6" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="5" t="n">
         <v>76</v>
       </c>
-      <c r="B77" s="8" t="inlineStr"/>
-      <c r="C77" s="8" t="inlineStr"/>
-      <c r="D77" s="8" t="inlineStr"/>
-      <c r="E77" s="8" t="inlineStr"/>
-      <c r="F77" s="8" t="inlineStr"/>
-      <c r="G77" s="8" t="inlineStr"/>
-      <c r="H77" s="8" t="inlineStr"/>
-      <c r="I77" s="8" t="inlineStr"/>
-      <c r="J77" s="8" t="inlineStr"/>
-      <c r="K77" s="8" t="inlineStr"/>
-      <c r="L77" s="8" t="inlineStr"/>
-      <c r="M77" s="8" t="inlineStr"/>
+      <c r="B77" s="6" t="inlineStr">
+        <is>
+          <t>陶房はせがわ</t>
+        </is>
+      </c>
+      <c r="C77" s="6" t="inlineStr">
+        <is>
+          <t>陶器店・ギャラリー</t>
+        </is>
+      </c>
+      <c r="D77" s="6" t="inlineStr">
+        <is>
+          <t>益子町</t>
+        </is>
+      </c>
+      <c r="E77" s="6" t="inlineStr"/>
+      <c r="F77" s="7" t="inlineStr"/>
+      <c r="G77" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H77" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I77" s="6" t="inlineStr">
+        <is>
+          <t>観光メディア掲載店</t>
+        </is>
+      </c>
+      <c r="J77" s="6" t="inlineStr"/>
+      <c r="K77" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L77" s="6" t="inlineStr"/>
+      <c r="M77" s="6" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="5" t="n">
         <v>77</v>
       </c>
-      <c r="B78" s="8" t="inlineStr"/>
-      <c r="C78" s="8" t="inlineStr"/>
-      <c r="D78" s="8" t="inlineStr"/>
-      <c r="E78" s="8" t="inlineStr"/>
-      <c r="F78" s="8" t="inlineStr"/>
-      <c r="G78" s="8" t="inlineStr"/>
-      <c r="H78" s="8" t="inlineStr"/>
-      <c r="I78" s="8" t="inlineStr"/>
-      <c r="J78" s="8" t="inlineStr"/>
-      <c r="K78" s="8" t="inlineStr"/>
-      <c r="L78" s="8" t="inlineStr"/>
-      <c r="M78" s="8" t="inlineStr"/>
+      <c r="B78" s="6" t="inlineStr">
+        <is>
+          <t>陶房日向</t>
+        </is>
+      </c>
+      <c r="C78" s="6" t="inlineStr">
+        <is>
+          <t>陶器店・ギャラリー</t>
+        </is>
+      </c>
+      <c r="D78" s="6" t="inlineStr">
+        <is>
+          <t>益子町</t>
+        </is>
+      </c>
+      <c r="E78" s="6" t="inlineStr"/>
+      <c r="F78" s="7" t="inlineStr"/>
+      <c r="G78" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H78" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I78" s="6" t="inlineStr">
+        <is>
+          <t>観光メディア掲載店</t>
+        </is>
+      </c>
+      <c r="J78" s="6" t="inlineStr"/>
+      <c r="K78" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L78" s="6" t="inlineStr"/>
+      <c r="M78" s="6" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="5" t="n">
         <v>78</v>
       </c>
-      <c r="B79" s="8" t="inlineStr"/>
-      <c r="C79" s="8" t="inlineStr"/>
-      <c r="D79" s="8" t="inlineStr"/>
-      <c r="E79" s="8" t="inlineStr"/>
-      <c r="F79" s="8" t="inlineStr"/>
-      <c r="G79" s="8" t="inlineStr"/>
-      <c r="H79" s="8" t="inlineStr"/>
-      <c r="I79" s="8" t="inlineStr"/>
-      <c r="J79" s="8" t="inlineStr"/>
-      <c r="K79" s="8" t="inlineStr"/>
-      <c r="L79" s="8" t="inlineStr"/>
-      <c r="M79" s="8" t="inlineStr"/>
+      <c r="B79" s="6" t="inlineStr">
+        <is>
+          <t>もえぎ 城内坂店</t>
+        </is>
+      </c>
+      <c r="C79" s="6" t="inlineStr">
+        <is>
+          <t>陶器店・ギャラリー</t>
+        </is>
+      </c>
+      <c r="D79" s="6" t="inlineStr">
+        <is>
+          <t>益子町</t>
+        </is>
+      </c>
+      <c r="E79" s="6" t="inlineStr">
+        <is>
+          <t>城内坂通り</t>
+        </is>
+      </c>
+      <c r="F79" s="7" t="inlineStr"/>
+      <c r="G79" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H79" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I79" s="6" t="inlineStr">
+        <is>
+          <t>観光メディア掲載店</t>
+        </is>
+      </c>
+      <c r="J79" s="6" t="inlineStr"/>
+      <c r="K79" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L79" s="6" t="inlineStr"/>
+      <c r="M79" s="6" t="inlineStr">
+        <is>
+          <t>約150名の作家作品を扱う、カフェ・レストラン併設</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="5" t="n">
         <v>79</v>
       </c>
-      <c r="B80" s="8" t="inlineStr"/>
-      <c r="C80" s="8" t="inlineStr"/>
-      <c r="D80" s="8" t="inlineStr"/>
-      <c r="E80" s="8" t="inlineStr"/>
-      <c r="F80" s="8" t="inlineStr"/>
-      <c r="G80" s="8" t="inlineStr"/>
-      <c r="H80" s="8" t="inlineStr"/>
-      <c r="I80" s="8" t="inlineStr"/>
-      <c r="J80" s="8" t="inlineStr"/>
-      <c r="K80" s="8" t="inlineStr"/>
-      <c r="L80" s="8" t="inlineStr"/>
-      <c r="M80" s="8" t="inlineStr"/>
+      <c r="B80" s="6" t="inlineStr">
+        <is>
+          <t>陶庫（とうこ）</t>
+        </is>
+      </c>
+      <c r="C80" s="6" t="inlineStr">
+        <is>
+          <t>陶器店・ギャラリー</t>
+        </is>
+      </c>
+      <c r="D80" s="6" t="inlineStr">
+        <is>
+          <t>益子町</t>
+        </is>
+      </c>
+      <c r="E80" s="6" t="inlineStr">
+        <is>
+          <t>城内坂2</t>
+        </is>
+      </c>
+      <c r="F80" s="7" t="inlineStr"/>
+      <c r="G80" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H80" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I80" s="6" t="inlineStr">
+        <is>
+          <t>公式サイト</t>
+        </is>
+      </c>
+      <c r="J80" s="6" t="inlineStr"/>
+      <c r="K80" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L80" s="6" t="inlineStr"/>
+      <c r="M80" s="6" t="inlineStr">
+        <is>
+          <t>約2週間ごとに展覧会、1000回以上開催のギャラリー</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="5" t="n">
         <v>80</v>
       </c>
-      <c r="B81" s="8" t="inlineStr"/>
-      <c r="C81" s="8" t="inlineStr"/>
-      <c r="D81" s="8" t="inlineStr"/>
-      <c r="E81" s="8" t="inlineStr"/>
-      <c r="F81" s="8" t="inlineStr"/>
-      <c r="G81" s="8" t="inlineStr"/>
-      <c r="H81" s="8" t="inlineStr"/>
-      <c r="I81" s="8" t="inlineStr"/>
-      <c r="J81" s="8" t="inlineStr"/>
-      <c r="K81" s="8" t="inlineStr"/>
-      <c r="L81" s="8" t="inlineStr"/>
-      <c r="M81" s="8" t="inlineStr"/>
+      <c r="B81" s="6" t="inlineStr">
+        <is>
+          <t>ギャラリー陶のね広場</t>
+        </is>
+      </c>
+      <c r="C81" s="6" t="inlineStr">
+        <is>
+          <t>陶器店・ギャラリー</t>
+        </is>
+      </c>
+      <c r="D81" s="6" t="inlineStr">
+        <is>
+          <t>益子町</t>
+        </is>
+      </c>
+      <c r="E81" s="6" t="inlineStr"/>
+      <c r="F81" s="7" t="inlineStr"/>
+      <c r="G81" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H81" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I81" s="6" t="inlineStr">
+        <is>
+          <t>益子陶器市 出店者情報</t>
+        </is>
+      </c>
+      <c r="J81" s="6" t="inlineStr"/>
+      <c r="K81" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L81" s="6" t="inlineStr"/>
+      <c r="M81" s="6" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="5" t="n">
         <v>81</v>
       </c>
-      <c r="B82" s="8" t="inlineStr"/>
-      <c r="C82" s="8" t="inlineStr"/>
-      <c r="D82" s="8" t="inlineStr"/>
-      <c r="E82" s="8" t="inlineStr"/>
-      <c r="F82" s="8" t="inlineStr"/>
-      <c r="G82" s="8" t="inlineStr"/>
-      <c r="H82" s="8" t="inlineStr"/>
-      <c r="I82" s="8" t="inlineStr"/>
-      <c r="J82" s="8" t="inlineStr"/>
-      <c r="K82" s="8" t="inlineStr"/>
-      <c r="L82" s="8" t="inlineStr"/>
-      <c r="M82" s="8" t="inlineStr"/>
+      <c r="B82" s="6" t="inlineStr">
+        <is>
+          <t>ギャラリー陶 塑瑠土</t>
+        </is>
+      </c>
+      <c r="C82" s="6" t="inlineStr">
+        <is>
+          <t>陶器店・ギャラリー</t>
+        </is>
+      </c>
+      <c r="D82" s="6" t="inlineStr">
+        <is>
+          <t>益子町</t>
+        </is>
+      </c>
+      <c r="E82" s="6" t="inlineStr"/>
+      <c r="F82" s="7" t="inlineStr"/>
+      <c r="G82" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H82" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I82" s="6" t="inlineStr">
+        <is>
+          <t>益子陶器市 出店者情報</t>
+        </is>
+      </c>
+      <c r="J82" s="6" t="inlineStr"/>
+      <c r="K82" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L82" s="6" t="inlineStr"/>
+      <c r="M82" s="6" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="5" t="n">
         <v>82</v>
       </c>
-      <c r="B83" s="8" t="inlineStr"/>
-      <c r="C83" s="8" t="inlineStr"/>
-      <c r="D83" s="8" t="inlineStr"/>
-      <c r="E83" s="8" t="inlineStr"/>
-      <c r="F83" s="8" t="inlineStr"/>
-      <c r="G83" s="8" t="inlineStr"/>
-      <c r="H83" s="8" t="inlineStr"/>
-      <c r="I83" s="8" t="inlineStr"/>
-      <c r="J83" s="8" t="inlineStr"/>
-      <c r="K83" s="8" t="inlineStr"/>
-      <c r="L83" s="8" t="inlineStr"/>
-      <c r="M83" s="8" t="inlineStr"/>
+      <c r="B83" s="6" t="inlineStr">
+        <is>
+          <t>茶房 風花</t>
+        </is>
+      </c>
+      <c r="C83" s="6" t="inlineStr">
+        <is>
+          <t>カフェ</t>
+        </is>
+      </c>
+      <c r="D83" s="6" t="inlineStr">
+        <is>
+          <t>さくら市</t>
+        </is>
+      </c>
+      <c r="E83" s="6" t="inlineStr">
+        <is>
+          <t>喜連川</t>
+        </is>
+      </c>
+      <c r="F83" s="7" t="inlineStr"/>
+      <c r="G83" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H83" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I83" s="6" t="inlineStr">
+        <is>
+          <t>地域情報サイト掲載店</t>
+        </is>
+      </c>
+      <c r="J83" s="6" t="inlineStr"/>
+      <c r="K83" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L83" s="6" t="inlineStr"/>
+      <c r="M83" s="6" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="5" t="n">
         <v>83</v>
       </c>
-      <c r="B84" s="8" t="inlineStr"/>
-      <c r="C84" s="8" t="inlineStr"/>
-      <c r="D84" s="8" t="inlineStr"/>
-      <c r="E84" s="8" t="inlineStr"/>
-      <c r="F84" s="8" t="inlineStr"/>
-      <c r="G84" s="8" t="inlineStr"/>
-      <c r="H84" s="8" t="inlineStr"/>
-      <c r="I84" s="8" t="inlineStr"/>
-      <c r="J84" s="8" t="inlineStr"/>
-      <c r="K84" s="8" t="inlineStr"/>
-      <c r="L84" s="8" t="inlineStr"/>
-      <c r="M84" s="8" t="inlineStr"/>
+      <c r="B84" s="6" t="inlineStr">
+        <is>
+          <t>わ</t>
+        </is>
+      </c>
+      <c r="C84" s="6" t="inlineStr">
+        <is>
+          <t>カフェ</t>
+        </is>
+      </c>
+      <c r="D84" s="6" t="inlineStr">
+        <is>
+          <t>さくら市</t>
+        </is>
+      </c>
+      <c r="E84" s="6" t="inlineStr">
+        <is>
+          <t>氏家駅近く</t>
+        </is>
+      </c>
+      <c r="F84" s="7" t="inlineStr"/>
+      <c r="G84" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H84" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I84" s="6" t="inlineStr">
+        <is>
+          <t>地域情報サイト掲載店</t>
+        </is>
+      </c>
+      <c r="J84" s="6" t="inlineStr"/>
+      <c r="K84" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L84" s="6" t="inlineStr"/>
+      <c r="M84" s="6" t="inlineStr">
+        <is>
+          <t>カフェレストラン</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="5" t="n">
         <v>84</v>
       </c>
-      <c r="B85" s="8" t="inlineStr"/>
-      <c r="C85" s="8" t="inlineStr"/>
-      <c r="D85" s="8" t="inlineStr"/>
-      <c r="E85" s="8" t="inlineStr"/>
-      <c r="F85" s="8" t="inlineStr"/>
-      <c r="G85" s="8" t="inlineStr"/>
-      <c r="H85" s="8" t="inlineStr"/>
-      <c r="I85" s="8" t="inlineStr"/>
-      <c r="J85" s="8" t="inlineStr"/>
-      <c r="K85" s="8" t="inlineStr"/>
-      <c r="L85" s="8" t="inlineStr"/>
-      <c r="M85" s="8" t="inlineStr"/>
+      <c r="B85" s="6" t="inlineStr">
+        <is>
+          <t>京月</t>
+        </is>
+      </c>
+      <c r="C85" s="6" t="inlineStr">
+        <is>
+          <t>和菓子店</t>
+        </is>
+      </c>
+      <c r="D85" s="6" t="inlineStr">
+        <is>
+          <t>さくら市</t>
+        </is>
+      </c>
+      <c r="E85" s="6" t="inlineStr"/>
+      <c r="F85" s="7" t="inlineStr"/>
+      <c r="G85" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H85" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I85" s="6" t="inlineStr">
+        <is>
+          <t>地域情報サイト掲載店</t>
+        </is>
+      </c>
+      <c r="J85" s="6" t="inlineStr"/>
+      <c r="K85" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L85" s="6" t="inlineStr"/>
+      <c r="M85" s="6" t="inlineStr">
+        <is>
+          <t>いちご大福が名物の老舗和菓子店</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="5" t="n">
         <v>85</v>
       </c>
-      <c r="B86" s="8" t="inlineStr"/>
-      <c r="C86" s="8" t="inlineStr"/>
-      <c r="D86" s="8" t="inlineStr"/>
-      <c r="E86" s="8" t="inlineStr"/>
-      <c r="F86" s="8" t="inlineStr"/>
-      <c r="G86" s="8" t="inlineStr"/>
-      <c r="H86" s="8" t="inlineStr"/>
-      <c r="I86" s="8" t="inlineStr"/>
-      <c r="J86" s="8" t="inlineStr"/>
-      <c r="K86" s="8" t="inlineStr"/>
-      <c r="L86" s="8" t="inlineStr"/>
-      <c r="M86" s="8" t="inlineStr"/>
+      <c r="B86" s="6" t="inlineStr">
+        <is>
+          <t>Butch Cafe（ブッチカフェ）</t>
+        </is>
+      </c>
+      <c r="C86" s="6" t="inlineStr">
+        <is>
+          <t>カフェ</t>
+        </is>
+      </c>
+      <c r="D86" s="6" t="inlineStr">
+        <is>
+          <t>上三川町</t>
+        </is>
+      </c>
+      <c r="E86" s="6" t="inlineStr">
+        <is>
+          <t>上三川4999-7</t>
+        </is>
+      </c>
+      <c r="F86" s="7" t="inlineStr"/>
+      <c r="G86" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H86" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I86" s="6" t="inlineStr">
+        <is>
+          <t>地域情報サイト掲載店</t>
+        </is>
+      </c>
+      <c r="J86" s="6" t="inlineStr"/>
+      <c r="K86" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L86" s="6" t="inlineStr"/>
+      <c r="M86" s="6" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="5" t="n">
         <v>86</v>
       </c>
-      <c r="B87" s="8" t="inlineStr"/>
-      <c r="C87" s="8" t="inlineStr"/>
-      <c r="D87" s="8" t="inlineStr"/>
-      <c r="E87" s="8" t="inlineStr"/>
-      <c r="F87" s="8" t="inlineStr"/>
-      <c r="G87" s="8" t="inlineStr"/>
-      <c r="H87" s="8" t="inlineStr"/>
-      <c r="I87" s="8" t="inlineStr"/>
-      <c r="J87" s="8" t="inlineStr"/>
-      <c r="K87" s="8" t="inlineStr"/>
-      <c r="L87" s="8" t="inlineStr"/>
-      <c r="M87" s="8" t="inlineStr"/>
+      <c r="B87" s="6" t="inlineStr">
+        <is>
+          <t>気まぐれSweets</t>
+        </is>
+      </c>
+      <c r="C87" s="6" t="inlineStr">
+        <is>
+          <t>カフェ</t>
+        </is>
+      </c>
+      <c r="D87" s="6" t="inlineStr">
+        <is>
+          <t>上三川町</t>
+        </is>
+      </c>
+      <c r="E87" s="6" t="inlineStr"/>
+      <c r="F87" s="7" t="inlineStr"/>
+      <c r="G87" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H87" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I87" s="6" t="inlineStr">
+        <is>
+          <t>地域情報サイト掲載店</t>
+        </is>
+      </c>
+      <c r="J87" s="6" t="inlineStr"/>
+      <c r="K87" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L87" s="6" t="inlineStr"/>
+      <c r="M87" s="6" t="inlineStr">
+        <is>
+          <t>店名表記は推定のため要確認、パンケーキが名物</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="5" t="n">
         <v>87</v>
       </c>
-      <c r="B88" s="8" t="inlineStr"/>
-      <c r="C88" s="8" t="inlineStr"/>
-      <c r="D88" s="8" t="inlineStr"/>
-      <c r="E88" s="8" t="inlineStr"/>
-      <c r="F88" s="8" t="inlineStr"/>
-      <c r="G88" s="8" t="inlineStr"/>
-      <c r="H88" s="8" t="inlineStr"/>
-      <c r="I88" s="8" t="inlineStr"/>
-      <c r="J88" s="8" t="inlineStr"/>
-      <c r="K88" s="8" t="inlineStr"/>
-      <c r="L88" s="8" t="inlineStr"/>
-      <c r="M88" s="8" t="inlineStr"/>
+      <c r="B88" s="6" t="inlineStr">
+        <is>
+          <t>カフェ三四八</t>
+        </is>
+      </c>
+      <c r="C88" s="6" t="inlineStr">
+        <is>
+          <t>カフェ</t>
+        </is>
+      </c>
+      <c r="D88" s="6" t="inlineStr">
+        <is>
+          <t>市貝町</t>
+        </is>
+      </c>
+      <c r="E88" s="6" t="inlineStr">
+        <is>
+          <t>市塙1270・道の駅サシバの里いちかい内</t>
+        </is>
+      </c>
+      <c r="F88" s="7" t="inlineStr"/>
+      <c r="G88" s="6" t="inlineStr">
+        <is>
+          <t>木曜日</t>
+        </is>
+      </c>
+      <c r="H88" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I88" s="6" t="inlineStr">
+        <is>
+          <t>公式サイト</t>
+        </is>
+      </c>
+      <c r="J88" s="6" t="inlineStr"/>
+      <c r="K88" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L88" s="6" t="inlineStr"/>
+      <c r="M88" s="6" t="inlineStr">
+        <is>
+          <t>オリジナルブレンドコーヒー、定休日: 木曜（要再確認）</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="5" t="n">
         <v>88</v>
       </c>
-      <c r="B89" s="8" t="inlineStr"/>
-      <c r="C89" s="8" t="inlineStr"/>
-      <c r="D89" s="8" t="inlineStr"/>
-      <c r="E89" s="8" t="inlineStr"/>
-      <c r="F89" s="8" t="inlineStr"/>
-      <c r="G89" s="8" t="inlineStr"/>
-      <c r="H89" s="8" t="inlineStr"/>
-      <c r="I89" s="8" t="inlineStr"/>
-      <c r="J89" s="8" t="inlineStr"/>
-      <c r="K89" s="8" t="inlineStr"/>
-      <c r="L89" s="8" t="inlineStr"/>
-      <c r="M89" s="8" t="inlineStr"/>
+      <c r="B89" s="6" t="inlineStr">
+        <is>
+          <t>ベリーベリー</t>
+        </is>
+      </c>
+      <c r="C89" s="6" t="inlineStr">
+        <is>
+          <t>カフェ</t>
+        </is>
+      </c>
+      <c r="D89" s="6" t="inlineStr">
+        <is>
+          <t>市貝町</t>
+        </is>
+      </c>
+      <c r="E89" s="6" t="inlineStr">
+        <is>
+          <t>赤羽</t>
+        </is>
+      </c>
+      <c r="F89" s="7" t="inlineStr"/>
+      <c r="G89" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H89" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I89" s="6" t="inlineStr">
+        <is>
+          <t>地域情報サイト掲載店</t>
+        </is>
+      </c>
+      <c r="J89" s="6" t="inlineStr"/>
+      <c r="K89" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L89" s="6" t="inlineStr"/>
+      <c r="M89" s="6" t="inlineStr">
+        <is>
+          <t>ジェラート専門</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="5" t="n">
         <v>89</v>
       </c>
-      <c r="B90" s="8" t="inlineStr"/>
-      <c r="C90" s="8" t="inlineStr"/>
-      <c r="D90" s="8" t="inlineStr"/>
-      <c r="E90" s="8" t="inlineStr"/>
-      <c r="F90" s="8" t="inlineStr"/>
-      <c r="G90" s="8" t="inlineStr"/>
-      <c r="H90" s="8" t="inlineStr"/>
-      <c r="I90" s="8" t="inlineStr"/>
-      <c r="J90" s="8" t="inlineStr"/>
-      <c r="K90" s="8" t="inlineStr"/>
-      <c r="L90" s="8" t="inlineStr"/>
-      <c r="M90" s="8" t="inlineStr"/>
+      <c r="B90" s="6" t="inlineStr">
+        <is>
+          <t>かざぐるま</t>
+        </is>
+      </c>
+      <c r="C90" s="6" t="inlineStr">
+        <is>
+          <t>カフェ</t>
+        </is>
+      </c>
+      <c r="D90" s="6" t="inlineStr">
+        <is>
+          <t>市貝町</t>
+        </is>
+      </c>
+      <c r="E90" s="6" t="inlineStr">
+        <is>
+          <t>赤羽</t>
+        </is>
+      </c>
+      <c r="F90" s="7" t="inlineStr"/>
+      <c r="G90" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H90" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I90" s="6" t="inlineStr">
+        <is>
+          <t>地域情報サイト掲載店</t>
+        </is>
+      </c>
+      <c r="J90" s="6" t="inlineStr"/>
+      <c r="K90" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L90" s="6" t="inlineStr"/>
+      <c r="M90" s="6" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="5" t="n">
         <v>90</v>
       </c>
-      <c r="B91" s="8" t="inlineStr"/>
-      <c r="C91" s="8" t="inlineStr"/>
-      <c r="D91" s="8" t="inlineStr"/>
-      <c r="E91" s="8" t="inlineStr"/>
-      <c r="F91" s="8" t="inlineStr"/>
-      <c r="G91" s="8" t="inlineStr"/>
-      <c r="H91" s="8" t="inlineStr"/>
-      <c r="I91" s="8" t="inlineStr"/>
-      <c r="J91" s="8" t="inlineStr"/>
-      <c r="K91" s="8" t="inlineStr"/>
-      <c r="L91" s="8" t="inlineStr"/>
-      <c r="M91" s="8" t="inlineStr"/>
+      <c r="B91" s="6" t="inlineStr">
+        <is>
+          <t>ポスト・ド・ブレ</t>
+        </is>
+      </c>
+      <c r="C91" s="6" t="inlineStr">
+        <is>
+          <t>パン屋</t>
+        </is>
+      </c>
+      <c r="D91" s="6" t="inlineStr">
+        <is>
+          <t>宇都宮市</t>
+        </is>
+      </c>
+      <c r="E91" s="6" t="inlineStr"/>
+      <c r="F91" s="7" t="inlineStr"/>
+      <c r="G91" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H91" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I91" s="6" t="inlineStr">
+        <is>
+          <t>グルメサイト掲載店</t>
+        </is>
+      </c>
+      <c r="J91" s="6" t="inlineStr"/>
+      <c r="K91" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L91" s="6" t="inlineStr"/>
+      <c r="M91" s="6" t="inlineStr">
+        <is>
+          <t>築90年の大谷石蔵をリノベーション</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="5" t="n">
         <v>91</v>
       </c>
-      <c r="B92" s="8" t="inlineStr"/>
-      <c r="C92" s="8" t="inlineStr"/>
-      <c r="D92" s="8" t="inlineStr"/>
-      <c r="E92" s="8" t="inlineStr"/>
-      <c r="F92" s="8" t="inlineStr"/>
-      <c r="G92" s="8" t="inlineStr"/>
-      <c r="H92" s="8" t="inlineStr"/>
-      <c r="I92" s="8" t="inlineStr"/>
-      <c r="J92" s="8" t="inlineStr"/>
-      <c r="K92" s="8" t="inlineStr"/>
-      <c r="L92" s="8" t="inlineStr"/>
-      <c r="M92" s="8" t="inlineStr"/>
+      <c r="B92" s="6" t="inlineStr">
+        <is>
+          <t>とろろとぱん</t>
+        </is>
+      </c>
+      <c r="C92" s="6" t="inlineStr">
+        <is>
+          <t>パン屋</t>
+        </is>
+      </c>
+      <c r="D92" s="6" t="inlineStr">
+        <is>
+          <t>宇都宮市</t>
+        </is>
+      </c>
+      <c r="E92" s="6" t="inlineStr"/>
+      <c r="F92" s="7" t="inlineStr"/>
+      <c r="G92" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H92" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I92" s="6" t="inlineStr">
+        <is>
+          <t>公式サイト</t>
+        </is>
+      </c>
+      <c r="J92" s="6" t="inlineStr"/>
+      <c r="K92" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L92" s="6" t="inlineStr"/>
+      <c r="M92" s="6" t="inlineStr">
+        <is>
+          <t>古民家改装、駄菓子屋コンセプト</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="5" t="n">
         <v>92</v>
       </c>
-      <c r="B93" s="8" t="inlineStr"/>
-      <c r="C93" s="8" t="inlineStr"/>
-      <c r="D93" s="8" t="inlineStr"/>
-      <c r="E93" s="8" t="inlineStr"/>
-      <c r="F93" s="8" t="inlineStr"/>
-      <c r="G93" s="8" t="inlineStr"/>
-      <c r="H93" s="8" t="inlineStr"/>
-      <c r="I93" s="8" t="inlineStr"/>
-      <c r="J93" s="8" t="inlineStr"/>
-      <c r="K93" s="8" t="inlineStr"/>
-      <c r="L93" s="8" t="inlineStr"/>
-      <c r="M93" s="8" t="inlineStr"/>
+      <c r="B93" s="6" t="inlineStr">
+        <is>
+          <t>石窯パン工房 Pan De Park</t>
+        </is>
+      </c>
+      <c r="C93" s="6" t="inlineStr">
+        <is>
+          <t>パン屋</t>
+        </is>
+      </c>
+      <c r="D93" s="6" t="inlineStr">
+        <is>
+          <t>宇都宮市</t>
+        </is>
+      </c>
+      <c r="E93" s="6" t="inlineStr"/>
+      <c r="F93" s="7" t="inlineStr"/>
+      <c r="G93" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H93" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I93" s="6" t="inlineStr">
+        <is>
+          <t>グルメサイト掲載店</t>
+        </is>
+      </c>
+      <c r="J93" s="6" t="inlineStr"/>
+      <c r="K93" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L93" s="6" t="inlineStr"/>
+      <c r="M93" s="6" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="5" t="n">
         <v>93</v>
       </c>
-      <c r="B94" s="8" t="inlineStr"/>
-      <c r="C94" s="8" t="inlineStr"/>
-      <c r="D94" s="8" t="inlineStr"/>
-      <c r="E94" s="8" t="inlineStr"/>
-      <c r="F94" s="8" t="inlineStr"/>
-      <c r="G94" s="8" t="inlineStr"/>
-      <c r="H94" s="8" t="inlineStr"/>
-      <c r="I94" s="8" t="inlineStr"/>
-      <c r="J94" s="8" t="inlineStr"/>
-      <c r="K94" s="8" t="inlineStr"/>
-      <c r="L94" s="8" t="inlineStr"/>
-      <c r="M94" s="8" t="inlineStr"/>
+      <c r="B94" s="6" t="inlineStr">
+        <is>
+          <t>ブーランジュリ・マルシェ</t>
+        </is>
+      </c>
+      <c r="C94" s="6" t="inlineStr">
+        <is>
+          <t>パン屋</t>
+        </is>
+      </c>
+      <c r="D94" s="6" t="inlineStr">
+        <is>
+          <t>宇都宮市</t>
+        </is>
+      </c>
+      <c r="E94" s="6" t="inlineStr"/>
+      <c r="F94" s="7" t="inlineStr"/>
+      <c r="G94" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H94" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I94" s="6" t="inlineStr">
+        <is>
+          <t>グルメサイト掲載店</t>
+        </is>
+      </c>
+      <c r="J94" s="6" t="inlineStr"/>
+      <c r="K94" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L94" s="6" t="inlineStr"/>
+      <c r="M94" s="6" t="inlineStr">
+        <is>
+          <t>本格フランス風パン屋</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="5" t="n">
         <v>94</v>
       </c>
-      <c r="B95" s="8" t="inlineStr"/>
-      <c r="C95" s="8" t="inlineStr"/>
-      <c r="D95" s="8" t="inlineStr"/>
-      <c r="E95" s="8" t="inlineStr"/>
-      <c r="F95" s="8" t="inlineStr"/>
-      <c r="G95" s="8" t="inlineStr"/>
-      <c r="H95" s="8" t="inlineStr"/>
-      <c r="I95" s="8" t="inlineStr"/>
-      <c r="J95" s="8" t="inlineStr"/>
-      <c r="K95" s="8" t="inlineStr"/>
-      <c r="L95" s="8" t="inlineStr"/>
-      <c r="M95" s="8" t="inlineStr"/>
+      <c r="B95" s="6" t="inlineStr">
+        <is>
+          <t>ペンション森のうーたん</t>
+        </is>
+      </c>
+      <c r="C95" s="6" t="inlineStr">
+        <is>
+          <t>飲食店</t>
+        </is>
+      </c>
+      <c r="D95" s="6" t="inlineStr">
+        <is>
+          <t>那須町</t>
+        </is>
+      </c>
+      <c r="E95" s="6" t="inlineStr">
+        <is>
+          <t>那須高原</t>
+        </is>
+      </c>
+      <c r="F95" s="7" t="inlineStr"/>
+      <c r="G95" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H95" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I95" s="6" t="inlineStr">
+        <is>
+          <t>観光メディア掲載店</t>
+        </is>
+      </c>
+      <c r="J95" s="6" t="inlineStr"/>
+      <c r="K95" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L95" s="6" t="inlineStr"/>
+      <c r="M95" s="6" t="inlineStr">
+        <is>
+          <t>国産牛ヒレステーキ、シーフードグラタン</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="5" t="n">
         <v>95</v>
       </c>
-      <c r="B96" s="8" t="inlineStr"/>
-      <c r="C96" s="8" t="inlineStr"/>
-      <c r="D96" s="8" t="inlineStr"/>
-      <c r="E96" s="8" t="inlineStr"/>
-      <c r="F96" s="8" t="inlineStr"/>
-      <c r="G96" s="8" t="inlineStr"/>
-      <c r="H96" s="8" t="inlineStr"/>
-      <c r="I96" s="8" t="inlineStr"/>
-      <c r="J96" s="8" t="inlineStr"/>
-      <c r="K96" s="8" t="inlineStr"/>
-      <c r="L96" s="8" t="inlineStr"/>
-      <c r="M96" s="8" t="inlineStr"/>
+      <c r="B96" s="6" t="inlineStr">
+        <is>
+          <t>プチホテル晩餐館</t>
+        </is>
+      </c>
+      <c r="C96" s="6" t="inlineStr">
+        <is>
+          <t>飲食店</t>
+        </is>
+      </c>
+      <c r="D96" s="6" t="inlineStr">
+        <is>
+          <t>那須町</t>
+        </is>
+      </c>
+      <c r="E96" s="6" t="inlineStr">
+        <is>
+          <t>那須高原</t>
+        </is>
+      </c>
+      <c r="F96" s="7" t="inlineStr"/>
+      <c r="G96" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H96" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I96" s="6" t="inlineStr">
+        <is>
+          <t>観光メディア掲載店</t>
+        </is>
+      </c>
+      <c r="J96" s="6" t="inlineStr"/>
+      <c r="K96" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L96" s="6" t="inlineStr"/>
+      <c r="M96" s="6" t="inlineStr">
+        <is>
+          <t>ステンドグラスのダイニング、ヒレステーキのフルコース</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="5" t="n">
         <v>96</v>
       </c>
-      <c r="B97" s="8" t="inlineStr"/>
-      <c r="C97" s="8" t="inlineStr"/>
-      <c r="D97" s="8" t="inlineStr"/>
-      <c r="E97" s="8" t="inlineStr"/>
-      <c r="F97" s="8" t="inlineStr"/>
-      <c r="G97" s="8" t="inlineStr"/>
-      <c r="H97" s="8" t="inlineStr"/>
-      <c r="I97" s="8" t="inlineStr"/>
-      <c r="J97" s="8" t="inlineStr"/>
-      <c r="K97" s="8" t="inlineStr"/>
-      <c r="L97" s="8" t="inlineStr"/>
-      <c r="M97" s="8" t="inlineStr"/>
+      <c r="B97" s="6" t="inlineStr">
+        <is>
+          <t>那須高原バル</t>
+        </is>
+      </c>
+      <c r="C97" s="6" t="inlineStr">
+        <is>
+          <t>飲食店</t>
+        </is>
+      </c>
+      <c r="D97" s="6" t="inlineStr">
+        <is>
+          <t>那須町</t>
+        </is>
+      </c>
+      <c r="E97" s="6" t="inlineStr">
+        <is>
+          <t>那須高原</t>
+        </is>
+      </c>
+      <c r="F97" s="7" t="inlineStr"/>
+      <c r="G97" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H97" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I97" s="6" t="inlineStr">
+        <is>
+          <t>公式サイト</t>
+        </is>
+      </c>
+      <c r="J97" s="6" t="inlineStr"/>
+      <c r="K97" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L97" s="6" t="inlineStr"/>
+      <c r="M97" s="6" t="inlineStr">
+        <is>
+          <t>那須産野菜・地場産品を使ったレストラン</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="5" t="n">
         <v>97</v>
       </c>
-      <c r="B98" s="8" t="inlineStr"/>
-      <c r="C98" s="8" t="inlineStr"/>
-      <c r="D98" s="8" t="inlineStr"/>
-      <c r="E98" s="8" t="inlineStr"/>
-      <c r="F98" s="8" t="inlineStr"/>
-      <c r="G98" s="8" t="inlineStr"/>
-      <c r="H98" s="8" t="inlineStr"/>
-      <c r="I98" s="8" t="inlineStr"/>
-      <c r="J98" s="8" t="inlineStr"/>
-      <c r="K98" s="8" t="inlineStr"/>
-      <c r="L98" s="8" t="inlineStr"/>
-      <c r="M98" s="8" t="inlineStr"/>
+      <c r="B98" s="6" t="inlineStr">
+        <is>
+          <t>豊田木工所</t>
+        </is>
+      </c>
+      <c r="C98" s="6" t="inlineStr">
+        <is>
+          <t>工芸品店</t>
+        </is>
+      </c>
+      <c r="D98" s="6" t="inlineStr">
+        <is>
+          <t>鹿沼市</t>
+        </is>
+      </c>
+      <c r="E98" s="6" t="inlineStr"/>
+      <c r="F98" s="7" t="inlineStr"/>
+      <c r="G98" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H98" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I98" s="6" t="inlineStr">
+        <is>
+          <t>地域メディア掲載店</t>
+        </is>
+      </c>
+      <c r="J98" s="6" t="inlineStr"/>
+      <c r="K98" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L98" s="6" t="inlineStr"/>
+      <c r="M98" s="6" t="inlineStr">
+        <is>
+          <t>鹿沼組子（寄木細工）の木工所、3代目</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="5" t="n">
         <v>98</v>
       </c>
-      <c r="B99" s="8" t="inlineStr"/>
-      <c r="C99" s="8" t="inlineStr"/>
-      <c r="D99" s="8" t="inlineStr"/>
-      <c r="E99" s="8" t="inlineStr"/>
-      <c r="F99" s="8" t="inlineStr"/>
-      <c r="G99" s="8" t="inlineStr"/>
-      <c r="H99" s="8" t="inlineStr"/>
-      <c r="I99" s="8" t="inlineStr"/>
-      <c r="J99" s="8" t="inlineStr"/>
-      <c r="K99" s="8" t="inlineStr"/>
-      <c r="L99" s="8" t="inlineStr"/>
-      <c r="M99" s="8" t="inlineStr"/>
+      <c r="B99" s="6" t="inlineStr">
+        <is>
+          <t>星野工業株式会社</t>
+        </is>
+      </c>
+      <c r="C99" s="6" t="inlineStr">
+        <is>
+          <t>工芸品店</t>
+        </is>
+      </c>
+      <c r="D99" s="6" t="inlineStr">
+        <is>
+          <t>鹿沼市</t>
+        </is>
+      </c>
+      <c r="E99" s="6" t="inlineStr">
+        <is>
+          <t>玉田町692-8</t>
+        </is>
+      </c>
+      <c r="F99" s="7" t="inlineStr"/>
+      <c r="G99" s="6" t="inlineStr">
+        <is>
+          <t>土・日・祝日</t>
+        </is>
+      </c>
+      <c r="H99" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I99" s="6" t="inlineStr">
+        <is>
+          <t>公式サイト</t>
+        </is>
+      </c>
+      <c r="J99" s="6" t="inlineStr"/>
+      <c r="K99" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L99" s="6" t="inlineStr"/>
+      <c r="M99" s="6" t="inlineStr">
+        <is>
+          <t>木工・組子、定休日: 土日祝（要再確認）</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="5" t="n">
         <v>99</v>
       </c>
-      <c r="B100" s="8" t="inlineStr"/>
-      <c r="C100" s="8" t="inlineStr"/>
-      <c r="D100" s="8" t="inlineStr"/>
-      <c r="E100" s="8" t="inlineStr"/>
-      <c r="F100" s="8" t="inlineStr"/>
-      <c r="G100" s="8" t="inlineStr"/>
-      <c r="H100" s="8" t="inlineStr"/>
-      <c r="I100" s="8" t="inlineStr"/>
-      <c r="J100" s="8" t="inlineStr"/>
-      <c r="K100" s="8" t="inlineStr"/>
-      <c r="L100" s="8" t="inlineStr"/>
-      <c r="M100" s="8" t="inlineStr"/>
+      <c r="B100" s="6" t="inlineStr">
+        <is>
+          <t>茶房直</t>
+        </is>
+      </c>
+      <c r="C100" s="6" t="inlineStr">
+        <is>
+          <t>カフェ</t>
+        </is>
+      </c>
+      <c r="D100" s="6" t="inlineStr">
+        <is>
+          <t>佐野市</t>
+        </is>
+      </c>
+      <c r="E100" s="6" t="inlineStr"/>
+      <c r="F100" s="7" t="inlineStr"/>
+      <c r="G100" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H100" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I100" s="6" t="inlineStr">
+        <is>
+          <t>地域情報サイト掲載店</t>
+        </is>
+      </c>
+      <c r="J100" s="6" t="inlineStr"/>
+      <c r="K100" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L100" s="6" t="inlineStr"/>
+      <c r="M100" s="6" t="inlineStr">
+        <is>
+          <t>古民家風レトロなカフェ</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="B101" s="8" t="inlineStr"/>
-      <c r="C101" s="8" t="inlineStr"/>
-      <c r="D101" s="8" t="inlineStr"/>
-      <c r="E101" s="8" t="inlineStr"/>
-      <c r="F101" s="8" t="inlineStr"/>
-      <c r="G101" s="8" t="inlineStr"/>
-      <c r="H101" s="8" t="inlineStr"/>
-      <c r="I101" s="8" t="inlineStr"/>
-      <c r="J101" s="8" t="inlineStr"/>
-      <c r="K101" s="8" t="inlineStr"/>
-      <c r="L101" s="8" t="inlineStr"/>
-      <c r="M101" s="8" t="inlineStr"/>
+      <c r="B101" s="6" t="inlineStr">
+        <is>
+          <t>プレジール</t>
+        </is>
+      </c>
+      <c r="C101" s="6" t="inlineStr">
+        <is>
+          <t>カフェ</t>
+        </is>
+      </c>
+      <c r="D101" s="6" t="inlineStr">
+        <is>
+          <t>佐野市</t>
+        </is>
+      </c>
+      <c r="E101" s="6" t="inlineStr"/>
+      <c r="F101" s="7" t="inlineStr"/>
+      <c r="G101" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H101" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I101" s="6" t="inlineStr">
+        <is>
+          <t>地域情報サイト掲載店</t>
+        </is>
+      </c>
+      <c r="J101" s="6" t="inlineStr"/>
+      <c r="K101" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L101" s="6" t="inlineStr"/>
+      <c r="M101" s="6" t="inlineStr">
+        <is>
+          <t>古民家カフェ</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="5" t="n">
         <v>101</v>
       </c>
-      <c r="B102" s="8" t="inlineStr"/>
-      <c r="C102" s="8" t="inlineStr"/>
-      <c r="D102" s="8" t="inlineStr"/>
-      <c r="E102" s="8" t="inlineStr"/>
-      <c r="F102" s="8" t="inlineStr"/>
-      <c r="G102" s="8" t="inlineStr"/>
-      <c r="H102" s="8" t="inlineStr"/>
-      <c r="I102" s="8" t="inlineStr"/>
-      <c r="J102" s="8" t="inlineStr"/>
-      <c r="K102" s="8" t="inlineStr"/>
-      <c r="L102" s="8" t="inlineStr"/>
-      <c r="M102" s="8" t="inlineStr"/>
+      <c r="B102" s="6" t="inlineStr">
+        <is>
+          <t>こんほーと</t>
+        </is>
+      </c>
+      <c r="C102" s="6" t="inlineStr">
+        <is>
+          <t>カフェ</t>
+        </is>
+      </c>
+      <c r="D102" s="6" t="inlineStr">
+        <is>
+          <t>佐野市</t>
+        </is>
+      </c>
+      <c r="E102" s="6" t="inlineStr"/>
+      <c r="F102" s="7" t="inlineStr"/>
+      <c r="G102" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H102" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I102" s="6" t="inlineStr">
+        <is>
+          <t>地域情報サイト掲載店</t>
+        </is>
+      </c>
+      <c r="J102" s="6" t="inlineStr"/>
+      <c r="K102" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L102" s="6" t="inlineStr"/>
+      <c r="M102" s="6" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="5" t="n">
         <v>102</v>
       </c>
-      <c r="B103" s="8" t="inlineStr"/>
-      <c r="C103" s="8" t="inlineStr"/>
-      <c r="D103" s="8" t="inlineStr"/>
-      <c r="E103" s="8" t="inlineStr"/>
-      <c r="F103" s="8" t="inlineStr"/>
-      <c r="G103" s="8" t="inlineStr"/>
-      <c r="H103" s="8" t="inlineStr"/>
-      <c r="I103" s="8" t="inlineStr"/>
-      <c r="J103" s="8" t="inlineStr"/>
-      <c r="K103" s="8" t="inlineStr"/>
-      <c r="L103" s="8" t="inlineStr"/>
-      <c r="M103" s="8" t="inlineStr"/>
+      <c r="B103" s="6" t="inlineStr">
+        <is>
+          <t>神谷カフェ</t>
+        </is>
+      </c>
+      <c r="C103" s="6" t="inlineStr">
+        <is>
+          <t>カフェ</t>
+        </is>
+      </c>
+      <c r="D103" s="6" t="inlineStr">
+        <is>
+          <t>佐野市</t>
+        </is>
+      </c>
+      <c r="E103" s="6" t="inlineStr"/>
+      <c r="F103" s="7" t="inlineStr"/>
+      <c r="G103" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H103" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I103" s="6" t="inlineStr">
+        <is>
+          <t>地域情報サイト掲載店</t>
+        </is>
+      </c>
+      <c r="J103" s="6" t="inlineStr"/>
+      <c r="K103" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L103" s="6" t="inlineStr"/>
+      <c r="M103" s="6" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="5" t="n">
         <v>103</v>
       </c>
-      <c r="B104" s="8" t="inlineStr"/>
-      <c r="C104" s="8" t="inlineStr"/>
-      <c r="D104" s="8" t="inlineStr"/>
-      <c r="E104" s="8" t="inlineStr"/>
-      <c r="F104" s="8" t="inlineStr"/>
-      <c r="G104" s="8" t="inlineStr"/>
-      <c r="H104" s="8" t="inlineStr"/>
-      <c r="I104" s="8" t="inlineStr"/>
-      <c r="J104" s="8" t="inlineStr"/>
-      <c r="K104" s="8" t="inlineStr"/>
-      <c r="L104" s="8" t="inlineStr"/>
-      <c r="M104" s="8" t="inlineStr"/>
+      <c r="B104" s="6" t="inlineStr">
+        <is>
+          <t>本陣カフェ</t>
+        </is>
+      </c>
+      <c r="C104" s="6" t="inlineStr">
+        <is>
+          <t>カフェ</t>
+        </is>
+      </c>
+      <c r="D104" s="6" t="inlineStr">
+        <is>
+          <t>日光市</t>
+        </is>
+      </c>
+      <c r="E104" s="6" t="inlineStr">
+        <is>
+          <t>今市719-1・道の駅日光 日光街道ニコニコ本陣内</t>
+        </is>
+      </c>
+      <c r="F104" s="7" t="inlineStr"/>
+      <c r="G104" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H104" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I104" s="6" t="inlineStr">
+        <is>
+          <t>公式サイト</t>
+        </is>
+      </c>
+      <c r="J104" s="6" t="inlineStr"/>
+      <c r="K104" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L104" s="6" t="inlineStr"/>
+      <c r="M104" s="6" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="5" t="n">
         <v>104</v>
       </c>
-      <c r="B105" s="8" t="inlineStr"/>
-      <c r="C105" s="8" t="inlineStr"/>
-      <c r="D105" s="8" t="inlineStr"/>
-      <c r="E105" s="8" t="inlineStr"/>
-      <c r="F105" s="8" t="inlineStr"/>
-      <c r="G105" s="8" t="inlineStr"/>
-      <c r="H105" s="8" t="inlineStr"/>
-      <c r="I105" s="8" t="inlineStr"/>
-      <c r="J105" s="8" t="inlineStr"/>
-      <c r="K105" s="8" t="inlineStr"/>
-      <c r="L105" s="8" t="inlineStr"/>
-      <c r="M105" s="8" t="inlineStr"/>
+      <c r="B105" s="6" t="inlineStr">
+        <is>
+          <t>mother tool（マザーツール）</t>
+        </is>
+      </c>
+      <c r="C105" s="6" t="inlineStr">
+        <is>
+          <t>雑貨店</t>
+        </is>
+      </c>
+      <c r="D105" s="6" t="inlineStr">
+        <is>
+          <t>足利市</t>
+        </is>
+      </c>
+      <c r="E105" s="6" t="inlineStr">
+        <is>
+          <t>足利学校通り沿い</t>
+        </is>
+      </c>
+      <c r="F105" s="7" t="inlineStr"/>
+      <c r="G105" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H105" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I105" s="6" t="inlineStr">
+        <is>
+          <t>観光メディア掲載店</t>
+        </is>
+      </c>
+      <c r="J105" s="6" t="inlineStr"/>
+      <c r="K105" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L105" s="6" t="inlineStr"/>
+      <c r="M105" s="6" t="inlineStr">
+        <is>
+          <t>つくり手のものを中心にセレクトした雑貨店</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="5" t="n">
         <v>105</v>
       </c>
-      <c r="B106" s="8" t="inlineStr"/>
-      <c r="C106" s="8" t="inlineStr"/>
-      <c r="D106" s="8" t="inlineStr"/>
-      <c r="E106" s="8" t="inlineStr"/>
-      <c r="F106" s="8" t="inlineStr"/>
-      <c r="G106" s="8" t="inlineStr"/>
-      <c r="H106" s="8" t="inlineStr"/>
-      <c r="I106" s="8" t="inlineStr"/>
-      <c r="J106" s="8" t="inlineStr"/>
-      <c r="K106" s="8" t="inlineStr"/>
-      <c r="L106" s="8" t="inlineStr"/>
-      <c r="M106" s="8" t="inlineStr"/>
+      <c r="B106" s="6" t="inlineStr">
+        <is>
+          <t>緑和堂</t>
+        </is>
+      </c>
+      <c r="C106" s="6" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="D106" s="6" t="inlineStr">
+        <is>
+          <t>足利市</t>
+        </is>
+      </c>
+      <c r="E106" s="6" t="inlineStr"/>
+      <c r="F106" s="7" t="inlineStr"/>
+      <c r="G106" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H106" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I106" s="6" t="inlineStr">
+        <is>
+          <t>公式サイト</t>
+        </is>
+      </c>
+      <c r="J106" s="6" t="inlineStr"/>
+      <c r="K106" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L106" s="6" t="inlineStr"/>
+      <c r="M106" s="6" t="inlineStr">
+        <is>
+          <t>骨董品・古美術品の買取店</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="5" t="n">
@@ -4814,18 +6018,664 @@
       <c r="L108" s="8" t="inlineStr"/>
       <c r="M108" s="8" t="inlineStr"/>
     </row>
+    <row r="109">
+      <c r="A109" s="5" t="n">
+        <v>108</v>
+      </c>
+      <c r="B109" s="8" t="inlineStr"/>
+      <c r="C109" s="8" t="inlineStr"/>
+      <c r="D109" s="8" t="inlineStr"/>
+      <c r="E109" s="8" t="inlineStr"/>
+      <c r="F109" s="8" t="inlineStr"/>
+      <c r="G109" s="8" t="inlineStr"/>
+      <c r="H109" s="8" t="inlineStr"/>
+      <c r="I109" s="8" t="inlineStr"/>
+      <c r="J109" s="8" t="inlineStr"/>
+      <c r="K109" s="8" t="inlineStr"/>
+      <c r="L109" s="8" t="inlineStr"/>
+      <c r="M109" s="8" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="5" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" s="8" t="inlineStr"/>
+      <c r="C110" s="8" t="inlineStr"/>
+      <c r="D110" s="8" t="inlineStr"/>
+      <c r="E110" s="8" t="inlineStr"/>
+      <c r="F110" s="8" t="inlineStr"/>
+      <c r="G110" s="8" t="inlineStr"/>
+      <c r="H110" s="8" t="inlineStr"/>
+      <c r="I110" s="8" t="inlineStr"/>
+      <c r="J110" s="8" t="inlineStr"/>
+      <c r="K110" s="8" t="inlineStr"/>
+      <c r="L110" s="8" t="inlineStr"/>
+      <c r="M110" s="8" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="5" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" s="8" t="inlineStr"/>
+      <c r="C111" s="8" t="inlineStr"/>
+      <c r="D111" s="8" t="inlineStr"/>
+      <c r="E111" s="8" t="inlineStr"/>
+      <c r="F111" s="8" t="inlineStr"/>
+      <c r="G111" s="8" t="inlineStr"/>
+      <c r="H111" s="8" t="inlineStr"/>
+      <c r="I111" s="8" t="inlineStr"/>
+      <c r="J111" s="8" t="inlineStr"/>
+      <c r="K111" s="8" t="inlineStr"/>
+      <c r="L111" s="8" t="inlineStr"/>
+      <c r="M111" s="8" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="5" t="n">
+        <v>111</v>
+      </c>
+      <c r="B112" s="8" t="inlineStr"/>
+      <c r="C112" s="8" t="inlineStr"/>
+      <c r="D112" s="8" t="inlineStr"/>
+      <c r="E112" s="8" t="inlineStr"/>
+      <c r="F112" s="8" t="inlineStr"/>
+      <c r="G112" s="8" t="inlineStr"/>
+      <c r="H112" s="8" t="inlineStr"/>
+      <c r="I112" s="8" t="inlineStr"/>
+      <c r="J112" s="8" t="inlineStr"/>
+      <c r="K112" s="8" t="inlineStr"/>
+      <c r="L112" s="8" t="inlineStr"/>
+      <c r="M112" s="8" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="5" t="n">
+        <v>112</v>
+      </c>
+      <c r="B113" s="8" t="inlineStr"/>
+      <c r="C113" s="8" t="inlineStr"/>
+      <c r="D113" s="8" t="inlineStr"/>
+      <c r="E113" s="8" t="inlineStr"/>
+      <c r="F113" s="8" t="inlineStr"/>
+      <c r="G113" s="8" t="inlineStr"/>
+      <c r="H113" s="8" t="inlineStr"/>
+      <c r="I113" s="8" t="inlineStr"/>
+      <c r="J113" s="8" t="inlineStr"/>
+      <c r="K113" s="8" t="inlineStr"/>
+      <c r="L113" s="8" t="inlineStr"/>
+      <c r="M113" s="8" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="5" t="n">
+        <v>113</v>
+      </c>
+      <c r="B114" s="8" t="inlineStr"/>
+      <c r="C114" s="8" t="inlineStr"/>
+      <c r="D114" s="8" t="inlineStr"/>
+      <c r="E114" s="8" t="inlineStr"/>
+      <c r="F114" s="8" t="inlineStr"/>
+      <c r="G114" s="8" t="inlineStr"/>
+      <c r="H114" s="8" t="inlineStr"/>
+      <c r="I114" s="8" t="inlineStr"/>
+      <c r="J114" s="8" t="inlineStr"/>
+      <c r="K114" s="8" t="inlineStr"/>
+      <c r="L114" s="8" t="inlineStr"/>
+      <c r="M114" s="8" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="5" t="n">
+        <v>114</v>
+      </c>
+      <c r="B115" s="8" t="inlineStr"/>
+      <c r="C115" s="8" t="inlineStr"/>
+      <c r="D115" s="8" t="inlineStr"/>
+      <c r="E115" s="8" t="inlineStr"/>
+      <c r="F115" s="8" t="inlineStr"/>
+      <c r="G115" s="8" t="inlineStr"/>
+      <c r="H115" s="8" t="inlineStr"/>
+      <c r="I115" s="8" t="inlineStr"/>
+      <c r="J115" s="8" t="inlineStr"/>
+      <c r="K115" s="8" t="inlineStr"/>
+      <c r="L115" s="8" t="inlineStr"/>
+      <c r="M115" s="8" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="5" t="n">
+        <v>115</v>
+      </c>
+      <c r="B116" s="8" t="inlineStr"/>
+      <c r="C116" s="8" t="inlineStr"/>
+      <c r="D116" s="8" t="inlineStr"/>
+      <c r="E116" s="8" t="inlineStr"/>
+      <c r="F116" s="8" t="inlineStr"/>
+      <c r="G116" s="8" t="inlineStr"/>
+      <c r="H116" s="8" t="inlineStr"/>
+      <c r="I116" s="8" t="inlineStr"/>
+      <c r="J116" s="8" t="inlineStr"/>
+      <c r="K116" s="8" t="inlineStr"/>
+      <c r="L116" s="8" t="inlineStr"/>
+      <c r="M116" s="8" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="5" t="n">
+        <v>116</v>
+      </c>
+      <c r="B117" s="8" t="inlineStr"/>
+      <c r="C117" s="8" t="inlineStr"/>
+      <c r="D117" s="8" t="inlineStr"/>
+      <c r="E117" s="8" t="inlineStr"/>
+      <c r="F117" s="8" t="inlineStr"/>
+      <c r="G117" s="8" t="inlineStr"/>
+      <c r="H117" s="8" t="inlineStr"/>
+      <c r="I117" s="8" t="inlineStr"/>
+      <c r="J117" s="8" t="inlineStr"/>
+      <c r="K117" s="8" t="inlineStr"/>
+      <c r="L117" s="8" t="inlineStr"/>
+      <c r="M117" s="8" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="5" t="n">
+        <v>117</v>
+      </c>
+      <c r="B118" s="8" t="inlineStr"/>
+      <c r="C118" s="8" t="inlineStr"/>
+      <c r="D118" s="8" t="inlineStr"/>
+      <c r="E118" s="8" t="inlineStr"/>
+      <c r="F118" s="8" t="inlineStr"/>
+      <c r="G118" s="8" t="inlineStr"/>
+      <c r="H118" s="8" t="inlineStr"/>
+      <c r="I118" s="8" t="inlineStr"/>
+      <c r="J118" s="8" t="inlineStr"/>
+      <c r="K118" s="8" t="inlineStr"/>
+      <c r="L118" s="8" t="inlineStr"/>
+      <c r="M118" s="8" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="5" t="n">
+        <v>118</v>
+      </c>
+      <c r="B119" s="8" t="inlineStr"/>
+      <c r="C119" s="8" t="inlineStr"/>
+      <c r="D119" s="8" t="inlineStr"/>
+      <c r="E119" s="8" t="inlineStr"/>
+      <c r="F119" s="8" t="inlineStr"/>
+      <c r="G119" s="8" t="inlineStr"/>
+      <c r="H119" s="8" t="inlineStr"/>
+      <c r="I119" s="8" t="inlineStr"/>
+      <c r="J119" s="8" t="inlineStr"/>
+      <c r="K119" s="8" t="inlineStr"/>
+      <c r="L119" s="8" t="inlineStr"/>
+      <c r="M119" s="8" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="5" t="n">
+        <v>119</v>
+      </c>
+      <c r="B120" s="8" t="inlineStr"/>
+      <c r="C120" s="8" t="inlineStr"/>
+      <c r="D120" s="8" t="inlineStr"/>
+      <c r="E120" s="8" t="inlineStr"/>
+      <c r="F120" s="8" t="inlineStr"/>
+      <c r="G120" s="8" t="inlineStr"/>
+      <c r="H120" s="8" t="inlineStr"/>
+      <c r="I120" s="8" t="inlineStr"/>
+      <c r="J120" s="8" t="inlineStr"/>
+      <c r="K120" s="8" t="inlineStr"/>
+      <c r="L120" s="8" t="inlineStr"/>
+      <c r="M120" s="8" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="5" t="n">
+        <v>120</v>
+      </c>
+      <c r="B121" s="8" t="inlineStr"/>
+      <c r="C121" s="8" t="inlineStr"/>
+      <c r="D121" s="8" t="inlineStr"/>
+      <c r="E121" s="8" t="inlineStr"/>
+      <c r="F121" s="8" t="inlineStr"/>
+      <c r="G121" s="8" t="inlineStr"/>
+      <c r="H121" s="8" t="inlineStr"/>
+      <c r="I121" s="8" t="inlineStr"/>
+      <c r="J121" s="8" t="inlineStr"/>
+      <c r="K121" s="8" t="inlineStr"/>
+      <c r="L121" s="8" t="inlineStr"/>
+      <c r="M121" s="8" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="5" t="n">
+        <v>121</v>
+      </c>
+      <c r="B122" s="8" t="inlineStr"/>
+      <c r="C122" s="8" t="inlineStr"/>
+      <c r="D122" s="8" t="inlineStr"/>
+      <c r="E122" s="8" t="inlineStr"/>
+      <c r="F122" s="8" t="inlineStr"/>
+      <c r="G122" s="8" t="inlineStr"/>
+      <c r="H122" s="8" t="inlineStr"/>
+      <c r="I122" s="8" t="inlineStr"/>
+      <c r="J122" s="8" t="inlineStr"/>
+      <c r="K122" s="8" t="inlineStr"/>
+      <c r="L122" s="8" t="inlineStr"/>
+      <c r="M122" s="8" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="5" t="n">
+        <v>122</v>
+      </c>
+      <c r="B123" s="8" t="inlineStr"/>
+      <c r="C123" s="8" t="inlineStr"/>
+      <c r="D123" s="8" t="inlineStr"/>
+      <c r="E123" s="8" t="inlineStr"/>
+      <c r="F123" s="8" t="inlineStr"/>
+      <c r="G123" s="8" t="inlineStr"/>
+      <c r="H123" s="8" t="inlineStr"/>
+      <c r="I123" s="8" t="inlineStr"/>
+      <c r="J123" s="8" t="inlineStr"/>
+      <c r="K123" s="8" t="inlineStr"/>
+      <c r="L123" s="8" t="inlineStr"/>
+      <c r="M123" s="8" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="5" t="n">
+        <v>123</v>
+      </c>
+      <c r="B124" s="8" t="inlineStr"/>
+      <c r="C124" s="8" t="inlineStr"/>
+      <c r="D124" s="8" t="inlineStr"/>
+      <c r="E124" s="8" t="inlineStr"/>
+      <c r="F124" s="8" t="inlineStr"/>
+      <c r="G124" s="8" t="inlineStr"/>
+      <c r="H124" s="8" t="inlineStr"/>
+      <c r="I124" s="8" t="inlineStr"/>
+      <c r="J124" s="8" t="inlineStr"/>
+      <c r="K124" s="8" t="inlineStr"/>
+      <c r="L124" s="8" t="inlineStr"/>
+      <c r="M124" s="8" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="5" t="n">
+        <v>124</v>
+      </c>
+      <c r="B125" s="8" t="inlineStr"/>
+      <c r="C125" s="8" t="inlineStr"/>
+      <c r="D125" s="8" t="inlineStr"/>
+      <c r="E125" s="8" t="inlineStr"/>
+      <c r="F125" s="8" t="inlineStr"/>
+      <c r="G125" s="8" t="inlineStr"/>
+      <c r="H125" s="8" t="inlineStr"/>
+      <c r="I125" s="8" t="inlineStr"/>
+      <c r="J125" s="8" t="inlineStr"/>
+      <c r="K125" s="8" t="inlineStr"/>
+      <c r="L125" s="8" t="inlineStr"/>
+      <c r="M125" s="8" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="5" t="n">
+        <v>125</v>
+      </c>
+      <c r="B126" s="8" t="inlineStr"/>
+      <c r="C126" s="8" t="inlineStr"/>
+      <c r="D126" s="8" t="inlineStr"/>
+      <c r="E126" s="8" t="inlineStr"/>
+      <c r="F126" s="8" t="inlineStr"/>
+      <c r="G126" s="8" t="inlineStr"/>
+      <c r="H126" s="8" t="inlineStr"/>
+      <c r="I126" s="8" t="inlineStr"/>
+      <c r="J126" s="8" t="inlineStr"/>
+      <c r="K126" s="8" t="inlineStr"/>
+      <c r="L126" s="8" t="inlineStr"/>
+      <c r="M126" s="8" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="5" t="n">
+        <v>126</v>
+      </c>
+      <c r="B127" s="8" t="inlineStr"/>
+      <c r="C127" s="8" t="inlineStr"/>
+      <c r="D127" s="8" t="inlineStr"/>
+      <c r="E127" s="8" t="inlineStr"/>
+      <c r="F127" s="8" t="inlineStr"/>
+      <c r="G127" s="8" t="inlineStr"/>
+      <c r="H127" s="8" t="inlineStr"/>
+      <c r="I127" s="8" t="inlineStr"/>
+      <c r="J127" s="8" t="inlineStr"/>
+      <c r="K127" s="8" t="inlineStr"/>
+      <c r="L127" s="8" t="inlineStr"/>
+      <c r="M127" s="8" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="5" t="n">
+        <v>127</v>
+      </c>
+      <c r="B128" s="8" t="inlineStr"/>
+      <c r="C128" s="8" t="inlineStr"/>
+      <c r="D128" s="8" t="inlineStr"/>
+      <c r="E128" s="8" t="inlineStr"/>
+      <c r="F128" s="8" t="inlineStr"/>
+      <c r="G128" s="8" t="inlineStr"/>
+      <c r="H128" s="8" t="inlineStr"/>
+      <c r="I128" s="8" t="inlineStr"/>
+      <c r="J128" s="8" t="inlineStr"/>
+      <c r="K128" s="8" t="inlineStr"/>
+      <c r="L128" s="8" t="inlineStr"/>
+      <c r="M128" s="8" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="5" t="n">
+        <v>128</v>
+      </c>
+      <c r="B129" s="8" t="inlineStr"/>
+      <c r="C129" s="8" t="inlineStr"/>
+      <c r="D129" s="8" t="inlineStr"/>
+      <c r="E129" s="8" t="inlineStr"/>
+      <c r="F129" s="8" t="inlineStr"/>
+      <c r="G129" s="8" t="inlineStr"/>
+      <c r="H129" s="8" t="inlineStr"/>
+      <c r="I129" s="8" t="inlineStr"/>
+      <c r="J129" s="8" t="inlineStr"/>
+      <c r="K129" s="8" t="inlineStr"/>
+      <c r="L129" s="8" t="inlineStr"/>
+      <c r="M129" s="8" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="5" t="n">
+        <v>129</v>
+      </c>
+      <c r="B130" s="8" t="inlineStr"/>
+      <c r="C130" s="8" t="inlineStr"/>
+      <c r="D130" s="8" t="inlineStr"/>
+      <c r="E130" s="8" t="inlineStr"/>
+      <c r="F130" s="8" t="inlineStr"/>
+      <c r="G130" s="8" t="inlineStr"/>
+      <c r="H130" s="8" t="inlineStr"/>
+      <c r="I130" s="8" t="inlineStr"/>
+      <c r="J130" s="8" t="inlineStr"/>
+      <c r="K130" s="8" t="inlineStr"/>
+      <c r="L130" s="8" t="inlineStr"/>
+      <c r="M130" s="8" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="5" t="n">
+        <v>130</v>
+      </c>
+      <c r="B131" s="8" t="inlineStr"/>
+      <c r="C131" s="8" t="inlineStr"/>
+      <c r="D131" s="8" t="inlineStr"/>
+      <c r="E131" s="8" t="inlineStr"/>
+      <c r="F131" s="8" t="inlineStr"/>
+      <c r="G131" s="8" t="inlineStr"/>
+      <c r="H131" s="8" t="inlineStr"/>
+      <c r="I131" s="8" t="inlineStr"/>
+      <c r="J131" s="8" t="inlineStr"/>
+      <c r="K131" s="8" t="inlineStr"/>
+      <c r="L131" s="8" t="inlineStr"/>
+      <c r="M131" s="8" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="5" t="n">
+        <v>131</v>
+      </c>
+      <c r="B132" s="8" t="inlineStr"/>
+      <c r="C132" s="8" t="inlineStr"/>
+      <c r="D132" s="8" t="inlineStr"/>
+      <c r="E132" s="8" t="inlineStr"/>
+      <c r="F132" s="8" t="inlineStr"/>
+      <c r="G132" s="8" t="inlineStr"/>
+      <c r="H132" s="8" t="inlineStr"/>
+      <c r="I132" s="8" t="inlineStr"/>
+      <c r="J132" s="8" t="inlineStr"/>
+      <c r="K132" s="8" t="inlineStr"/>
+      <c r="L132" s="8" t="inlineStr"/>
+      <c r="M132" s="8" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="5" t="n">
+        <v>132</v>
+      </c>
+      <c r="B133" s="8" t="inlineStr"/>
+      <c r="C133" s="8" t="inlineStr"/>
+      <c r="D133" s="8" t="inlineStr"/>
+      <c r="E133" s="8" t="inlineStr"/>
+      <c r="F133" s="8" t="inlineStr"/>
+      <c r="G133" s="8" t="inlineStr"/>
+      <c r="H133" s="8" t="inlineStr"/>
+      <c r="I133" s="8" t="inlineStr"/>
+      <c r="J133" s="8" t="inlineStr"/>
+      <c r="K133" s="8" t="inlineStr"/>
+      <c r="L133" s="8" t="inlineStr"/>
+      <c r="M133" s="8" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="5" t="n">
+        <v>133</v>
+      </c>
+      <c r="B134" s="8" t="inlineStr"/>
+      <c r="C134" s="8" t="inlineStr"/>
+      <c r="D134" s="8" t="inlineStr"/>
+      <c r="E134" s="8" t="inlineStr"/>
+      <c r="F134" s="8" t="inlineStr"/>
+      <c r="G134" s="8" t="inlineStr"/>
+      <c r="H134" s="8" t="inlineStr"/>
+      <c r="I134" s="8" t="inlineStr"/>
+      <c r="J134" s="8" t="inlineStr"/>
+      <c r="K134" s="8" t="inlineStr"/>
+      <c r="L134" s="8" t="inlineStr"/>
+      <c r="M134" s="8" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="5" t="n">
+        <v>134</v>
+      </c>
+      <c r="B135" s="8" t="inlineStr"/>
+      <c r="C135" s="8" t="inlineStr"/>
+      <c r="D135" s="8" t="inlineStr"/>
+      <c r="E135" s="8" t="inlineStr"/>
+      <c r="F135" s="8" t="inlineStr"/>
+      <c r="G135" s="8" t="inlineStr"/>
+      <c r="H135" s="8" t="inlineStr"/>
+      <c r="I135" s="8" t="inlineStr"/>
+      <c r="J135" s="8" t="inlineStr"/>
+      <c r="K135" s="8" t="inlineStr"/>
+      <c r="L135" s="8" t="inlineStr"/>
+      <c r="M135" s="8" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="5" t="n">
+        <v>135</v>
+      </c>
+      <c r="B136" s="8" t="inlineStr"/>
+      <c r="C136" s="8" t="inlineStr"/>
+      <c r="D136" s="8" t="inlineStr"/>
+      <c r="E136" s="8" t="inlineStr"/>
+      <c r="F136" s="8" t="inlineStr"/>
+      <c r="G136" s="8" t="inlineStr"/>
+      <c r="H136" s="8" t="inlineStr"/>
+      <c r="I136" s="8" t="inlineStr"/>
+      <c r="J136" s="8" t="inlineStr"/>
+      <c r="K136" s="8" t="inlineStr"/>
+      <c r="L136" s="8" t="inlineStr"/>
+      <c r="M136" s="8" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="5" t="n">
+        <v>136</v>
+      </c>
+      <c r="B137" s="8" t="inlineStr"/>
+      <c r="C137" s="8" t="inlineStr"/>
+      <c r="D137" s="8" t="inlineStr"/>
+      <c r="E137" s="8" t="inlineStr"/>
+      <c r="F137" s="8" t="inlineStr"/>
+      <c r="G137" s="8" t="inlineStr"/>
+      <c r="H137" s="8" t="inlineStr"/>
+      <c r="I137" s="8" t="inlineStr"/>
+      <c r="J137" s="8" t="inlineStr"/>
+      <c r="K137" s="8" t="inlineStr"/>
+      <c r="L137" s="8" t="inlineStr"/>
+      <c r="M137" s="8" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="5" t="n">
+        <v>137</v>
+      </c>
+      <c r="B138" s="8" t="inlineStr"/>
+      <c r="C138" s="8" t="inlineStr"/>
+      <c r="D138" s="8" t="inlineStr"/>
+      <c r="E138" s="8" t="inlineStr"/>
+      <c r="F138" s="8" t="inlineStr"/>
+      <c r="G138" s="8" t="inlineStr"/>
+      <c r="H138" s="8" t="inlineStr"/>
+      <c r="I138" s="8" t="inlineStr"/>
+      <c r="J138" s="8" t="inlineStr"/>
+      <c r="K138" s="8" t="inlineStr"/>
+      <c r="L138" s="8" t="inlineStr"/>
+      <c r="M138" s="8" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="5" t="n">
+        <v>138</v>
+      </c>
+      <c r="B139" s="8" t="inlineStr"/>
+      <c r="C139" s="8" t="inlineStr"/>
+      <c r="D139" s="8" t="inlineStr"/>
+      <c r="E139" s="8" t="inlineStr"/>
+      <c r="F139" s="8" t="inlineStr"/>
+      <c r="G139" s="8" t="inlineStr"/>
+      <c r="H139" s="8" t="inlineStr"/>
+      <c r="I139" s="8" t="inlineStr"/>
+      <c r="J139" s="8" t="inlineStr"/>
+      <c r="K139" s="8" t="inlineStr"/>
+      <c r="L139" s="8" t="inlineStr"/>
+      <c r="M139" s="8" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="5" t="n">
+        <v>139</v>
+      </c>
+      <c r="B140" s="8" t="inlineStr"/>
+      <c r="C140" s="8" t="inlineStr"/>
+      <c r="D140" s="8" t="inlineStr"/>
+      <c r="E140" s="8" t="inlineStr"/>
+      <c r="F140" s="8" t="inlineStr"/>
+      <c r="G140" s="8" t="inlineStr"/>
+      <c r="H140" s="8" t="inlineStr"/>
+      <c r="I140" s="8" t="inlineStr"/>
+      <c r="J140" s="8" t="inlineStr"/>
+      <c r="K140" s="8" t="inlineStr"/>
+      <c r="L140" s="8" t="inlineStr"/>
+      <c r="M140" s="8" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="5" t="n">
+        <v>140</v>
+      </c>
+      <c r="B141" s="8" t="inlineStr"/>
+      <c r="C141" s="8" t="inlineStr"/>
+      <c r="D141" s="8" t="inlineStr"/>
+      <c r="E141" s="8" t="inlineStr"/>
+      <c r="F141" s="8" t="inlineStr"/>
+      <c r="G141" s="8" t="inlineStr"/>
+      <c r="H141" s="8" t="inlineStr"/>
+      <c r="I141" s="8" t="inlineStr"/>
+      <c r="J141" s="8" t="inlineStr"/>
+      <c r="K141" s="8" t="inlineStr"/>
+      <c r="L141" s="8" t="inlineStr"/>
+      <c r="M141" s="8" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="5" t="n">
+        <v>141</v>
+      </c>
+      <c r="B142" s="8" t="inlineStr"/>
+      <c r="C142" s="8" t="inlineStr"/>
+      <c r="D142" s="8" t="inlineStr"/>
+      <c r="E142" s="8" t="inlineStr"/>
+      <c r="F142" s="8" t="inlineStr"/>
+      <c r="G142" s="8" t="inlineStr"/>
+      <c r="H142" s="8" t="inlineStr"/>
+      <c r="I142" s="8" t="inlineStr"/>
+      <c r="J142" s="8" t="inlineStr"/>
+      <c r="K142" s="8" t="inlineStr"/>
+      <c r="L142" s="8" t="inlineStr"/>
+      <c r="M142" s="8" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="5" t="n">
+        <v>142</v>
+      </c>
+      <c r="B143" s="8" t="inlineStr"/>
+      <c r="C143" s="8" t="inlineStr"/>
+      <c r="D143" s="8" t="inlineStr"/>
+      <c r="E143" s="8" t="inlineStr"/>
+      <c r="F143" s="8" t="inlineStr"/>
+      <c r="G143" s="8" t="inlineStr"/>
+      <c r="H143" s="8" t="inlineStr"/>
+      <c r="I143" s="8" t="inlineStr"/>
+      <c r="J143" s="8" t="inlineStr"/>
+      <c r="K143" s="8" t="inlineStr"/>
+      <c r="L143" s="8" t="inlineStr"/>
+      <c r="M143" s="8" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="5" t="n">
+        <v>143</v>
+      </c>
+      <c r="B144" s="8" t="inlineStr"/>
+      <c r="C144" s="8" t="inlineStr"/>
+      <c r="D144" s="8" t="inlineStr"/>
+      <c r="E144" s="8" t="inlineStr"/>
+      <c r="F144" s="8" t="inlineStr"/>
+      <c r="G144" s="8" t="inlineStr"/>
+      <c r="H144" s="8" t="inlineStr"/>
+      <c r="I144" s="8" t="inlineStr"/>
+      <c r="J144" s="8" t="inlineStr"/>
+      <c r="K144" s="8" t="inlineStr"/>
+      <c r="L144" s="8" t="inlineStr"/>
+      <c r="M144" s="8" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="5" t="n">
+        <v>144</v>
+      </c>
+      <c r="B145" s="8" t="inlineStr"/>
+      <c r="C145" s="8" t="inlineStr"/>
+      <c r="D145" s="8" t="inlineStr"/>
+      <c r="E145" s="8" t="inlineStr"/>
+      <c r="F145" s="8" t="inlineStr"/>
+      <c r="G145" s="8" t="inlineStr"/>
+      <c r="H145" s="8" t="inlineStr"/>
+      <c r="I145" s="8" t="inlineStr"/>
+      <c r="J145" s="8" t="inlineStr"/>
+      <c r="K145" s="8" t="inlineStr"/>
+      <c r="L145" s="8" t="inlineStr"/>
+      <c r="M145" s="8" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="5" t="n">
+        <v>145</v>
+      </c>
+      <c r="B146" s="8" t="inlineStr"/>
+      <c r="C146" s="8" t="inlineStr"/>
+      <c r="D146" s="8" t="inlineStr"/>
+      <c r="E146" s="8" t="inlineStr"/>
+      <c r="F146" s="8" t="inlineStr"/>
+      <c r="G146" s="8" t="inlineStr"/>
+      <c r="H146" s="8" t="inlineStr"/>
+      <c r="I146" s="8" t="inlineStr"/>
+      <c r="J146" s="8" t="inlineStr"/>
+      <c r="K146" s="8" t="inlineStr"/>
+      <c r="L146" s="8" t="inlineStr"/>
+      <c r="M146" s="8" t="inlineStr"/>
+    </row>
   </sheetData>
   <dataValidations count="4">
-    <dataValidation sqref="C2:C108" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"カフェ,飲食店,和菓子店,雑貨店,陶器店・ギャラリー,土産店,美容室,理容室,その他"</formula1>
+    <dataValidation sqref="C2:C146" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"カフェ,飲食店,和菓子店,雑貨店,陶器店・ギャラリー,工芸品店,土産店,パン屋,美容室,理容室,その他"</formula1>
     </dataValidation>
-    <dataValidation sqref="D2:D108" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"栃木市,益子町,那須町,日光市,宇都宮市,足利市,佐野市,小山市,鹿沼市,那須塩原市,真岡市,大田原市,壬生町,那珂川町,那須烏山市,矢板市,茂木町,下野市,野木町,高根沢町,芳賀町,塩谷町,その他"</formula1>
+    <dataValidation sqref="D2:D146" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"栃木市,益子町,那須町,日光市,宇都宮市,足利市,佐野市,小山市,鹿沼市,那須塩原市,真岡市,大田原市,壬生町,那珂川町,那須烏山市,矢板市,茂木町,下野市,野木町,高根沢町,芳賀町,塩谷町,さくら市,上三川町,その他"</formula1>
     </dataValidation>
-    <dataValidation sqref="K2:K108" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K2:K146" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"未架電,不在,拒否,資料送付OK,アポ確定,見送り"</formula1>
     </dataValidation>
-    <dataValidation sqref="H2:H108" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H2:H146" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"不明,あり（古い）,あり（最近）,なし"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4839,7 +6689,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:D32"/>
+  <dimension ref="B2:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="2" max="2"/>
@@ -4860,7 +6710,7 @@
         </is>
       </c>
       <c r="D4" s="2">
-        <f>COUNTIF(架電リスト!B2:B108,"?*")</f>
+        <f>COUNTIF(架電リスト!B2:B146,"?*")</f>
         <v/>
       </c>
     </row>
@@ -4871,7 +6721,7 @@
         </is>
       </c>
       <c r="D5" s="2">
-        <f>COUNTIFS(架電リスト!K2:K108,"&lt;&gt;未架電",架電リスト!K2:K108,"&lt;&gt;")</f>
+        <f>COUNTIFS(架電リスト!K2:K146,"&lt;&gt;未架電",架電リスト!K2:K146,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -4882,7 +6732,7 @@
         </is>
       </c>
       <c r="D6" s="2">
-        <f>COUNTIF(架電リスト!K2:K108,"資料送付OK")</f>
+        <f>COUNTIF(架電リスト!K2:K146,"資料送付OK")</f>
         <v/>
       </c>
     </row>
@@ -4893,7 +6743,7 @@
         </is>
       </c>
       <c r="D7" s="2">
-        <f>COUNTIF(架電リスト!K2:K108,"アポ確定")</f>
+        <f>COUNTIF(架電リスト!K2:K146,"アポ確定")</f>
         <v/>
       </c>
     </row>
@@ -4922,7 +6772,7 @@
         </is>
       </c>
       <c r="D11" s="10">
-        <f>COUNTIF(架電リスト!D2:D108,"栃木市")</f>
+        <f>COUNTIF(架電リスト!D2:D146,"栃木市")</f>
         <v/>
       </c>
     </row>
@@ -4933,7 +6783,7 @@
         </is>
       </c>
       <c r="D12" s="10">
-        <f>COUNTIF(架電リスト!D2:D108,"益子町")</f>
+        <f>COUNTIF(架電リスト!D2:D146,"益子町")</f>
         <v/>
       </c>
     </row>
@@ -4944,7 +6794,7 @@
         </is>
       </c>
       <c r="D13" s="10">
-        <f>COUNTIF(架電リスト!D2:D108,"那須町")</f>
+        <f>COUNTIF(架電リスト!D2:D146,"那須町")</f>
         <v/>
       </c>
     </row>
@@ -4955,7 +6805,7 @@
         </is>
       </c>
       <c r="D14" s="10">
-        <f>COUNTIF(架電リスト!D2:D108,"日光市")</f>
+        <f>COUNTIF(架電リスト!D2:D146,"日光市")</f>
         <v/>
       </c>
     </row>
@@ -4966,7 +6816,7 @@
         </is>
       </c>
       <c r="D15" s="10">
-        <f>COUNTIF(架電リスト!D2:D108,"宇都宮市")</f>
+        <f>COUNTIF(架電リスト!D2:D146,"宇都宮市")</f>
         <v/>
       </c>
     </row>
@@ -4977,7 +6827,7 @@
         </is>
       </c>
       <c r="D16" s="10">
-        <f>COUNTIF(架電リスト!D2:D108,"足利市")</f>
+        <f>COUNTIF(架電リスト!D2:D146,"足利市")</f>
         <v/>
       </c>
     </row>
@@ -4988,7 +6838,7 @@
         </is>
       </c>
       <c r="D17" s="10">
-        <f>COUNTIF(架電リスト!D2:D108,"佐野市")</f>
+        <f>COUNTIF(架電リスト!D2:D146,"佐野市")</f>
         <v/>
       </c>
     </row>
@@ -4999,7 +6849,7 @@
         </is>
       </c>
       <c r="D18" s="10">
-        <f>COUNTIF(架電リスト!D2:D108,"小山市")</f>
+        <f>COUNTIF(架電リスト!D2:D146,"小山市")</f>
         <v/>
       </c>
     </row>
@@ -5010,7 +6860,7 @@
         </is>
       </c>
       <c r="D19" s="10">
-        <f>COUNTIF(架電リスト!D2:D108,"鹿沼市")</f>
+        <f>COUNTIF(架電リスト!D2:D146,"鹿沼市")</f>
         <v/>
       </c>
     </row>
@@ -5021,7 +6871,7 @@
         </is>
       </c>
       <c r="D20" s="10">
-        <f>COUNTIF(架電リスト!D2:D108,"那須塩原市")</f>
+        <f>COUNTIF(架電リスト!D2:D146,"那須塩原市")</f>
         <v/>
       </c>
     </row>
@@ -5032,7 +6882,7 @@
         </is>
       </c>
       <c r="D21" s="10">
-        <f>COUNTIF(架電リスト!D2:D108,"真岡市")</f>
+        <f>COUNTIF(架電リスト!D2:D146,"真岡市")</f>
         <v/>
       </c>
     </row>
@@ -5043,7 +6893,7 @@
         </is>
       </c>
       <c r="D22" s="10">
-        <f>COUNTIF(架電リスト!D2:D108,"大田原市")</f>
+        <f>COUNTIF(架電リスト!D2:D146,"大田原市")</f>
         <v/>
       </c>
     </row>
@@ -5054,7 +6904,7 @@
         </is>
       </c>
       <c r="D23" s="10">
-        <f>COUNTIF(架電リスト!D2:D108,"壬生町")</f>
+        <f>COUNTIF(架電リスト!D2:D146,"壬生町")</f>
         <v/>
       </c>
     </row>
@@ -5065,7 +6915,7 @@
         </is>
       </c>
       <c r="D24" s="10">
-        <f>COUNTIF(架電リスト!D2:D108,"那珂川町")</f>
+        <f>COUNTIF(架電リスト!D2:D146,"那珂川町")</f>
         <v/>
       </c>
     </row>
@@ -5076,7 +6926,7 @@
         </is>
       </c>
       <c r="D25" s="10">
-        <f>COUNTIF(架電リスト!D2:D108,"那須烏山市")</f>
+        <f>COUNTIF(架電リスト!D2:D146,"那須烏山市")</f>
         <v/>
       </c>
     </row>
@@ -5087,7 +6937,7 @@
         </is>
       </c>
       <c r="D26" s="10">
-        <f>COUNTIF(架電リスト!D2:D108,"矢板市")</f>
+        <f>COUNTIF(架電リスト!D2:D146,"矢板市")</f>
         <v/>
       </c>
     </row>
@@ -5098,7 +6948,7 @@
         </is>
       </c>
       <c r="D27" s="10">
-        <f>COUNTIF(架電リスト!D2:D108,"茂木町")</f>
+        <f>COUNTIF(架電リスト!D2:D146,"茂木町")</f>
         <v/>
       </c>
     </row>
@@ -5109,7 +6959,7 @@
         </is>
       </c>
       <c r="D28" s="10">
-        <f>COUNTIF(架電リスト!D2:D108,"下野市")</f>
+        <f>COUNTIF(架電リスト!D2:D146,"下野市")</f>
         <v/>
       </c>
     </row>
@@ -5120,7 +6970,7 @@
         </is>
       </c>
       <c r="D29" s="10">
-        <f>COUNTIF(架電リスト!D2:D108,"野木町")</f>
+        <f>COUNTIF(架電リスト!D2:D146,"野木町")</f>
         <v/>
       </c>
     </row>
@@ -5131,7 +6981,7 @@
         </is>
       </c>
       <c r="D30" s="10">
-        <f>COUNTIF(架電リスト!D2:D108,"高根沢町")</f>
+        <f>COUNTIF(架電リスト!D2:D146,"高根沢町")</f>
         <v/>
       </c>
     </row>
@@ -5142,7 +6992,7 @@
         </is>
       </c>
       <c r="D31" s="10">
-        <f>COUNTIF(架電リスト!D2:D108,"芳賀町")</f>
+        <f>COUNTIF(架電リスト!D2:D146,"芳賀町")</f>
         <v/>
       </c>
     </row>
@@ -5153,7 +7003,29 @@
         </is>
       </c>
       <c r="D32" s="10">
-        <f>COUNTIF(架電リスト!D2:D108,"塩谷町")</f>
+        <f>COUNTIF(架電リスト!D2:D146,"塩谷町")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>さくら市</t>
+        </is>
+      </c>
+      <c r="D33" s="10">
+        <f>COUNTIF(架電リスト!D2:D146,"さくら市")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>上三川町</t>
+        </is>
+      </c>
+      <c r="D34" s="10">
+        <f>COUNTIF(架電リスト!D2:D146,"上三川町")</f>
         <v/>
       </c>
     </row>

--- a/projects/tel-appo/call-list.xlsx
+++ b/projects/tel-appo/call-list.xlsx
@@ -626,7 +626,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M146"/>
+  <dimension ref="A1:M238"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -5988,694 +5988,5474 @@
       <c r="A107" s="5" t="n">
         <v>106</v>
       </c>
-      <c r="B107" s="8" t="inlineStr"/>
-      <c r="C107" s="8" t="inlineStr"/>
-      <c r="D107" s="8" t="inlineStr"/>
-      <c r="E107" s="8" t="inlineStr"/>
-      <c r="F107" s="8" t="inlineStr"/>
-      <c r="G107" s="8" t="inlineStr"/>
-      <c r="H107" s="8" t="inlineStr"/>
-      <c r="I107" s="8" t="inlineStr"/>
-      <c r="J107" s="8" t="inlineStr"/>
-      <c r="K107" s="8" t="inlineStr"/>
-      <c r="L107" s="8" t="inlineStr"/>
-      <c r="M107" s="8" t="inlineStr"/>
+      <c r="B107" s="6" t="inlineStr">
+        <is>
+          <t>マギー美容室</t>
+        </is>
+      </c>
+      <c r="C107" s="6" t="inlineStr">
+        <is>
+          <t>美容室</t>
+        </is>
+      </c>
+      <c r="D107" s="6" t="inlineStr">
+        <is>
+          <t>栃木市</t>
+        </is>
+      </c>
+      <c r="E107" s="6" t="inlineStr"/>
+      <c r="F107" s="6" t="inlineStr">
+        <is>
+          <t>0282-27-0421</t>
+        </is>
+      </c>
+      <c r="G107" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H107" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I107" s="6" t="inlineStr">
+        <is>
+          <t>NAVITIME 電話帳</t>
+        </is>
+      </c>
+      <c r="J107" s="6" t="inlineStr"/>
+      <c r="K107" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L107" s="6" t="inlineStr"/>
+      <c r="M107" s="6" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="5" t="n">
         <v>107</v>
       </c>
-      <c r="B108" s="8" t="inlineStr"/>
-      <c r="C108" s="8" t="inlineStr"/>
-      <c r="D108" s="8" t="inlineStr"/>
-      <c r="E108" s="8" t="inlineStr"/>
-      <c r="F108" s="8" t="inlineStr"/>
-      <c r="G108" s="8" t="inlineStr"/>
-      <c r="H108" s="8" t="inlineStr"/>
-      <c r="I108" s="8" t="inlineStr"/>
-      <c r="J108" s="8" t="inlineStr"/>
-      <c r="K108" s="8" t="inlineStr"/>
-      <c r="L108" s="8" t="inlineStr"/>
-      <c r="M108" s="8" t="inlineStr"/>
+      <c r="B108" s="6" t="inlineStr">
+        <is>
+          <t>サロンドムーラン</t>
+        </is>
+      </c>
+      <c r="C108" s="6" t="inlineStr">
+        <is>
+          <t>美容室</t>
+        </is>
+      </c>
+      <c r="D108" s="6" t="inlineStr">
+        <is>
+          <t>栃木市</t>
+        </is>
+      </c>
+      <c r="E108" s="6" t="inlineStr"/>
+      <c r="F108" s="6" t="inlineStr">
+        <is>
+          <t>0282-22-3250</t>
+        </is>
+      </c>
+      <c r="G108" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H108" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I108" s="6" t="inlineStr">
+        <is>
+          <t>NAVITIME 電話帳</t>
+        </is>
+      </c>
+      <c r="J108" s="6" t="inlineStr"/>
+      <c r="K108" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L108" s="6" t="inlineStr"/>
+      <c r="M108" s="6" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="5" t="n">
         <v>108</v>
       </c>
-      <c r="B109" s="8" t="inlineStr"/>
-      <c r="C109" s="8" t="inlineStr"/>
-      <c r="D109" s="8" t="inlineStr"/>
-      <c r="E109" s="8" t="inlineStr"/>
-      <c r="F109" s="8" t="inlineStr"/>
-      <c r="G109" s="8" t="inlineStr"/>
-      <c r="H109" s="8" t="inlineStr"/>
-      <c r="I109" s="8" t="inlineStr"/>
-      <c r="J109" s="8" t="inlineStr"/>
-      <c r="K109" s="8" t="inlineStr"/>
-      <c r="L109" s="8" t="inlineStr"/>
-      <c r="M109" s="8" t="inlineStr"/>
+      <c r="B109" s="6" t="inlineStr">
+        <is>
+          <t>八重美容室</t>
+        </is>
+      </c>
+      <c r="C109" s="6" t="inlineStr">
+        <is>
+          <t>美容室</t>
+        </is>
+      </c>
+      <c r="D109" s="6" t="inlineStr">
+        <is>
+          <t>栃木市</t>
+        </is>
+      </c>
+      <c r="E109" s="6" t="inlineStr"/>
+      <c r="F109" s="6" t="inlineStr">
+        <is>
+          <t>0282-23-0387</t>
+        </is>
+      </c>
+      <c r="G109" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H109" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I109" s="6" t="inlineStr">
+        <is>
+          <t>NAVITIME 電話帳</t>
+        </is>
+      </c>
+      <c r="J109" s="6" t="inlineStr"/>
+      <c r="K109" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L109" s="6" t="inlineStr"/>
+      <c r="M109" s="6" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="5" t="n">
         <v>109</v>
       </c>
-      <c r="B110" s="8" t="inlineStr"/>
-      <c r="C110" s="8" t="inlineStr"/>
-      <c r="D110" s="8" t="inlineStr"/>
-      <c r="E110" s="8" t="inlineStr"/>
-      <c r="F110" s="8" t="inlineStr"/>
-      <c r="G110" s="8" t="inlineStr"/>
-      <c r="H110" s="8" t="inlineStr"/>
-      <c r="I110" s="8" t="inlineStr"/>
-      <c r="J110" s="8" t="inlineStr"/>
-      <c r="K110" s="8" t="inlineStr"/>
-      <c r="L110" s="8" t="inlineStr"/>
-      <c r="M110" s="8" t="inlineStr"/>
+      <c r="B110" s="6" t="inlineStr">
+        <is>
+          <t>ラ・スール美容室</t>
+        </is>
+      </c>
+      <c r="C110" s="6" t="inlineStr">
+        <is>
+          <t>美容室</t>
+        </is>
+      </c>
+      <c r="D110" s="6" t="inlineStr">
+        <is>
+          <t>栃木市</t>
+        </is>
+      </c>
+      <c r="E110" s="6" t="inlineStr"/>
+      <c r="F110" s="6" t="inlineStr">
+        <is>
+          <t>0282-22-6336</t>
+        </is>
+      </c>
+      <c r="G110" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H110" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I110" s="6" t="inlineStr">
+        <is>
+          <t>NAVITIME 電話帳</t>
+        </is>
+      </c>
+      <c r="J110" s="6" t="inlineStr"/>
+      <c r="K110" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L110" s="6" t="inlineStr"/>
+      <c r="M110" s="6" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="5" t="n">
         <v>110</v>
       </c>
-      <c r="B111" s="8" t="inlineStr"/>
-      <c r="C111" s="8" t="inlineStr"/>
-      <c r="D111" s="8" t="inlineStr"/>
-      <c r="E111" s="8" t="inlineStr"/>
-      <c r="F111" s="8" t="inlineStr"/>
-      <c r="G111" s="8" t="inlineStr"/>
-      <c r="H111" s="8" t="inlineStr"/>
-      <c r="I111" s="8" t="inlineStr"/>
-      <c r="J111" s="8" t="inlineStr"/>
-      <c r="K111" s="8" t="inlineStr"/>
-      <c r="L111" s="8" t="inlineStr"/>
-      <c r="M111" s="8" t="inlineStr"/>
+      <c r="B111" s="6" t="inlineStr">
+        <is>
+          <t>はるみ美容室</t>
+        </is>
+      </c>
+      <c r="C111" s="6" t="inlineStr">
+        <is>
+          <t>美容室</t>
+        </is>
+      </c>
+      <c r="D111" s="6" t="inlineStr">
+        <is>
+          <t>栃木市</t>
+        </is>
+      </c>
+      <c r="E111" s="6" t="inlineStr">
+        <is>
+          <t>川原田町495-1</t>
+        </is>
+      </c>
+      <c r="F111" s="6" t="inlineStr">
+        <is>
+          <t>0282-23-4723</t>
+        </is>
+      </c>
+      <c r="G111" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H111" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I111" s="6" t="inlineStr">
+        <is>
+          <t>iタウンページ</t>
+        </is>
+      </c>
+      <c r="J111" s="6" t="inlineStr"/>
+      <c r="K111" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L111" s="6" t="inlineStr"/>
+      <c r="M111" s="6" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="5" t="n">
         <v>111</v>
       </c>
-      <c r="B112" s="8" t="inlineStr"/>
-      <c r="C112" s="8" t="inlineStr"/>
-      <c r="D112" s="8" t="inlineStr"/>
-      <c r="E112" s="8" t="inlineStr"/>
-      <c r="F112" s="8" t="inlineStr"/>
-      <c r="G112" s="8" t="inlineStr"/>
-      <c r="H112" s="8" t="inlineStr"/>
-      <c r="I112" s="8" t="inlineStr"/>
-      <c r="J112" s="8" t="inlineStr"/>
-      <c r="K112" s="8" t="inlineStr"/>
-      <c r="L112" s="8" t="inlineStr"/>
-      <c r="M112" s="8" t="inlineStr"/>
+      <c r="B112" s="6" t="inlineStr">
+        <is>
+          <t>ヘアーサロンカタギリ</t>
+        </is>
+      </c>
+      <c r="C112" s="6" t="inlineStr">
+        <is>
+          <t>理容室</t>
+        </is>
+      </c>
+      <c r="D112" s="6" t="inlineStr">
+        <is>
+          <t>栃木市</t>
+        </is>
+      </c>
+      <c r="E112" s="6" t="inlineStr">
+        <is>
+          <t>吹上町1363-6</t>
+        </is>
+      </c>
+      <c r="F112" s="6" t="inlineStr">
+        <is>
+          <t>0282-31-2163</t>
+        </is>
+      </c>
+      <c r="G112" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H112" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I112" s="6" t="inlineStr">
+        <is>
+          <t>NAVITIME 電話帳</t>
+        </is>
+      </c>
+      <c r="J112" s="6" t="inlineStr"/>
+      <c r="K112" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L112" s="6" t="inlineStr"/>
+      <c r="M112" s="6" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="5" t="n">
         <v>112</v>
       </c>
-      <c r="B113" s="8" t="inlineStr"/>
-      <c r="C113" s="8" t="inlineStr"/>
-      <c r="D113" s="8" t="inlineStr"/>
-      <c r="E113" s="8" t="inlineStr"/>
-      <c r="F113" s="8" t="inlineStr"/>
-      <c r="G113" s="8" t="inlineStr"/>
-      <c r="H113" s="8" t="inlineStr"/>
-      <c r="I113" s="8" t="inlineStr"/>
-      <c r="J113" s="8" t="inlineStr"/>
-      <c r="K113" s="8" t="inlineStr"/>
-      <c r="L113" s="8" t="inlineStr"/>
-      <c r="M113" s="8" t="inlineStr"/>
+      <c r="B113" s="6" t="inlineStr">
+        <is>
+          <t>カット&amp;パーマ・クラフト</t>
+        </is>
+      </c>
+      <c r="C113" s="6" t="inlineStr">
+        <is>
+          <t>理容室</t>
+        </is>
+      </c>
+      <c r="D113" s="6" t="inlineStr">
+        <is>
+          <t>栃木市</t>
+        </is>
+      </c>
+      <c r="E113" s="6" t="inlineStr">
+        <is>
+          <t>城内町2-31-9</t>
+        </is>
+      </c>
+      <c r="F113" s="6" t="inlineStr">
+        <is>
+          <t>0282-24-1868</t>
+        </is>
+      </c>
+      <c r="G113" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H113" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I113" s="6" t="inlineStr">
+        <is>
+          <t>NAVITIME 電話帳</t>
+        </is>
+      </c>
+      <c r="J113" s="6" t="inlineStr"/>
+      <c r="K113" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L113" s="6" t="inlineStr"/>
+      <c r="M113" s="6" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="5" t="n">
         <v>113</v>
       </c>
-      <c r="B114" s="8" t="inlineStr"/>
-      <c r="C114" s="8" t="inlineStr"/>
-      <c r="D114" s="8" t="inlineStr"/>
-      <c r="E114" s="8" t="inlineStr"/>
-      <c r="F114" s="8" t="inlineStr"/>
-      <c r="G114" s="8" t="inlineStr"/>
-      <c r="H114" s="8" t="inlineStr"/>
-      <c r="I114" s="8" t="inlineStr"/>
-      <c r="J114" s="8" t="inlineStr"/>
-      <c r="K114" s="8" t="inlineStr"/>
-      <c r="L114" s="8" t="inlineStr"/>
-      <c r="M114" s="8" t="inlineStr"/>
+      <c r="B114" s="6" t="inlineStr">
+        <is>
+          <t>カットスタジオY'S</t>
+        </is>
+      </c>
+      <c r="C114" s="6" t="inlineStr">
+        <is>
+          <t>理容室</t>
+        </is>
+      </c>
+      <c r="D114" s="6" t="inlineStr">
+        <is>
+          <t>栃木市</t>
+        </is>
+      </c>
+      <c r="E114" s="6" t="inlineStr">
+        <is>
+          <t>本町1-23</t>
+        </is>
+      </c>
+      <c r="F114" s="6" t="inlineStr">
+        <is>
+          <t>0282-24-8667</t>
+        </is>
+      </c>
+      <c r="G114" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H114" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I114" s="6" t="inlineStr">
+        <is>
+          <t>NAVITIME 電話帳</t>
+        </is>
+      </c>
+      <c r="J114" s="6" t="inlineStr"/>
+      <c r="K114" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L114" s="6" t="inlineStr"/>
+      <c r="M114" s="6" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="5" t="n">
         <v>114</v>
       </c>
-      <c r="B115" s="8" t="inlineStr"/>
-      <c r="C115" s="8" t="inlineStr"/>
-      <c r="D115" s="8" t="inlineStr"/>
-      <c r="E115" s="8" t="inlineStr"/>
-      <c r="F115" s="8" t="inlineStr"/>
-      <c r="G115" s="8" t="inlineStr"/>
-      <c r="H115" s="8" t="inlineStr"/>
-      <c r="I115" s="8" t="inlineStr"/>
-      <c r="J115" s="8" t="inlineStr"/>
-      <c r="K115" s="8" t="inlineStr"/>
-      <c r="L115" s="8" t="inlineStr"/>
-      <c r="M115" s="8" t="inlineStr"/>
+      <c r="B115" s="6" t="inlineStr">
+        <is>
+          <t>ヘアーサロン清水</t>
+        </is>
+      </c>
+      <c r="C115" s="6" t="inlineStr">
+        <is>
+          <t>理容室</t>
+        </is>
+      </c>
+      <c r="D115" s="6" t="inlineStr">
+        <is>
+          <t>栃木市</t>
+        </is>
+      </c>
+      <c r="E115" s="6" t="inlineStr">
+        <is>
+          <t>箱森町10-4</t>
+        </is>
+      </c>
+      <c r="F115" s="6" t="inlineStr">
+        <is>
+          <t>0282-23-8700</t>
+        </is>
+      </c>
+      <c r="G115" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H115" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I115" s="6" t="inlineStr">
+        <is>
+          <t>NAVITIME 電話帳</t>
+        </is>
+      </c>
+      <c r="J115" s="6" t="inlineStr"/>
+      <c r="K115" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L115" s="6" t="inlineStr"/>
+      <c r="M115" s="6" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="5" t="n">
         <v>115</v>
       </c>
-      <c r="B116" s="8" t="inlineStr"/>
-      <c r="C116" s="8" t="inlineStr"/>
-      <c r="D116" s="8" t="inlineStr"/>
-      <c r="E116" s="8" t="inlineStr"/>
-      <c r="F116" s="8" t="inlineStr"/>
-      <c r="G116" s="8" t="inlineStr"/>
-      <c r="H116" s="8" t="inlineStr"/>
-      <c r="I116" s="8" t="inlineStr"/>
-      <c r="J116" s="8" t="inlineStr"/>
-      <c r="K116" s="8" t="inlineStr"/>
-      <c r="L116" s="8" t="inlineStr"/>
-      <c r="M116" s="8" t="inlineStr"/>
+      <c r="B116" s="6" t="inlineStr">
+        <is>
+          <t>ヘアーサロンイシカワ</t>
+        </is>
+      </c>
+      <c r="C116" s="6" t="inlineStr">
+        <is>
+          <t>理容室</t>
+        </is>
+      </c>
+      <c r="D116" s="6" t="inlineStr">
+        <is>
+          <t>栃木市</t>
+        </is>
+      </c>
+      <c r="E116" s="6" t="inlineStr">
+        <is>
+          <t>室町1-11</t>
+        </is>
+      </c>
+      <c r="F116" s="7" t="inlineStr"/>
+      <c r="G116" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H116" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I116" s="6" t="inlineStr">
+        <is>
+          <t>NAVITIME 電話帳</t>
+        </is>
+      </c>
+      <c r="J116" s="6" t="inlineStr"/>
+      <c r="K116" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L116" s="6" t="inlineStr"/>
+      <c r="M116" s="6" t="inlineStr">
+        <is>
+          <t>電話番号は検索で確認できず</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="5" t="n">
         <v>116</v>
       </c>
-      <c r="B117" s="8" t="inlineStr"/>
-      <c r="C117" s="8" t="inlineStr"/>
-      <c r="D117" s="8" t="inlineStr"/>
-      <c r="E117" s="8" t="inlineStr"/>
-      <c r="F117" s="8" t="inlineStr"/>
-      <c r="G117" s="8" t="inlineStr"/>
-      <c r="H117" s="8" t="inlineStr"/>
-      <c r="I117" s="8" t="inlineStr"/>
-      <c r="J117" s="8" t="inlineStr"/>
-      <c r="K117" s="8" t="inlineStr"/>
-      <c r="L117" s="8" t="inlineStr"/>
-      <c r="M117" s="8" t="inlineStr"/>
+      <c r="B117" s="6" t="inlineStr">
+        <is>
+          <t>イイジマ理容</t>
+        </is>
+      </c>
+      <c r="C117" s="6" t="inlineStr">
+        <is>
+          <t>理容室</t>
+        </is>
+      </c>
+      <c r="D117" s="6" t="inlineStr">
+        <is>
+          <t>栃木市</t>
+        </is>
+      </c>
+      <c r="E117" s="6" t="inlineStr">
+        <is>
+          <t>神田町5-41</t>
+        </is>
+      </c>
+      <c r="F117" s="6" t="inlineStr">
+        <is>
+          <t>0282-23-3343</t>
+        </is>
+      </c>
+      <c r="G117" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H117" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I117" s="6" t="inlineStr">
+        <is>
+          <t>NAVITIME 電話帳</t>
+        </is>
+      </c>
+      <c r="J117" s="6" t="inlineStr"/>
+      <c r="K117" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L117" s="6" t="inlineStr"/>
+      <c r="M117" s="6" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="5" t="n">
         <v>117</v>
       </c>
-      <c r="B118" s="8" t="inlineStr"/>
-      <c r="C118" s="8" t="inlineStr"/>
-      <c r="D118" s="8" t="inlineStr"/>
-      <c r="E118" s="8" t="inlineStr"/>
-      <c r="F118" s="8" t="inlineStr"/>
-      <c r="G118" s="8" t="inlineStr"/>
-      <c r="H118" s="8" t="inlineStr"/>
-      <c r="I118" s="8" t="inlineStr"/>
-      <c r="J118" s="8" t="inlineStr"/>
-      <c r="K118" s="8" t="inlineStr"/>
-      <c r="L118" s="8" t="inlineStr"/>
-      <c r="M118" s="8" t="inlineStr"/>
+      <c r="B118" s="6" t="inlineStr">
+        <is>
+          <t>ヘア・フォーラム町田</t>
+        </is>
+      </c>
+      <c r="C118" s="6" t="inlineStr">
+        <is>
+          <t>理容室</t>
+        </is>
+      </c>
+      <c r="D118" s="6" t="inlineStr">
+        <is>
+          <t>栃木市</t>
+        </is>
+      </c>
+      <c r="E118" s="6" t="inlineStr">
+        <is>
+          <t>日ノ出町1-50</t>
+        </is>
+      </c>
+      <c r="F118" s="6" t="inlineStr">
+        <is>
+          <t>0282-23-1138</t>
+        </is>
+      </c>
+      <c r="G118" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H118" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I118" s="6" t="inlineStr">
+        <is>
+          <t>NAVITIME 電話帳</t>
+        </is>
+      </c>
+      <c r="J118" s="6" t="inlineStr"/>
+      <c r="K118" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L118" s="6" t="inlineStr"/>
+      <c r="M118" s="6" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="5" t="n">
         <v>118</v>
       </c>
-      <c r="B119" s="8" t="inlineStr"/>
-      <c r="C119" s="8" t="inlineStr"/>
-      <c r="D119" s="8" t="inlineStr"/>
-      <c r="E119" s="8" t="inlineStr"/>
-      <c r="F119" s="8" t="inlineStr"/>
-      <c r="G119" s="8" t="inlineStr"/>
-      <c r="H119" s="8" t="inlineStr"/>
-      <c r="I119" s="8" t="inlineStr"/>
-      <c r="J119" s="8" t="inlineStr"/>
-      <c r="K119" s="8" t="inlineStr"/>
-      <c r="L119" s="8" t="inlineStr"/>
-      <c r="M119" s="8" t="inlineStr"/>
+      <c r="B119" s="6" t="inlineStr">
+        <is>
+          <t>美容室ファーストクラス佐野店</t>
+        </is>
+      </c>
+      <c r="C119" s="6" t="inlineStr">
+        <is>
+          <t>美容室</t>
+        </is>
+      </c>
+      <c r="D119" s="6" t="inlineStr">
+        <is>
+          <t>佐野市</t>
+        </is>
+      </c>
+      <c r="E119" s="6" t="inlineStr">
+        <is>
+          <t>田島町47-5</t>
+        </is>
+      </c>
+      <c r="F119" s="6" t="inlineStr">
+        <is>
+          <t>0283-21-2266</t>
+        </is>
+      </c>
+      <c r="G119" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H119" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I119" s="6" t="inlineStr">
+        <is>
+          <t>NAVITIME 電話帳</t>
+        </is>
+      </c>
+      <c r="J119" s="6" t="inlineStr"/>
+      <c r="K119" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L119" s="6" t="inlineStr"/>
+      <c r="M119" s="6" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="5" t="n">
         <v>119</v>
       </c>
-      <c r="B120" s="8" t="inlineStr"/>
-      <c r="C120" s="8" t="inlineStr"/>
-      <c r="D120" s="8" t="inlineStr"/>
-      <c r="E120" s="8" t="inlineStr"/>
-      <c r="F120" s="8" t="inlineStr"/>
-      <c r="G120" s="8" t="inlineStr"/>
-      <c r="H120" s="8" t="inlineStr"/>
-      <c r="I120" s="8" t="inlineStr"/>
-      <c r="J120" s="8" t="inlineStr"/>
-      <c r="K120" s="8" t="inlineStr"/>
-      <c r="L120" s="8" t="inlineStr"/>
-      <c r="M120" s="8" t="inlineStr"/>
+      <c r="B120" s="6" t="inlineStr">
+        <is>
+          <t>しずか美容室</t>
+        </is>
+      </c>
+      <c r="C120" s="6" t="inlineStr">
+        <is>
+          <t>美容室</t>
+        </is>
+      </c>
+      <c r="D120" s="6" t="inlineStr">
+        <is>
+          <t>佐野市</t>
+        </is>
+      </c>
+      <c r="E120" s="6" t="inlineStr">
+        <is>
+          <t>植上町1513-7</t>
+        </is>
+      </c>
+      <c r="F120" s="6" t="inlineStr">
+        <is>
+          <t>0283-23-2126</t>
+        </is>
+      </c>
+      <c r="G120" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H120" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I120" s="6" t="inlineStr">
+        <is>
+          <t>NAVITIME 電話帳</t>
+        </is>
+      </c>
+      <c r="J120" s="6" t="inlineStr"/>
+      <c r="K120" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L120" s="6" t="inlineStr"/>
+      <c r="M120" s="6" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="5" t="n">
         <v>120</v>
       </c>
-      <c r="B121" s="8" t="inlineStr"/>
-      <c r="C121" s="8" t="inlineStr"/>
-      <c r="D121" s="8" t="inlineStr"/>
-      <c r="E121" s="8" t="inlineStr"/>
-      <c r="F121" s="8" t="inlineStr"/>
-      <c r="G121" s="8" t="inlineStr"/>
-      <c r="H121" s="8" t="inlineStr"/>
-      <c r="I121" s="8" t="inlineStr"/>
-      <c r="J121" s="8" t="inlineStr"/>
-      <c r="K121" s="8" t="inlineStr"/>
-      <c r="L121" s="8" t="inlineStr"/>
-      <c r="M121" s="8" t="inlineStr"/>
+      <c r="B121" s="6" t="inlineStr">
+        <is>
+          <t>美容室プレール</t>
+        </is>
+      </c>
+      <c r="C121" s="6" t="inlineStr">
+        <is>
+          <t>美容室</t>
+        </is>
+      </c>
+      <c r="D121" s="6" t="inlineStr">
+        <is>
+          <t>佐野市</t>
+        </is>
+      </c>
+      <c r="E121" s="6" t="inlineStr">
+        <is>
+          <t>田沼町281-6</t>
+        </is>
+      </c>
+      <c r="F121" s="6" t="inlineStr">
+        <is>
+          <t>0283-62-8686</t>
+        </is>
+      </c>
+      <c r="G121" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H121" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I121" s="6" t="inlineStr">
+        <is>
+          <t>NAVITIME 電話帳</t>
+        </is>
+      </c>
+      <c r="J121" s="6" t="inlineStr"/>
+      <c r="K121" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L121" s="6" t="inlineStr"/>
+      <c r="M121" s="6" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="5" t="n">
         <v>121</v>
       </c>
-      <c r="B122" s="8" t="inlineStr"/>
-      <c r="C122" s="8" t="inlineStr"/>
-      <c r="D122" s="8" t="inlineStr"/>
-      <c r="E122" s="8" t="inlineStr"/>
-      <c r="F122" s="8" t="inlineStr"/>
-      <c r="G122" s="8" t="inlineStr"/>
-      <c r="H122" s="8" t="inlineStr"/>
-      <c r="I122" s="8" t="inlineStr"/>
-      <c r="J122" s="8" t="inlineStr"/>
-      <c r="K122" s="8" t="inlineStr"/>
-      <c r="L122" s="8" t="inlineStr"/>
-      <c r="M122" s="8" t="inlineStr"/>
+      <c r="B122" s="6" t="inlineStr">
+        <is>
+          <t>カズ美容室</t>
+        </is>
+      </c>
+      <c r="C122" s="6" t="inlineStr">
+        <is>
+          <t>美容室</t>
+        </is>
+      </c>
+      <c r="D122" s="6" t="inlineStr">
+        <is>
+          <t>佐野市</t>
+        </is>
+      </c>
+      <c r="E122" s="6" t="inlineStr">
+        <is>
+          <t>犬伏中町2275-12</t>
+        </is>
+      </c>
+      <c r="F122" s="6" t="inlineStr">
+        <is>
+          <t>0283-23-3720</t>
+        </is>
+      </c>
+      <c r="G122" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H122" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I122" s="6" t="inlineStr">
+        <is>
+          <t>NAVITIME 電話帳</t>
+        </is>
+      </c>
+      <c r="J122" s="6" t="inlineStr"/>
+      <c r="K122" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L122" s="6" t="inlineStr"/>
+      <c r="M122" s="6" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="5" t="n">
         <v>122</v>
       </c>
-      <c r="B123" s="8" t="inlineStr"/>
-      <c r="C123" s="8" t="inlineStr"/>
-      <c r="D123" s="8" t="inlineStr"/>
-      <c r="E123" s="8" t="inlineStr"/>
-      <c r="F123" s="8" t="inlineStr"/>
-      <c r="G123" s="8" t="inlineStr"/>
-      <c r="H123" s="8" t="inlineStr"/>
-      <c r="I123" s="8" t="inlineStr"/>
-      <c r="J123" s="8" t="inlineStr"/>
-      <c r="K123" s="8" t="inlineStr"/>
-      <c r="L123" s="8" t="inlineStr"/>
-      <c r="M123" s="8" t="inlineStr"/>
+      <c r="B123" s="6" t="inlineStr">
+        <is>
+          <t>若菜美容室</t>
+        </is>
+      </c>
+      <c r="C123" s="6" t="inlineStr">
+        <is>
+          <t>美容室</t>
+        </is>
+      </c>
+      <c r="D123" s="6" t="inlineStr">
+        <is>
+          <t>佐野市</t>
+        </is>
+      </c>
+      <c r="E123" s="6" t="inlineStr">
+        <is>
+          <t>大町2983</t>
+        </is>
+      </c>
+      <c r="F123" s="6" t="inlineStr">
+        <is>
+          <t>0283-22-4831</t>
+        </is>
+      </c>
+      <c r="G123" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H123" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I123" s="6" t="inlineStr">
+        <is>
+          <t>NAVITIME 電話帳</t>
+        </is>
+      </c>
+      <c r="J123" s="6" t="inlineStr"/>
+      <c r="K123" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L123" s="6" t="inlineStr"/>
+      <c r="M123" s="6" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="5" t="n">
         <v>123</v>
       </c>
-      <c r="B124" s="8" t="inlineStr"/>
-      <c r="C124" s="8" t="inlineStr"/>
-      <c r="D124" s="8" t="inlineStr"/>
-      <c r="E124" s="8" t="inlineStr"/>
-      <c r="F124" s="8" t="inlineStr"/>
-      <c r="G124" s="8" t="inlineStr"/>
-      <c r="H124" s="8" t="inlineStr"/>
-      <c r="I124" s="8" t="inlineStr"/>
-      <c r="J124" s="8" t="inlineStr"/>
-      <c r="K124" s="8" t="inlineStr"/>
-      <c r="L124" s="8" t="inlineStr"/>
-      <c r="M124" s="8" t="inlineStr"/>
+      <c r="B124" s="6" t="inlineStr">
+        <is>
+          <t>美容室MINT</t>
+        </is>
+      </c>
+      <c r="C124" s="6" t="inlineStr">
+        <is>
+          <t>美容室</t>
+        </is>
+      </c>
+      <c r="D124" s="6" t="inlineStr">
+        <is>
+          <t>佐野市</t>
+        </is>
+      </c>
+      <c r="E124" s="6" t="inlineStr">
+        <is>
+          <t>中町1179-4</t>
+        </is>
+      </c>
+      <c r="F124" s="6" t="inlineStr">
+        <is>
+          <t>0283-25-8177</t>
+        </is>
+      </c>
+      <c r="G124" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H124" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I124" s="6" t="inlineStr">
+        <is>
+          <t>NAVITIME 電話帳</t>
+        </is>
+      </c>
+      <c r="J124" s="6" t="inlineStr"/>
+      <c r="K124" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L124" s="6" t="inlineStr"/>
+      <c r="M124" s="6" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="5" t="n">
         <v>124</v>
       </c>
-      <c r="B125" s="8" t="inlineStr"/>
-      <c r="C125" s="8" t="inlineStr"/>
-      <c r="D125" s="8" t="inlineStr"/>
-      <c r="E125" s="8" t="inlineStr"/>
-      <c r="F125" s="8" t="inlineStr"/>
-      <c r="G125" s="8" t="inlineStr"/>
-      <c r="H125" s="8" t="inlineStr"/>
-      <c r="I125" s="8" t="inlineStr"/>
-      <c r="J125" s="8" t="inlineStr"/>
-      <c r="K125" s="8" t="inlineStr"/>
-      <c r="L125" s="8" t="inlineStr"/>
-      <c r="M125" s="8" t="inlineStr"/>
+      <c r="B125" s="6" t="inlineStr">
+        <is>
+          <t>アルム</t>
+        </is>
+      </c>
+      <c r="C125" s="6" t="inlineStr">
+        <is>
+          <t>理容室</t>
+        </is>
+      </c>
+      <c r="D125" s="6" t="inlineStr">
+        <is>
+          <t>佐野市</t>
+        </is>
+      </c>
+      <c r="E125" s="6" t="inlineStr">
+        <is>
+          <t>田沼町666-11</t>
+        </is>
+      </c>
+      <c r="F125" s="6" t="inlineStr">
+        <is>
+          <t>0283-62-3848</t>
+        </is>
+      </c>
+      <c r="G125" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H125" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I125" s="6" t="inlineStr">
+        <is>
+          <t>NAVITIME 電話帳</t>
+        </is>
+      </c>
+      <c r="J125" s="6" t="inlineStr"/>
+      <c r="K125" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L125" s="6" t="inlineStr"/>
+      <c r="M125" s="6" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="5" t="n">
         <v>125</v>
       </c>
-      <c r="B126" s="8" t="inlineStr"/>
-      <c r="C126" s="8" t="inlineStr"/>
-      <c r="D126" s="8" t="inlineStr"/>
-      <c r="E126" s="8" t="inlineStr"/>
-      <c r="F126" s="8" t="inlineStr"/>
-      <c r="G126" s="8" t="inlineStr"/>
-      <c r="H126" s="8" t="inlineStr"/>
-      <c r="I126" s="8" t="inlineStr"/>
-      <c r="J126" s="8" t="inlineStr"/>
-      <c r="K126" s="8" t="inlineStr"/>
-      <c r="L126" s="8" t="inlineStr"/>
-      <c r="M126" s="8" t="inlineStr"/>
+      <c r="B126" s="6" t="inlineStr">
+        <is>
+          <t>理容プラージュ佐野店</t>
+        </is>
+      </c>
+      <c r="C126" s="6" t="inlineStr">
+        <is>
+          <t>理容室</t>
+        </is>
+      </c>
+      <c r="D126" s="6" t="inlineStr">
+        <is>
+          <t>佐野市</t>
+        </is>
+      </c>
+      <c r="E126" s="6" t="inlineStr">
+        <is>
+          <t>高萩町1338-5</t>
+        </is>
+      </c>
+      <c r="F126" s="6" t="inlineStr">
+        <is>
+          <t>0283-23-0155</t>
+        </is>
+      </c>
+      <c r="G126" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H126" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I126" s="6" t="inlineStr">
+        <is>
+          <t>NAVITIME 電話帳</t>
+        </is>
+      </c>
+      <c r="J126" s="6" t="inlineStr"/>
+      <c r="K126" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L126" s="6" t="inlineStr"/>
+      <c r="M126" s="6" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="5" t="n">
         <v>126</v>
       </c>
-      <c r="B127" s="8" t="inlineStr"/>
-      <c r="C127" s="8" t="inlineStr"/>
-      <c r="D127" s="8" t="inlineStr"/>
-      <c r="E127" s="8" t="inlineStr"/>
-      <c r="F127" s="8" t="inlineStr"/>
-      <c r="G127" s="8" t="inlineStr"/>
-      <c r="H127" s="8" t="inlineStr"/>
-      <c r="I127" s="8" t="inlineStr"/>
-      <c r="J127" s="8" t="inlineStr"/>
-      <c r="K127" s="8" t="inlineStr"/>
-      <c r="L127" s="8" t="inlineStr"/>
-      <c r="M127" s="8" t="inlineStr"/>
+      <c r="B127" s="6" t="inlineStr">
+        <is>
+          <t>イマジン</t>
+        </is>
+      </c>
+      <c r="C127" s="6" t="inlineStr">
+        <is>
+          <t>理容室</t>
+        </is>
+      </c>
+      <c r="D127" s="6" t="inlineStr">
+        <is>
+          <t>佐野市</t>
+        </is>
+      </c>
+      <c r="E127" s="6" t="inlineStr">
+        <is>
+          <t>堀米町2576-9</t>
+        </is>
+      </c>
+      <c r="F127" s="6" t="inlineStr">
+        <is>
+          <t>0283-21-8237</t>
+        </is>
+      </c>
+      <c r="G127" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H127" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I127" s="6" t="inlineStr">
+        <is>
+          <t>NAVITIME 電話帳</t>
+        </is>
+      </c>
+      <c r="J127" s="6" t="inlineStr"/>
+      <c r="K127" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L127" s="6" t="inlineStr"/>
+      <c r="M127" s="6" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="5" t="n">
         <v>127</v>
       </c>
-      <c r="B128" s="8" t="inlineStr"/>
-      <c r="C128" s="8" t="inlineStr"/>
-      <c r="D128" s="8" t="inlineStr"/>
-      <c r="E128" s="8" t="inlineStr"/>
-      <c r="F128" s="8" t="inlineStr"/>
-      <c r="G128" s="8" t="inlineStr"/>
-      <c r="H128" s="8" t="inlineStr"/>
-      <c r="I128" s="8" t="inlineStr"/>
-      <c r="J128" s="8" t="inlineStr"/>
-      <c r="K128" s="8" t="inlineStr"/>
-      <c r="L128" s="8" t="inlineStr"/>
-      <c r="M128" s="8" t="inlineStr"/>
+      <c r="B128" s="6" t="inlineStr">
+        <is>
+          <t>理容cut-A佐野店</t>
+        </is>
+      </c>
+      <c r="C128" s="6" t="inlineStr">
+        <is>
+          <t>理容室</t>
+        </is>
+      </c>
+      <c r="D128" s="6" t="inlineStr">
+        <is>
+          <t>佐野市</t>
+        </is>
+      </c>
+      <c r="E128" s="6" t="inlineStr">
+        <is>
+          <t>浅沼町11-1</t>
+        </is>
+      </c>
+      <c r="F128" s="6" t="inlineStr">
+        <is>
+          <t>0120-81-1538</t>
+        </is>
+      </c>
+      <c r="G128" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H128" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I128" s="6" t="inlineStr">
+        <is>
+          <t>NAVITIME 電話帳</t>
+        </is>
+      </c>
+      <c r="J128" s="6" t="inlineStr"/>
+      <c r="K128" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L128" s="6" t="inlineStr"/>
+      <c r="M128" s="6" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="5" t="n">
         <v>128</v>
       </c>
-      <c r="B129" s="8" t="inlineStr"/>
-      <c r="C129" s="8" t="inlineStr"/>
-      <c r="D129" s="8" t="inlineStr"/>
-      <c r="E129" s="8" t="inlineStr"/>
-      <c r="F129" s="8" t="inlineStr"/>
-      <c r="G129" s="8" t="inlineStr"/>
-      <c r="H129" s="8" t="inlineStr"/>
-      <c r="I129" s="8" t="inlineStr"/>
-      <c r="J129" s="8" t="inlineStr"/>
-      <c r="K129" s="8" t="inlineStr"/>
-      <c r="L129" s="8" t="inlineStr"/>
-      <c r="M129" s="8" t="inlineStr"/>
+      <c r="B129" s="6" t="inlineStr">
+        <is>
+          <t>イソガイ理容室</t>
+        </is>
+      </c>
+      <c r="C129" s="6" t="inlineStr">
+        <is>
+          <t>理容室</t>
+        </is>
+      </c>
+      <c r="D129" s="6" t="inlineStr">
+        <is>
+          <t>佐野市</t>
+        </is>
+      </c>
+      <c r="E129" s="6" t="inlineStr">
+        <is>
+          <t>伊勢山町3-5</t>
+        </is>
+      </c>
+      <c r="F129" s="6" t="inlineStr">
+        <is>
+          <t>0283-23-4173</t>
+        </is>
+      </c>
+      <c r="G129" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H129" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I129" s="6" t="inlineStr">
+        <is>
+          <t>NAVITIME 電話帳</t>
+        </is>
+      </c>
+      <c r="J129" s="6" t="inlineStr"/>
+      <c r="K129" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L129" s="6" t="inlineStr"/>
+      <c r="M129" s="6" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="5" t="n">
         <v>129</v>
       </c>
-      <c r="B130" s="8" t="inlineStr"/>
-      <c r="C130" s="8" t="inlineStr"/>
-      <c r="D130" s="8" t="inlineStr"/>
-      <c r="E130" s="8" t="inlineStr"/>
-      <c r="F130" s="8" t="inlineStr"/>
-      <c r="G130" s="8" t="inlineStr"/>
-      <c r="H130" s="8" t="inlineStr"/>
-      <c r="I130" s="8" t="inlineStr"/>
-      <c r="J130" s="8" t="inlineStr"/>
-      <c r="K130" s="8" t="inlineStr"/>
-      <c r="L130" s="8" t="inlineStr"/>
-      <c r="M130" s="8" t="inlineStr"/>
+      <c r="B130" s="6" t="inlineStr">
+        <is>
+          <t>寺内理容所</t>
+        </is>
+      </c>
+      <c r="C130" s="6" t="inlineStr">
+        <is>
+          <t>理容室</t>
+        </is>
+      </c>
+      <c r="D130" s="6" t="inlineStr">
+        <is>
+          <t>佐野市</t>
+        </is>
+      </c>
+      <c r="E130" s="6" t="inlineStr">
+        <is>
+          <t>中町955-5</t>
+        </is>
+      </c>
+      <c r="F130" s="6" t="inlineStr">
+        <is>
+          <t>0283-86-4080</t>
+        </is>
+      </c>
+      <c r="G130" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H130" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I130" s="6" t="inlineStr">
+        <is>
+          <t>NAVITIME 電話帳</t>
+        </is>
+      </c>
+      <c r="J130" s="6" t="inlineStr"/>
+      <c r="K130" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L130" s="6" t="inlineStr"/>
+      <c r="M130" s="6" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="5" t="n">
         <v>130</v>
       </c>
-      <c r="B131" s="8" t="inlineStr"/>
-      <c r="C131" s="8" t="inlineStr"/>
-      <c r="D131" s="8" t="inlineStr"/>
-      <c r="E131" s="8" t="inlineStr"/>
-      <c r="F131" s="8" t="inlineStr"/>
-      <c r="G131" s="8" t="inlineStr"/>
-      <c r="H131" s="8" t="inlineStr"/>
-      <c r="I131" s="8" t="inlineStr"/>
-      <c r="J131" s="8" t="inlineStr"/>
-      <c r="K131" s="8" t="inlineStr"/>
-      <c r="L131" s="8" t="inlineStr"/>
-      <c r="M131" s="8" t="inlineStr"/>
+      <c r="B131" s="6" t="inlineStr">
+        <is>
+          <t>永島理容</t>
+        </is>
+      </c>
+      <c r="C131" s="6" t="inlineStr">
+        <is>
+          <t>理容室</t>
+        </is>
+      </c>
+      <c r="D131" s="6" t="inlineStr">
+        <is>
+          <t>佐野市</t>
+        </is>
+      </c>
+      <c r="E131" s="6" t="inlineStr">
+        <is>
+          <t>田沼町1289-11</t>
+        </is>
+      </c>
+      <c r="F131" s="6" t="inlineStr">
+        <is>
+          <t>0283-62-0645</t>
+        </is>
+      </c>
+      <c r="G131" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H131" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I131" s="6" t="inlineStr">
+        <is>
+          <t>NAVITIME 電話帳</t>
+        </is>
+      </c>
+      <c r="J131" s="6" t="inlineStr"/>
+      <c r="K131" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L131" s="6" t="inlineStr"/>
+      <c r="M131" s="6" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="5" t="n">
         <v>131</v>
       </c>
-      <c r="B132" s="8" t="inlineStr"/>
-      <c r="C132" s="8" t="inlineStr"/>
-      <c r="D132" s="8" t="inlineStr"/>
-      <c r="E132" s="8" t="inlineStr"/>
-      <c r="F132" s="8" t="inlineStr"/>
-      <c r="G132" s="8" t="inlineStr"/>
-      <c r="H132" s="8" t="inlineStr"/>
-      <c r="I132" s="8" t="inlineStr"/>
-      <c r="J132" s="8" t="inlineStr"/>
-      <c r="K132" s="8" t="inlineStr"/>
-      <c r="L132" s="8" t="inlineStr"/>
-      <c r="M132" s="8" t="inlineStr"/>
+      <c r="B132" s="6" t="inlineStr">
+        <is>
+          <t>福田理容店</t>
+        </is>
+      </c>
+      <c r="C132" s="6" t="inlineStr">
+        <is>
+          <t>理容室</t>
+        </is>
+      </c>
+      <c r="D132" s="6" t="inlineStr">
+        <is>
+          <t>佐野市</t>
+        </is>
+      </c>
+      <c r="E132" s="6" t="inlineStr">
+        <is>
+          <t>石塚町568-168</t>
+        </is>
+      </c>
+      <c r="F132" s="6" t="inlineStr">
+        <is>
+          <t>0283-25-1256</t>
+        </is>
+      </c>
+      <c r="G132" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H132" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I132" s="6" t="inlineStr">
+        <is>
+          <t>NAVITIME 電話帳</t>
+        </is>
+      </c>
+      <c r="J132" s="6" t="inlineStr"/>
+      <c r="K132" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L132" s="6" t="inlineStr"/>
+      <c r="M132" s="6" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="5" t="n">
         <v>132</v>
       </c>
-      <c r="B133" s="8" t="inlineStr"/>
-      <c r="C133" s="8" t="inlineStr"/>
-      <c r="D133" s="8" t="inlineStr"/>
-      <c r="E133" s="8" t="inlineStr"/>
-      <c r="F133" s="8" t="inlineStr"/>
-      <c r="G133" s="8" t="inlineStr"/>
-      <c r="H133" s="8" t="inlineStr"/>
-      <c r="I133" s="8" t="inlineStr"/>
-      <c r="J133" s="8" t="inlineStr"/>
-      <c r="K133" s="8" t="inlineStr"/>
-      <c r="L133" s="8" t="inlineStr"/>
-      <c r="M133" s="8" t="inlineStr"/>
+      <c r="B133" s="6" t="inlineStr">
+        <is>
+          <t>ヘアーサロンカワセイ</t>
+        </is>
+      </c>
+      <c r="C133" s="6" t="inlineStr">
+        <is>
+          <t>理容室</t>
+        </is>
+      </c>
+      <c r="D133" s="6" t="inlineStr">
+        <is>
+          <t>佐野市</t>
+        </is>
+      </c>
+      <c r="E133" s="6" t="inlineStr">
+        <is>
+          <t>天明町2228</t>
+        </is>
+      </c>
+      <c r="F133" s="6" t="inlineStr">
+        <is>
+          <t>0283-23-0234</t>
+        </is>
+      </c>
+      <c r="G133" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H133" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I133" s="6" t="inlineStr">
+        <is>
+          <t>NAVITIME 電話帳</t>
+        </is>
+      </c>
+      <c r="J133" s="6" t="inlineStr"/>
+      <c r="K133" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L133" s="6" t="inlineStr"/>
+      <c r="M133" s="6" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="5" t="n">
         <v>133</v>
       </c>
-      <c r="B134" s="8" t="inlineStr"/>
-      <c r="C134" s="8" t="inlineStr"/>
-      <c r="D134" s="8" t="inlineStr"/>
-      <c r="E134" s="8" t="inlineStr"/>
-      <c r="F134" s="8" t="inlineStr"/>
-      <c r="G134" s="8" t="inlineStr"/>
-      <c r="H134" s="8" t="inlineStr"/>
-      <c r="I134" s="8" t="inlineStr"/>
-      <c r="J134" s="8" t="inlineStr"/>
-      <c r="K134" s="8" t="inlineStr"/>
-      <c r="L134" s="8" t="inlineStr"/>
-      <c r="M134" s="8" t="inlineStr"/>
+      <c r="B134" s="6" t="inlineStr">
+        <is>
+          <t>新宿理容所</t>
+        </is>
+      </c>
+      <c r="C134" s="6" t="inlineStr">
+        <is>
+          <t>理容室</t>
+        </is>
+      </c>
+      <c r="D134" s="6" t="inlineStr">
+        <is>
+          <t>佐野市</t>
+        </is>
+      </c>
+      <c r="E134" s="6" t="inlineStr">
+        <is>
+          <t>田沼町12-2</t>
+        </is>
+      </c>
+      <c r="F134" s="6" t="inlineStr">
+        <is>
+          <t>0283-62-3514</t>
+        </is>
+      </c>
+      <c r="G134" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H134" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I134" s="6" t="inlineStr">
+        <is>
+          <t>NAVITIME 電話帳</t>
+        </is>
+      </c>
+      <c r="J134" s="6" t="inlineStr"/>
+      <c r="K134" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L134" s="6" t="inlineStr"/>
+      <c r="M134" s="6" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="5" t="n">
         <v>134</v>
       </c>
-      <c r="B135" s="8" t="inlineStr"/>
-      <c r="C135" s="8" t="inlineStr"/>
-      <c r="D135" s="8" t="inlineStr"/>
-      <c r="E135" s="8" t="inlineStr"/>
-      <c r="F135" s="8" t="inlineStr"/>
-      <c r="G135" s="8" t="inlineStr"/>
-      <c r="H135" s="8" t="inlineStr"/>
-      <c r="I135" s="8" t="inlineStr"/>
-      <c r="J135" s="8" t="inlineStr"/>
-      <c r="K135" s="8" t="inlineStr"/>
-      <c r="L135" s="8" t="inlineStr"/>
-      <c r="M135" s="8" t="inlineStr"/>
+      <c r="B135" s="6" t="inlineStr">
+        <is>
+          <t>はせがわ理容室</t>
+        </is>
+      </c>
+      <c r="C135" s="6" t="inlineStr">
+        <is>
+          <t>理容室</t>
+        </is>
+      </c>
+      <c r="D135" s="6" t="inlineStr">
+        <is>
+          <t>佐野市</t>
+        </is>
+      </c>
+      <c r="E135" s="6" t="inlineStr">
+        <is>
+          <t>飛駒町1475-2</t>
+        </is>
+      </c>
+      <c r="F135" s="6" t="inlineStr">
+        <is>
+          <t>0283-66-2833</t>
+        </is>
+      </c>
+      <c r="G135" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H135" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I135" s="6" t="inlineStr">
+        <is>
+          <t>NAVITIME 電話帳</t>
+        </is>
+      </c>
+      <c r="J135" s="6" t="inlineStr"/>
+      <c r="K135" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L135" s="6" t="inlineStr"/>
+      <c r="M135" s="6" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="5" t="n">
         <v>135</v>
       </c>
-      <c r="B136" s="8" t="inlineStr"/>
-      <c r="C136" s="8" t="inlineStr"/>
-      <c r="D136" s="8" t="inlineStr"/>
-      <c r="E136" s="8" t="inlineStr"/>
-      <c r="F136" s="8" t="inlineStr"/>
-      <c r="G136" s="8" t="inlineStr"/>
-      <c r="H136" s="8" t="inlineStr"/>
-      <c r="I136" s="8" t="inlineStr"/>
-      <c r="J136" s="8" t="inlineStr"/>
-      <c r="K136" s="8" t="inlineStr"/>
-      <c r="L136" s="8" t="inlineStr"/>
-      <c r="M136" s="8" t="inlineStr"/>
+      <c r="B136" s="6" t="inlineStr">
+        <is>
+          <t>かみおか理容室</t>
+        </is>
+      </c>
+      <c r="C136" s="6" t="inlineStr">
+        <is>
+          <t>理容室</t>
+        </is>
+      </c>
+      <c r="D136" s="6" t="inlineStr">
+        <is>
+          <t>佐野市</t>
+        </is>
+      </c>
+      <c r="E136" s="6" t="inlineStr">
+        <is>
+          <t>並木町1857</t>
+        </is>
+      </c>
+      <c r="F136" s="6" t="inlineStr">
+        <is>
+          <t>0283-22-3938</t>
+        </is>
+      </c>
+      <c r="G136" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H136" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I136" s="6" t="inlineStr">
+        <is>
+          <t>NAVITIME 電話帳</t>
+        </is>
+      </c>
+      <c r="J136" s="6" t="inlineStr"/>
+      <c r="K136" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L136" s="6" t="inlineStr"/>
+      <c r="M136" s="6" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" s="5" t="n">
         <v>136</v>
       </c>
-      <c r="B137" s="8" t="inlineStr"/>
-      <c r="C137" s="8" t="inlineStr"/>
-      <c r="D137" s="8" t="inlineStr"/>
-      <c r="E137" s="8" t="inlineStr"/>
-      <c r="F137" s="8" t="inlineStr"/>
-      <c r="G137" s="8" t="inlineStr"/>
-      <c r="H137" s="8" t="inlineStr"/>
-      <c r="I137" s="8" t="inlineStr"/>
-      <c r="J137" s="8" t="inlineStr"/>
-      <c r="K137" s="8" t="inlineStr"/>
-      <c r="L137" s="8" t="inlineStr"/>
-      <c r="M137" s="8" t="inlineStr"/>
+      <c r="B137" s="6" t="inlineStr">
+        <is>
+          <t>おりおん理容室</t>
+        </is>
+      </c>
+      <c r="C137" s="6" t="inlineStr">
+        <is>
+          <t>理容室</t>
+        </is>
+      </c>
+      <c r="D137" s="6" t="inlineStr">
+        <is>
+          <t>佐野市</t>
+        </is>
+      </c>
+      <c r="E137" s="6" t="inlineStr">
+        <is>
+          <t>若宮上町4-1</t>
+        </is>
+      </c>
+      <c r="F137" s="6" t="inlineStr">
+        <is>
+          <t>0283-22-2051</t>
+        </is>
+      </c>
+      <c r="G137" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H137" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I137" s="6" t="inlineStr">
+        <is>
+          <t>NAVITIME 電話帳</t>
+        </is>
+      </c>
+      <c r="J137" s="6" t="inlineStr"/>
+      <c r="K137" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L137" s="6" t="inlineStr"/>
+      <c r="M137" s="6" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="5" t="n">
         <v>137</v>
       </c>
-      <c r="B138" s="8" t="inlineStr"/>
-      <c r="C138" s="8" t="inlineStr"/>
-      <c r="D138" s="8" t="inlineStr"/>
-      <c r="E138" s="8" t="inlineStr"/>
-      <c r="F138" s="8" t="inlineStr"/>
-      <c r="G138" s="8" t="inlineStr"/>
-      <c r="H138" s="8" t="inlineStr"/>
-      <c r="I138" s="8" t="inlineStr"/>
-      <c r="J138" s="8" t="inlineStr"/>
-      <c r="K138" s="8" t="inlineStr"/>
-      <c r="L138" s="8" t="inlineStr"/>
-      <c r="M138" s="8" t="inlineStr"/>
+      <c r="B138" s="6" t="inlineStr">
+        <is>
+          <t>理容室クローバー</t>
+        </is>
+      </c>
+      <c r="C138" s="6" t="inlineStr">
+        <is>
+          <t>理容室</t>
+        </is>
+      </c>
+      <c r="D138" s="6" t="inlineStr">
+        <is>
+          <t>佐野市</t>
+        </is>
+      </c>
+      <c r="E138" s="6" t="inlineStr">
+        <is>
+          <t>植上町1583-1</t>
+        </is>
+      </c>
+      <c r="F138" s="6" t="inlineStr">
+        <is>
+          <t>0283-55-4700</t>
+        </is>
+      </c>
+      <c r="G138" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H138" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I138" s="6" t="inlineStr">
+        <is>
+          <t>NAVITIME 電話帳</t>
+        </is>
+      </c>
+      <c r="J138" s="6" t="inlineStr"/>
+      <c r="K138" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L138" s="6" t="inlineStr"/>
+      <c r="M138" s="6" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" s="5" t="n">
         <v>138</v>
       </c>
-      <c r="B139" s="8" t="inlineStr"/>
-      <c r="C139" s="8" t="inlineStr"/>
-      <c r="D139" s="8" t="inlineStr"/>
-      <c r="E139" s="8" t="inlineStr"/>
-      <c r="F139" s="8" t="inlineStr"/>
-      <c r="G139" s="8" t="inlineStr"/>
-      <c r="H139" s="8" t="inlineStr"/>
-      <c r="I139" s="8" t="inlineStr"/>
-      <c r="J139" s="8" t="inlineStr"/>
-      <c r="K139" s="8" t="inlineStr"/>
-      <c r="L139" s="8" t="inlineStr"/>
-      <c r="M139" s="8" t="inlineStr"/>
+      <c r="B139" s="6" t="inlineStr">
+        <is>
+          <t>三浦理容室</t>
+        </is>
+      </c>
+      <c r="C139" s="6" t="inlineStr">
+        <is>
+          <t>理容室</t>
+        </is>
+      </c>
+      <c r="D139" s="6" t="inlineStr">
+        <is>
+          <t>佐野市</t>
+        </is>
+      </c>
+      <c r="E139" s="6" t="inlineStr">
+        <is>
+          <t>葛生西2-2-19</t>
+        </is>
+      </c>
+      <c r="F139" s="6" t="inlineStr">
+        <is>
+          <t>0283-85-2277</t>
+        </is>
+      </c>
+      <c r="G139" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H139" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I139" s="6" t="inlineStr">
+        <is>
+          <t>NAVITIME 電話帳</t>
+        </is>
+      </c>
+      <c r="J139" s="6" t="inlineStr"/>
+      <c r="K139" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L139" s="6" t="inlineStr"/>
+      <c r="M139" s="6" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" s="5" t="n">
         <v>139</v>
       </c>
-      <c r="B140" s="8" t="inlineStr"/>
-      <c r="C140" s="8" t="inlineStr"/>
-      <c r="D140" s="8" t="inlineStr"/>
-      <c r="E140" s="8" t="inlineStr"/>
-      <c r="F140" s="8" t="inlineStr"/>
-      <c r="G140" s="8" t="inlineStr"/>
-      <c r="H140" s="8" t="inlineStr"/>
-      <c r="I140" s="8" t="inlineStr"/>
-      <c r="J140" s="8" t="inlineStr"/>
-      <c r="K140" s="8" t="inlineStr"/>
-      <c r="L140" s="8" t="inlineStr"/>
-      <c r="M140" s="8" t="inlineStr"/>
+      <c r="B140" s="6" t="inlineStr">
+        <is>
+          <t>美容室Sena西口店</t>
+        </is>
+      </c>
+      <c r="C140" s="6" t="inlineStr">
+        <is>
+          <t>美容室</t>
+        </is>
+      </c>
+      <c r="D140" s="6" t="inlineStr">
+        <is>
+          <t>小山市</t>
+        </is>
+      </c>
+      <c r="E140" s="6" t="inlineStr"/>
+      <c r="F140" s="6" t="inlineStr">
+        <is>
+          <t>0285-22-5741</t>
+        </is>
+      </c>
+      <c r="G140" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H140" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I140" s="6" t="inlineStr">
+        <is>
+          <t>NAVITIME 電話帳</t>
+        </is>
+      </c>
+      <c r="J140" s="6" t="inlineStr"/>
+      <c r="K140" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L140" s="6" t="inlineStr"/>
+      <c r="M140" s="6" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" s="5" t="n">
         <v>140</v>
       </c>
-      <c r="B141" s="8" t="inlineStr"/>
-      <c r="C141" s="8" t="inlineStr"/>
-      <c r="D141" s="8" t="inlineStr"/>
-      <c r="E141" s="8" t="inlineStr"/>
-      <c r="F141" s="8" t="inlineStr"/>
-      <c r="G141" s="8" t="inlineStr"/>
-      <c r="H141" s="8" t="inlineStr"/>
-      <c r="I141" s="8" t="inlineStr"/>
-      <c r="J141" s="8" t="inlineStr"/>
-      <c r="K141" s="8" t="inlineStr"/>
-      <c r="L141" s="8" t="inlineStr"/>
-      <c r="M141" s="8" t="inlineStr"/>
+      <c r="B141" s="6" t="inlineStr">
+        <is>
+          <t>スギモト美容室 小山東口店</t>
+        </is>
+      </c>
+      <c r="C141" s="6" t="inlineStr">
+        <is>
+          <t>美容室</t>
+        </is>
+      </c>
+      <c r="D141" s="6" t="inlineStr">
+        <is>
+          <t>小山市</t>
+        </is>
+      </c>
+      <c r="E141" s="6" t="inlineStr"/>
+      <c r="F141" s="6" t="inlineStr">
+        <is>
+          <t>0285-25-5663</t>
+        </is>
+      </c>
+      <c r="G141" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H141" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I141" s="6" t="inlineStr">
+        <is>
+          <t>NAVITIME 電話帳</t>
+        </is>
+      </c>
+      <c r="J141" s="6" t="inlineStr"/>
+      <c r="K141" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L141" s="6" t="inlineStr"/>
+      <c r="M141" s="6" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" s="5" t="n">
         <v>141</v>
       </c>
-      <c r="B142" s="8" t="inlineStr"/>
-      <c r="C142" s="8" t="inlineStr"/>
-      <c r="D142" s="8" t="inlineStr"/>
-      <c r="E142" s="8" t="inlineStr"/>
-      <c r="F142" s="8" t="inlineStr"/>
-      <c r="G142" s="8" t="inlineStr"/>
-      <c r="H142" s="8" t="inlineStr"/>
-      <c r="I142" s="8" t="inlineStr"/>
-      <c r="J142" s="8" t="inlineStr"/>
-      <c r="K142" s="8" t="inlineStr"/>
-      <c r="L142" s="8" t="inlineStr"/>
-      <c r="M142" s="8" t="inlineStr"/>
+      <c r="B142" s="6" t="inlineStr">
+        <is>
+          <t>ビューティサロン・エル</t>
+        </is>
+      </c>
+      <c r="C142" s="6" t="inlineStr">
+        <is>
+          <t>美容室</t>
+        </is>
+      </c>
+      <c r="D142" s="6" t="inlineStr">
+        <is>
+          <t>小山市</t>
+        </is>
+      </c>
+      <c r="E142" s="6" t="inlineStr"/>
+      <c r="F142" s="6" t="inlineStr">
+        <is>
+          <t>0285-23-3965</t>
+        </is>
+      </c>
+      <c r="G142" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H142" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I142" s="6" t="inlineStr">
+        <is>
+          <t>NAVITIME 電話帳</t>
+        </is>
+      </c>
+      <c r="J142" s="6" t="inlineStr"/>
+      <c r="K142" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L142" s="6" t="inlineStr"/>
+      <c r="M142" s="6" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" s="5" t="n">
         <v>142</v>
       </c>
-      <c r="B143" s="8" t="inlineStr"/>
-      <c r="C143" s="8" t="inlineStr"/>
-      <c r="D143" s="8" t="inlineStr"/>
-      <c r="E143" s="8" t="inlineStr"/>
-      <c r="F143" s="8" t="inlineStr"/>
-      <c r="G143" s="8" t="inlineStr"/>
-      <c r="H143" s="8" t="inlineStr"/>
-      <c r="I143" s="8" t="inlineStr"/>
-      <c r="J143" s="8" t="inlineStr"/>
-      <c r="K143" s="8" t="inlineStr"/>
-      <c r="L143" s="8" t="inlineStr"/>
-      <c r="M143" s="8" t="inlineStr"/>
+      <c r="B143" s="6" t="inlineStr">
+        <is>
+          <t>美容室Hairchouchou</t>
+        </is>
+      </c>
+      <c r="C143" s="6" t="inlineStr">
+        <is>
+          <t>美容室</t>
+        </is>
+      </c>
+      <c r="D143" s="6" t="inlineStr">
+        <is>
+          <t>小山市</t>
+        </is>
+      </c>
+      <c r="E143" s="6" t="inlineStr"/>
+      <c r="F143" s="6" t="inlineStr">
+        <is>
+          <t>0285-25-1041</t>
+        </is>
+      </c>
+      <c r="G143" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H143" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I143" s="6" t="inlineStr">
+        <is>
+          <t>NAVITIME 電話帳</t>
+        </is>
+      </c>
+      <c r="J143" s="6" t="inlineStr"/>
+      <c r="K143" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L143" s="6" t="inlineStr"/>
+      <c r="M143" s="6" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" s="5" t="n">
         <v>143</v>
       </c>
-      <c r="B144" s="8" t="inlineStr"/>
-      <c r="C144" s="8" t="inlineStr"/>
-      <c r="D144" s="8" t="inlineStr"/>
-      <c r="E144" s="8" t="inlineStr"/>
-      <c r="F144" s="8" t="inlineStr"/>
-      <c r="G144" s="8" t="inlineStr"/>
-      <c r="H144" s="8" t="inlineStr"/>
-      <c r="I144" s="8" t="inlineStr"/>
-      <c r="J144" s="8" t="inlineStr"/>
-      <c r="K144" s="8" t="inlineStr"/>
-      <c r="L144" s="8" t="inlineStr"/>
-      <c r="M144" s="8" t="inlineStr"/>
+      <c r="B144" s="6" t="inlineStr">
+        <is>
+          <t>美容室シルエット</t>
+        </is>
+      </c>
+      <c r="C144" s="6" t="inlineStr">
+        <is>
+          <t>美容室</t>
+        </is>
+      </c>
+      <c r="D144" s="6" t="inlineStr">
+        <is>
+          <t>小山市</t>
+        </is>
+      </c>
+      <c r="E144" s="6" t="inlineStr"/>
+      <c r="F144" s="6" t="inlineStr">
+        <is>
+          <t>0285-22-2120</t>
+        </is>
+      </c>
+      <c r="G144" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H144" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I144" s="6" t="inlineStr">
+        <is>
+          <t>NAVITIME 電話帳</t>
+        </is>
+      </c>
+      <c r="J144" s="6" t="inlineStr"/>
+      <c r="K144" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L144" s="6" t="inlineStr"/>
+      <c r="M144" s="6" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" s="5" t="n">
         <v>144</v>
       </c>
-      <c r="B145" s="8" t="inlineStr"/>
-      <c r="C145" s="8" t="inlineStr"/>
-      <c r="D145" s="8" t="inlineStr"/>
-      <c r="E145" s="8" t="inlineStr"/>
-      <c r="F145" s="8" t="inlineStr"/>
-      <c r="G145" s="8" t="inlineStr"/>
-      <c r="H145" s="8" t="inlineStr"/>
-      <c r="I145" s="8" t="inlineStr"/>
-      <c r="J145" s="8" t="inlineStr"/>
-      <c r="K145" s="8" t="inlineStr"/>
-      <c r="L145" s="8" t="inlineStr"/>
-      <c r="M145" s="8" t="inlineStr"/>
+      <c r="B145" s="6" t="inlineStr">
+        <is>
+          <t>ヘアーメモリア</t>
+        </is>
+      </c>
+      <c r="C145" s="6" t="inlineStr">
+        <is>
+          <t>美容室</t>
+        </is>
+      </c>
+      <c r="D145" s="6" t="inlineStr">
+        <is>
+          <t>小山市</t>
+        </is>
+      </c>
+      <c r="E145" s="6" t="inlineStr"/>
+      <c r="F145" s="6" t="inlineStr">
+        <is>
+          <t>0285-39-6499</t>
+        </is>
+      </c>
+      <c r="G145" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H145" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I145" s="6" t="inlineStr">
+        <is>
+          <t>NAVITIME 電話帳</t>
+        </is>
+      </c>
+      <c r="J145" s="6" t="inlineStr"/>
+      <c r="K145" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L145" s="6" t="inlineStr"/>
+      <c r="M145" s="6" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" s="5" t="n">
         <v>145</v>
       </c>
-      <c r="B146" s="8" t="inlineStr"/>
-      <c r="C146" s="8" t="inlineStr"/>
-      <c r="D146" s="8" t="inlineStr"/>
-      <c r="E146" s="8" t="inlineStr"/>
-      <c r="F146" s="8" t="inlineStr"/>
-      <c r="G146" s="8" t="inlineStr"/>
-      <c r="H146" s="8" t="inlineStr"/>
-      <c r="I146" s="8" t="inlineStr"/>
-      <c r="J146" s="8" t="inlineStr"/>
-      <c r="K146" s="8" t="inlineStr"/>
-      <c r="L146" s="8" t="inlineStr"/>
-      <c r="M146" s="8" t="inlineStr"/>
+      <c r="B146" s="6" t="inlineStr">
+        <is>
+          <t>美容室サークル・サークル小山店</t>
+        </is>
+      </c>
+      <c r="C146" s="6" t="inlineStr">
+        <is>
+          <t>美容室</t>
+        </is>
+      </c>
+      <c r="D146" s="6" t="inlineStr">
+        <is>
+          <t>小山市</t>
+        </is>
+      </c>
+      <c r="E146" s="6" t="inlineStr"/>
+      <c r="F146" s="6" t="inlineStr">
+        <is>
+          <t>0285-25-0960</t>
+        </is>
+      </c>
+      <c r="G146" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H146" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I146" s="6" t="inlineStr">
+        <is>
+          <t>NAVITIME 電話帳</t>
+        </is>
+      </c>
+      <c r="J146" s="6" t="inlineStr"/>
+      <c r="K146" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L146" s="6" t="inlineStr"/>
+      <c r="M146" s="6" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="5" t="n">
+        <v>146</v>
+      </c>
+      <c r="B147" s="6" t="inlineStr">
+        <is>
+          <t>アイスキャンディーNATURALBEAUTY</t>
+        </is>
+      </c>
+      <c r="C147" s="6" t="inlineStr">
+        <is>
+          <t>美容室</t>
+        </is>
+      </c>
+      <c r="D147" s="6" t="inlineStr">
+        <is>
+          <t>小山市</t>
+        </is>
+      </c>
+      <c r="E147" s="6" t="inlineStr"/>
+      <c r="F147" s="6" t="inlineStr">
+        <is>
+          <t>0285-23-8723</t>
+        </is>
+      </c>
+      <c r="G147" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H147" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I147" s="6" t="inlineStr">
+        <is>
+          <t>NAVITIME 電話帳</t>
+        </is>
+      </c>
+      <c r="J147" s="6" t="inlineStr"/>
+      <c r="K147" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L147" s="6" t="inlineStr"/>
+      <c r="M147" s="6" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="5" t="n">
+        <v>147</v>
+      </c>
+      <c r="B148" s="6" t="inlineStr">
+        <is>
+          <t>Agu hair rothes小山駅東通り店</t>
+        </is>
+      </c>
+      <c r="C148" s="6" t="inlineStr">
+        <is>
+          <t>美容室</t>
+        </is>
+      </c>
+      <c r="D148" s="6" t="inlineStr">
+        <is>
+          <t>小山市</t>
+        </is>
+      </c>
+      <c r="E148" s="6" t="inlineStr">
+        <is>
+          <t>駅東通り</t>
+        </is>
+      </c>
+      <c r="F148" s="6" t="inlineStr">
+        <is>
+          <t>0285-39-6969</t>
+        </is>
+      </c>
+      <c r="G148" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H148" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I148" s="6" t="inlineStr">
+        <is>
+          <t>NAVITIME 電話帳</t>
+        </is>
+      </c>
+      <c r="J148" s="6" t="inlineStr"/>
+      <c r="K148" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L148" s="6" t="inlineStr"/>
+      <c r="M148" s="6" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="5" t="n">
+        <v>148</v>
+      </c>
+      <c r="B149" s="6" t="inlineStr">
+        <is>
+          <t>美容室コレクション</t>
+        </is>
+      </c>
+      <c r="C149" s="6" t="inlineStr">
+        <is>
+          <t>美容室</t>
+        </is>
+      </c>
+      <c r="D149" s="6" t="inlineStr">
+        <is>
+          <t>小山市</t>
+        </is>
+      </c>
+      <c r="E149" s="6" t="inlineStr"/>
+      <c r="F149" s="6" t="inlineStr">
+        <is>
+          <t>0285-22-1990</t>
+        </is>
+      </c>
+      <c r="G149" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H149" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I149" s="6" t="inlineStr">
+        <is>
+          <t>NAVITIME 電話帳</t>
+        </is>
+      </c>
+      <c r="J149" s="6" t="inlineStr"/>
+      <c r="K149" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L149" s="6" t="inlineStr"/>
+      <c r="M149" s="6" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="5" t="n">
+        <v>149</v>
+      </c>
+      <c r="B150" s="6" t="inlineStr">
+        <is>
+          <t>美容室イフ</t>
+        </is>
+      </c>
+      <c r="C150" s="6" t="inlineStr">
+        <is>
+          <t>美容室</t>
+        </is>
+      </c>
+      <c r="D150" s="6" t="inlineStr">
+        <is>
+          <t>小山市</t>
+        </is>
+      </c>
+      <c r="E150" s="6" t="inlineStr"/>
+      <c r="F150" s="6" t="inlineStr">
+        <is>
+          <t>0285-27-9696</t>
+        </is>
+      </c>
+      <c r="G150" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H150" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I150" s="6" t="inlineStr">
+        <is>
+          <t>NAVITIME 電話帳</t>
+        </is>
+      </c>
+      <c r="J150" s="6" t="inlineStr"/>
+      <c r="K150" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L150" s="6" t="inlineStr"/>
+      <c r="M150" s="6" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="5" t="n">
+        <v>150</v>
+      </c>
+      <c r="B151" s="6" t="inlineStr">
+        <is>
+          <t>美容室ルル(LouLou)</t>
+        </is>
+      </c>
+      <c r="C151" s="6" t="inlineStr">
+        <is>
+          <t>美容室</t>
+        </is>
+      </c>
+      <c r="D151" s="6" t="inlineStr">
+        <is>
+          <t>小山市</t>
+        </is>
+      </c>
+      <c r="E151" s="6" t="inlineStr"/>
+      <c r="F151" s="6" t="inlineStr">
+        <is>
+          <t>0285-39-7738</t>
+        </is>
+      </c>
+      <c r="G151" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H151" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I151" s="6" t="inlineStr">
+        <is>
+          <t>NAVITIME 電話帳</t>
+        </is>
+      </c>
+      <c r="J151" s="6" t="inlineStr"/>
+      <c r="K151" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L151" s="6" t="inlineStr"/>
+      <c r="M151" s="6" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="5" t="n">
+        <v>151</v>
+      </c>
+      <c r="B152" s="6" t="inlineStr">
+        <is>
+          <t>大出理容所</t>
+        </is>
+      </c>
+      <c r="C152" s="6" t="inlineStr">
+        <is>
+          <t>理容室</t>
+        </is>
+      </c>
+      <c r="D152" s="6" t="inlineStr">
+        <is>
+          <t>小山市</t>
+        </is>
+      </c>
+      <c r="E152" s="6" t="inlineStr"/>
+      <c r="F152" s="6" t="inlineStr">
+        <is>
+          <t>0285-45-0312</t>
+        </is>
+      </c>
+      <c r="G152" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H152" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I152" s="6" t="inlineStr">
+        <is>
+          <t>NAVITIME 電話帳</t>
+        </is>
+      </c>
+      <c r="J152" s="6" t="inlineStr"/>
+      <c r="K152" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L152" s="6" t="inlineStr"/>
+      <c r="M152" s="6" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="5" t="n">
+        <v>152</v>
+      </c>
+      <c r="B153" s="6" t="inlineStr">
+        <is>
+          <t>大島理容店</t>
+        </is>
+      </c>
+      <c r="C153" s="6" t="inlineStr">
+        <is>
+          <t>理容室</t>
+        </is>
+      </c>
+      <c r="D153" s="6" t="inlineStr">
+        <is>
+          <t>小山市</t>
+        </is>
+      </c>
+      <c r="E153" s="6" t="inlineStr"/>
+      <c r="F153" s="6" t="inlineStr">
+        <is>
+          <t>0285-23-3485</t>
+        </is>
+      </c>
+      <c r="G153" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H153" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I153" s="6" t="inlineStr">
+        <is>
+          <t>NAVITIME 電話帳</t>
+        </is>
+      </c>
+      <c r="J153" s="6" t="inlineStr"/>
+      <c r="K153" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L153" s="6" t="inlineStr"/>
+      <c r="M153" s="6" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="5" t="n">
+        <v>153</v>
+      </c>
+      <c r="B154" s="6" t="inlineStr">
+        <is>
+          <t>いたばし</t>
+        </is>
+      </c>
+      <c r="C154" s="6" t="inlineStr">
+        <is>
+          <t>理容室</t>
+        </is>
+      </c>
+      <c r="D154" s="6" t="inlineStr">
+        <is>
+          <t>小山市</t>
+        </is>
+      </c>
+      <c r="E154" s="6" t="inlineStr"/>
+      <c r="F154" s="6" t="inlineStr">
+        <is>
+          <t>0285-37-0160</t>
+        </is>
+      </c>
+      <c r="G154" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H154" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I154" s="6" t="inlineStr">
+        <is>
+          <t>NAVITIME 電話帳</t>
+        </is>
+      </c>
+      <c r="J154" s="6" t="inlineStr"/>
+      <c r="K154" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L154" s="6" t="inlineStr"/>
+      <c r="M154" s="6" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="5" t="n">
+        <v>154</v>
+      </c>
+      <c r="B155" s="6" t="inlineStr">
+        <is>
+          <t>小野口理容室</t>
+        </is>
+      </c>
+      <c r="C155" s="6" t="inlineStr">
+        <is>
+          <t>理容室</t>
+        </is>
+      </c>
+      <c r="D155" s="6" t="inlineStr">
+        <is>
+          <t>小山市</t>
+        </is>
+      </c>
+      <c r="E155" s="6" t="inlineStr"/>
+      <c r="F155" s="6" t="inlineStr">
+        <is>
+          <t>0285-25-5706</t>
+        </is>
+      </c>
+      <c r="G155" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H155" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I155" s="6" t="inlineStr">
+        <is>
+          <t>NAVITIME 電話帳</t>
+        </is>
+      </c>
+      <c r="J155" s="6" t="inlineStr"/>
+      <c r="K155" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L155" s="6" t="inlineStr"/>
+      <c r="M155" s="6" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="5" t="n">
+        <v>155</v>
+      </c>
+      <c r="B156" s="6" t="inlineStr">
+        <is>
+          <t>GINZASFEEL小山店</t>
+        </is>
+      </c>
+      <c r="C156" s="6" t="inlineStr">
+        <is>
+          <t>理容室</t>
+        </is>
+      </c>
+      <c r="D156" s="6" t="inlineStr">
+        <is>
+          <t>小山市</t>
+        </is>
+      </c>
+      <c r="E156" s="6" t="inlineStr">
+        <is>
+          <t>駅東通り</t>
+        </is>
+      </c>
+      <c r="F156" s="6" t="inlineStr">
+        <is>
+          <t>0285-23-8807</t>
+        </is>
+      </c>
+      <c r="G156" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H156" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I156" s="6" t="inlineStr">
+        <is>
+          <t>NAVITIME 電話帳</t>
+        </is>
+      </c>
+      <c r="J156" s="6" t="inlineStr"/>
+      <c r="K156" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L156" s="6" t="inlineStr"/>
+      <c r="M156" s="6" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="5" t="n">
+        <v>156</v>
+      </c>
+      <c r="B157" s="6" t="inlineStr">
+        <is>
+          <t>BarBerAI</t>
+        </is>
+      </c>
+      <c r="C157" s="6" t="inlineStr">
+        <is>
+          <t>理容室</t>
+        </is>
+      </c>
+      <c r="D157" s="6" t="inlineStr">
+        <is>
+          <t>小山市</t>
+        </is>
+      </c>
+      <c r="E157" s="6" t="inlineStr">
+        <is>
+          <t>駅東通り</t>
+        </is>
+      </c>
+      <c r="F157" s="6" t="inlineStr">
+        <is>
+          <t>070-3350-2075</t>
+        </is>
+      </c>
+      <c r="G157" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H157" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I157" s="6" t="inlineStr">
+        <is>
+          <t>NAVITIME 電話帳</t>
+        </is>
+      </c>
+      <c r="J157" s="6" t="inlineStr"/>
+      <c r="K157" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L157" s="6" t="inlineStr"/>
+      <c r="M157" s="6" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="5" t="n">
+        <v>157</v>
+      </c>
+      <c r="B158" s="6" t="inlineStr">
+        <is>
+          <t>カール理容室</t>
+        </is>
+      </c>
+      <c r="C158" s="6" t="inlineStr">
+        <is>
+          <t>理容室</t>
+        </is>
+      </c>
+      <c r="D158" s="6" t="inlineStr">
+        <is>
+          <t>小山市</t>
+        </is>
+      </c>
+      <c r="E158" s="6" t="inlineStr">
+        <is>
+          <t>駅東通り</t>
+        </is>
+      </c>
+      <c r="F158" s="6" t="inlineStr">
+        <is>
+          <t>0285-22-8822</t>
+        </is>
+      </c>
+      <c r="G158" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H158" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I158" s="6" t="inlineStr">
+        <is>
+          <t>NAVITIME 電話帳</t>
+        </is>
+      </c>
+      <c r="J158" s="6" t="inlineStr"/>
+      <c r="K158" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L158" s="6" t="inlineStr"/>
+      <c r="M158" s="6" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="5" t="n">
+        <v>158</v>
+      </c>
+      <c r="B159" s="6" t="inlineStr">
+        <is>
+          <t>OHNUKI Refine</t>
+        </is>
+      </c>
+      <c r="C159" s="6" t="inlineStr">
+        <is>
+          <t>理容室</t>
+        </is>
+      </c>
+      <c r="D159" s="6" t="inlineStr">
+        <is>
+          <t>小山市</t>
+        </is>
+      </c>
+      <c r="E159" s="6" t="inlineStr">
+        <is>
+          <t>駅東通り</t>
+        </is>
+      </c>
+      <c r="F159" s="6" t="inlineStr">
+        <is>
+          <t>0120-74-4910</t>
+        </is>
+      </c>
+      <c r="G159" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H159" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I159" s="6" t="inlineStr">
+        <is>
+          <t>NAVITIME 電話帳</t>
+        </is>
+      </c>
+      <c r="J159" s="6" t="inlineStr"/>
+      <c r="K159" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L159" s="6" t="inlineStr"/>
+      <c r="M159" s="6" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="5" t="n">
+        <v>159</v>
+      </c>
+      <c r="B160" s="6" t="inlineStr">
+        <is>
+          <t>美容室コレクション足利店</t>
+        </is>
+      </c>
+      <c r="C160" s="6" t="inlineStr">
+        <is>
+          <t>美容室</t>
+        </is>
+      </c>
+      <c r="D160" s="6" t="inlineStr">
+        <is>
+          <t>足利市</t>
+        </is>
+      </c>
+      <c r="E160" s="6" t="inlineStr"/>
+      <c r="F160" s="6" t="inlineStr">
+        <is>
+          <t>0284-40-3266</t>
+        </is>
+      </c>
+      <c r="G160" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H160" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I160" s="6" t="inlineStr">
+        <is>
+          <t>NAVITIME 電話帳</t>
+        </is>
+      </c>
+      <c r="J160" s="6" t="inlineStr"/>
+      <c r="K160" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L160" s="6" t="inlineStr"/>
+      <c r="M160" s="6" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="5" t="n">
+        <v>160</v>
+      </c>
+      <c r="B161" s="6" t="inlineStr">
+        <is>
+          <t>美容室アトリエAIRプラス</t>
+        </is>
+      </c>
+      <c r="C161" s="6" t="inlineStr">
+        <is>
+          <t>美容室</t>
+        </is>
+      </c>
+      <c r="D161" s="6" t="inlineStr">
+        <is>
+          <t>足利市</t>
+        </is>
+      </c>
+      <c r="E161" s="6" t="inlineStr"/>
+      <c r="F161" s="6" t="inlineStr">
+        <is>
+          <t>0284-41-2723</t>
+        </is>
+      </c>
+      <c r="G161" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H161" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I161" s="6" t="inlineStr">
+        <is>
+          <t>NAVITIME 電話帳</t>
+        </is>
+      </c>
+      <c r="J161" s="6" t="inlineStr"/>
+      <c r="K161" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L161" s="6" t="inlineStr"/>
+      <c r="M161" s="6" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="5" t="n">
+        <v>161</v>
+      </c>
+      <c r="B162" s="6" t="inlineStr">
+        <is>
+          <t>のり美容室</t>
+        </is>
+      </c>
+      <c r="C162" s="6" t="inlineStr">
+        <is>
+          <t>美容室</t>
+        </is>
+      </c>
+      <c r="D162" s="6" t="inlineStr">
+        <is>
+          <t>足利市</t>
+        </is>
+      </c>
+      <c r="E162" s="6" t="inlineStr"/>
+      <c r="F162" s="6" t="inlineStr">
+        <is>
+          <t>0284-21-5902</t>
+        </is>
+      </c>
+      <c r="G162" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H162" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I162" s="6" t="inlineStr">
+        <is>
+          <t>NAVITIME 電話帳</t>
+        </is>
+      </c>
+      <c r="J162" s="6" t="inlineStr"/>
+      <c r="K162" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L162" s="6" t="inlineStr"/>
+      <c r="M162" s="6" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="5" t="n">
+        <v>162</v>
+      </c>
+      <c r="B163" s="6" t="inlineStr">
+        <is>
+          <t>美容室ドットコム</t>
+        </is>
+      </c>
+      <c r="C163" s="6" t="inlineStr">
+        <is>
+          <t>美容室</t>
+        </is>
+      </c>
+      <c r="D163" s="6" t="inlineStr">
+        <is>
+          <t>足利市</t>
+        </is>
+      </c>
+      <c r="E163" s="6" t="inlineStr"/>
+      <c r="F163" s="6" t="inlineStr">
+        <is>
+          <t>0284-41-1335</t>
+        </is>
+      </c>
+      <c r="G163" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H163" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I163" s="6" t="inlineStr">
+        <is>
+          <t>NAVITIME 電話帳</t>
+        </is>
+      </c>
+      <c r="J163" s="6" t="inlineStr"/>
+      <c r="K163" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L163" s="6" t="inlineStr"/>
+      <c r="M163" s="6" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="5" t="n">
+        <v>163</v>
+      </c>
+      <c r="B164" s="6" t="inlineStr">
+        <is>
+          <t>美容室ラファエロ</t>
+        </is>
+      </c>
+      <c r="C164" s="6" t="inlineStr">
+        <is>
+          <t>美容室</t>
+        </is>
+      </c>
+      <c r="D164" s="6" t="inlineStr">
+        <is>
+          <t>足利市</t>
+        </is>
+      </c>
+      <c r="E164" s="6" t="inlineStr"/>
+      <c r="F164" s="6" t="inlineStr">
+        <is>
+          <t>0284-91-3131</t>
+        </is>
+      </c>
+      <c r="G164" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H164" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I164" s="6" t="inlineStr">
+        <is>
+          <t>NAVITIME 電話帳</t>
+        </is>
+      </c>
+      <c r="J164" s="6" t="inlineStr"/>
+      <c r="K164" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L164" s="6" t="inlineStr"/>
+      <c r="M164" s="6" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="5" t="n">
+        <v>164</v>
+      </c>
+      <c r="B165" s="6" t="inlineStr">
+        <is>
+          <t>タマ美容室</t>
+        </is>
+      </c>
+      <c r="C165" s="6" t="inlineStr">
+        <is>
+          <t>美容室</t>
+        </is>
+      </c>
+      <c r="D165" s="6" t="inlineStr">
+        <is>
+          <t>足利市</t>
+        </is>
+      </c>
+      <c r="E165" s="6" t="inlineStr"/>
+      <c r="F165" s="6" t="inlineStr">
+        <is>
+          <t>0284-71-5756</t>
+        </is>
+      </c>
+      <c r="G165" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H165" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I165" s="6" t="inlineStr">
+        <is>
+          <t>NAVITIME 電話帳</t>
+        </is>
+      </c>
+      <c r="J165" s="6" t="inlineStr"/>
+      <c r="K165" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L165" s="6" t="inlineStr"/>
+      <c r="M165" s="6" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="5" t="n">
+        <v>165</v>
+      </c>
+      <c r="B166" s="6" t="inlineStr">
+        <is>
+          <t>メローズ美容室</t>
+        </is>
+      </c>
+      <c r="C166" s="6" t="inlineStr">
+        <is>
+          <t>美容室</t>
+        </is>
+      </c>
+      <c r="D166" s="6" t="inlineStr">
+        <is>
+          <t>足利市</t>
+        </is>
+      </c>
+      <c r="E166" s="6" t="inlineStr"/>
+      <c r="F166" s="6" t="inlineStr">
+        <is>
+          <t>0284-91-2521</t>
+        </is>
+      </c>
+      <c r="G166" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H166" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I166" s="6" t="inlineStr">
+        <is>
+          <t>NAVITIME 電話帳</t>
+        </is>
+      </c>
+      <c r="J166" s="6" t="inlineStr"/>
+      <c r="K166" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L166" s="6" t="inlineStr"/>
+      <c r="M166" s="6" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="5" t="n">
+        <v>166</v>
+      </c>
+      <c r="B167" s="6" t="inlineStr">
+        <is>
+          <t>HAIR Firstclass足利店</t>
+        </is>
+      </c>
+      <c r="C167" s="6" t="inlineStr">
+        <is>
+          <t>美容室</t>
+        </is>
+      </c>
+      <c r="D167" s="6" t="inlineStr">
+        <is>
+          <t>足利市</t>
+        </is>
+      </c>
+      <c r="E167" s="6" t="inlineStr"/>
+      <c r="F167" s="6" t="inlineStr">
+        <is>
+          <t>0284-72-2277</t>
+        </is>
+      </c>
+      <c r="G167" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H167" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I167" s="6" t="inlineStr">
+        <is>
+          <t>NAVITIME 電話帳</t>
+        </is>
+      </c>
+      <c r="J167" s="6" t="inlineStr"/>
+      <c r="K167" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L167" s="6" t="inlineStr"/>
+      <c r="M167" s="6" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="5" t="n">
+        <v>167</v>
+      </c>
+      <c r="B168" s="6" t="inlineStr">
+        <is>
+          <t>石坂理容院</t>
+        </is>
+      </c>
+      <c r="C168" s="6" t="inlineStr">
+        <is>
+          <t>理容室</t>
+        </is>
+      </c>
+      <c r="D168" s="6" t="inlineStr">
+        <is>
+          <t>足利市</t>
+        </is>
+      </c>
+      <c r="E168" s="6" t="inlineStr">
+        <is>
+          <t>福居町650-6</t>
+        </is>
+      </c>
+      <c r="F168" s="6" t="inlineStr">
+        <is>
+          <t>0284-71-1611</t>
+        </is>
+      </c>
+      <c r="G168" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H168" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I168" s="6" t="inlineStr">
+        <is>
+          <t>NAVITIME 電話帳</t>
+        </is>
+      </c>
+      <c r="J168" s="6" t="inlineStr"/>
+      <c r="K168" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L168" s="6" t="inlineStr"/>
+      <c r="M168" s="6" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="5" t="n">
+        <v>168</v>
+      </c>
+      <c r="B169" s="6" t="inlineStr">
+        <is>
+          <t>石井理容所</t>
+        </is>
+      </c>
+      <c r="C169" s="6" t="inlineStr">
+        <is>
+          <t>理容室</t>
+        </is>
+      </c>
+      <c r="D169" s="6" t="inlineStr">
+        <is>
+          <t>足利市</t>
+        </is>
+      </c>
+      <c r="E169" s="6" t="inlineStr">
+        <is>
+          <t>通4-2798</t>
+        </is>
+      </c>
+      <c r="F169" s="6" t="inlineStr">
+        <is>
+          <t>0284-21-5744</t>
+        </is>
+      </c>
+      <c r="G169" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H169" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I169" s="6" t="inlineStr">
+        <is>
+          <t>NAVITIME 電話帳</t>
+        </is>
+      </c>
+      <c r="J169" s="6" t="inlineStr"/>
+      <c r="K169" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L169" s="6" t="inlineStr"/>
+      <c r="M169" s="6" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="5" t="n">
+        <v>169</v>
+      </c>
+      <c r="B170" s="6" t="inlineStr">
+        <is>
+          <t>内山理容所</t>
+        </is>
+      </c>
+      <c r="C170" s="6" t="inlineStr">
+        <is>
+          <t>理容室</t>
+        </is>
+      </c>
+      <c r="D170" s="6" t="inlineStr">
+        <is>
+          <t>足利市</t>
+        </is>
+      </c>
+      <c r="E170" s="6" t="inlineStr">
+        <is>
+          <t>毛野新町3-13</t>
+        </is>
+      </c>
+      <c r="F170" s="6" t="inlineStr">
+        <is>
+          <t>0284-42-3147</t>
+        </is>
+      </c>
+      <c r="G170" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H170" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I170" s="6" t="inlineStr">
+        <is>
+          <t>NAVITIME 電話帳</t>
+        </is>
+      </c>
+      <c r="J170" s="6" t="inlineStr"/>
+      <c r="K170" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L170" s="6" t="inlineStr"/>
+      <c r="M170" s="6" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="5" t="n">
+        <v>170</v>
+      </c>
+      <c r="B171" s="6" t="inlineStr">
+        <is>
+          <t>ハル理容室</t>
+        </is>
+      </c>
+      <c r="C171" s="6" t="inlineStr">
+        <is>
+          <t>理容室</t>
+        </is>
+      </c>
+      <c r="D171" s="6" t="inlineStr">
+        <is>
+          <t>足利市</t>
+        </is>
+      </c>
+      <c r="E171" s="6" t="inlineStr">
+        <is>
+          <t>山川町949-1</t>
+        </is>
+      </c>
+      <c r="F171" s="6" t="inlineStr">
+        <is>
+          <t>0284-41-5615</t>
+        </is>
+      </c>
+      <c r="G171" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H171" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I171" s="6" t="inlineStr">
+        <is>
+          <t>NAVITIME 電話帳</t>
+        </is>
+      </c>
+      <c r="J171" s="6" t="inlineStr"/>
+      <c r="K171" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L171" s="6" t="inlineStr"/>
+      <c r="M171" s="6" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="5" t="n">
+        <v>171</v>
+      </c>
+      <c r="B172" s="6" t="inlineStr">
+        <is>
+          <t>ひかりヘアースタジオ</t>
+        </is>
+      </c>
+      <c r="C172" s="6" t="inlineStr">
+        <is>
+          <t>理容室</t>
+        </is>
+      </c>
+      <c r="D172" s="6" t="inlineStr">
+        <is>
+          <t>足利市</t>
+        </is>
+      </c>
+      <c r="E172" s="6" t="inlineStr">
+        <is>
+          <t>山川町2-15</t>
+        </is>
+      </c>
+      <c r="F172" s="6" t="inlineStr">
+        <is>
+          <t>0284-42-3660</t>
+        </is>
+      </c>
+      <c r="G172" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H172" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I172" s="6" t="inlineStr">
+        <is>
+          <t>NAVITIME 電話帳</t>
+        </is>
+      </c>
+      <c r="J172" s="6" t="inlineStr"/>
+      <c r="K172" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L172" s="6" t="inlineStr"/>
+      <c r="M172" s="6" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="5" t="n">
+        <v>172</v>
+      </c>
+      <c r="B173" s="6" t="inlineStr">
+        <is>
+          <t>サニー理容室</t>
+        </is>
+      </c>
+      <c r="C173" s="6" t="inlineStr">
+        <is>
+          <t>理容室</t>
+        </is>
+      </c>
+      <c r="D173" s="6" t="inlineStr">
+        <is>
+          <t>足利市</t>
+        </is>
+      </c>
+      <c r="E173" s="6" t="inlineStr">
+        <is>
+          <t>山川町8-6</t>
+        </is>
+      </c>
+      <c r="F173" s="6" t="inlineStr">
+        <is>
+          <t>0284-42-1453</t>
+        </is>
+      </c>
+      <c r="G173" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H173" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I173" s="6" t="inlineStr">
+        <is>
+          <t>NAVITIME 電話帳</t>
+        </is>
+      </c>
+      <c r="J173" s="6" t="inlineStr"/>
+      <c r="K173" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L173" s="6" t="inlineStr"/>
+      <c r="M173" s="6" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="5" t="n">
+        <v>173</v>
+      </c>
+      <c r="B174" s="6" t="inlineStr">
+        <is>
+          <t>ヘアーカットシープ</t>
+        </is>
+      </c>
+      <c r="C174" s="6" t="inlineStr">
+        <is>
+          <t>理容室</t>
+        </is>
+      </c>
+      <c r="D174" s="6" t="inlineStr">
+        <is>
+          <t>足利市</t>
+        </is>
+      </c>
+      <c r="E174" s="6" t="inlineStr">
+        <is>
+          <t>八幡町1-22-15</t>
+        </is>
+      </c>
+      <c r="F174" s="6" t="inlineStr">
+        <is>
+          <t>0284-72-2900</t>
+        </is>
+      </c>
+      <c r="G174" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H174" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I174" s="6" t="inlineStr">
+        <is>
+          <t>NAVITIME 電話帳</t>
+        </is>
+      </c>
+      <c r="J174" s="6" t="inlineStr"/>
+      <c r="K174" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L174" s="6" t="inlineStr"/>
+      <c r="M174" s="6" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="5" t="n">
+        <v>174</v>
+      </c>
+      <c r="B175" s="6" t="inlineStr">
+        <is>
+          <t>ヘアー・ファクトリー</t>
+        </is>
+      </c>
+      <c r="C175" s="6" t="inlineStr">
+        <is>
+          <t>理容室</t>
+        </is>
+      </c>
+      <c r="D175" s="6" t="inlineStr">
+        <is>
+          <t>足利市</t>
+        </is>
+      </c>
+      <c r="E175" s="6" t="inlineStr">
+        <is>
+          <t>福居町631-2</t>
+        </is>
+      </c>
+      <c r="F175" s="6" t="inlineStr">
+        <is>
+          <t>0284-72-3932</t>
+        </is>
+      </c>
+      <c r="G175" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H175" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I175" s="6" t="inlineStr">
+        <is>
+          <t>NAVITIME 電話帳</t>
+        </is>
+      </c>
+      <c r="J175" s="6" t="inlineStr"/>
+      <c r="K175" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L175" s="6" t="inlineStr"/>
+      <c r="M175" s="6" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" s="5" t="n">
+        <v>175</v>
+      </c>
+      <c r="B176" s="6" t="inlineStr">
+        <is>
+          <t>やまざき美容室</t>
+        </is>
+      </c>
+      <c r="C176" s="6" t="inlineStr">
+        <is>
+          <t>美容室</t>
+        </is>
+      </c>
+      <c r="D176" s="6" t="inlineStr">
+        <is>
+          <t>日光市</t>
+        </is>
+      </c>
+      <c r="E176" s="6" t="inlineStr">
+        <is>
+          <t>今市374-9</t>
+        </is>
+      </c>
+      <c r="F176" s="6" t="inlineStr">
+        <is>
+          <t>0288-21-0577</t>
+        </is>
+      </c>
+      <c r="G176" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H176" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I176" s="6" t="inlineStr">
+        <is>
+          <t>NAVITIME 電話帳</t>
+        </is>
+      </c>
+      <c r="J176" s="6" t="inlineStr"/>
+      <c r="K176" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L176" s="6" t="inlineStr"/>
+      <c r="M176" s="6" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" s="5" t="n">
+        <v>176</v>
+      </c>
+      <c r="B177" s="6" t="inlineStr">
+        <is>
+          <t>髪細工美容室</t>
+        </is>
+      </c>
+      <c r="C177" s="6" t="inlineStr">
+        <is>
+          <t>美容室</t>
+        </is>
+      </c>
+      <c r="D177" s="6" t="inlineStr">
+        <is>
+          <t>日光市</t>
+        </is>
+      </c>
+      <c r="E177" s="6" t="inlineStr">
+        <is>
+          <t>今市1100-12</t>
+        </is>
+      </c>
+      <c r="F177" s="6" t="inlineStr">
+        <is>
+          <t>0288-22-1879</t>
+        </is>
+      </c>
+      <c r="G177" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H177" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I177" s="6" t="inlineStr">
+        <is>
+          <t>NAVITIME 電話帳</t>
+        </is>
+      </c>
+      <c r="J177" s="6" t="inlineStr"/>
+      <c r="K177" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L177" s="6" t="inlineStr"/>
+      <c r="M177" s="6" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="5" t="n">
+        <v>177</v>
+      </c>
+      <c r="B178" s="6" t="inlineStr">
+        <is>
+          <t>セピア美容室</t>
+        </is>
+      </c>
+      <c r="C178" s="6" t="inlineStr">
+        <is>
+          <t>美容室</t>
+        </is>
+      </c>
+      <c r="D178" s="6" t="inlineStr">
+        <is>
+          <t>日光市</t>
+        </is>
+      </c>
+      <c r="E178" s="6" t="inlineStr">
+        <is>
+          <t>今市1430</t>
+        </is>
+      </c>
+      <c r="F178" s="6" t="inlineStr">
+        <is>
+          <t>0288-22-4859</t>
+        </is>
+      </c>
+      <c r="G178" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H178" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I178" s="6" t="inlineStr">
+        <is>
+          <t>NAVITIME 電話帳</t>
+        </is>
+      </c>
+      <c r="J178" s="6" t="inlineStr"/>
+      <c r="K178" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L178" s="6" t="inlineStr"/>
+      <c r="M178" s="6" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="5" t="n">
+        <v>178</v>
+      </c>
+      <c r="B179" s="6" t="inlineStr">
+        <is>
+          <t>あけみ美容室</t>
+        </is>
+      </c>
+      <c r="C179" s="6" t="inlineStr">
+        <is>
+          <t>美容室</t>
+        </is>
+      </c>
+      <c r="D179" s="6" t="inlineStr">
+        <is>
+          <t>日光市</t>
+        </is>
+      </c>
+      <c r="E179" s="6" t="inlineStr">
+        <is>
+          <t>今市1371-2</t>
+        </is>
+      </c>
+      <c r="F179" s="6" t="inlineStr">
+        <is>
+          <t>0288-21-2912</t>
+        </is>
+      </c>
+      <c r="G179" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H179" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I179" s="6" t="inlineStr">
+        <is>
+          <t>NAVITIME 電話帳</t>
+        </is>
+      </c>
+      <c r="J179" s="6" t="inlineStr"/>
+      <c r="K179" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L179" s="6" t="inlineStr"/>
+      <c r="M179" s="6" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="5" t="n">
+        <v>179</v>
+      </c>
+      <c r="B180" s="6" t="inlineStr">
+        <is>
+          <t>Agu hair lgin日光店</t>
+        </is>
+      </c>
+      <c r="C180" s="6" t="inlineStr">
+        <is>
+          <t>美容室</t>
+        </is>
+      </c>
+      <c r="D180" s="6" t="inlineStr">
+        <is>
+          <t>日光市</t>
+        </is>
+      </c>
+      <c r="E180" s="6" t="inlineStr">
+        <is>
+          <t>今市1233-1</t>
+        </is>
+      </c>
+      <c r="F180" s="6" t="inlineStr">
+        <is>
+          <t>0288-25-7381</t>
+        </is>
+      </c>
+      <c r="G180" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H180" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I180" s="6" t="inlineStr">
+        <is>
+          <t>NAVITIME 電話帳</t>
+        </is>
+      </c>
+      <c r="J180" s="6" t="inlineStr"/>
+      <c r="K180" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L180" s="6" t="inlineStr"/>
+      <c r="M180" s="6" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="5" t="n">
+        <v>180</v>
+      </c>
+      <c r="B181" s="6" t="inlineStr">
+        <is>
+          <t>ヘアーデザインVIVID</t>
+        </is>
+      </c>
+      <c r="C181" s="6" t="inlineStr">
+        <is>
+          <t>美容室</t>
+        </is>
+      </c>
+      <c r="D181" s="6" t="inlineStr">
+        <is>
+          <t>日光市</t>
+        </is>
+      </c>
+      <c r="E181" s="6" t="inlineStr">
+        <is>
+          <t>今市1164-1</t>
+        </is>
+      </c>
+      <c r="F181" s="6" t="inlineStr">
+        <is>
+          <t>0288-21-5003</t>
+        </is>
+      </c>
+      <c r="G181" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H181" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I181" s="6" t="inlineStr">
+        <is>
+          <t>NAVITIME 電話帳</t>
+        </is>
+      </c>
+      <c r="J181" s="6" t="inlineStr"/>
+      <c r="K181" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L181" s="6" t="inlineStr"/>
+      <c r="M181" s="6" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="5" t="n">
+        <v>181</v>
+      </c>
+      <c r="B182" s="6" t="inlineStr">
+        <is>
+          <t>TAKAHASHI理容室</t>
+        </is>
+      </c>
+      <c r="C182" s="6" t="inlineStr">
+        <is>
+          <t>理容室</t>
+        </is>
+      </c>
+      <c r="D182" s="6" t="inlineStr">
+        <is>
+          <t>日光市</t>
+        </is>
+      </c>
+      <c r="E182" s="6" t="inlineStr">
+        <is>
+          <t>今市1659-219</t>
+        </is>
+      </c>
+      <c r="F182" s="6" t="inlineStr">
+        <is>
+          <t>0288-21-0394</t>
+        </is>
+      </c>
+      <c r="G182" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H182" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I182" s="6" t="inlineStr">
+        <is>
+          <t>NAVITIME 電話帳</t>
+        </is>
+      </c>
+      <c r="J182" s="6" t="inlineStr"/>
+      <c r="K182" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L182" s="6" t="inlineStr"/>
+      <c r="M182" s="6" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="5" t="n">
+        <v>182</v>
+      </c>
+      <c r="B183" s="6" t="inlineStr">
+        <is>
+          <t>伊谷理容店</t>
+        </is>
+      </c>
+      <c r="C183" s="6" t="inlineStr">
+        <is>
+          <t>理容室</t>
+        </is>
+      </c>
+      <c r="D183" s="6" t="inlineStr">
+        <is>
+          <t>日光市</t>
+        </is>
+      </c>
+      <c r="E183" s="6" t="inlineStr">
+        <is>
+          <t>久次良町122-8</t>
+        </is>
+      </c>
+      <c r="F183" s="6" t="inlineStr">
+        <is>
+          <t>0288-53-3736</t>
+        </is>
+      </c>
+      <c r="G183" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H183" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I183" s="6" t="inlineStr">
+        <is>
+          <t>NAVITIME 電話帳</t>
+        </is>
+      </c>
+      <c r="J183" s="6" t="inlineStr"/>
+      <c r="K183" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L183" s="6" t="inlineStr"/>
+      <c r="M183" s="6" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="5" t="n">
+        <v>183</v>
+      </c>
+      <c r="B184" s="6" t="inlineStr">
+        <is>
+          <t>加藤理容所</t>
+        </is>
+      </c>
+      <c r="C184" s="6" t="inlineStr">
+        <is>
+          <t>理容室</t>
+        </is>
+      </c>
+      <c r="D184" s="6" t="inlineStr">
+        <is>
+          <t>日光市</t>
+        </is>
+      </c>
+      <c r="E184" s="6" t="inlineStr">
+        <is>
+          <t>鬼怒川温泉大原2-80</t>
+        </is>
+      </c>
+      <c r="F184" s="6" t="inlineStr">
+        <is>
+          <t>0288-77-2200</t>
+        </is>
+      </c>
+      <c r="G184" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H184" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I184" s="6" t="inlineStr">
+        <is>
+          <t>NAVITIME 電話帳</t>
+        </is>
+      </c>
+      <c r="J184" s="6" t="inlineStr"/>
+      <c r="K184" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L184" s="6" t="inlineStr"/>
+      <c r="M184" s="6" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" s="5" t="n">
+        <v>184</v>
+      </c>
+      <c r="B185" s="6" t="inlineStr">
+        <is>
+          <t>伊藤理容所</t>
+        </is>
+      </c>
+      <c r="C185" s="6" t="inlineStr">
+        <is>
+          <t>理容室</t>
+        </is>
+      </c>
+      <c r="D185" s="6" t="inlineStr">
+        <is>
+          <t>日光市</t>
+        </is>
+      </c>
+      <c r="E185" s="6" t="inlineStr">
+        <is>
+          <t>小林2697-2</t>
+        </is>
+      </c>
+      <c r="F185" s="6" t="inlineStr">
+        <is>
+          <t>0288-26-8828</t>
+        </is>
+      </c>
+      <c r="G185" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H185" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I185" s="6" t="inlineStr">
+        <is>
+          <t>NAVITIME 電話帳</t>
+        </is>
+      </c>
+      <c r="J185" s="6" t="inlineStr"/>
+      <c r="K185" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L185" s="6" t="inlineStr"/>
+      <c r="M185" s="6" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" s="5" t="n">
+        <v>185</v>
+      </c>
+      <c r="B186" s="6" t="inlineStr">
+        <is>
+          <t>大久保理容所</t>
+        </is>
+      </c>
+      <c r="C186" s="6" t="inlineStr">
+        <is>
+          <t>理容室</t>
+        </is>
+      </c>
+      <c r="D186" s="6" t="inlineStr">
+        <is>
+          <t>日光市</t>
+        </is>
+      </c>
+      <c r="E186" s="6" t="inlineStr">
+        <is>
+          <t>所野1122-132</t>
+        </is>
+      </c>
+      <c r="F186" s="6" t="inlineStr">
+        <is>
+          <t>0288-54-3013</t>
+        </is>
+      </c>
+      <c r="G186" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H186" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I186" s="6" t="inlineStr">
+        <is>
+          <t>NAVITIME 電話帳</t>
+        </is>
+      </c>
+      <c r="J186" s="6" t="inlineStr"/>
+      <c r="K186" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L186" s="6" t="inlineStr"/>
+      <c r="M186" s="6" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="5" t="n">
+        <v>186</v>
+      </c>
+      <c r="B187" s="6" t="inlineStr">
+        <is>
+          <t>岸理容店</t>
+        </is>
+      </c>
+      <c r="C187" s="6" t="inlineStr">
+        <is>
+          <t>理容室</t>
+        </is>
+      </c>
+      <c r="D187" s="6" t="inlineStr">
+        <is>
+          <t>日光市</t>
+        </is>
+      </c>
+      <c r="E187" s="6" t="inlineStr">
+        <is>
+          <t>瀬川232-6</t>
+        </is>
+      </c>
+      <c r="F187" s="6" t="inlineStr">
+        <is>
+          <t>0288-21-2881</t>
+        </is>
+      </c>
+      <c r="G187" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H187" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I187" s="6" t="inlineStr">
+        <is>
+          <t>NAVITIME 電話帳</t>
+        </is>
+      </c>
+      <c r="J187" s="6" t="inlineStr"/>
+      <c r="K187" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L187" s="6" t="inlineStr"/>
+      <c r="M187" s="6" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="5" t="n">
+        <v>187</v>
+      </c>
+      <c r="B188" s="6" t="inlineStr">
+        <is>
+          <t>上吉原理容所</t>
+        </is>
+      </c>
+      <c r="C188" s="6" t="inlineStr">
+        <is>
+          <t>理容室</t>
+        </is>
+      </c>
+      <c r="D188" s="6" t="inlineStr">
+        <is>
+          <t>日光市</t>
+        </is>
+      </c>
+      <c r="E188" s="6" t="inlineStr">
+        <is>
+          <t>瀬尾77</t>
+        </is>
+      </c>
+      <c r="F188" s="6" t="inlineStr">
+        <is>
+          <t>0288-21-2913</t>
+        </is>
+      </c>
+      <c r="G188" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H188" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I188" s="6" t="inlineStr">
+        <is>
+          <t>NAVITIME 電話帳</t>
+        </is>
+      </c>
+      <c r="J188" s="6" t="inlineStr"/>
+      <c r="K188" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L188" s="6" t="inlineStr"/>
+      <c r="M188" s="6" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" s="5" t="n">
+        <v>188</v>
+      </c>
+      <c r="B189" s="6" t="inlineStr">
+        <is>
+          <t>美容室おおらか そすいスクエアAQUAS店</t>
+        </is>
+      </c>
+      <c r="C189" s="6" t="inlineStr">
+        <is>
+          <t>美容室</t>
+        </is>
+      </c>
+      <c r="D189" s="6" t="inlineStr">
+        <is>
+          <t>那須塩原市</t>
+        </is>
+      </c>
+      <c r="E189" s="6" t="inlineStr">
+        <is>
+          <t>西那須野町1-8 そすいスクエアAQUAS 2F</t>
+        </is>
+      </c>
+      <c r="F189" s="6" t="inlineStr">
+        <is>
+          <t>0287-38-0842</t>
+        </is>
+      </c>
+      <c r="G189" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H189" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I189" s="6" t="inlineStr">
+        <is>
+          <t>NAVITIME 電話帳</t>
+        </is>
+      </c>
+      <c r="J189" s="6" t="inlineStr"/>
+      <c r="K189" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L189" s="6" t="inlineStr"/>
+      <c r="M189" s="6" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" s="5" t="n">
+        <v>189</v>
+      </c>
+      <c r="B190" s="6" t="inlineStr">
+        <is>
+          <t>美容室とびら</t>
+        </is>
+      </c>
+      <c r="C190" s="6" t="inlineStr">
+        <is>
+          <t>美容室</t>
+        </is>
+      </c>
+      <c r="D190" s="6" t="inlineStr">
+        <is>
+          <t>那須塩原市</t>
+        </is>
+      </c>
+      <c r="E190" s="6" t="inlineStr">
+        <is>
+          <t>五軒町1-13 マンションアカデミー1F</t>
+        </is>
+      </c>
+      <c r="F190" s="6" t="inlineStr">
+        <is>
+          <t>0287-46-5165</t>
+        </is>
+      </c>
+      <c r="G190" s="6" t="inlineStr">
+        <is>
+          <t>日曜日</t>
+        </is>
+      </c>
+      <c r="H190" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I190" s="6" t="inlineStr">
+        <is>
+          <t>NAVITIME 電話帳</t>
+        </is>
+      </c>
+      <c r="J190" s="6" t="inlineStr"/>
+      <c r="K190" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L190" s="6" t="inlineStr"/>
+      <c r="M190" s="6" t="inlineStr">
+        <is>
+          <t>定休日: 日曜（要再確認）</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="5" t="n">
+        <v>190</v>
+      </c>
+      <c r="B191" s="6" t="inlineStr">
+        <is>
+          <t>美容室アイビー</t>
+        </is>
+      </c>
+      <c r="C191" s="6" t="inlineStr">
+        <is>
+          <t>美容室</t>
+        </is>
+      </c>
+      <c r="D191" s="6" t="inlineStr">
+        <is>
+          <t>那須塩原市</t>
+        </is>
+      </c>
+      <c r="E191" s="6" t="inlineStr">
+        <is>
+          <t>埼玉373-4</t>
+        </is>
+      </c>
+      <c r="F191" s="6" t="inlineStr">
+        <is>
+          <t>0287-60-5065</t>
+        </is>
+      </c>
+      <c r="G191" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H191" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I191" s="6" t="inlineStr">
+        <is>
+          <t>NAVITIME 電話帳</t>
+        </is>
+      </c>
+      <c r="J191" s="6" t="inlineStr"/>
+      <c r="K191" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L191" s="6" t="inlineStr"/>
+      <c r="M191" s="6" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" s="5" t="n">
+        <v>191</v>
+      </c>
+      <c r="B192" s="6" t="inlineStr">
+        <is>
+          <t>ファーストクラス那須塩原店</t>
+        </is>
+      </c>
+      <c r="C192" s="6" t="inlineStr">
+        <is>
+          <t>美容室</t>
+        </is>
+      </c>
+      <c r="D192" s="6" t="inlineStr">
+        <is>
+          <t>那須塩原市</t>
+        </is>
+      </c>
+      <c r="E192" s="6" t="inlineStr">
+        <is>
+          <t>島方455 イオンスーパーセンター那須塩原内</t>
+        </is>
+      </c>
+      <c r="F192" s="6" t="inlineStr">
+        <is>
+          <t>0287-74-3334</t>
+        </is>
+      </c>
+      <c r="G192" s="6" t="inlineStr">
+        <is>
+          <t>日曜日</t>
+        </is>
+      </c>
+      <c r="H192" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I192" s="6" t="inlineStr">
+        <is>
+          <t>NAVITIME 電話帳</t>
+        </is>
+      </c>
+      <c r="J192" s="6" t="inlineStr"/>
+      <c r="K192" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L192" s="6" t="inlineStr"/>
+      <c r="M192" s="6" t="inlineStr">
+        <is>
+          <t>定休日: 日曜（要再確認）</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="5" t="n">
+        <v>192</v>
+      </c>
+      <c r="B193" s="6" t="inlineStr">
+        <is>
+          <t>ラ・パレット美容室</t>
+        </is>
+      </c>
+      <c r="C193" s="6" t="inlineStr">
+        <is>
+          <t>美容室</t>
+        </is>
+      </c>
+      <c r="D193" s="6" t="inlineStr">
+        <is>
+          <t>那須塩原市</t>
+        </is>
+      </c>
+      <c r="E193" s="6" t="inlineStr">
+        <is>
+          <t>新緑町98-130</t>
+        </is>
+      </c>
+      <c r="F193" s="6" t="inlineStr">
+        <is>
+          <t>0287-63-9469</t>
+        </is>
+      </c>
+      <c r="G193" s="6" t="inlineStr">
+        <is>
+          <t>火曜日</t>
+        </is>
+      </c>
+      <c r="H193" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I193" s="6" t="inlineStr">
+        <is>
+          <t>NAVITIME 電話帳</t>
+        </is>
+      </c>
+      <c r="J193" s="6" t="inlineStr"/>
+      <c r="K193" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L193" s="6" t="inlineStr"/>
+      <c r="M193" s="6" t="inlineStr">
+        <is>
+          <t>定休日: 火曜（要再確認）</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="5" t="n">
+        <v>193</v>
+      </c>
+      <c r="B194" s="6" t="inlineStr">
+        <is>
+          <t>理容さつき</t>
+        </is>
+      </c>
+      <c r="C194" s="6" t="inlineStr">
+        <is>
+          <t>理容室</t>
+        </is>
+      </c>
+      <c r="D194" s="6" t="inlineStr">
+        <is>
+          <t>那須塩原市</t>
+        </is>
+      </c>
+      <c r="E194" s="6" t="inlineStr">
+        <is>
+          <t>東栄1-4-9</t>
+        </is>
+      </c>
+      <c r="F194" s="6" t="inlineStr">
+        <is>
+          <t>0287-62-1386</t>
+        </is>
+      </c>
+      <c r="G194" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H194" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I194" s="6" t="inlineStr">
+        <is>
+          <t>NAVITIME 電話帳</t>
+        </is>
+      </c>
+      <c r="J194" s="6" t="inlineStr"/>
+      <c r="K194" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L194" s="6" t="inlineStr"/>
+      <c r="M194" s="6" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="A195" s="5" t="n">
+        <v>194</v>
+      </c>
+      <c r="B195" s="6" t="inlineStr">
+        <is>
+          <t>いんなみ理容室</t>
+        </is>
+      </c>
+      <c r="C195" s="6" t="inlineStr">
+        <is>
+          <t>理容室</t>
+        </is>
+      </c>
+      <c r="D195" s="6" t="inlineStr">
+        <is>
+          <t>那須塩原市</t>
+        </is>
+      </c>
+      <c r="E195" s="6" t="inlineStr">
+        <is>
+          <t>箕輪199-27</t>
+        </is>
+      </c>
+      <c r="F195" s="6" t="inlineStr">
+        <is>
+          <t>0287-68-0608</t>
+        </is>
+      </c>
+      <c r="G195" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H195" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I195" s="6" t="inlineStr">
+        <is>
+          <t>NAVITIME 電話帳</t>
+        </is>
+      </c>
+      <c r="J195" s="6" t="inlineStr"/>
+      <c r="K195" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L195" s="6" t="inlineStr"/>
+      <c r="M195" s="6" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" s="5" t="n">
+        <v>195</v>
+      </c>
+      <c r="B196" s="6" t="inlineStr">
+        <is>
+          <t>ヘアスペース・ハーティー</t>
+        </is>
+      </c>
+      <c r="C196" s="6" t="inlineStr">
+        <is>
+          <t>理容室</t>
+        </is>
+      </c>
+      <c r="D196" s="6" t="inlineStr">
+        <is>
+          <t>那須塩原市</t>
+        </is>
+      </c>
+      <c r="E196" s="6" t="inlineStr">
+        <is>
+          <t>下永田6-1229-13</t>
+        </is>
+      </c>
+      <c r="F196" s="6" t="inlineStr">
+        <is>
+          <t>0287-37-5008</t>
+        </is>
+      </c>
+      <c r="G196" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H196" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I196" s="6" t="inlineStr">
+        <is>
+          <t>NAVITIME 電話帳</t>
+        </is>
+      </c>
+      <c r="J196" s="6" t="inlineStr"/>
+      <c r="K196" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L196" s="6" t="inlineStr"/>
+      <c r="M196" s="6" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" s="5" t="n">
+        <v>196</v>
+      </c>
+      <c r="B197" s="6" t="inlineStr">
+        <is>
+          <t>ヘアーサロンインナミ</t>
+        </is>
+      </c>
+      <c r="C197" s="6" t="inlineStr">
+        <is>
+          <t>理容室</t>
+        </is>
+      </c>
+      <c r="D197" s="6" t="inlineStr">
+        <is>
+          <t>那須塩原市</t>
+        </is>
+      </c>
+      <c r="E197" s="6" t="inlineStr">
+        <is>
+          <t>五軒町7-7</t>
+        </is>
+      </c>
+      <c r="F197" s="6" t="inlineStr">
+        <is>
+          <t>0287-36-0501</t>
+        </is>
+      </c>
+      <c r="G197" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H197" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I197" s="6" t="inlineStr">
+        <is>
+          <t>NAVITIME 電話帳</t>
+        </is>
+      </c>
+      <c r="J197" s="6" t="inlineStr"/>
+      <c r="K197" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L197" s="6" t="inlineStr"/>
+      <c r="M197" s="6" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" s="5" t="n">
+        <v>197</v>
+      </c>
+      <c r="B198" s="6" t="inlineStr">
+        <is>
+          <t>うめや</t>
+        </is>
+      </c>
+      <c r="C198" s="6" t="inlineStr">
+        <is>
+          <t>理容室</t>
+        </is>
+      </c>
+      <c r="D198" s="6" t="inlineStr">
+        <is>
+          <t>那須塩原市</t>
+        </is>
+      </c>
+      <c r="E198" s="6" t="inlineStr">
+        <is>
+          <t>鴫内528</t>
+        </is>
+      </c>
+      <c r="F198" s="6" t="inlineStr">
+        <is>
+          <t>0287-68-0858</t>
+        </is>
+      </c>
+      <c r="G198" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H198" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I198" s="6" t="inlineStr">
+        <is>
+          <t>NAVITIME 電話帳</t>
+        </is>
+      </c>
+      <c r="J198" s="6" t="inlineStr"/>
+      <c r="K198" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L198" s="6" t="inlineStr"/>
+      <c r="M198" s="6" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" s="5" t="n">
+        <v>198</v>
+      </c>
+      <c r="B199" s="8" t="inlineStr"/>
+      <c r="C199" s="8" t="inlineStr"/>
+      <c r="D199" s="8" t="inlineStr"/>
+      <c r="E199" s="8" t="inlineStr"/>
+      <c r="F199" s="8" t="inlineStr"/>
+      <c r="G199" s="8" t="inlineStr"/>
+      <c r="H199" s="8" t="inlineStr"/>
+      <c r="I199" s="8" t="inlineStr"/>
+      <c r="J199" s="8" t="inlineStr"/>
+      <c r="K199" s="8" t="inlineStr"/>
+      <c r="L199" s="8" t="inlineStr"/>
+      <c r="M199" s="8" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" s="5" t="n">
+        <v>199</v>
+      </c>
+      <c r="B200" s="8" t="inlineStr"/>
+      <c r="C200" s="8" t="inlineStr"/>
+      <c r="D200" s="8" t="inlineStr"/>
+      <c r="E200" s="8" t="inlineStr"/>
+      <c r="F200" s="8" t="inlineStr"/>
+      <c r="G200" s="8" t="inlineStr"/>
+      <c r="H200" s="8" t="inlineStr"/>
+      <c r="I200" s="8" t="inlineStr"/>
+      <c r="J200" s="8" t="inlineStr"/>
+      <c r="K200" s="8" t="inlineStr"/>
+      <c r="L200" s="8" t="inlineStr"/>
+      <c r="M200" s="8" t="inlineStr"/>
+    </row>
+    <row r="201">
+      <c r="A201" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="B201" s="8" t="inlineStr"/>
+      <c r="C201" s="8" t="inlineStr"/>
+      <c r="D201" s="8" t="inlineStr"/>
+      <c r="E201" s="8" t="inlineStr"/>
+      <c r="F201" s="8" t="inlineStr"/>
+      <c r="G201" s="8" t="inlineStr"/>
+      <c r="H201" s="8" t="inlineStr"/>
+      <c r="I201" s="8" t="inlineStr"/>
+      <c r="J201" s="8" t="inlineStr"/>
+      <c r="K201" s="8" t="inlineStr"/>
+      <c r="L201" s="8" t="inlineStr"/>
+      <c r="M201" s="8" t="inlineStr"/>
+    </row>
+    <row r="202">
+      <c r="A202" s="5" t="n">
+        <v>201</v>
+      </c>
+      <c r="B202" s="8" t="inlineStr"/>
+      <c r="C202" s="8" t="inlineStr"/>
+      <c r="D202" s="8" t="inlineStr"/>
+      <c r="E202" s="8" t="inlineStr"/>
+      <c r="F202" s="8" t="inlineStr"/>
+      <c r="G202" s="8" t="inlineStr"/>
+      <c r="H202" s="8" t="inlineStr"/>
+      <c r="I202" s="8" t="inlineStr"/>
+      <c r="J202" s="8" t="inlineStr"/>
+      <c r="K202" s="8" t="inlineStr"/>
+      <c r="L202" s="8" t="inlineStr"/>
+      <c r="M202" s="8" t="inlineStr"/>
+    </row>
+    <row r="203">
+      <c r="A203" s="5" t="n">
+        <v>202</v>
+      </c>
+      <c r="B203" s="8" t="inlineStr"/>
+      <c r="C203" s="8" t="inlineStr"/>
+      <c r="D203" s="8" t="inlineStr"/>
+      <c r="E203" s="8" t="inlineStr"/>
+      <c r="F203" s="8" t="inlineStr"/>
+      <c r="G203" s="8" t="inlineStr"/>
+      <c r="H203" s="8" t="inlineStr"/>
+      <c r="I203" s="8" t="inlineStr"/>
+      <c r="J203" s="8" t="inlineStr"/>
+      <c r="K203" s="8" t="inlineStr"/>
+      <c r="L203" s="8" t="inlineStr"/>
+      <c r="M203" s="8" t="inlineStr"/>
+    </row>
+    <row r="204">
+      <c r="A204" s="5" t="n">
+        <v>203</v>
+      </c>
+      <c r="B204" s="8" t="inlineStr"/>
+      <c r="C204" s="8" t="inlineStr"/>
+      <c r="D204" s="8" t="inlineStr"/>
+      <c r="E204" s="8" t="inlineStr"/>
+      <c r="F204" s="8" t="inlineStr"/>
+      <c r="G204" s="8" t="inlineStr"/>
+      <c r="H204" s="8" t="inlineStr"/>
+      <c r="I204" s="8" t="inlineStr"/>
+      <c r="J204" s="8" t="inlineStr"/>
+      <c r="K204" s="8" t="inlineStr"/>
+      <c r="L204" s="8" t="inlineStr"/>
+      <c r="M204" s="8" t="inlineStr"/>
+    </row>
+    <row r="205">
+      <c r="A205" s="5" t="n">
+        <v>204</v>
+      </c>
+      <c r="B205" s="8" t="inlineStr"/>
+      <c r="C205" s="8" t="inlineStr"/>
+      <c r="D205" s="8" t="inlineStr"/>
+      <c r="E205" s="8" t="inlineStr"/>
+      <c r="F205" s="8" t="inlineStr"/>
+      <c r="G205" s="8" t="inlineStr"/>
+      <c r="H205" s="8" t="inlineStr"/>
+      <c r="I205" s="8" t="inlineStr"/>
+      <c r="J205" s="8" t="inlineStr"/>
+      <c r="K205" s="8" t="inlineStr"/>
+      <c r="L205" s="8" t="inlineStr"/>
+      <c r="M205" s="8" t="inlineStr"/>
+    </row>
+    <row r="206">
+      <c r="A206" s="5" t="n">
+        <v>205</v>
+      </c>
+      <c r="B206" s="8" t="inlineStr"/>
+      <c r="C206" s="8" t="inlineStr"/>
+      <c r="D206" s="8" t="inlineStr"/>
+      <c r="E206" s="8" t="inlineStr"/>
+      <c r="F206" s="8" t="inlineStr"/>
+      <c r="G206" s="8" t="inlineStr"/>
+      <c r="H206" s="8" t="inlineStr"/>
+      <c r="I206" s="8" t="inlineStr"/>
+      <c r="J206" s="8" t="inlineStr"/>
+      <c r="K206" s="8" t="inlineStr"/>
+      <c r="L206" s="8" t="inlineStr"/>
+      <c r="M206" s="8" t="inlineStr"/>
+    </row>
+    <row r="207">
+      <c r="A207" s="5" t="n">
+        <v>206</v>
+      </c>
+      <c r="B207" s="8" t="inlineStr"/>
+      <c r="C207" s="8" t="inlineStr"/>
+      <c r="D207" s="8" t="inlineStr"/>
+      <c r="E207" s="8" t="inlineStr"/>
+      <c r="F207" s="8" t="inlineStr"/>
+      <c r="G207" s="8" t="inlineStr"/>
+      <c r="H207" s="8" t="inlineStr"/>
+      <c r="I207" s="8" t="inlineStr"/>
+      <c r="J207" s="8" t="inlineStr"/>
+      <c r="K207" s="8" t="inlineStr"/>
+      <c r="L207" s="8" t="inlineStr"/>
+      <c r="M207" s="8" t="inlineStr"/>
+    </row>
+    <row r="208">
+      <c r="A208" s="5" t="n">
+        <v>207</v>
+      </c>
+      <c r="B208" s="8" t="inlineStr"/>
+      <c r="C208" s="8" t="inlineStr"/>
+      <c r="D208" s="8" t="inlineStr"/>
+      <c r="E208" s="8" t="inlineStr"/>
+      <c r="F208" s="8" t="inlineStr"/>
+      <c r="G208" s="8" t="inlineStr"/>
+      <c r="H208" s="8" t="inlineStr"/>
+      <c r="I208" s="8" t="inlineStr"/>
+      <c r="J208" s="8" t="inlineStr"/>
+      <c r="K208" s="8" t="inlineStr"/>
+      <c r="L208" s="8" t="inlineStr"/>
+      <c r="M208" s="8" t="inlineStr"/>
+    </row>
+    <row r="209">
+      <c r="A209" s="5" t="n">
+        <v>208</v>
+      </c>
+      <c r="B209" s="8" t="inlineStr"/>
+      <c r="C209" s="8" t="inlineStr"/>
+      <c r="D209" s="8" t="inlineStr"/>
+      <c r="E209" s="8" t="inlineStr"/>
+      <c r="F209" s="8" t="inlineStr"/>
+      <c r="G209" s="8" t="inlineStr"/>
+      <c r="H209" s="8" t="inlineStr"/>
+      <c r="I209" s="8" t="inlineStr"/>
+      <c r="J209" s="8" t="inlineStr"/>
+      <c r="K209" s="8" t="inlineStr"/>
+      <c r="L209" s="8" t="inlineStr"/>
+      <c r="M209" s="8" t="inlineStr"/>
+    </row>
+    <row r="210">
+      <c r="A210" s="5" t="n">
+        <v>209</v>
+      </c>
+      <c r="B210" s="8" t="inlineStr"/>
+      <c r="C210" s="8" t="inlineStr"/>
+      <c r="D210" s="8" t="inlineStr"/>
+      <c r="E210" s="8" t="inlineStr"/>
+      <c r="F210" s="8" t="inlineStr"/>
+      <c r="G210" s="8" t="inlineStr"/>
+      <c r="H210" s="8" t="inlineStr"/>
+      <c r="I210" s="8" t="inlineStr"/>
+      <c r="J210" s="8" t="inlineStr"/>
+      <c r="K210" s="8" t="inlineStr"/>
+      <c r="L210" s="8" t="inlineStr"/>
+      <c r="M210" s="8" t="inlineStr"/>
+    </row>
+    <row r="211">
+      <c r="A211" s="5" t="n">
+        <v>210</v>
+      </c>
+      <c r="B211" s="8" t="inlineStr"/>
+      <c r="C211" s="8" t="inlineStr"/>
+      <c r="D211" s="8" t="inlineStr"/>
+      <c r="E211" s="8" t="inlineStr"/>
+      <c r="F211" s="8" t="inlineStr"/>
+      <c r="G211" s="8" t="inlineStr"/>
+      <c r="H211" s="8" t="inlineStr"/>
+      <c r="I211" s="8" t="inlineStr"/>
+      <c r="J211" s="8" t="inlineStr"/>
+      <c r="K211" s="8" t="inlineStr"/>
+      <c r="L211" s="8" t="inlineStr"/>
+      <c r="M211" s="8" t="inlineStr"/>
+    </row>
+    <row r="212">
+      <c r="A212" s="5" t="n">
+        <v>211</v>
+      </c>
+      <c r="B212" s="8" t="inlineStr"/>
+      <c r="C212" s="8" t="inlineStr"/>
+      <c r="D212" s="8" t="inlineStr"/>
+      <c r="E212" s="8" t="inlineStr"/>
+      <c r="F212" s="8" t="inlineStr"/>
+      <c r="G212" s="8" t="inlineStr"/>
+      <c r="H212" s="8" t="inlineStr"/>
+      <c r="I212" s="8" t="inlineStr"/>
+      <c r="J212" s="8" t="inlineStr"/>
+      <c r="K212" s="8" t="inlineStr"/>
+      <c r="L212" s="8" t="inlineStr"/>
+      <c r="M212" s="8" t="inlineStr"/>
+    </row>
+    <row r="213">
+      <c r="A213" s="5" t="n">
+        <v>212</v>
+      </c>
+      <c r="B213" s="8" t="inlineStr"/>
+      <c r="C213" s="8" t="inlineStr"/>
+      <c r="D213" s="8" t="inlineStr"/>
+      <c r="E213" s="8" t="inlineStr"/>
+      <c r="F213" s="8" t="inlineStr"/>
+      <c r="G213" s="8" t="inlineStr"/>
+      <c r="H213" s="8" t="inlineStr"/>
+      <c r="I213" s="8" t="inlineStr"/>
+      <c r="J213" s="8" t="inlineStr"/>
+      <c r="K213" s="8" t="inlineStr"/>
+      <c r="L213" s="8" t="inlineStr"/>
+      <c r="M213" s="8" t="inlineStr"/>
+    </row>
+    <row r="214">
+      <c r="A214" s="5" t="n">
+        <v>213</v>
+      </c>
+      <c r="B214" s="8" t="inlineStr"/>
+      <c r="C214" s="8" t="inlineStr"/>
+      <c r="D214" s="8" t="inlineStr"/>
+      <c r="E214" s="8" t="inlineStr"/>
+      <c r="F214" s="8" t="inlineStr"/>
+      <c r="G214" s="8" t="inlineStr"/>
+      <c r="H214" s="8" t="inlineStr"/>
+      <c r="I214" s="8" t="inlineStr"/>
+      <c r="J214" s="8" t="inlineStr"/>
+      <c r="K214" s="8" t="inlineStr"/>
+      <c r="L214" s="8" t="inlineStr"/>
+      <c r="M214" s="8" t="inlineStr"/>
+    </row>
+    <row r="215">
+      <c r="A215" s="5" t="n">
+        <v>214</v>
+      </c>
+      <c r="B215" s="8" t="inlineStr"/>
+      <c r="C215" s="8" t="inlineStr"/>
+      <c r="D215" s="8" t="inlineStr"/>
+      <c r="E215" s="8" t="inlineStr"/>
+      <c r="F215" s="8" t="inlineStr"/>
+      <c r="G215" s="8" t="inlineStr"/>
+      <c r="H215" s="8" t="inlineStr"/>
+      <c r="I215" s="8" t="inlineStr"/>
+      <c r="J215" s="8" t="inlineStr"/>
+      <c r="K215" s="8" t="inlineStr"/>
+      <c r="L215" s="8" t="inlineStr"/>
+      <c r="M215" s="8" t="inlineStr"/>
+    </row>
+    <row r="216">
+      <c r="A216" s="5" t="n">
+        <v>215</v>
+      </c>
+      <c r="B216" s="8" t="inlineStr"/>
+      <c r="C216" s="8" t="inlineStr"/>
+      <c r="D216" s="8" t="inlineStr"/>
+      <c r="E216" s="8" t="inlineStr"/>
+      <c r="F216" s="8" t="inlineStr"/>
+      <c r="G216" s="8" t="inlineStr"/>
+      <c r="H216" s="8" t="inlineStr"/>
+      <c r="I216" s="8" t="inlineStr"/>
+      <c r="J216" s="8" t="inlineStr"/>
+      <c r="K216" s="8" t="inlineStr"/>
+      <c r="L216" s="8" t="inlineStr"/>
+      <c r="M216" s="8" t="inlineStr"/>
+    </row>
+    <row r="217">
+      <c r="A217" s="5" t="n">
+        <v>216</v>
+      </c>
+      <c r="B217" s="8" t="inlineStr"/>
+      <c r="C217" s="8" t="inlineStr"/>
+      <c r="D217" s="8" t="inlineStr"/>
+      <c r="E217" s="8" t="inlineStr"/>
+      <c r="F217" s="8" t="inlineStr"/>
+      <c r="G217" s="8" t="inlineStr"/>
+      <c r="H217" s="8" t="inlineStr"/>
+      <c r="I217" s="8" t="inlineStr"/>
+      <c r="J217" s="8" t="inlineStr"/>
+      <c r="K217" s="8" t="inlineStr"/>
+      <c r="L217" s="8" t="inlineStr"/>
+      <c r="M217" s="8" t="inlineStr"/>
+    </row>
+    <row r="218">
+      <c r="A218" s="5" t="n">
+        <v>217</v>
+      </c>
+      <c r="B218" s="8" t="inlineStr"/>
+      <c r="C218" s="8" t="inlineStr"/>
+      <c r="D218" s="8" t="inlineStr"/>
+      <c r="E218" s="8" t="inlineStr"/>
+      <c r="F218" s="8" t="inlineStr"/>
+      <c r="G218" s="8" t="inlineStr"/>
+      <c r="H218" s="8" t="inlineStr"/>
+      <c r="I218" s="8" t="inlineStr"/>
+      <c r="J218" s="8" t="inlineStr"/>
+      <c r="K218" s="8" t="inlineStr"/>
+      <c r="L218" s="8" t="inlineStr"/>
+      <c r="M218" s="8" t="inlineStr"/>
+    </row>
+    <row r="219">
+      <c r="A219" s="5" t="n">
+        <v>218</v>
+      </c>
+      <c r="B219" s="8" t="inlineStr"/>
+      <c r="C219" s="8" t="inlineStr"/>
+      <c r="D219" s="8" t="inlineStr"/>
+      <c r="E219" s="8" t="inlineStr"/>
+      <c r="F219" s="8" t="inlineStr"/>
+      <c r="G219" s="8" t="inlineStr"/>
+      <c r="H219" s="8" t="inlineStr"/>
+      <c r="I219" s="8" t="inlineStr"/>
+      <c r="J219" s="8" t="inlineStr"/>
+      <c r="K219" s="8" t="inlineStr"/>
+      <c r="L219" s="8" t="inlineStr"/>
+      <c r="M219" s="8" t="inlineStr"/>
+    </row>
+    <row r="220">
+      <c r="A220" s="5" t="n">
+        <v>219</v>
+      </c>
+      <c r="B220" s="8" t="inlineStr"/>
+      <c r="C220" s="8" t="inlineStr"/>
+      <c r="D220" s="8" t="inlineStr"/>
+      <c r="E220" s="8" t="inlineStr"/>
+      <c r="F220" s="8" t="inlineStr"/>
+      <c r="G220" s="8" t="inlineStr"/>
+      <c r="H220" s="8" t="inlineStr"/>
+      <c r="I220" s="8" t="inlineStr"/>
+      <c r="J220" s="8" t="inlineStr"/>
+      <c r="K220" s="8" t="inlineStr"/>
+      <c r="L220" s="8" t="inlineStr"/>
+      <c r="M220" s="8" t="inlineStr"/>
+    </row>
+    <row r="221">
+      <c r="A221" s="5" t="n">
+        <v>220</v>
+      </c>
+      <c r="B221" s="8" t="inlineStr"/>
+      <c r="C221" s="8" t="inlineStr"/>
+      <c r="D221" s="8" t="inlineStr"/>
+      <c r="E221" s="8" t="inlineStr"/>
+      <c r="F221" s="8" t="inlineStr"/>
+      <c r="G221" s="8" t="inlineStr"/>
+      <c r="H221" s="8" t="inlineStr"/>
+      <c r="I221" s="8" t="inlineStr"/>
+      <c r="J221" s="8" t="inlineStr"/>
+      <c r="K221" s="8" t="inlineStr"/>
+      <c r="L221" s="8" t="inlineStr"/>
+      <c r="M221" s="8" t="inlineStr"/>
+    </row>
+    <row r="222">
+      <c r="A222" s="5" t="n">
+        <v>221</v>
+      </c>
+      <c r="B222" s="8" t="inlineStr"/>
+      <c r="C222" s="8" t="inlineStr"/>
+      <c r="D222" s="8" t="inlineStr"/>
+      <c r="E222" s="8" t="inlineStr"/>
+      <c r="F222" s="8" t="inlineStr"/>
+      <c r="G222" s="8" t="inlineStr"/>
+      <c r="H222" s="8" t="inlineStr"/>
+      <c r="I222" s="8" t="inlineStr"/>
+      <c r="J222" s="8" t="inlineStr"/>
+      <c r="K222" s="8" t="inlineStr"/>
+      <c r="L222" s="8" t="inlineStr"/>
+      <c r="M222" s="8" t="inlineStr"/>
+    </row>
+    <row r="223">
+      <c r="A223" s="5" t="n">
+        <v>222</v>
+      </c>
+      <c r="B223" s="8" t="inlineStr"/>
+      <c r="C223" s="8" t="inlineStr"/>
+      <c r="D223" s="8" t="inlineStr"/>
+      <c r="E223" s="8" t="inlineStr"/>
+      <c r="F223" s="8" t="inlineStr"/>
+      <c r="G223" s="8" t="inlineStr"/>
+      <c r="H223" s="8" t="inlineStr"/>
+      <c r="I223" s="8" t="inlineStr"/>
+      <c r="J223" s="8" t="inlineStr"/>
+      <c r="K223" s="8" t="inlineStr"/>
+      <c r="L223" s="8" t="inlineStr"/>
+      <c r="M223" s="8" t="inlineStr"/>
+    </row>
+    <row r="224">
+      <c r="A224" s="5" t="n">
+        <v>223</v>
+      </c>
+      <c r="B224" s="8" t="inlineStr"/>
+      <c r="C224" s="8" t="inlineStr"/>
+      <c r="D224" s="8" t="inlineStr"/>
+      <c r="E224" s="8" t="inlineStr"/>
+      <c r="F224" s="8" t="inlineStr"/>
+      <c r="G224" s="8" t="inlineStr"/>
+      <c r="H224" s="8" t="inlineStr"/>
+      <c r="I224" s="8" t="inlineStr"/>
+      <c r="J224" s="8" t="inlineStr"/>
+      <c r="K224" s="8" t="inlineStr"/>
+      <c r="L224" s="8" t="inlineStr"/>
+      <c r="M224" s="8" t="inlineStr"/>
+    </row>
+    <row r="225">
+      <c r="A225" s="5" t="n">
+        <v>224</v>
+      </c>
+      <c r="B225" s="8" t="inlineStr"/>
+      <c r="C225" s="8" t="inlineStr"/>
+      <c r="D225" s="8" t="inlineStr"/>
+      <c r="E225" s="8" t="inlineStr"/>
+      <c r="F225" s="8" t="inlineStr"/>
+      <c r="G225" s="8" t="inlineStr"/>
+      <c r="H225" s="8" t="inlineStr"/>
+      <c r="I225" s="8" t="inlineStr"/>
+      <c r="J225" s="8" t="inlineStr"/>
+      <c r="K225" s="8" t="inlineStr"/>
+      <c r="L225" s="8" t="inlineStr"/>
+      <c r="M225" s="8" t="inlineStr"/>
+    </row>
+    <row r="226">
+      <c r="A226" s="5" t="n">
+        <v>225</v>
+      </c>
+      <c r="B226" s="8" t="inlineStr"/>
+      <c r="C226" s="8" t="inlineStr"/>
+      <c r="D226" s="8" t="inlineStr"/>
+      <c r="E226" s="8" t="inlineStr"/>
+      <c r="F226" s="8" t="inlineStr"/>
+      <c r="G226" s="8" t="inlineStr"/>
+      <c r="H226" s="8" t="inlineStr"/>
+      <c r="I226" s="8" t="inlineStr"/>
+      <c r="J226" s="8" t="inlineStr"/>
+      <c r="K226" s="8" t="inlineStr"/>
+      <c r="L226" s="8" t="inlineStr"/>
+      <c r="M226" s="8" t="inlineStr"/>
+    </row>
+    <row r="227">
+      <c r="A227" s="5" t="n">
+        <v>226</v>
+      </c>
+      <c r="B227" s="8" t="inlineStr"/>
+      <c r="C227" s="8" t="inlineStr"/>
+      <c r="D227" s="8" t="inlineStr"/>
+      <c r="E227" s="8" t="inlineStr"/>
+      <c r="F227" s="8" t="inlineStr"/>
+      <c r="G227" s="8" t="inlineStr"/>
+      <c r="H227" s="8" t="inlineStr"/>
+      <c r="I227" s="8" t="inlineStr"/>
+      <c r="J227" s="8" t="inlineStr"/>
+      <c r="K227" s="8" t="inlineStr"/>
+      <c r="L227" s="8" t="inlineStr"/>
+      <c r="M227" s="8" t="inlineStr"/>
+    </row>
+    <row r="228">
+      <c r="A228" s="5" t="n">
+        <v>227</v>
+      </c>
+      <c r="B228" s="8" t="inlineStr"/>
+      <c r="C228" s="8" t="inlineStr"/>
+      <c r="D228" s="8" t="inlineStr"/>
+      <c r="E228" s="8" t="inlineStr"/>
+      <c r="F228" s="8" t="inlineStr"/>
+      <c r="G228" s="8" t="inlineStr"/>
+      <c r="H228" s="8" t="inlineStr"/>
+      <c r="I228" s="8" t="inlineStr"/>
+      <c r="J228" s="8" t="inlineStr"/>
+      <c r="K228" s="8" t="inlineStr"/>
+      <c r="L228" s="8" t="inlineStr"/>
+      <c r="M228" s="8" t="inlineStr"/>
+    </row>
+    <row r="229">
+      <c r="A229" s="5" t="n">
+        <v>228</v>
+      </c>
+      <c r="B229" s="8" t="inlineStr"/>
+      <c r="C229" s="8" t="inlineStr"/>
+      <c r="D229" s="8" t="inlineStr"/>
+      <c r="E229" s="8" t="inlineStr"/>
+      <c r="F229" s="8" t="inlineStr"/>
+      <c r="G229" s="8" t="inlineStr"/>
+      <c r="H229" s="8" t="inlineStr"/>
+      <c r="I229" s="8" t="inlineStr"/>
+      <c r="J229" s="8" t="inlineStr"/>
+      <c r="K229" s="8" t="inlineStr"/>
+      <c r="L229" s="8" t="inlineStr"/>
+      <c r="M229" s="8" t="inlineStr"/>
+    </row>
+    <row r="230">
+      <c r="A230" s="5" t="n">
+        <v>229</v>
+      </c>
+      <c r="B230" s="8" t="inlineStr"/>
+      <c r="C230" s="8" t="inlineStr"/>
+      <c r="D230" s="8" t="inlineStr"/>
+      <c r="E230" s="8" t="inlineStr"/>
+      <c r="F230" s="8" t="inlineStr"/>
+      <c r="G230" s="8" t="inlineStr"/>
+      <c r="H230" s="8" t="inlineStr"/>
+      <c r="I230" s="8" t="inlineStr"/>
+      <c r="J230" s="8" t="inlineStr"/>
+      <c r="K230" s="8" t="inlineStr"/>
+      <c r="L230" s="8" t="inlineStr"/>
+      <c r="M230" s="8" t="inlineStr"/>
+    </row>
+    <row r="231">
+      <c r="A231" s="5" t="n">
+        <v>230</v>
+      </c>
+      <c r="B231" s="8" t="inlineStr"/>
+      <c r="C231" s="8" t="inlineStr"/>
+      <c r="D231" s="8" t="inlineStr"/>
+      <c r="E231" s="8" t="inlineStr"/>
+      <c r="F231" s="8" t="inlineStr"/>
+      <c r="G231" s="8" t="inlineStr"/>
+      <c r="H231" s="8" t="inlineStr"/>
+      <c r="I231" s="8" t="inlineStr"/>
+      <c r="J231" s="8" t="inlineStr"/>
+      <c r="K231" s="8" t="inlineStr"/>
+      <c r="L231" s="8" t="inlineStr"/>
+      <c r="M231" s="8" t="inlineStr"/>
+    </row>
+    <row r="232">
+      <c r="A232" s="5" t="n">
+        <v>231</v>
+      </c>
+      <c r="B232" s="8" t="inlineStr"/>
+      <c r="C232" s="8" t="inlineStr"/>
+      <c r="D232" s="8" t="inlineStr"/>
+      <c r="E232" s="8" t="inlineStr"/>
+      <c r="F232" s="8" t="inlineStr"/>
+      <c r="G232" s="8" t="inlineStr"/>
+      <c r="H232" s="8" t="inlineStr"/>
+      <c r="I232" s="8" t="inlineStr"/>
+      <c r="J232" s="8" t="inlineStr"/>
+      <c r="K232" s="8" t="inlineStr"/>
+      <c r="L232" s="8" t="inlineStr"/>
+      <c r="M232" s="8" t="inlineStr"/>
+    </row>
+    <row r="233">
+      <c r="A233" s="5" t="n">
+        <v>232</v>
+      </c>
+      <c r="B233" s="8" t="inlineStr"/>
+      <c r="C233" s="8" t="inlineStr"/>
+      <c r="D233" s="8" t="inlineStr"/>
+      <c r="E233" s="8" t="inlineStr"/>
+      <c r="F233" s="8" t="inlineStr"/>
+      <c r="G233" s="8" t="inlineStr"/>
+      <c r="H233" s="8" t="inlineStr"/>
+      <c r="I233" s="8" t="inlineStr"/>
+      <c r="J233" s="8" t="inlineStr"/>
+      <c r="K233" s="8" t="inlineStr"/>
+      <c r="L233" s="8" t="inlineStr"/>
+      <c r="M233" s="8" t="inlineStr"/>
+    </row>
+    <row r="234">
+      <c r="A234" s="5" t="n">
+        <v>233</v>
+      </c>
+      <c r="B234" s="8" t="inlineStr"/>
+      <c r="C234" s="8" t="inlineStr"/>
+      <c r="D234" s="8" t="inlineStr"/>
+      <c r="E234" s="8" t="inlineStr"/>
+      <c r="F234" s="8" t="inlineStr"/>
+      <c r="G234" s="8" t="inlineStr"/>
+      <c r="H234" s="8" t="inlineStr"/>
+      <c r="I234" s="8" t="inlineStr"/>
+      <c r="J234" s="8" t="inlineStr"/>
+      <c r="K234" s="8" t="inlineStr"/>
+      <c r="L234" s="8" t="inlineStr"/>
+      <c r="M234" s="8" t="inlineStr"/>
+    </row>
+    <row r="235">
+      <c r="A235" s="5" t="n">
+        <v>234</v>
+      </c>
+      <c r="B235" s="8" t="inlineStr"/>
+      <c r="C235" s="8" t="inlineStr"/>
+      <c r="D235" s="8" t="inlineStr"/>
+      <c r="E235" s="8" t="inlineStr"/>
+      <c r="F235" s="8" t="inlineStr"/>
+      <c r="G235" s="8" t="inlineStr"/>
+      <c r="H235" s="8" t="inlineStr"/>
+      <c r="I235" s="8" t="inlineStr"/>
+      <c r="J235" s="8" t="inlineStr"/>
+      <c r="K235" s="8" t="inlineStr"/>
+      <c r="L235" s="8" t="inlineStr"/>
+      <c r="M235" s="8" t="inlineStr"/>
+    </row>
+    <row r="236">
+      <c r="A236" s="5" t="n">
+        <v>235</v>
+      </c>
+      <c r="B236" s="8" t="inlineStr"/>
+      <c r="C236" s="8" t="inlineStr"/>
+      <c r="D236" s="8" t="inlineStr"/>
+      <c r="E236" s="8" t="inlineStr"/>
+      <c r="F236" s="8" t="inlineStr"/>
+      <c r="G236" s="8" t="inlineStr"/>
+      <c r="H236" s="8" t="inlineStr"/>
+      <c r="I236" s="8" t="inlineStr"/>
+      <c r="J236" s="8" t="inlineStr"/>
+      <c r="K236" s="8" t="inlineStr"/>
+      <c r="L236" s="8" t="inlineStr"/>
+      <c r="M236" s="8" t="inlineStr"/>
+    </row>
+    <row r="237">
+      <c r="A237" s="5" t="n">
+        <v>236</v>
+      </c>
+      <c r="B237" s="8" t="inlineStr"/>
+      <c r="C237" s="8" t="inlineStr"/>
+      <c r="D237" s="8" t="inlineStr"/>
+      <c r="E237" s="8" t="inlineStr"/>
+      <c r="F237" s="8" t="inlineStr"/>
+      <c r="G237" s="8" t="inlineStr"/>
+      <c r="H237" s="8" t="inlineStr"/>
+      <c r="I237" s="8" t="inlineStr"/>
+      <c r="J237" s="8" t="inlineStr"/>
+      <c r="K237" s="8" t="inlineStr"/>
+      <c r="L237" s="8" t="inlineStr"/>
+      <c r="M237" s="8" t="inlineStr"/>
+    </row>
+    <row r="238">
+      <c r="A238" s="5" t="n">
+        <v>237</v>
+      </c>
+      <c r="B238" s="8" t="inlineStr"/>
+      <c r="C238" s="8" t="inlineStr"/>
+      <c r="D238" s="8" t="inlineStr"/>
+      <c r="E238" s="8" t="inlineStr"/>
+      <c r="F238" s="8" t="inlineStr"/>
+      <c r="G238" s="8" t="inlineStr"/>
+      <c r="H238" s="8" t="inlineStr"/>
+      <c r="I238" s="8" t="inlineStr"/>
+      <c r="J238" s="8" t="inlineStr"/>
+      <c r="K238" s="8" t="inlineStr"/>
+      <c r="L238" s="8" t="inlineStr"/>
+      <c r="M238" s="8" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="4">
-    <dataValidation sqref="C2:C146" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C2:C238" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"カフェ,飲食店,和菓子店,雑貨店,陶器店・ギャラリー,工芸品店,土産店,パン屋,美容室,理容室,その他"</formula1>
     </dataValidation>
-    <dataValidation sqref="D2:D146" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="D2:D238" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"栃木市,益子町,那須町,日光市,宇都宮市,足利市,佐野市,小山市,鹿沼市,那須塩原市,真岡市,大田原市,壬生町,那珂川町,那須烏山市,矢板市,茂木町,下野市,野木町,高根沢町,芳賀町,塩谷町,さくら市,上三川町,その他"</formula1>
     </dataValidation>
-    <dataValidation sqref="K2:K146" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K2:K238" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"未架電,不在,拒否,資料送付OK,アポ確定,見送り"</formula1>
     </dataValidation>
-    <dataValidation sqref="H2:H146" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H2:H238" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"不明,あり（古い）,あり（最近）,なし"</formula1>
     </dataValidation>
   </dataValidations>
@@ -6710,7 +11490,7 @@
         </is>
       </c>
       <c r="D4" s="2">
-        <f>COUNTIF(架電リスト!B2:B146,"?*")</f>
+        <f>COUNTIF(架電リスト!B2:B238,"?*")</f>
         <v/>
       </c>
     </row>
@@ -6721,7 +11501,7 @@
         </is>
       </c>
       <c r="D5" s="2">
-        <f>COUNTIFS(架電リスト!K2:K146,"&lt;&gt;未架電",架電リスト!K2:K146,"&lt;&gt;")</f>
+        <f>COUNTIFS(架電リスト!K2:K238,"&lt;&gt;未架電",架電リスト!K2:K238,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -6732,7 +11512,7 @@
         </is>
       </c>
       <c r="D6" s="2">
-        <f>COUNTIF(架電リスト!K2:K146,"資料送付OK")</f>
+        <f>COUNTIF(架電リスト!K2:K238,"資料送付OK")</f>
         <v/>
       </c>
     </row>
@@ -6743,7 +11523,7 @@
         </is>
       </c>
       <c r="D7" s="2">
-        <f>COUNTIF(架電リスト!K2:K146,"アポ確定")</f>
+        <f>COUNTIF(架電リスト!K2:K238,"アポ確定")</f>
         <v/>
       </c>
     </row>
@@ -6772,7 +11552,7 @@
         </is>
       </c>
       <c r="D11" s="10">
-        <f>COUNTIF(架電リスト!D2:D146,"栃木市")</f>
+        <f>COUNTIF(架電リスト!D2:D238,"栃木市")</f>
         <v/>
       </c>
     </row>
@@ -6783,7 +11563,7 @@
         </is>
       </c>
       <c r="D12" s="10">
-        <f>COUNTIF(架電リスト!D2:D146,"益子町")</f>
+        <f>COUNTIF(架電リスト!D2:D238,"益子町")</f>
         <v/>
       </c>
     </row>
@@ -6794,7 +11574,7 @@
         </is>
       </c>
       <c r="D13" s="10">
-        <f>COUNTIF(架電リスト!D2:D146,"那須町")</f>
+        <f>COUNTIF(架電リスト!D2:D238,"那須町")</f>
         <v/>
       </c>
     </row>
@@ -6805,7 +11585,7 @@
         </is>
       </c>
       <c r="D14" s="10">
-        <f>COUNTIF(架電リスト!D2:D146,"日光市")</f>
+        <f>COUNTIF(架電リスト!D2:D238,"日光市")</f>
         <v/>
       </c>
     </row>
@@ -6816,7 +11596,7 @@
         </is>
       </c>
       <c r="D15" s="10">
-        <f>COUNTIF(架電リスト!D2:D146,"宇都宮市")</f>
+        <f>COUNTIF(架電リスト!D2:D238,"宇都宮市")</f>
         <v/>
       </c>
     </row>
@@ -6827,7 +11607,7 @@
         </is>
       </c>
       <c r="D16" s="10">
-        <f>COUNTIF(架電リスト!D2:D146,"足利市")</f>
+        <f>COUNTIF(架電リスト!D2:D238,"足利市")</f>
         <v/>
       </c>
     </row>
@@ -6838,7 +11618,7 @@
         </is>
       </c>
       <c r="D17" s="10">
-        <f>COUNTIF(架電リスト!D2:D146,"佐野市")</f>
+        <f>COUNTIF(架電リスト!D2:D238,"佐野市")</f>
         <v/>
       </c>
     </row>
@@ -6849,7 +11629,7 @@
         </is>
       </c>
       <c r="D18" s="10">
-        <f>COUNTIF(架電リスト!D2:D146,"小山市")</f>
+        <f>COUNTIF(架電リスト!D2:D238,"小山市")</f>
         <v/>
       </c>
     </row>
@@ -6860,7 +11640,7 @@
         </is>
       </c>
       <c r="D19" s="10">
-        <f>COUNTIF(架電リスト!D2:D146,"鹿沼市")</f>
+        <f>COUNTIF(架電リスト!D2:D238,"鹿沼市")</f>
         <v/>
       </c>
     </row>
@@ -6871,7 +11651,7 @@
         </is>
       </c>
       <c r="D20" s="10">
-        <f>COUNTIF(架電リスト!D2:D146,"那須塩原市")</f>
+        <f>COUNTIF(架電リスト!D2:D238,"那須塩原市")</f>
         <v/>
       </c>
     </row>
@@ -6882,7 +11662,7 @@
         </is>
       </c>
       <c r="D21" s="10">
-        <f>COUNTIF(架電リスト!D2:D146,"真岡市")</f>
+        <f>COUNTIF(架電リスト!D2:D238,"真岡市")</f>
         <v/>
       </c>
     </row>
@@ -6893,7 +11673,7 @@
         </is>
       </c>
       <c r="D22" s="10">
-        <f>COUNTIF(架電リスト!D2:D146,"大田原市")</f>
+        <f>COUNTIF(架電リスト!D2:D238,"大田原市")</f>
         <v/>
       </c>
     </row>
@@ -6904,7 +11684,7 @@
         </is>
       </c>
       <c r="D23" s="10">
-        <f>COUNTIF(架電リスト!D2:D146,"壬生町")</f>
+        <f>COUNTIF(架電リスト!D2:D238,"壬生町")</f>
         <v/>
       </c>
     </row>
@@ -6915,7 +11695,7 @@
         </is>
       </c>
       <c r="D24" s="10">
-        <f>COUNTIF(架電リスト!D2:D146,"那珂川町")</f>
+        <f>COUNTIF(架電リスト!D2:D238,"那珂川町")</f>
         <v/>
       </c>
     </row>
@@ -6926,7 +11706,7 @@
         </is>
       </c>
       <c r="D25" s="10">
-        <f>COUNTIF(架電リスト!D2:D146,"那須烏山市")</f>
+        <f>COUNTIF(架電リスト!D2:D238,"那須烏山市")</f>
         <v/>
       </c>
     </row>
@@ -6937,7 +11717,7 @@
         </is>
       </c>
       <c r="D26" s="10">
-        <f>COUNTIF(架電リスト!D2:D146,"矢板市")</f>
+        <f>COUNTIF(架電リスト!D2:D238,"矢板市")</f>
         <v/>
       </c>
     </row>
@@ -6948,7 +11728,7 @@
         </is>
       </c>
       <c r="D27" s="10">
-        <f>COUNTIF(架電リスト!D2:D146,"茂木町")</f>
+        <f>COUNTIF(架電リスト!D2:D238,"茂木町")</f>
         <v/>
       </c>
     </row>
@@ -6959,7 +11739,7 @@
         </is>
       </c>
       <c r="D28" s="10">
-        <f>COUNTIF(架電リスト!D2:D146,"下野市")</f>
+        <f>COUNTIF(架電リスト!D2:D238,"下野市")</f>
         <v/>
       </c>
     </row>
@@ -6970,7 +11750,7 @@
         </is>
       </c>
       <c r="D29" s="10">
-        <f>COUNTIF(架電リスト!D2:D146,"野木町")</f>
+        <f>COUNTIF(架電リスト!D2:D238,"野木町")</f>
         <v/>
       </c>
     </row>
@@ -6981,7 +11761,7 @@
         </is>
       </c>
       <c r="D30" s="10">
-        <f>COUNTIF(架電リスト!D2:D146,"高根沢町")</f>
+        <f>COUNTIF(架電リスト!D2:D238,"高根沢町")</f>
         <v/>
       </c>
     </row>
@@ -6992,7 +11772,7 @@
         </is>
       </c>
       <c r="D31" s="10">
-        <f>COUNTIF(架電リスト!D2:D146,"芳賀町")</f>
+        <f>COUNTIF(架電リスト!D2:D238,"芳賀町")</f>
         <v/>
       </c>
     </row>
@@ -7003,7 +11783,7 @@
         </is>
       </c>
       <c r="D32" s="10">
-        <f>COUNTIF(架電リスト!D2:D146,"塩谷町")</f>
+        <f>COUNTIF(架電リスト!D2:D238,"塩谷町")</f>
         <v/>
       </c>
     </row>
@@ -7014,7 +11794,7 @@
         </is>
       </c>
       <c r="D33" s="10">
-        <f>COUNTIF(架電リスト!D2:D146,"さくら市")</f>
+        <f>COUNTIF(架電リスト!D2:D238,"さくら市")</f>
         <v/>
       </c>
     </row>
@@ -7025,7 +11805,7 @@
         </is>
       </c>
       <c r="D34" s="10">
-        <f>COUNTIF(架電リスト!D2:D146,"上三川町")</f>
+        <f>COUNTIF(架電リスト!D2:D238,"上三川町")</f>
         <v/>
       </c>
     </row>

--- a/projects/tel-appo/call-list.xlsx
+++ b/projects/tel-appo/call-list.xlsx
@@ -626,7 +626,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M238"/>
+  <dimension ref="A1:M251"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -10768,222 +10768,690 @@
       <c r="A199" s="5" t="n">
         <v>198</v>
       </c>
-      <c r="B199" s="8" t="inlineStr"/>
-      <c r="C199" s="8" t="inlineStr"/>
-      <c r="D199" s="8" t="inlineStr"/>
-      <c r="E199" s="8" t="inlineStr"/>
-      <c r="F199" s="8" t="inlineStr"/>
-      <c r="G199" s="8" t="inlineStr"/>
-      <c r="H199" s="8" t="inlineStr"/>
-      <c r="I199" s="8" t="inlineStr"/>
-      <c r="J199" s="8" t="inlineStr"/>
-      <c r="K199" s="8" t="inlineStr"/>
-      <c r="L199" s="8" t="inlineStr"/>
-      <c r="M199" s="8" t="inlineStr"/>
+      <c r="B199" s="6" t="inlineStr">
+        <is>
+          <t>ホシ美容室</t>
+        </is>
+      </c>
+      <c r="C199" s="6" t="inlineStr">
+        <is>
+          <t>美容室</t>
+        </is>
+      </c>
+      <c r="D199" s="6" t="inlineStr">
+        <is>
+          <t>宇都宮市</t>
+        </is>
+      </c>
+      <c r="E199" s="6" t="inlineStr">
+        <is>
+          <t>簗瀬3-13-19</t>
+        </is>
+      </c>
+      <c r="F199" s="6" t="inlineStr">
+        <is>
+          <t>0286-34-2601</t>
+        </is>
+      </c>
+      <c r="G199" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H199" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I199" s="6" t="inlineStr">
+        <is>
+          <t>NAVITIME 電話帳</t>
+        </is>
+      </c>
+      <c r="J199" s="6" t="inlineStr"/>
+      <c r="K199" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L199" s="6" t="inlineStr"/>
+      <c r="M199" s="6" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" s="5" t="n">
         <v>199</v>
       </c>
-      <c r="B200" s="8" t="inlineStr"/>
-      <c r="C200" s="8" t="inlineStr"/>
-      <c r="D200" s="8" t="inlineStr"/>
-      <c r="E200" s="8" t="inlineStr"/>
-      <c r="F200" s="8" t="inlineStr"/>
-      <c r="G200" s="8" t="inlineStr"/>
-      <c r="H200" s="8" t="inlineStr"/>
-      <c r="I200" s="8" t="inlineStr"/>
-      <c r="J200" s="8" t="inlineStr"/>
-      <c r="K200" s="8" t="inlineStr"/>
-      <c r="L200" s="8" t="inlineStr"/>
-      <c r="M200" s="8" t="inlineStr"/>
+      <c r="B200" s="6" t="inlineStr">
+        <is>
+          <t>るうべる美容室</t>
+        </is>
+      </c>
+      <c r="C200" s="6" t="inlineStr">
+        <is>
+          <t>美容室</t>
+        </is>
+      </c>
+      <c r="D200" s="6" t="inlineStr">
+        <is>
+          <t>宇都宮市</t>
+        </is>
+      </c>
+      <c r="E200" s="6" t="inlineStr">
+        <is>
+          <t>石井町3427-9</t>
+        </is>
+      </c>
+      <c r="F200" s="6" t="inlineStr">
+        <is>
+          <t>0286-56-4462</t>
+        </is>
+      </c>
+      <c r="G200" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H200" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I200" s="6" t="inlineStr">
+        <is>
+          <t>NAVITIME 電話帳</t>
+        </is>
+      </c>
+      <c r="J200" s="6" t="inlineStr"/>
+      <c r="K200" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L200" s="6" t="inlineStr"/>
+      <c r="M200" s="6" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" s="5" t="n">
         <v>200</v>
       </c>
-      <c r="B201" s="8" t="inlineStr"/>
-      <c r="C201" s="8" t="inlineStr"/>
-      <c r="D201" s="8" t="inlineStr"/>
-      <c r="E201" s="8" t="inlineStr"/>
-      <c r="F201" s="8" t="inlineStr"/>
-      <c r="G201" s="8" t="inlineStr"/>
-      <c r="H201" s="8" t="inlineStr"/>
-      <c r="I201" s="8" t="inlineStr"/>
-      <c r="J201" s="8" t="inlineStr"/>
-      <c r="K201" s="8" t="inlineStr"/>
-      <c r="L201" s="8" t="inlineStr"/>
-      <c r="M201" s="8" t="inlineStr"/>
+      <c r="B201" s="6" t="inlineStr">
+        <is>
+          <t>マミー美容室</t>
+        </is>
+      </c>
+      <c r="C201" s="6" t="inlineStr">
+        <is>
+          <t>美容室</t>
+        </is>
+      </c>
+      <c r="D201" s="6" t="inlineStr">
+        <is>
+          <t>宇都宮市</t>
+        </is>
+      </c>
+      <c r="E201" s="6" t="inlineStr">
+        <is>
+          <t>下岡本町2108</t>
+        </is>
+      </c>
+      <c r="F201" s="6" t="inlineStr">
+        <is>
+          <t>0286-73-3662</t>
+        </is>
+      </c>
+      <c r="G201" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H201" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I201" s="6" t="inlineStr">
+        <is>
+          <t>NAVITIME 電話帳</t>
+        </is>
+      </c>
+      <c r="J201" s="6" t="inlineStr"/>
+      <c r="K201" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L201" s="6" t="inlineStr"/>
+      <c r="M201" s="6" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" s="5" t="n">
         <v>201</v>
       </c>
-      <c r="B202" s="8" t="inlineStr"/>
-      <c r="C202" s="8" t="inlineStr"/>
-      <c r="D202" s="8" t="inlineStr"/>
-      <c r="E202" s="8" t="inlineStr"/>
-      <c r="F202" s="8" t="inlineStr"/>
-      <c r="G202" s="8" t="inlineStr"/>
-      <c r="H202" s="8" t="inlineStr"/>
-      <c r="I202" s="8" t="inlineStr"/>
-      <c r="J202" s="8" t="inlineStr"/>
-      <c r="K202" s="8" t="inlineStr"/>
-      <c r="L202" s="8" t="inlineStr"/>
-      <c r="M202" s="8" t="inlineStr"/>
+      <c r="B202" s="6" t="inlineStr">
+        <is>
+          <t>はやかわ美容室</t>
+        </is>
+      </c>
+      <c r="C202" s="6" t="inlineStr">
+        <is>
+          <t>美容室</t>
+        </is>
+      </c>
+      <c r="D202" s="6" t="inlineStr">
+        <is>
+          <t>宇都宮市</t>
+        </is>
+      </c>
+      <c r="E202" s="6" t="inlineStr">
+        <is>
+          <t>松が峰2-1-9</t>
+        </is>
+      </c>
+      <c r="F202" s="6" t="inlineStr">
+        <is>
+          <t>0286-34-4869</t>
+        </is>
+      </c>
+      <c r="G202" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H202" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I202" s="6" t="inlineStr">
+        <is>
+          <t>NAVITIME 電話帳</t>
+        </is>
+      </c>
+      <c r="J202" s="6" t="inlineStr"/>
+      <c r="K202" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L202" s="6" t="inlineStr"/>
+      <c r="M202" s="6" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" s="5" t="n">
         <v>202</v>
       </c>
-      <c r="B203" s="8" t="inlineStr"/>
-      <c r="C203" s="8" t="inlineStr"/>
-      <c r="D203" s="8" t="inlineStr"/>
-      <c r="E203" s="8" t="inlineStr"/>
-      <c r="F203" s="8" t="inlineStr"/>
-      <c r="G203" s="8" t="inlineStr"/>
-      <c r="H203" s="8" t="inlineStr"/>
-      <c r="I203" s="8" t="inlineStr"/>
-      <c r="J203" s="8" t="inlineStr"/>
-      <c r="K203" s="8" t="inlineStr"/>
-      <c r="L203" s="8" t="inlineStr"/>
-      <c r="M203" s="8" t="inlineStr"/>
+      <c r="B203" s="6" t="inlineStr">
+        <is>
+          <t>イチサンマル美容室</t>
+        </is>
+      </c>
+      <c r="C203" s="6" t="inlineStr">
+        <is>
+          <t>美容室</t>
+        </is>
+      </c>
+      <c r="D203" s="6" t="inlineStr">
+        <is>
+          <t>宇都宮市</t>
+        </is>
+      </c>
+      <c r="E203" s="6" t="inlineStr">
+        <is>
+          <t>宿郷2-9-6</t>
+        </is>
+      </c>
+      <c r="F203" s="6" t="inlineStr">
+        <is>
+          <t>0286-37-8433</t>
+        </is>
+      </c>
+      <c r="G203" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H203" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I203" s="6" t="inlineStr">
+        <is>
+          <t>NAVITIME 電話帳</t>
+        </is>
+      </c>
+      <c r="J203" s="6" t="inlineStr"/>
+      <c r="K203" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L203" s="6" t="inlineStr"/>
+      <c r="M203" s="6" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" s="5" t="n">
         <v>203</v>
       </c>
-      <c r="B204" s="8" t="inlineStr"/>
-      <c r="C204" s="8" t="inlineStr"/>
-      <c r="D204" s="8" t="inlineStr"/>
-      <c r="E204" s="8" t="inlineStr"/>
-      <c r="F204" s="8" t="inlineStr"/>
-      <c r="G204" s="8" t="inlineStr"/>
-      <c r="H204" s="8" t="inlineStr"/>
-      <c r="I204" s="8" t="inlineStr"/>
-      <c r="J204" s="8" t="inlineStr"/>
-      <c r="K204" s="8" t="inlineStr"/>
-      <c r="L204" s="8" t="inlineStr"/>
-      <c r="M204" s="8" t="inlineStr"/>
+      <c r="B204" s="6" t="inlineStr">
+        <is>
+          <t>コララ美容室</t>
+        </is>
+      </c>
+      <c r="C204" s="6" t="inlineStr">
+        <is>
+          <t>美容室</t>
+        </is>
+      </c>
+      <c r="D204" s="6" t="inlineStr">
+        <is>
+          <t>宇都宮市</t>
+        </is>
+      </c>
+      <c r="E204" s="6" t="inlineStr">
+        <is>
+          <t>西川田本町4-15-13</t>
+        </is>
+      </c>
+      <c r="F204" s="6" t="inlineStr">
+        <is>
+          <t>0286-59-7874</t>
+        </is>
+      </c>
+      <c r="G204" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H204" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I204" s="6" t="inlineStr">
+        <is>
+          <t>NAVITIME 電話帳</t>
+        </is>
+      </c>
+      <c r="J204" s="6" t="inlineStr"/>
+      <c r="K204" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L204" s="6" t="inlineStr"/>
+      <c r="M204" s="6" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" s="5" t="n">
         <v>204</v>
       </c>
-      <c r="B205" s="8" t="inlineStr"/>
-      <c r="C205" s="8" t="inlineStr"/>
-      <c r="D205" s="8" t="inlineStr"/>
-      <c r="E205" s="8" t="inlineStr"/>
-      <c r="F205" s="8" t="inlineStr"/>
-      <c r="G205" s="8" t="inlineStr"/>
-      <c r="H205" s="8" t="inlineStr"/>
-      <c r="I205" s="8" t="inlineStr"/>
-      <c r="J205" s="8" t="inlineStr"/>
-      <c r="K205" s="8" t="inlineStr"/>
-      <c r="L205" s="8" t="inlineStr"/>
-      <c r="M205" s="8" t="inlineStr"/>
+      <c r="B205" s="6" t="inlineStr">
+        <is>
+          <t>ミナル美容室</t>
+        </is>
+      </c>
+      <c r="C205" s="6" t="inlineStr">
+        <is>
+          <t>美容室</t>
+        </is>
+      </c>
+      <c r="D205" s="6" t="inlineStr">
+        <is>
+          <t>宇都宮市</t>
+        </is>
+      </c>
+      <c r="E205" s="6" t="inlineStr">
+        <is>
+          <t>江曽島町1446-7</t>
+        </is>
+      </c>
+      <c r="F205" s="6" t="inlineStr">
+        <is>
+          <t>0286-58-4654</t>
+        </is>
+      </c>
+      <c r="G205" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H205" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I205" s="6" t="inlineStr">
+        <is>
+          <t>NAVITIME 電話帳</t>
+        </is>
+      </c>
+      <c r="J205" s="6" t="inlineStr"/>
+      <c r="K205" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L205" s="6" t="inlineStr"/>
+      <c r="M205" s="6" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" s="5" t="n">
         <v>205</v>
       </c>
-      <c r="B206" s="8" t="inlineStr"/>
-      <c r="C206" s="8" t="inlineStr"/>
-      <c r="D206" s="8" t="inlineStr"/>
-      <c r="E206" s="8" t="inlineStr"/>
-      <c r="F206" s="8" t="inlineStr"/>
-      <c r="G206" s="8" t="inlineStr"/>
-      <c r="H206" s="8" t="inlineStr"/>
-      <c r="I206" s="8" t="inlineStr"/>
-      <c r="J206" s="8" t="inlineStr"/>
-      <c r="K206" s="8" t="inlineStr"/>
-      <c r="L206" s="8" t="inlineStr"/>
-      <c r="M206" s="8" t="inlineStr"/>
+      <c r="B206" s="6" t="inlineStr">
+        <is>
+          <t>ロックザボート</t>
+        </is>
+      </c>
+      <c r="C206" s="6" t="inlineStr">
+        <is>
+          <t>美容室</t>
+        </is>
+      </c>
+      <c r="D206" s="6" t="inlineStr">
+        <is>
+          <t>宇都宮市</t>
+        </is>
+      </c>
+      <c r="E206" s="6" t="inlineStr">
+        <is>
+          <t>陽東5-7-43</t>
+        </is>
+      </c>
+      <c r="F206" s="6" t="inlineStr">
+        <is>
+          <t>0286-60-6900</t>
+        </is>
+      </c>
+      <c r="G206" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H206" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I206" s="6" t="inlineStr">
+        <is>
+          <t>NAVITIME 電話帳</t>
+        </is>
+      </c>
+      <c r="J206" s="6" t="inlineStr"/>
+      <c r="K206" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L206" s="6" t="inlineStr"/>
+      <c r="M206" s="6" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" s="5" t="n">
         <v>206</v>
       </c>
-      <c r="B207" s="8" t="inlineStr"/>
-      <c r="C207" s="8" t="inlineStr"/>
-      <c r="D207" s="8" t="inlineStr"/>
-      <c r="E207" s="8" t="inlineStr"/>
-      <c r="F207" s="8" t="inlineStr"/>
-      <c r="G207" s="8" t="inlineStr"/>
-      <c r="H207" s="8" t="inlineStr"/>
-      <c r="I207" s="8" t="inlineStr"/>
-      <c r="J207" s="8" t="inlineStr"/>
-      <c r="K207" s="8" t="inlineStr"/>
-      <c r="L207" s="8" t="inlineStr"/>
-      <c r="M207" s="8" t="inlineStr"/>
+      <c r="B207" s="6" t="inlineStr">
+        <is>
+          <t>ヘアーサロンオリーブ</t>
+        </is>
+      </c>
+      <c r="C207" s="6" t="inlineStr">
+        <is>
+          <t>美容室</t>
+        </is>
+      </c>
+      <c r="D207" s="6" t="inlineStr">
+        <is>
+          <t>宇都宮市</t>
+        </is>
+      </c>
+      <c r="E207" s="6" t="inlineStr">
+        <is>
+          <t>泉が丘2-2-9</t>
+        </is>
+      </c>
+      <c r="F207" s="6" t="inlineStr">
+        <is>
+          <t>0286-62-3090</t>
+        </is>
+      </c>
+      <c r="G207" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H207" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I207" s="6" t="inlineStr">
+        <is>
+          <t>NAVITIME 電話帳</t>
+        </is>
+      </c>
+      <c r="J207" s="6" t="inlineStr"/>
+      <c r="K207" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L207" s="6" t="inlineStr"/>
+      <c r="M207" s="6" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" s="5" t="n">
         <v>207</v>
       </c>
-      <c r="B208" s="8" t="inlineStr"/>
-      <c r="C208" s="8" t="inlineStr"/>
-      <c r="D208" s="8" t="inlineStr"/>
-      <c r="E208" s="8" t="inlineStr"/>
-      <c r="F208" s="8" t="inlineStr"/>
-      <c r="G208" s="8" t="inlineStr"/>
-      <c r="H208" s="8" t="inlineStr"/>
-      <c r="I208" s="8" t="inlineStr"/>
-      <c r="J208" s="8" t="inlineStr"/>
-      <c r="K208" s="8" t="inlineStr"/>
-      <c r="L208" s="8" t="inlineStr"/>
-      <c r="M208" s="8" t="inlineStr"/>
+      <c r="B208" s="6" t="inlineStr">
+        <is>
+          <t>美容室 隆（りゅう） 中央店</t>
+        </is>
+      </c>
+      <c r="C208" s="6" t="inlineStr">
+        <is>
+          <t>美容室</t>
+        </is>
+      </c>
+      <c r="D208" s="6" t="inlineStr">
+        <is>
+          <t>宇都宮市</t>
+        </is>
+      </c>
+      <c r="E208" s="6" t="inlineStr">
+        <is>
+          <t>操町4-11</t>
+        </is>
+      </c>
+      <c r="F208" s="7" t="inlineStr"/>
+      <c r="G208" s="6" t="inlineStr">
+        <is>
+          <t>火曜・第3月曜</t>
+        </is>
+      </c>
+      <c r="H208" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I208" s="6" t="inlineStr">
+        <is>
+          <t>NAVITIME 電話帳</t>
+        </is>
+      </c>
+      <c r="J208" s="6" t="inlineStr"/>
+      <c r="K208" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L208" s="6" t="inlineStr"/>
+      <c r="M208" s="6" t="inlineStr">
+        <is>
+          <t>定休日は火曜・第3月曜（要再確認）、電話番号は検索で確認できず</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" s="5" t="n">
         <v>208</v>
       </c>
-      <c r="B209" s="8" t="inlineStr"/>
-      <c r="C209" s="8" t="inlineStr"/>
-      <c r="D209" s="8" t="inlineStr"/>
-      <c r="E209" s="8" t="inlineStr"/>
-      <c r="F209" s="8" t="inlineStr"/>
-      <c r="G209" s="8" t="inlineStr"/>
-      <c r="H209" s="8" t="inlineStr"/>
-      <c r="I209" s="8" t="inlineStr"/>
-      <c r="J209" s="8" t="inlineStr"/>
-      <c r="K209" s="8" t="inlineStr"/>
-      <c r="L209" s="8" t="inlineStr"/>
-      <c r="M209" s="8" t="inlineStr"/>
+      <c r="B209" s="6" t="inlineStr">
+        <is>
+          <t>理容室スズキ</t>
+        </is>
+      </c>
+      <c r="C209" s="6" t="inlineStr">
+        <is>
+          <t>理容室</t>
+        </is>
+      </c>
+      <c r="D209" s="6" t="inlineStr">
+        <is>
+          <t>宇都宮市</t>
+        </is>
+      </c>
+      <c r="E209" s="6" t="inlineStr">
+        <is>
+          <t>泉町6-25</t>
+        </is>
+      </c>
+      <c r="F209" s="6" t="inlineStr">
+        <is>
+          <t>0286-22-3931</t>
+        </is>
+      </c>
+      <c r="G209" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H209" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I209" s="6" t="inlineStr">
+        <is>
+          <t>NAVITIME 電話帳</t>
+        </is>
+      </c>
+      <c r="J209" s="6" t="inlineStr"/>
+      <c r="K209" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L209" s="6" t="inlineStr"/>
+      <c r="M209" s="6" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" s="5" t="n">
         <v>209</v>
       </c>
-      <c r="B210" s="8" t="inlineStr"/>
-      <c r="C210" s="8" t="inlineStr"/>
-      <c r="D210" s="8" t="inlineStr"/>
-      <c r="E210" s="8" t="inlineStr"/>
-      <c r="F210" s="8" t="inlineStr"/>
-      <c r="G210" s="8" t="inlineStr"/>
-      <c r="H210" s="8" t="inlineStr"/>
-      <c r="I210" s="8" t="inlineStr"/>
-      <c r="J210" s="8" t="inlineStr"/>
-      <c r="K210" s="8" t="inlineStr"/>
-      <c r="L210" s="8" t="inlineStr"/>
-      <c r="M210" s="8" t="inlineStr"/>
+      <c r="B210" s="6" t="inlineStr">
+        <is>
+          <t>スズキ理容室</t>
+        </is>
+      </c>
+      <c r="C210" s="6" t="inlineStr">
+        <is>
+          <t>理容室</t>
+        </is>
+      </c>
+      <c r="D210" s="6" t="inlineStr">
+        <is>
+          <t>宇都宮市</t>
+        </is>
+      </c>
+      <c r="E210" s="6" t="inlineStr">
+        <is>
+          <t>双葉3-2-9</t>
+        </is>
+      </c>
+      <c r="F210" s="6" t="inlineStr">
+        <is>
+          <t>0286-58-1693</t>
+        </is>
+      </c>
+      <c r="G210" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H210" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I210" s="6" t="inlineStr">
+        <is>
+          <t>NAVITIME 電話帳</t>
+        </is>
+      </c>
+      <c r="J210" s="6" t="inlineStr"/>
+      <c r="K210" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L210" s="6" t="inlineStr"/>
+      <c r="M210" s="6" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" s="5" t="n">
         <v>210</v>
       </c>
-      <c r="B211" s="8" t="inlineStr"/>
-      <c r="C211" s="8" t="inlineStr"/>
-      <c r="D211" s="8" t="inlineStr"/>
-      <c r="E211" s="8" t="inlineStr"/>
-      <c r="F211" s="8" t="inlineStr"/>
-      <c r="G211" s="8" t="inlineStr"/>
-      <c r="H211" s="8" t="inlineStr"/>
-      <c r="I211" s="8" t="inlineStr"/>
-      <c r="J211" s="8" t="inlineStr"/>
-      <c r="K211" s="8" t="inlineStr"/>
-      <c r="L211" s="8" t="inlineStr"/>
-      <c r="M211" s="8" t="inlineStr"/>
+      <c r="B211" s="6" t="inlineStr">
+        <is>
+          <t>ミノリ理容所</t>
+        </is>
+      </c>
+      <c r="C211" s="6" t="inlineStr">
+        <is>
+          <t>理容室</t>
+        </is>
+      </c>
+      <c r="D211" s="6" t="inlineStr">
+        <is>
+          <t>宇都宮市</t>
+        </is>
+      </c>
+      <c r="E211" s="6" t="inlineStr">
+        <is>
+          <t>桜4-21-2</t>
+        </is>
+      </c>
+      <c r="F211" s="6" t="inlineStr">
+        <is>
+          <t>0286-24-0181</t>
+        </is>
+      </c>
+      <c r="G211" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H211" s="6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I211" s="6" t="inlineStr">
+        <is>
+          <t>NAVITIME 電話帳</t>
+        </is>
+      </c>
+      <c r="J211" s="6" t="inlineStr"/>
+      <c r="K211" s="6" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="L211" s="6" t="inlineStr"/>
+      <c r="M211" s="6" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" s="5" t="n">
@@ -11444,18 +11912,239 @@
       <c r="L238" s="8" t="inlineStr"/>
       <c r="M238" s="8" t="inlineStr"/>
     </row>
+    <row r="239">
+      <c r="A239" s="5" t="n">
+        <v>238</v>
+      </c>
+      <c r="B239" s="8" t="inlineStr"/>
+      <c r="C239" s="8" t="inlineStr"/>
+      <c r="D239" s="8" t="inlineStr"/>
+      <c r="E239" s="8" t="inlineStr"/>
+      <c r="F239" s="8" t="inlineStr"/>
+      <c r="G239" s="8" t="inlineStr"/>
+      <c r="H239" s="8" t="inlineStr"/>
+      <c r="I239" s="8" t="inlineStr"/>
+      <c r="J239" s="8" t="inlineStr"/>
+      <c r="K239" s="8" t="inlineStr"/>
+      <c r="L239" s="8" t="inlineStr"/>
+      <c r="M239" s="8" t="inlineStr"/>
+    </row>
+    <row r="240">
+      <c r="A240" s="5" t="n">
+        <v>239</v>
+      </c>
+      <c r="B240" s="8" t="inlineStr"/>
+      <c r="C240" s="8" t="inlineStr"/>
+      <c r="D240" s="8" t="inlineStr"/>
+      <c r="E240" s="8" t="inlineStr"/>
+      <c r="F240" s="8" t="inlineStr"/>
+      <c r="G240" s="8" t="inlineStr"/>
+      <c r="H240" s="8" t="inlineStr"/>
+      <c r="I240" s="8" t="inlineStr"/>
+      <c r="J240" s="8" t="inlineStr"/>
+      <c r="K240" s="8" t="inlineStr"/>
+      <c r="L240" s="8" t="inlineStr"/>
+      <c r="M240" s="8" t="inlineStr"/>
+    </row>
+    <row r="241">
+      <c r="A241" s="5" t="n">
+        <v>240</v>
+      </c>
+      <c r="B241" s="8" t="inlineStr"/>
+      <c r="C241" s="8" t="inlineStr"/>
+      <c r="D241" s="8" t="inlineStr"/>
+      <c r="E241" s="8" t="inlineStr"/>
+      <c r="F241" s="8" t="inlineStr"/>
+      <c r="G241" s="8" t="inlineStr"/>
+      <c r="H241" s="8" t="inlineStr"/>
+      <c r="I241" s="8" t="inlineStr"/>
+      <c r="J241" s="8" t="inlineStr"/>
+      <c r="K241" s="8" t="inlineStr"/>
+      <c r="L241" s="8" t="inlineStr"/>
+      <c r="M241" s="8" t="inlineStr"/>
+    </row>
+    <row r="242">
+      <c r="A242" s="5" t="n">
+        <v>241</v>
+      </c>
+      <c r="B242" s="8" t="inlineStr"/>
+      <c r="C242" s="8" t="inlineStr"/>
+      <c r="D242" s="8" t="inlineStr"/>
+      <c r="E242" s="8" t="inlineStr"/>
+      <c r="F242" s="8" t="inlineStr"/>
+      <c r="G242" s="8" t="inlineStr"/>
+      <c r="H242" s="8" t="inlineStr"/>
+      <c r="I242" s="8" t="inlineStr"/>
+      <c r="J242" s="8" t="inlineStr"/>
+      <c r="K242" s="8" t="inlineStr"/>
+      <c r="L242" s="8" t="inlineStr"/>
+      <c r="M242" s="8" t="inlineStr"/>
+    </row>
+    <row r="243">
+      <c r="A243" s="5" t="n">
+        <v>242</v>
+      </c>
+      <c r="B243" s="8" t="inlineStr"/>
+      <c r="C243" s="8" t="inlineStr"/>
+      <c r="D243" s="8" t="inlineStr"/>
+      <c r="E243" s="8" t="inlineStr"/>
+      <c r="F243" s="8" t="inlineStr"/>
+      <c r="G243" s="8" t="inlineStr"/>
+      <c r="H243" s="8" t="inlineStr"/>
+      <c r="I243" s="8" t="inlineStr"/>
+      <c r="J243" s="8" t="inlineStr"/>
+      <c r="K243" s="8" t="inlineStr"/>
+      <c r="L243" s="8" t="inlineStr"/>
+      <c r="M243" s="8" t="inlineStr"/>
+    </row>
+    <row r="244">
+      <c r="A244" s="5" t="n">
+        <v>243</v>
+      </c>
+      <c r="B244" s="8" t="inlineStr"/>
+      <c r="C244" s="8" t="inlineStr"/>
+      <c r="D244" s="8" t="inlineStr"/>
+      <c r="E244" s="8" t="inlineStr"/>
+      <c r="F244" s="8" t="inlineStr"/>
+      <c r="G244" s="8" t="inlineStr"/>
+      <c r="H244" s="8" t="inlineStr"/>
+      <c r="I244" s="8" t="inlineStr"/>
+      <c r="J244" s="8" t="inlineStr"/>
+      <c r="K244" s="8" t="inlineStr"/>
+      <c r="L244" s="8" t="inlineStr"/>
+      <c r="M244" s="8" t="inlineStr"/>
+    </row>
+    <row r="245">
+      <c r="A245" s="5" t="n">
+        <v>244</v>
+      </c>
+      <c r="B245" s="8" t="inlineStr"/>
+      <c r="C245" s="8" t="inlineStr"/>
+      <c r="D245" s="8" t="inlineStr"/>
+      <c r="E245" s="8" t="inlineStr"/>
+      <c r="F245" s="8" t="inlineStr"/>
+      <c r="G245" s="8" t="inlineStr"/>
+      <c r="H245" s="8" t="inlineStr"/>
+      <c r="I245" s="8" t="inlineStr"/>
+      <c r="J245" s="8" t="inlineStr"/>
+      <c r="K245" s="8" t="inlineStr"/>
+      <c r="L245" s="8" t="inlineStr"/>
+      <c r="M245" s="8" t="inlineStr"/>
+    </row>
+    <row r="246">
+      <c r="A246" s="5" t="n">
+        <v>245</v>
+      </c>
+      <c r="B246" s="8" t="inlineStr"/>
+      <c r="C246" s="8" t="inlineStr"/>
+      <c r="D246" s="8" t="inlineStr"/>
+      <c r="E246" s="8" t="inlineStr"/>
+      <c r="F246" s="8" t="inlineStr"/>
+      <c r="G246" s="8" t="inlineStr"/>
+      <c r="H246" s="8" t="inlineStr"/>
+      <c r="I246" s="8" t="inlineStr"/>
+      <c r="J246" s="8" t="inlineStr"/>
+      <c r="K246" s="8" t="inlineStr"/>
+      <c r="L246" s="8" t="inlineStr"/>
+      <c r="M246" s="8" t="inlineStr"/>
+    </row>
+    <row r="247">
+      <c r="A247" s="5" t="n">
+        <v>246</v>
+      </c>
+      <c r="B247" s="8" t="inlineStr"/>
+      <c r="C247" s="8" t="inlineStr"/>
+      <c r="D247" s="8" t="inlineStr"/>
+      <c r="E247" s="8" t="inlineStr"/>
+      <c r="F247" s="8" t="inlineStr"/>
+      <c r="G247" s="8" t="inlineStr"/>
+      <c r="H247" s="8" t="inlineStr"/>
+      <c r="I247" s="8" t="inlineStr"/>
+      <c r="J247" s="8" t="inlineStr"/>
+      <c r="K247" s="8" t="inlineStr"/>
+      <c r="L247" s="8" t="inlineStr"/>
+      <c r="M247" s="8" t="inlineStr"/>
+    </row>
+    <row r="248">
+      <c r="A248" s="5" t="n">
+        <v>247</v>
+      </c>
+      <c r="B248" s="8" t="inlineStr"/>
+      <c r="C248" s="8" t="inlineStr"/>
+      <c r="D248" s="8" t="inlineStr"/>
+      <c r="E248" s="8" t="inlineStr"/>
+      <c r="F248" s="8" t="inlineStr"/>
+      <c r="G248" s="8" t="inlineStr"/>
+      <c r="H248" s="8" t="inlineStr"/>
+      <c r="I248" s="8" t="inlineStr"/>
+      <c r="J248" s="8" t="inlineStr"/>
+      <c r="K248" s="8" t="inlineStr"/>
+      <c r="L248" s="8" t="inlineStr"/>
+      <c r="M248" s="8" t="inlineStr"/>
+    </row>
+    <row r="249">
+      <c r="A249" s="5" t="n">
+        <v>248</v>
+      </c>
+      <c r="B249" s="8" t="inlineStr"/>
+      <c r="C249" s="8" t="inlineStr"/>
+      <c r="D249" s="8" t="inlineStr"/>
+      <c r="E249" s="8" t="inlineStr"/>
+      <c r="F249" s="8" t="inlineStr"/>
+      <c r="G249" s="8" t="inlineStr"/>
+      <c r="H249" s="8" t="inlineStr"/>
+      <c r="I249" s="8" t="inlineStr"/>
+      <c r="J249" s="8" t="inlineStr"/>
+      <c r="K249" s="8" t="inlineStr"/>
+      <c r="L249" s="8" t="inlineStr"/>
+      <c r="M249" s="8" t="inlineStr"/>
+    </row>
+    <row r="250">
+      <c r="A250" s="5" t="n">
+        <v>249</v>
+      </c>
+      <c r="B250" s="8" t="inlineStr"/>
+      <c r="C250" s="8" t="inlineStr"/>
+      <c r="D250" s="8" t="inlineStr"/>
+      <c r="E250" s="8" t="inlineStr"/>
+      <c r="F250" s="8" t="inlineStr"/>
+      <c r="G250" s="8" t="inlineStr"/>
+      <c r="H250" s="8" t="inlineStr"/>
+      <c r="I250" s="8" t="inlineStr"/>
+      <c r="J250" s="8" t="inlineStr"/>
+      <c r="K250" s="8" t="inlineStr"/>
+      <c r="L250" s="8" t="inlineStr"/>
+      <c r="M250" s="8" t="inlineStr"/>
+    </row>
+    <row r="251">
+      <c r="A251" s="5" t="n">
+        <v>250</v>
+      </c>
+      <c r="B251" s="8" t="inlineStr"/>
+      <c r="C251" s="8" t="inlineStr"/>
+      <c r="D251" s="8" t="inlineStr"/>
+      <c r="E251" s="8" t="inlineStr"/>
+      <c r="F251" s="8" t="inlineStr"/>
+      <c r="G251" s="8" t="inlineStr"/>
+      <c r="H251" s="8" t="inlineStr"/>
+      <c r="I251" s="8" t="inlineStr"/>
+      <c r="J251" s="8" t="inlineStr"/>
+      <c r="K251" s="8" t="inlineStr"/>
+      <c r="L251" s="8" t="inlineStr"/>
+      <c r="M251" s="8" t="inlineStr"/>
+    </row>
   </sheetData>
   <dataValidations count="4">
-    <dataValidation sqref="C2:C238" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C2:C251" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"カフェ,飲食店,和菓子店,雑貨店,陶器店・ギャラリー,工芸品店,土産店,パン屋,美容室,理容室,その他"</formula1>
     </dataValidation>
-    <dataValidation sqref="D2:D238" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="D2:D251" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"栃木市,益子町,那須町,日光市,宇都宮市,足利市,佐野市,小山市,鹿沼市,那須塩原市,真岡市,大田原市,壬生町,那珂川町,那須烏山市,矢板市,茂木町,下野市,野木町,高根沢町,芳賀町,塩谷町,さくら市,上三川町,その他"</formula1>
     </dataValidation>
-    <dataValidation sqref="K2:K238" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K2:K251" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"未架電,不在,拒否,資料送付OK,アポ確定,見送り"</formula1>
     </dataValidation>
-    <dataValidation sqref="H2:H238" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H2:H251" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"不明,あり（古い）,あり（最近）,なし"</formula1>
     </dataValidation>
   </dataValidations>
@@ -11490,7 +12179,7 @@
         </is>
       </c>
       <c r="D4" s="2">
-        <f>COUNTIF(架電リスト!B2:B238,"?*")</f>
+        <f>COUNTIF(架電リスト!B2:B251,"?*")</f>
         <v/>
       </c>
     </row>
@@ -11501,7 +12190,7 @@
         </is>
       </c>
       <c r="D5" s="2">
-        <f>COUNTIFS(架電リスト!K2:K238,"&lt;&gt;未架電",架電リスト!K2:K238,"&lt;&gt;")</f>
+        <f>COUNTIFS(架電リスト!K2:K251,"&lt;&gt;未架電",架電リスト!K2:K251,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -11512,7 +12201,7 @@
         </is>
       </c>
       <c r="D6" s="2">
-        <f>COUNTIF(架電リスト!K2:K238,"資料送付OK")</f>
+        <f>COUNTIF(架電リスト!K2:K251,"資料送付OK")</f>
         <v/>
       </c>
     </row>
@@ -11523,7 +12212,7 @@
         </is>
       </c>
       <c r="D7" s="2">
-        <f>COUNTIF(架電リスト!K2:K238,"アポ確定")</f>
+        <f>COUNTIF(架電リスト!K2:K251,"アポ確定")</f>
         <v/>
       </c>
     </row>
@@ -11552,7 +12241,7 @@
         </is>
       </c>
       <c r="D11" s="10">
-        <f>COUNTIF(架電リスト!D2:D238,"栃木市")</f>
+        <f>COUNTIF(架電リスト!D2:D251,"栃木市")</f>
         <v/>
       </c>
     </row>
@@ -11563,7 +12252,7 @@
         </is>
       </c>
       <c r="D12" s="10">
-        <f>COUNTIF(架電リスト!D2:D238,"益子町")</f>
+        <f>COUNTIF(架電リスト!D2:D251,"益子町")</f>
         <v/>
       </c>
     </row>
@@ -11574,7 +12263,7 @@
         </is>
       </c>
       <c r="D13" s="10">
-        <f>COUNTIF(架電リスト!D2:D238,"那須町")</f>
+        <f>COUNTIF(架電リスト!D2:D251,"那須町")</f>
         <v/>
       </c>
     </row>
@@ -11585,7 +12274,7 @@
         </is>
       </c>
       <c r="D14" s="10">
-        <f>COUNTIF(架電リスト!D2:D238,"日光市")</f>
+        <f>COUNTIF(架電リスト!D2:D251,"日光市")</f>
         <v/>
       </c>
     </row>
@@ -11596,7 +12285,7 @@
         </is>
       </c>
       <c r="D15" s="10">
-        <f>COUNTIF(架電リスト!D2:D238,"宇都宮市")</f>
+        <f>COUNTIF(架電リスト!D2:D251,"宇都宮市")</f>
         <v/>
       </c>
     </row>
@@ -11607,7 +12296,7 @@
         </is>
       </c>
       <c r="D16" s="10">
-        <f>COUNTIF(架電リスト!D2:D238,"足利市")</f>
+        <f>COUNTIF(架電リスト!D2:D251,"足利市")</f>
         <v/>
       </c>
     </row>
@@ -11618,7 +12307,7 @@
         </is>
       </c>
       <c r="D17" s="10">
-        <f>COUNTIF(架電リスト!D2:D238,"佐野市")</f>
+        <f>COUNTIF(架電リスト!D2:D251,"佐野市")</f>
         <v/>
       </c>
     </row>
@@ -11629,7 +12318,7 @@
         </is>
       </c>
       <c r="D18" s="10">
-        <f>COUNTIF(架電リスト!D2:D238,"小山市")</f>
+        <f>COUNTIF(架電リスト!D2:D251,"小山市")</f>
         <v/>
       </c>
     </row>
@@ -11640,7 +12329,7 @@
         </is>
       </c>
       <c r="D19" s="10">
-        <f>COUNTIF(架電リスト!D2:D238,"鹿沼市")</f>
+        <f>COUNTIF(架電リスト!D2:D251,"鹿沼市")</f>
         <v/>
       </c>
     </row>
@@ -11651,7 +12340,7 @@
         </is>
       </c>
       <c r="D20" s="10">
-        <f>COUNTIF(架電リスト!D2:D238,"那須塩原市")</f>
+        <f>COUNTIF(架電リスト!D2:D251,"那須塩原市")</f>
         <v/>
       </c>
     </row>
@@ -11662,7 +12351,7 @@
         </is>
       </c>
       <c r="D21" s="10">
-        <f>COUNTIF(架電リスト!D2:D238,"真岡市")</f>
+        <f>COUNTIF(架電リスト!D2:D251,"真岡市")</f>
         <v/>
       </c>
     </row>
@@ -11673,7 +12362,7 @@
         </is>
       </c>
       <c r="D22" s="10">
-        <f>COUNTIF(架電リスト!D2:D238,"大田原市")</f>
+        <f>COUNTIF(架電リスト!D2:D251,"大田原市")</f>
         <v/>
       </c>
     </row>
@@ -11684,7 +12373,7 @@
         </is>
       </c>
       <c r="D23" s="10">
-        <f>COUNTIF(架電リスト!D2:D238,"壬生町")</f>
+        <f>COUNTIF(架電リスト!D2:D251,"壬生町")</f>
         <v/>
       </c>
     </row>
@@ -11695,7 +12384,7 @@
         </is>
       </c>
       <c r="D24" s="10">
-        <f>COUNTIF(架電リスト!D2:D238,"那珂川町")</f>
+        <f>COUNTIF(架電リスト!D2:D251,"那珂川町")</f>
         <v/>
       </c>
     </row>
@@ -11706,7 +12395,7 @@
         </is>
       </c>
       <c r="D25" s="10">
-        <f>COUNTIF(架電リスト!D2:D238,"那須烏山市")</f>
+        <f>COUNTIF(架電リスト!D2:D251,"那須烏山市")</f>
         <v/>
       </c>
     </row>
@@ -11717,7 +12406,7 @@
         </is>
       </c>
       <c r="D26" s="10">
-        <f>COUNTIF(架電リスト!D2:D238,"矢板市")</f>
+        <f>COUNTIF(架電リスト!D2:D251,"矢板市")</f>
         <v/>
       </c>
     </row>
@@ -11728,7 +12417,7 @@
         </is>
       </c>
       <c r="D27" s="10">
-        <f>COUNTIF(架電リスト!D2:D238,"茂木町")</f>
+        <f>COUNTIF(架電リスト!D2:D251,"茂木町")</f>
         <v/>
       </c>
     </row>
@@ -11739,7 +12428,7 @@
         </is>
       </c>
       <c r="D28" s="10">
-        <f>COUNTIF(架電リスト!D2:D238,"下野市")</f>
+        <f>COUNTIF(架電リスト!D2:D251,"下野市")</f>
         <v/>
       </c>
     </row>
@@ -11750,7 +12439,7 @@
         </is>
       </c>
       <c r="D29" s="10">
-        <f>COUNTIF(架電リスト!D2:D238,"野木町")</f>
+        <f>COUNTIF(架電リスト!D2:D251,"野木町")</f>
         <v/>
       </c>
     </row>
@@ -11761,7 +12450,7 @@
         </is>
       </c>
       <c r="D30" s="10">
-        <f>COUNTIF(架電リスト!D2:D238,"高根沢町")</f>
+        <f>COUNTIF(架電リスト!D2:D251,"高根沢町")</f>
         <v/>
       </c>
     </row>
@@ -11772,7 +12461,7 @@
         </is>
       </c>
       <c r="D31" s="10">
-        <f>COUNTIF(架電リスト!D2:D238,"芳賀町")</f>
+        <f>COUNTIF(架電リスト!D2:D251,"芳賀町")</f>
         <v/>
       </c>
     </row>
@@ -11783,7 +12472,7 @@
         </is>
       </c>
       <c r="D32" s="10">
-        <f>COUNTIF(架電リスト!D2:D238,"塩谷町")</f>
+        <f>COUNTIF(架電リスト!D2:D251,"塩谷町")</f>
         <v/>
       </c>
     </row>
@@ -11794,7 +12483,7 @@
         </is>
       </c>
       <c r="D33" s="10">
-        <f>COUNTIF(架電リスト!D2:D238,"さくら市")</f>
+        <f>COUNTIF(架電リスト!D2:D251,"さくら市")</f>
         <v/>
       </c>
     </row>
@@ -11805,7 +12494,7 @@
         </is>
       </c>
       <c r="D34" s="10">
-        <f>COUNTIF(架電リスト!D2:D238,"上三川町")</f>
+        <f>COUNTIF(架電リスト!D2:D251,"上三川町")</f>
         <v/>
       </c>
     </row>
